--- a/exports/xlsx/terms.xlsx
+++ b/exports/xlsx/terms.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W148"/>
+  <dimension ref="A1:W147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,36 +536,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Geolocating</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>- base
-- controversial</t>
+          <t>- core
+description: Geopositioning of an Object using a Physical Sensor Model or a True Replacement Model.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Place referenced by a single set of coordinates within a coordinate Reference system.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>- Opposite to (previous) ISO definition, position shall be used only for 0-dimensional primitives (points).</t>
-        </is>
-      </c>
+          <t>Geopositioning of an Object using a Physical Sensor Model or a True Replacement Model.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>- ISO 19133:2005, modified to cover only points, also called ‘direct position’</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>- ISO 19115-2:2009, 4.11</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Determination of the geographic location of a feature of two or more dimensions.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>- ISO 19130-1:2018, 3.36 ('geopositioning'), modified</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -582,25 +586,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Anthroposphere</t>
+          <t>Spectral Bandwidth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>- high impact</t>
+          <t>- core
+description: Range of the Spectral Band.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>one of the Earth spheres consisting predominantly of matter processed by humans such as construction wood, bricks, concrete, asphalt, glass or plastics</t>
+          <t>Range of the Spectral Band.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -623,31 +628,56 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Policy file</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>Instrument Data</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>- core
+description: Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Policy documents that represent the official written Reference for a given Policy.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>- These data consist of instrument science and engineering data, and possibly ancillary data. Instrument engineering data is produced by engineering sensor(s) of an instrument, used either for operating the instrument or for processing the science data generated by the instrument. Instrument science data is produced by the science sensor(s) of an instrument, usually constituting the basic reason for existence of an instrument.</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Data created by an instrument including scientific measurements and any engineering or ancillary data which may be included in the data packets.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Data produced and transmitted by the science and engineering sensors of an instrument, and, in the spacecraft environment, any additional data packaged with the instrument's sensor data by virtue of services provided.</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
@@ -660,41 +690,59 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Location</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>Auxiliary Data</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>- core
+- approved</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Particular Place referenced by an identifier.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>- While a (geo)location identifies a geographic Place, it may also be associated with objects other than the Earth.
-- While location in principle covers 0- to 3-dimensional spatial geometries, it should not be used for 0- and 1-dimensional geometries (positions and paths)</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>- Madrid 
-- California</t>
-        </is>
-      </c>
+          <t>Data that enhance the processing and utilisation of main Sensor Data. Auxiliary Data are usually not captured by the same Data collection Process or on the same platform as the main Sensor Data. Examples include meteorological Data received from ECMWF/Met Offices or DEMs. Auxiliary Data help in Data processing, but are also Data sets in their own right.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>- [ISO 19112:2019](https://www.iso.org/standard/70742.html), (E), 3.1.3, modified, note 2 added</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+          <t>- ESA/CEOS?, modified
+- ENMAP Glossary of Terms, https://www.enmap.org/Data/doc/EnMAP_Terms.pdf, 20210624
+- EO Data Stewardship Glossary</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Data required to perform processing of Sensor Data which is not obtained from the Sensor itself. Includes: (a) Data provided by the spacecraft (e.g. orbit Position and velocity, attitude, instrument house-keeping Data, on-board time); (b) Data not available from on-board sources.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>For EnMAP, this includes (a) orbit files, attitude files, Calibration Data, instrument house-keeping Data; (b) atmospheric parameters, reference images.</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>- ENMAP Glossary of Terms, https://www.enmap.org/Data/doc/EnMAP_Terms.pdf, 20210624
+- EO Data Stewardship Glossary</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Data required for instrument processing that does not originate in the instrument itself or from the satellite. Some Auxiliary Data will be generated in the ground segment, whilst other Data will be provided from external sources.</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>- CEOS-ARD PFS template 20220302</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
@@ -707,25 +755,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Geocoding</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
+          <t>Dispose</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>- core
+description: Action of permanently and irrecoverably removing all copies of data held by an organization.</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Translation of one form of Location into another.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>- Geocoding usually refers to the translation of "address" or "intersection" to "direct Position." Many services providers also include a "reverse geocoding" interface to their geocoder, thus extending the definition of the service as a general translator of Location. Because routing services use internal Location encodings not usually available to others, a geocoder is an integral part of the internals of such a service.</t>
-        </is>
-      </c>
+          <t>Action of permanently and irrecoverably removing all copies of data held by an organization.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>- ISO 19133:2005; https://www.iso.org/standard/32551.html</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -748,21 +797,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Place</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>- base
+- controversial
+description: Place referenced by a single set of coordinates within a coordinate reference system.</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Part of any space referenced by an identifier.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>Place referenced by a single set of coordinates within a coordinate reference system.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>- Opposite to (previous) ISO definition, Position shall be used only for 0-dimensional primitives (points).</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>- ISO 19155:2012, 4.8</t>
+          <t>- ISO 19133:2005, modified to cover only points, also called 'direct position'</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -785,25 +844,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Backup</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>- core
+description: Electronic data package distributable to users; content is derived from instrument data via processing involving ancillary and auxiliary data.</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>A general practice of making copies of current baseline and derived products of EO Collections, in specified time intervals, and storing those copies in a manner that will not affect the data if the primary distribution environment is compromised.</t>
+          <t>Electronic data package distributable to users; content is derived from instrument data via processing involving ancillary and auxiliary data.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>- The emphasis is on the ability to retrieve a copy of the entire EO Collection on demand if the original data is lost or compromised.</t>
+          <t>- Products may be accompanied by metadata and browse images.
+- A Product may be part of a collection — a distinction useful for archiving and cataloguing purposes.
+- The term Product may be used to denote a product type, such as e.g. ENVISAT_ASAR_L1B_PRI data products.
+- End users may distinguish between (input, "raw") data and products, i.e., the derived geophysical parameters.
+- See also granule.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -826,21 +894,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data format</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>- base
+description: Series of activities that interact to produce a result.</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Structured Data that is machine readable and can be automatically read and processed by a computer, such as HDF, NetCDF, CSV, JSON, XML, etc.</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>Series of activities that interact to produce a result.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>- A Process may occur once-only or be recurrent or periodic.</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>- CEOS Wiki</t>
+          <t>- [Wikipedia](https://en.wikipedia.org/wiki/Process)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -863,27 +940,36 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Atmosphere</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>- core
+description: Phenomenon whose values for specific properties are known and understood with an Uncertainty significantly lower than that of the Observation with which it is compared.</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>the layer of gases, commonly known as air, including suspended liquid and solid particles known as aerosols (incl. dust, clouds, snow and ice).</t>
+          <t>Phenomenon whose values for specific properties are known and understood with an Uncertainty significantly lower (quantify?) than that of the Observation with which it is compared.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>- Guth et al. 2021</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sort of data acquired with an Uncertainty significantly lower (quantify?) than that of the data it is being compared with.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>- VIM?, modified</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -900,19 +986,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Earth Observation Based Output</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>- to be defined</t>
+          <t>- core
+description: Higher-level processing and integration output (indicative level 4 and beyond) that goes beyond basic data processing, often designed for policy or decision-making needs.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Higher-level processing and integration output (indicative level 4 and beyond) that goes beyond basic data processing. These outputs are often designed specifically for policy or decision-making needs, and can be categorized into sub-categories:
+- Outputs from models/model integration: use of EO products as inputs in numerical models or combining them with other data sources in modelling frameworks.
+- Indicator-based outputs: EO products transformed through specialized algorithms (including statistical methods, machine learning, and pattern recognition) to create meaningful metrics based on spatio-temporal analysis.
+- Outputs from reanalysis: merging of EO products with other observations and models, creating consistent long-term records of past atmospheric, oceanic, and land surface conditions, and filling gaps through data assimilation techniques.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
@@ -933,27 +1031,44 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Collection Update</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>- base
+description: Something that has separate and distinct existence and objective or conceptual reality.</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Minor revisions to a relatively small number of products within a collection for the purpose of correcting errors and maintaining consistent quality.</t>
+          <t>Something that has separate and distinct existence and objective or conceptual reality.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>- ISO 19119:2016, 4.1.6</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Government or business organization that is formed to conduct business or represent the government of the day.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>CEOS Entities include Working Groups, Virtual Constellations, etc.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -970,90 +1085,63 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Uncertainty</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>- core
+- approved</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>A parameter, associated with the result of a Measurement, that characterises the dispersion of the values that could reasonably be attributed to the Measurand.</t>
+          <t>Group of products that have been processed using a consistent radiometric calibration, geometric registration base, data/metadata format, and version of processing algorithms.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>- GUM</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Non-negative parameter, associated with Data, which characterizes the dispersion of the values of a [Trait ]that could reasonably be attributed to a Phenomenon [by means of sensing or modelling].</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>- In case of quantitative(continuous) Data the uncertainty may be, for example, a standard deviation (or a given multiple of it), or the half-width of an interval having a stated level of confidence. (see e.g. standard and Expanded uncertainty)
-- For qualitative (categorical?) Data uncertainty may be, for example, expressed by commission and omission (‘confusion matrix’) or overall errors.</t>
-        </is>
-      </c>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>- modified from GUM, VIM4 :3.1, FIDUCEO, Notes added</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Uncertainty is a measure of the spread of the distribution of possible values.</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>- [FIDUCEO Glossary](https://research.reading.ac.uk/fiduceo/glossary/), VIM?, modified</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Parameter, associated with the result of Measurement, that characterizes the dispersion of values that could reasonably be attributed to the Measurand.</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>- When the quality of Accuracy or precision of measured values, such as coordinates, is to be characterized quantitatively, the quality parameter is an estimate of the uncertainty of the Measurement results. Because Accuracy is a qualitative concept, one should not use it quantitatively, that is associate numbers with it; numbers should be associated with measures of uncertainty instead.</t>
-        </is>
-      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>- ISO 19116:2004(E)</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Parameter characterizing the dispersion of the values being attributed to a Measurand, based on the Information used.</t>
-        </is>
-      </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>- VIM4: 3.1</t>
-        </is>
-      </c>
+      <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Spatial resolution</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
+          <t>Geographic Grid</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>- core
+description: Regular grid based on a Geographic Coordinate Reference System (CRS).</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Regular grid based on a Geographic Coordinate Reference System (CRS).</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
@@ -1081,21 +1169,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Geosphere</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>- core
+- approved</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>the masses of minerals that constitute planet Earth.</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>System that stores data products, guaranteeing their preservation for future use.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>- This function includes all operations to identify, store and retrieve the data and ensure their integrity.</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1118,30 +1215,30 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Remote Sensing</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Remote Observation</t>
-        </is>
-      </c>
+          <t>Steward</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>- core
+description: Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>type of Observation performed at a significant distance from a Phenomenon.</t>
+          <t>Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>- ‘Significant’ in this context means that the distance has, or may have, a non-negligible impact on the Value of the Property observed.
-- The effect of the distance on the acquired Data is the main distinction criterion between ‘remote’ and ‘in-situ’ observations.</t>
+          <t>- See also Custodian.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -1164,54 +1261,42 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Verification</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
+          <t>Sample</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>- controversial
+description: Subset of one or more entities.</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Provision of objective evidence that a given item fulfils specified requirements.</t>
+          <t>Subset of one or more entities.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>- When applicable, Measurement uncertainty should be taken into consideration.
-- The item may be, e.g. a Process, Measurement procedure, material, compound, or measuring system.
-- The specified requirements may be, e.g. that a manufacturer's specifications are met.
-- Verification should not be confused with Calibration. Not every verification is a Validation.</t>
+          <t>- A Sample may be spatial, temporal, spectral, or in any other dimension or Trait.
+- Each Sample is contiguous, i.e. it does not consist of more than one discontinuous geometry in any dimension.
+- The Process of obtaining a Sample is called sampling.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>- ISO/IEC Guide 99:2007, 2.44</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>The evaluation of whether or not a product, service, or system complies with a regulation requirement, specification, or imposed condition. It is often an internal Process.</t>
-        </is>
-      </c>
+          <t>- KCEO</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>- EU-US Land Imaging EO Collaboration</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Verification serves as a means to evaluate the reliability of the Data in the absence of a Reference dataset, allowing for an assessment of its standalone performance. It involves confirming the consistency and internal coherence of the Data without direct comparison to external Reference sources.</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
@@ -1224,19 +1309,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Calibration</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
+          <t>Temporal Extent</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>- core
+description: Period during which data was collected, observations were made, or for which the model was run.</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>The Process of quantitatively defining a system’s (e.g. a Sensor or Model’s) response to known, controlled inputs produced for example by references. In Remote Sensing, it implies the collection of pre-flight and in-flight calibration measurements and in-situ Data that is to be used in the Data calibration processing routine.</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
+          <t>Period during which data was collected, observations were made, or for which the model was run.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>- In W3C this is the definition of temporal coverage.
+- Time Period covered by a series of observations inclusive of the specified date/time indications (measurement history). Defined based on the beginning and end dates of observations.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>- WIGOS Metadata</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>- Adapted from W3C</t>
+        </is>
+      </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
@@ -1257,25 +1360,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Period Identifier</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
+          <t>Thematic Uncertainty</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>- core
+description: Uncertainty associated with the method of classification.</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Temporal Reference in the for of a label or code that identifies a Period.</t>
+          <t>Uncertainty associated with the method of classification.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>- Period identifiers are the temporal equivalent of geographic identifiers as specified in ISO 19912</t>
+          <t>- Typically, computed from the error matrix.
+- For a review of classification Uncertainty metrics, consult Ye et al. 2018.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>- ISO 19170:2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -1298,29 +1407,26 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
+          <t>Cryosphere</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>- core
+- approved</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Electronic data package distributable to users; content is derived from instrument data via processing involving ancillary and auxiliary data.</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>- Products may be accompanied by metadata and browse images. 
-- A product may be part of a collection – a distinction useful for archiving and cataloguing purposes. 
-- The term product may be used to denote a product type, such as e.g. ENVISAT_ASAR_L1B_PRI data products. 
-- End users may distinguish between (input, "raw") data and products, i.e., the derived geophysical parameters. 
-- See also granule.</t>
-        </is>
-      </c>
+          <t>Masses of frozen water, such as sea ice, ice shields, glaciers, and snow.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -1343,21 +1449,30 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Version Control</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
+          <t>Spatial Reporting Unit</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>- core
+description: Smallest spatial object of interest that may be used for reporting and for which the information should be aggregated.</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>A method of working with collections, similar to the version control systems used in traditional software development but optimized to allow better processing of data and collaboration in the context of data analytics, research, and any other form of data analysis.</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>Smallest spatial object of interest that may be used for reporting and for which the information should be aggregated.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>- WIGOS 2019 uses 'spatial reporting interval', probably assuming observations are reported on a grid with regular spacing/intervals.</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>- [Wikipedia](https://en.wikipedia.org/wiki/Data_version_control)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -1380,27 +1495,30 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Area of Interest</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
+          <t>Decommissioned Product</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>- core
+description: Products and collections that have been superseded by new versions and are no longer available.</t>
+        </is>
+      </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>The zone in 2D or 3D for which the Information or Data is requested. It can be discontinuous in space, in other words it can consist in the union of many separate zones (e.g., Natural Reserves in Africa, Urban environments, etc.). The attribute indicates a request for spatially complete Data within the AOI zone(s).</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>| Type                              | Entry format example    | Valid units |
-|-----------------------------------|-------------------------|-------------|
-| Geographical/administrative identifier | NUTS3, LAU, Natura 2000 site | unitless    |</t>
-        </is>
-      </c>
+          <t>Products and collections that have been superseded by new versions and are no longer available.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>- Decommissioned products are no longer supported, i.e. corrections will not be made, new data will not be added, and support is not available.</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -1423,21 +1541,36 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Expanded uncertainty</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
+          <t>Location</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>- base
+description: Particular Place referenced by an identifier.</t>
+        </is>
+      </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Expanded Uncertainty is the Standard Uncertainty multiplied by a coverage factor, k. The coverage factor is chosen to obtain a desired level of confidence. Most commonly a 95% Confidence interval is chosen. For a Gaussian distribution, this is achieved with a coverage factor k = 2. (Note that strictly this provides a 95.45% Confidence interval).</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+          <t>Particular Place referenced by an identifier.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>- While a (geo)location identifies a geographic Place, it may also be associated with objects other than the Earth.
+- While Location in principle covers 0- to 3-dimensional spatial geometries, it should not be used for 0- and 1-dimensional geometries (positions and paths).</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>- Madrid
+- California</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [ISO 19112:2019](https://www.iso.org/standard/70742.html), (E), 3.1.3, modified, note 2 added</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -1460,21 +1593,30 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Copernicus Service Provider</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>- base
+description: Particular era or span of time.</t>
+        </is>
+      </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>An institutional body, an organisation or programme that provides reliable, trusted (authoritative?) EO Information and that has the financial resources to sustain the provision. It utilizes satellite Data, ground-based measurements, and other sources to generate accurate and timely Data products related to various aspects of the Earth's environment, such as land, Atmosphere, oceans, and climate.</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
+          <t>Particular era or span of time.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>- Periods are intervals named with a Period Identifier.</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO 19170:2021</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -1497,25 +1639,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Archive</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
+          <t>Geospatial Data</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>- core
+description: Data consisting of, derived from, or relating to information that is directly linked to specific geographical locations.</t>
+        </is>
+      </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Stores data products, guaranteeing their preservation for future use</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>- This function includes all operations to identify, store and retrieve the data and ensure their integrity.</t>
-        </is>
-      </c>
+          <t>Data consisting of, derived from, or relating to information that is directly linked to specific geographical locations.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- https://www.merriam-webster.com/dictionary/geospatial
+- https://isotc211.geolexica.org/Concepts/202/, accessed 20221010</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -1538,29 +1682,26 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Confidence Interval</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>- base</t>
+          <t>- controversial
+- approved</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Abstraction of real-world phenomena</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>- A feature may occur as a type or an instance.</t>
-        </is>
-      </c>
+          <t>Probability that the Quantity lies in the interval, conditioned on the measuring or modelling assumptions.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>- ISO 19101-1:2014, 4.1.11, modified</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -1583,25 +1724,30 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Custodian</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
+          <t>Granule</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>- core
+description: The smallest aggregation of data which is independently managed (i.e. described, inventoried, retrievable).</t>
+        </is>
+      </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
+          <t>The smallest aggregation of data which is independently managed (i.e. described, inventoried, retrievable). Granules may be managed as logical granules and/or physical granules.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>- See also Steward</t>
+          <t>- See also product.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- [NASA EarthData](https://www.earthdata.nasa.gov/learn/glossary)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -1624,32 +1770,30 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Earth spheres</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>- controversial
+description: An, often numeric, theoretical (or otherwise abstract) representation of an Entity intended to generate Data describing one or more of its traits.</t>
+        </is>
+      </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Spheres dividing planet Earth into subsystems, which are collectives of (physical) matter sharing specific traits</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>- Atmosphere
-- Hydrosphere
-- Cryosphere
-- Biosphere
-- Lithosphere
-- Anthroposhere</t>
-        </is>
-      </c>
+          <t>An, often numeric, theoretical (or otherwise abstract) representation of an Entity intended to generate Data describing one or more of its traits (as a result of pre-set conditions).</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>- The Process of generating Data using a model is called modelling.</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>- Hugget, R., et al, 2024, DOI: 10.1177/03091333241275465
-- Guth, P., et al, 2021, https://doi.org/10.3390/rs13183581
-- Martin, Y.E, et al, 2012</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -1672,31 +1816,44 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Catalogue</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
+          <t>Georectifying</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>- core
+description: Correcting for positional displacement with respect to the surface of the Earth.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Orthorectifying</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Provides the discovery of information to the user on which EO products can be obtained.</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>- A 'Product Catalogue' can organise products and collections with varying access level depending on product and user type.</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Correcting for positional displacement with respect to the surface of the Earth.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>- Source: ISO 19115-2:2019, 3.11; ISO 19115-2:2009(E); https://www.iso.org/standard/67039.html, modified</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>The correction of sample locations to achieve some sort of geometric regularity, e.g., a regular 2D geographic grid.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
@@ -1713,29 +1870,26 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Timeliness</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
+          <t>Policy Making</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>- high-impact
+description: Process by which governments translate their political vision into programmes and actions to deliver outcomes — desired change in the real world.</t>
+        </is>
+      </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>The Period between the moment of requesting Information to the moment of availability of Information. 
-- Near Real-Time (NRT): delivered less than 3 hours after requesting Information 
-- Slow-Time Critical (STC): delivered within 48 hours after requesting Information 
-- Non-Time Critical (NTC): typically delivered within 1 month after requesting Information</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>- In some context also known as delivery time.
-- C3S URDB describes timeliness as “the ability of the publish/subscribe middleware to provide the expected service within known time bounds”</t>
-        </is>
-      </c>
+          <t>Process by which governments translate their political vision into programmes and actions to deliver outcomes — desired change in the real world.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>- Adapted from ESA S3 User Guide</t>
+          <t>- [ESA/CEOS?, modified](https://digital-strategy.ec.europa.eu/en/library/quality-public-administration-toolbox-practitioners)</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -1758,72 +1912,109 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ancillary Data</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
+          <t>Uncertainty</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>- core
+description: Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
+        </is>
+      </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Data acquired on the same platform but not obtained from the main Sensor itself (usually provided as part of Level 0 Data). They have the primary purpose to serve the processing of main instrument Data (e.g. Position and velocity of platform).</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>This can be divided into data referred to as spacecraft ‘engineering’, ‘core housekeeping’ or ‘subsystem’ data obtained from other parts of the platform and includes parameters such as orbit position and velocity, attitude and its
-range of change, time, temperatures, pressures, jet firings, water dumps, internally produced magnet fields, and other environmental measurements. Ancillary refers to data that exist purely to serve the data processing.</t>
-        </is>
-      </c>
+          <t>Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>- ESA/CEOS?, modified
-- EO Data Stewardship Glossary)</t>
+          <t>- GUM</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Data other than instrument measurements, originating in the instrument itself or from the satellite, required to perform processing of the Data. They include orbit Data, attitude Data, time Information, and spacecraft engineering Data, Calibration Data, Data quality Information, and Data from other instruments or earth system models.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>Non-negative parameter, associated with data, which characterizes the dispersion of the values of a Trait that could reasonably be attributed to a Phenomenon by means of sensing or modelling.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>- In case of quantitative (continuous) data the uncertainty may be, for example, a standard deviation (or a given multiple of it), or the half-width of an interval having a stated level of confidence (see e.g. Standard and Expanded Uncertainty).
+- For qualitative (categorical?) data, uncertainty may be expressed by commission and omission ('confusion matrix') or overall errors.</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>- CEOS-ARD PFS template 20220302</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
+          <t>- Modified from GUM, VIM4:3.1, FIDUCEO, Notes added</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Measure of the spread of the distribution of possible values.</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>- [FIDUCEO Glossary](https://research.reading.ac.uk/fiduceo/glossary/), VIM?, modified</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Parameter, associated with the result of measurement, that characterizes the dispersion of values that could reasonably be attributed to the measurand.</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>- When the quality of accuracy or precision of measured values, such as coordinates, is to be characterized quantitatively, the quality parameter is an estimate of the uncertainty of the measurement results. Because accuracy is a qualitative concept, one should not use it quantitatively, that is associate numbers with it; numbers should be associated with measures of uncertainty instead.</t>
+        </is>
+      </c>
       <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>- ISO 19116:2004(E)</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Parameter characterizing the dispersion of the values being attributed to a measurand, based on the information used.</t>
+        </is>
+      </c>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>- VIM4: 3.1</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Standard Uncertainty</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
+          <t>Climate Projection</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>- core
+- approved</t>
+        </is>
+      </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Standard Uncertainty describes the standard deviation of the probability distribution describing the spread of possible values in quantitative/continuous [Data].</t>
+          <t>Simulated response of the climate system to a scenario of future emission or concentration of greenhouse gases (GHGs) and aerosols, generally derived using climate models. Climate Projections are distinguished from climate predictions by their dependence on the emission/concentration/radiative forcing scenario used, which is in turn based on assumptions concerning, for example, future socioeconomic and technological developments that may or may not be realised.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- IPCC</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -1846,36 +2037,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Geolocating</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
+          <t>Data Format</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>- core
+description: Structured Data that is machine readable and can be automatically read and processed by a computer, such as HDF, NetCDF, CSV, JSON, XML, etc.</t>
+        </is>
+      </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Geopositioning an Object using a Physical Sensor Model or a True Replacement Model.</t>
+          <t>Structured Data that is machine readable and can be automatically read and processed by a computer, such as HDF, NetCDF, CSV, JSON, XML, etc.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>- ISO 19115-2:2009, 4.11
----</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Determination of the geographic location of a &gt;=2D feature(?).</t>
-        </is>
-      </c>
+          <t>- CEOS Wiki</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>- ISO 19130-1:2018, 3.36 (‘geopositioning’), modified</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
@@ -1892,21 +2079,26 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Deprecated Product</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
+          <t>Classification System Levels</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>- core
+- approved</t>
+        </is>
+      </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Products and collections that have been superseded by a version and are still available, but whose use is discouraged since they will be decommissioned in the future.</t>
+          <t>Levels in a hierarchical Classification System.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -1929,25 +2121,30 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Granule</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
+          <t>Geocoding</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>- core
+description: Translation of one form of Location into another.</t>
+        </is>
+      </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>The smallest aggregation of data which is independently managed (i.e. described, inventoried, retrievable). Granules may be managed as logical granules and/or physical granules.</t>
+          <t>Translation of one form of Location into another.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>- See also product.</t>
+          <t>- Geocoding usually refers to the translation of "address" or "intersection" to "direct Position." Many service providers also include a "reverse geocoding" interface to their geocoder, thus extending the definition of the service as a general translator of Location. Because routing services use internal Location encodings not usually available to others, a geocoder is an integral part of the internals of such a service.</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>- [NASA EarthData](https://www.earthdata.nasa.gov/learn/glossary)</t>
+          <t>- ISO 19133:2005; https://www.iso.org/standard/32551.html</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -1970,43 +2167,38 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Entity</t>
+          <t>Band Central Wavelength</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>- base</t>
+          <t>- core
+- approved</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Something that has separate and distinct existence and objective or conceptual reality.</t>
+          <t>Single wavelength Value within the sensitivity interval of a spectroradiometric Sensor which represents the respective band. It could be either the mean, the median, the maximum sensitivity, or any other reasonable Value chosen to be representative.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>| Entry format example | Valid unit                                        |
+|----------------------|---------------------------------------------------|
+| 0.545 μm             | micrometre (μm), millimetre (mm), centimetre (cm) |</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>- ISO 19119:2016, 4.1.6</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>A government or business organization that is formed to conduct business or represent the government of the day.</t>
-        </is>
-      </c>
+          <t>- KCEO</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>CEOS Entities include Working Groups, Virtual Constellations, etc.</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data)</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
@@ -2023,23 +2215,19 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Policy milestone</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
+          <t>Cartographic Projection</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>- core</t>
+        </is>
+      </c>
       <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Policy milestones mark significant progress in addressing specific issues, or crucial decision points where significant choices are made. Concrete examples of Policy milestones are: Policy planning and proposing, impact assessment, implementation, or implementation cycles (e.g., Water Framework Directive, Marine Strategy Framework Directive), achievement of Policy objectives and Policy targets, evaluating evaluating and improvement of existing laws.</t>
-        </is>
-      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
@@ -2060,43 +2248,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Georectifying</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Orthorectifying</t>
-        </is>
-      </c>
+          <t>Copernicus Service Provider</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>- core
+- approved</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Correcting for positional displacement with respect to the surface of the Earth.</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>- Source: ISO 19115-2:2019, 3.11; ISO 19115-2:2009(E); https://www.iso.org/standard/67039.html, modified</t>
-        </is>
-      </c>
+          <t>Institutional body, organisation or programme that provides reliable, trusted (authoritative?) EO Information and that has the financial resources to sustain the provision. It utilises satellite Data, ground-based measurements, and other sources to generate accurate and timely Data products related to various aspects of the Earth's environment, such as land, Atmosphere, oceans, and climate.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>---</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>The correction of sample locations to achieve some sort of geometric regularity, e.g., a regular 2D geographic grid.</t>
-        </is>
-      </c>
+          <t>- KCEO</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
@@ -2113,25 +2290,26 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Process</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
+          <t>Location Error</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>- core
+description: Measure of the agreement between the represented Location of an Object and the true Location.</t>
+        </is>
+      </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>A series of activities that interact to produce a result.</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>A process may occur once-only or be recurrent or periodic.</t>
-        </is>
-      </c>
+          <t>Measure of the agreement between the represented Location of an Object and the true Location.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>- [Wikipedia](https://en.wikipedia.org/wiki/Process)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -2154,55 +2332,32 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Characteristic</t>
+          <t>Version Control</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>- base</t>
+          <t>- core
+description: Method of working with collections, similar to version control systems used in traditional software development but optimized to allow better processing of data and collaboration in data analytics and research contexts.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Distinguishing Feature</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>- A characteristic can be inherent or assigned.
-- A characteristic can be qualitative or quantitative.
-- There are various classes of characteristics, such as the following:
-  - physical (e.g. mechanical, electrical, chemical, biological);
-  - sensory (e.g. relating to smell, touch, taste, sight, hearing);
-  - behavioural (e.g. courtesy, honesty, veracity);
-  - temporal (e.g. punctuality, reliability, availability);
-  - ergonomic (e.g. physiological characteristic or related to human safety);
-  - functional (e.g. maximum speed of an aircraft).</t>
-        </is>
-      </c>
+          <t>Method of working with collections, similar to the version control systems used in traditional software development but optimized to allow better processing of data and collaboration in the context of data analytics, research, and any other form of data analysis.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>- ISO 9000:2005, 3.5.1</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Abstraction of a Property of an Object or of a set of objects.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>- Characteristics are used for describing Concepts.</t>
-        </is>
-      </c>
+          <t>- [Wikipedia](https://en.wikipedia.org/wiki/Data_version_control)</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>- ISO 1087-1:2000, 3.2.4; ISO 19146:2010(E); https://www.iso.org/standard/20057.html</t>
-        </is>
-      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
@@ -2219,21 +2374,22 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Laboratory Observation</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
+          <t>Data Access</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>- core
+description: Service to disseminate Data.</t>
+        </is>
+      </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Laboratory observations are (usually) in-situ observations in which the Object or Phenomenon is isolated from other systems or altered in its ‘original’ conditions or environment.</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>- It's important to consider that laboratory observations are typically conducted in controlled conditions, allowing for isolation or alteration of the Object or Phenomenon from its natural environment or other systems.</t>
-        </is>
-      </c>
+          <t>Service to disseminate Data.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
@@ -2260,21 +2416,26 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Lead time</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
+          <t>Collection Upgrade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>- core
+- approved</t>
+        </is>
+      </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Minimum time of interval between an Observation being tasked and being performed</t>
+          <t>New and improved major version of all products within a collection due to comprehensive reprocessing.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -2297,21 +2458,26 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data licencing</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
+          <t>Thematic Resolution</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>- core
+description: Level of categorical detail of information expressed by the number of classes.</t>
+        </is>
+      </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>A legal instrument by which a copyright holder may grant rights over the protected work. Data and content is open if it is subject to an explicitly-applied licence that conforms to the Open Definition. A range of standard open licenses are  available, such as the Creative Commons CC-BY licence, which requires only attribution.</t>
+          <t>Level of categorical detail of information expressed by the number of classes.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>- CEOS Wiki</t>
+          <t>- CGLS</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -2334,25 +2500,26 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Phenomenon</t>
+          <t>Standard Uncertainty</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>- base</t>
+          <t>- core
+description: Standard deviation of the probability distribution describing the spread of possible values in quantitative/continuous data.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Entity with at least one Property referenced by an identifier.</t>
+          <t>Standard deviation of the probability distribution describing the spread of possible values in quantitative/continuous data.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>- KCEO, modified after Wikipedia and the Columbia Encyclopaedia 2008</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -2375,23 +2542,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Earth observation product</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
+          <t>Coverage Interval</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>- core
+- approved</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Coverage extent</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>(indicative levels 2 and 3) are the direct output from standardized satellite Data processing chains, representing fundamental geophysical and biophysical variables. These products demonstrate direct Traceability to original satellite measurements through rigorous Calibration and Validation processes. The processing methodology prioritizes the conversion of raw Sensor Data into quantifiable physical measurements, maintaining strict adherence to standardized processing protocols and Validation requirements.</t>
+          <t>Range or specific subset of values associated with a coverage dataset.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>- Soil moisture from microwave sensors
-- Forest canopy height from LiDAR Data</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
           <t>- KCEO</t>
@@ -2417,27 +2588,30 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Temporal Reporting Period</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
+          <t>Path</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>- base
+description: "Line defined in an algorithmic way using at least two positions (can be open-ended). Alternative: line connecting two positions in an algorithmic way (limited by end points)."</t>
+        </is>
+      </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>The time Period used for reporting and for which the Information should be aggregated from the native Temporal Resolution.</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>| Entry format example | Valid unit                    |
-|----------------------|-------------------------------|
-| 1 s, 2 h, 1 d         | second, hour, day, month, year |</t>
-        </is>
-      </c>
+          <t>Line defined in an algorithmic way using at least two positions (can be open-ended). Alternative: line connecting two positions in an algorithmic way (limited by end points).</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>- A Path is a 1-dimensional Place.</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>- modified WIGOS Metadata Standard 2019</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -2460,21 +2634,26 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Spectral Bandwidth</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
+          <t>Source Data</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>- core
+description: Data required for production of an EO Collection (e.g., unenhanced satellite mission data) as well as further processed Level-1 data, or any other pre-processed format meeting program requirements.</t>
+        </is>
+      </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>The range of the Spectral band.</t>
+          <t>Data required for production of an EO Collection (e.g., unenhanced satellite mission data) as well as further processed Level-1 data (precision geometrically and radiometrically corrected radiance at the sensor), or any other pre-processed format that suppliers are providing access to that meets program requirements.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -2497,27 +2676,26 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Band Central Wavelength</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
+          <t>Atmosphere</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>- core
+- approved</t>
+        </is>
+      </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>A single wavelength Value within the sensitivity interval of a spectroradiometric Sensor which represents the respective band. It could be either the mean, the median, the maximum sensitivity, or any other reasonable Value chosen to be representative.</t>
+          <t>Layer of gases, commonly known as air, including suspended liquid and solid particles known as aerosols (incl. dust, clouds, snow and ice).</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>| Entry format example | Valid unit                                |
-|----------------------|-------------------------------------------|
-| 0.545 μm             | micrometre (μm), millimetre (mm), centimetre (cm) |</t>
-        </is>
-      </c>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -2540,35 +2718,64 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>- core
+description: Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
+        </is>
+      </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Particular era or span of time.</t>
+          <t>Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>- Periods are intervals named with a Period identifier.</t>
+          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>- ISO 19170:2021</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
+          <t>- ISO/TS 19101‑2:2008, 4.41</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Process aimed at verifying that the specified requirements are achieved or compliant. Involves comparing mission products with representative reference data, considering various observation conditions, ensuring the quality and traceability of the reference data used.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>- BIPM; QA4EO; ESA?, modified</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Assurance that a product, service, or system meets the needs of the customer and other identified stakeholders. Often involves acceptance and suitability with external customers.</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>- EU-US Land Imaging EO Collaboration</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
@@ -2581,25 +2788,31 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Steward</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
+          <t>Long Term Preservation</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>- core
+description: The act of maintaining information in a correct and independently understandable form over the long term.</t>
+        </is>
+      </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
+          <t>The act of maintaining information in a correct and independently understandable form over the long term.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>- See also Custodian</t>
+          <t>- Long term refers to a period of time long enough to be concerned with the impact which changing technologies, including support for media and data formats, and changing user communities will have on the information being held in a repository.
+- See also preservation.</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
@@ -2622,21 +2835,30 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Policy cycle</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
+          <t>Catalogue</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>- core
+- approved</t>
+        </is>
+      </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>A well-established concept, which is typically taught as the rational Model of Policy decision-making. It is an idealised view of the Policy Process.</t>
+          <t>System that provides users with discovery of information on which EO products can be obtained.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>- A 'Product Catalogue' can organise products and collections with varying access levels depending on product and user type.</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>- [ESA/CEOS?, modified](https://digital-strategy.ec.europa.eu/en/library/quality-public-administration-toolbox-practitioners )</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
@@ -2659,25 +2881,26 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
+          <t>Minimum Mapping Unit</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>- core
+description: The area of the smallest Feature that is still represented on a map.</t>
+        </is>
+      </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>An, often numeric, theoretical (or otherwise abstract) representation of an Entity intended to generate Data describing one or more of its traits (as a result of pre-set conditions).</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>- The Process of generating Data using a model is called modelling.</t>
-        </is>
-      </c>
+          <t>The area of the smallest Feature that is still represented on a map.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- CGLS</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
@@ -2700,21 +2923,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Dispose</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
+          <t>Temporal Reporting Period</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>- core
+description: Time period used for reporting and for which the information should be aggregated from the native temporal resolution.</t>
+        </is>
+      </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>To permanently and irrecoverably remove all copies of data held by an organization.</t>
+          <t>Time Period used for reporting and for which the information should be aggregated from the native Temporal Resolution.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>| Entry format example | Valid unit                     |
+|----------------------|-------------------------------|
+| 1 s, 2 h, 1 d        | second, hour, day, month, year |</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- Modified WIGOS Metadata Standard 2019</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
@@ -2737,22 +2971,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Thematic Uncertainty</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
+          <t>Policy File</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>- high-impact
+description: Policy documents that represent the official written reference for a given Policy.</t>
+        </is>
+      </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Uncertainty associated with the method of classification.</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>- Typically, it is computed from the error matrix.
-- For a review of classification Uncertainty metrics, consult Ye et al. 2018.</t>
-        </is>
-      </c>
+          <t>Policy documents that represent the official written reference for a given Policy.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
@@ -2779,31 +3013,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Reference</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>- core
+description: Regarded long-term according to X. However, in the Horizon Europe Missions terminology, regarded short-term.</t>
+        </is>
+      </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>A Phenomenon whose values for specific properties are known and understood with an Uncertainty significantly lower (quantify?) than that of the Observation with which it is compared.</t>
+          <t>Regarded long-term according to X. However, in the Horizon Europe Missions terminology, regarded short-term.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>A sort of Data acquired with an Uncertainty significantly lower (quantify?) than that of the Data it is being compared with.</t>
-        </is>
-      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>- VIM?, modified</t>
-        </is>
-      </c>
+      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
@@ -2820,33 +3055,24 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sample</t>
+          <t>Calibration</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>- controversial</t>
+          <t>- core
+- approved</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Subset of one or more entities.</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>- A sample may be spatial, temporal, spectral, or in any other dimension or Trait.
-- Each sample is contiguous, i.e. it does not consist of more than one discontinuous geometry in any dimension.
-- The Process of obtaining a sample is called sampling.</t>
-        </is>
-      </c>
+          <t>Process of quantitatively defining a system's (e.g. a Sensor or Model's) response to known, controlled inputs produced for example by references. In Remote Sensing, it implies the collection of pre-flight and in-flight calibration measurements and in-situ Data that is to be used in the Data calibration processing routine.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
@@ -2867,27 +3093,52 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Latency</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>- base
+description: Value and possibly Uncertainty of a Trait of a specific Entity.</t>
+        </is>
+      </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Period between the end of sensing of a Phenomenon to the beginning of availability of a specific product</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
+          <t>Value and possibly Uncertainty of a Trait of a specific Entity.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>- Data simply describe entities using certain traits and are not targeted at a particular use or audience.</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Data can be categorised into:
+- factual (i.e. obtained by Observation) or fictional (obtained e.g. through modelling, estimating or assigning)
+- quantitative (continuous) or qualitative (categorical)
+- analogue or digital
+(list not exhaustive!)</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>- ?</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>- KCEO</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Scientific or technical measurements, values calculated therefrom, observations, or facts that can be represented by numbers, tables, graphs, models, text, or symbols which are used as a basis for reasoning and further calculation.</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
@@ -2904,31 +3155,40 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Coverage interval</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Coverage extent</t>
-        </is>
-      </c>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>- base
+description: Property having a magnitude that can be expressed as a number from a continuous and contiguous range and a reference.</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Refers to a range or a specific subset of values associated with a coverage dataset.</t>
+          <t>Property having a magnitude that can be expressed as a number from a continuous and contiguous range and a reference.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>- ISO/IEC Guide 99:2007, 1.1, modified — Notes omitted</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Property whose instances can be compared by ratio or only by order.</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>- gEOGlos (VIM4 Notes omitted)</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
@@ -2945,30 +3205,26 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Spatial extent</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
+          <t>Policy Milestone</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>- high-impact
+description: Markers of significant progress in addressing specific issues, or crucial decision points where significant choices are made within a policy process.</t>
+        </is>
+      </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>The zone or region of space described by a Geographic Identifier in the form of a label or code, or by a bounding box. It consists in the maximum extent (the spatial boundary or limits) within which the User is requesting Data.  
-The attribute represents the maximum spatial extent of the AOI, and in case the AOI is made of many discontinuous zones then it represents the maximum extent of the union of all the zones.</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>- WIGOS metadata standard defines it as the typical spatial georeferenced volume covered by the observations</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>- if a User is requesting Information about degradation of African protected sites, then the AOIs are the protected sites, and the spatial extent is the African continent.</t>
-        </is>
-      </c>
+          <t>Markers of significant progress in addressing specific issues, or crucial decision points where significant choices are made. Concrete examples include: policy planning and proposing, impact assessment, implementation, or implementation cycles (e.g., Water Framework Directive, Marine Strategy Framework Directive), achievement of Policy Objectives and Policy Targets, and evaluating and improving existing laws.</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>- Adapted from ISO 19170-1:2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -2991,21 +3247,31 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Reproducibility</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>- base
+description: Element of a type domain.</t>
+        </is>
+      </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Is concerned with the validity of the results of that particular study, i.e., the possibility of readers to check whether results have been manipulated, by reproducing exactly the same study using the same Data and methods.</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
+          <t>Element of a type domain.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>- A Value may consider a possible state of an object within a class or type (domain).
+- A data value is an instance of a data type, a value without identity.</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>- Ostermann and Granell (2015)</t>
+          <t>- ISO/IEC 19501:2005, 0000_5</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -3028,25 +3294,26 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Spatial reporting unit</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
+          <t>Collection Update</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>- core
+- approved</t>
+        </is>
+      </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>The smallest spatial Object of interest that may be used for reporting and for which the Information should be aggregated.</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>- WIGOS 2019 use ‘spatial reporting interval’ probably assuming the observations are reported on a Grid with regular spacing/intervals.</t>
-        </is>
-      </c>
+          <t>Minor revisions to a relatively small number of products within a collection for the purpose of correcting errors and maintaining consistent quality.</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -3069,19 +3336,24 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Information</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr"/>
+          <t>Laboratory Observation</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>- core
+description: Usually in-situ observations in which the Object or Phenomenon is isolated from other systems or altered in its original conditions or environment.</t>
+        </is>
+      </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>The result of organisation, interpretation, categorisation, classification, or some other form of processing of Data attaching to it a certain meaning that can be understood by the addressee.</t>
+          <t>Usually in-situ observations in which the Object or Phenomenon is isolated from other systems or altered in its original conditions or environment.</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>- Information depends on Data and is targeted.</t>
+          <t>- It is important to consider that Laboratory Observations are typically conducted in controlled conditions, allowing for isolation or alteration of the Object or Phenomenon from its natural environment or other systems.</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -3110,27 +3382,20 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Accuracy</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr"/>
+          <t>Environmental Process</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>- core
+description: ""</t>
+        </is>
+      </c>
       <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Accuracy is the proximity of Measurement results to the accepted Value; precision is the degree to which repeated or reproducible measurements under unchanged conditions show the same results.</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>- In essence, accuracy reflects how close measurements are to the accepted Value, while precision gauges the reliability and consistency of those measurements.</t>
-        </is>
-      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>- BS ISO 5725-1</t>
-        </is>
-      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
@@ -3151,30 +3416,26 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>In-Situ Observation</t>
+          <t>Measurement Uncertainty</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>- controversial</t>
+          <t>- core
+description: Uncertainty associated with the method of Measurement.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Observations performed in the same Place where a Phenomenon occurs, normally without isolating it from other systems (its environment) or altering its pre-Observation state</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>- The main Characteristic of such observations is that distance has no or only negligible (within Uncertainty) influence on the Value of the Property observed. In-situ observations therefore often require either direct physical contact or small distances between a Sensor and the observed Phenomenon. 
-- Observations not fulfilling these conditions are considered Remote Sensing</t>
-        </is>
-      </c>
+          <t>Uncertainty associated with the method of Measurement.</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- CEOS Wiki adopted from JCGM GUM</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
@@ -3197,18 +3458,34 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Policy target</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr"/>
+          <t>Temporal Revisit</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>- core
+description: Interval between successive observations.</t>
+        </is>
+      </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Specific level or rate set for the Policy objective.</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
+          <t>Interval between successive observations.</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>- In Remote Sensing it is also called repeat cycle.
+- More generally it is known as temporal sampling interval.</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>| Entry format example | Valid unit                     |
+|----------------------|-------------------------------|
+| 1 s, 2 h             | second, hour, day, month, year |</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr">
         <is>
           <t>- KCEO</t>
@@ -3234,21 +3511,30 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>impact</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr"/>
+          <t>Period Identifier</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>- core
+description: Temporal reference in the form of a label or code that identifies a Period.</t>
+        </is>
+      </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>impact is regarded long-term according to X. However, in the Horizon Europe Missions terminology, impact is regarded short-term.</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr"/>
+          <t>Temporal reference in the form of a label or code that identifies a Period.</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>- Period Identifiers are the temporal equivalent of geographic identifiers as specified in ISO 19912.</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO 19170:2021</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
@@ -3271,21 +3557,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Object</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
+          <t>Area of Interest</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>- core
+- approved</t>
+        </is>
+      </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Entity with a well-defined boundary and identity that encapsulates state and behaviour.</t>
+          <t>Zone in 2D or 3D for which the Information or Data is requested. It can be discontinuous in space — in other words it can consist of the union of many separate zones (e.g., Natural Reserves in Africa, Urban environments, etc.). The attribute indicates a request for spatially complete Data within the AOI zone(s).</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>| Type                                    | Entry format example              | Valid units |
+|-----------------------------------------|-----------------------------------|-------------|
+| Geographical/administrative identifier  | NUTS3, LAU, Natura 2000 site      | unitless    |</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>- ISO/IEC 19501:2005</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
@@ -3308,28 +3605,34 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Earth Observation based output</t>
+          <t>Timeliness</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>- to be defined</t>
+          <t>- core
+description: Period between the moment of requesting information and the moment of availability of information.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>(indicative level 4 and beyond) represent a higher level of processing and integration that goes beyond basic Data processing. These outputs are often designed specifically for Policy or decision-making needs, and can be categorized into sub-categories:
-- Outputs from models/Model Integration involves using EO products as inputs in numerical models or combining them with other Data sources in modeling frameworks. 
-- Indicator-Based Outputs:  EO products are transformed through specialized algorithms (including statistical methods, machine learning, and pattern recognition) to create meaningful metrics based on spatio-temporal analysis.
-- Outputs from Reanalysis: involves merging EO products with other observations and models, creating consistent long-term records of past atmospheric, oceanic, and land surface conditions, and filling gaps through Data assimilation techniques.</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr"/>
+          <t>Period between the moment of requesting information and the moment of availability of information.
+- Near Real-Time (NRT): delivered less than 3 hours after requesting information.
+- Slow-Time Critical (STC): delivered within 48 hours after requesting information.
+- Non-Time Critical (NTC): typically delivered within 1 month after requesting information.</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>- In some contexts also known as delivery time.
+- C3S URDB describes timeliness as "the ability of the publish/subscribe middleware to provide the expected service within known time bounds".</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Adapted from ESA S3 User Guide</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
@@ -3352,25 +3655,26 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Property</t>
+          <t>Hydrosphere</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>- base</t>
+          <t>- core
+description: The masses of liquid water, such as oceans, lakes, and rivers.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>observable Trait</t>
+          <t>The masses of liquid water, such as oceans, lakes, and rivers.</t>
         </is>
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
@@ -3393,21 +3697,30 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Geographic Grid</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr"/>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>- core
+- approved</t>
+        </is>
+      </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>(Regular) Grid based on a Geographic Coordinate Reference System (CRS).</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr"/>
+          <t>Proximity of Measurement results to the accepted Value; precision is the degree to which repeated or reproducible measurements under unchanged conditions show the same results.</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>- In essence, Accuracy reflects how close measurements are to the accepted Value, while precision gauges the reliability and consistency of those measurements.</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- BS ISO 5725-1</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
@@ -3430,21 +3743,26 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Minimum Mapping Width</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
+          <t>Traceability</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>- core
+description: Property of a measurement result whereby the result can be related to a reference through a documented unbroken chain of calibrations each contributing to the measurement uncertainty.</t>
+        </is>
+      </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>The width of the smallest linear Feature that is still represented on a map.</t>
+          <t>Property of a measurement result whereby the result can be related to a Reference through a documented unbroken chain of calibrations, each contributing to the measurement uncertainty.</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>- CGLS</t>
+          <t>- https://www.isobudgets.com/Measurement-traceability-complying-iso-17025-requirements/</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
@@ -3467,51 +3785,36 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Instrument Data</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr"/>
+          <t>Biosphere</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>- core
+- approved</t>
+        </is>
+      </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>- These data consist of instrument science and engineering data, and possibly ancillary data. Instrument engineering data is produced by engineering sensor(s) of an instrument, used either for operating the instrument or for processing the science data generated by the instrument. Instrument science data is produced by the science sensor(s) of an instrument, usually constituting the basic reason for existence of an instrument.</t>
-        </is>
-      </c>
+          <t>Masses of living organisms, such as vegetation and animals, including dead but still connected parts such as roots, trunks or branches.</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Data created by an instrument including scientific measurements and any engineering or ancillary data which may be included in the data packets.</t>
-        </is>
-      </c>
+          <t>- Guth et al. 2021</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>Data produced and transmitted by the science and engineering sensors of an instrument, and, in the spacecraft environment, any additional data packaged with the instrument’s sensor data by virtue of services provided</t>
-        </is>
-      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
-        </is>
-      </c>
+      <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
@@ -3524,26 +3827,30 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Grid</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
+          <t>Update Frequency</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>- core
+description: Frequency at which the product is available to users.</t>
+        </is>
+      </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Network composed of two or more sets of curves in which the members of each set intersect the members of the other sets in an algorithmic way.</t>
+          <t>Frequency at which the product is available to users.</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>- The curves partition a space into grid cells or zones.
-- The intersection points of the curves are called nodes.</t>
+          <t>- Also known in product catalogues as dissemination frequency.</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>- ISO 19123:2005, 4.1.23; Note 1 modified; Note 2 added</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
@@ -3566,21 +3873,26 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Geolocation Information</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr"/>
+          <t>Lithosphere</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>- core
+description: The solid, inanimate outer layer of the Geosphere. For the purposes of Earth Observation, includes soils ('pedosphere').</t>
+        </is>
+      </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Information used to determine geographic Location.</t>
+          <t>The solid, inanimate outer layer of the Geosphere. For the purposes of Earth Observation, the Lithosphere is considered to include soils ('pedosphere').</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>- ISO 19130-1:2018, 3.34</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -3603,25 +3915,30 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Decommissioned Product</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr"/>
+          <t>Information</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>- base
+description: The result of organisation, interpretation, categorisation, classification, or some other form of processing of Data attaching to it a certain meaning that can be understood by the addressee.</t>
+        </is>
+      </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Products and collections that have been superseded by new versions and are no longer available.</t>
+          <t>The result of organisation, interpretation, categorisation, classification, or some other form of processing of Data attaching to it a certain meaning that can be understood by the addressee.</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>- Decommissioned products are no longer supported i.e corrections will not be made, new data will not be added, support is not available.</t>
+          <t>- Information depends on Data and is targeted.</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
@@ -3644,28 +3961,23 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Temporal Resolution</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr"/>
+          <t>Temporal Consistency</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>- core
+description: Condition where the temporal statistical properties of the sample depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
+        </is>
+      </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>The Observation or Model output representing regular intervals and specifying the length of the interval that determines the smallest event or Process that can be resolved (e.g., the Period between observations, the time steps in a Model).</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>- WIGOS 2019 distinguishes between sampling time Period, as the Period over which a Measurement is taken, and temporal sampling interval as the time Period between the beginning of consecutive sampling periods. Temporal resolution in this Glossary is equivalent to sampling time Period as used by WIGOS.</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>| Entry format example | Valid unit                    |
-|----------------------|-------------------------------|
-| 1 s, 2 h, 1 m         | second, hour, day, month, year |</t>
-        </is>
-      </c>
+          <t>Condition where the temporal statistical properties of the Sample depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
           <t>- KCEO</t>
@@ -3691,21 +4003,31 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Policy</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
+          <t>Metadata</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>- core
+description: Data describing other data, providing an understanding of the content and utility of a product or collection.</t>
+        </is>
+      </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>A deliberate system of guidelines to guide decisions and achieve rational outcomes. A policy is a statement of intent and is implemented as a procedure or protocol. Policies are typically promulgated through official written documents.</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr"/>
+          <t>Data describing other data, providing an understanding of the content and utility of a product or collection.</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>- Metadata may be used to select data for a particular scientific investigation.
+- Metadata is intended as information describing significant aspects of a resource (Earth Observation space data in this context). They are created for the purposes of data search, discovery and access management and may exist at various levels, typically from data collection through to the individual variables of each product in a collection.</t>
+        </is>
+      </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
@@ -3728,16 +4050,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Spatial consistency</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
+          <t>Spatial Resolution</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>- core
+description: ''</t>
+        </is>
+      </c>
       <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>The spatial statistical properties of the Data depend only on the underlaying physical processes and don’t depend on other factors such as fusing different products or sensors. Also, the validity of the assumptions of the procedure to produce Information holds true across the whole spatial range.</t>
-        </is>
-      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
@@ -3765,26 +4088,26 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Preservation</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr"/>
+          <t>Phenomenon</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>- base
+description: Entity with at least one Property referenced by an identifier.</t>
+        </is>
+      </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Processes and operations used to ensure data technical and intellectual survival through time.</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>- It grants data integrity, its discoverability and accessibility, and facilitates its (re)-use in the long term. 
-- Preservation is one of the tasks of data curation.</t>
-        </is>
-      </c>
+          <t>Entity with at least one Property referenced by an identifier.</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- KCEO, modified after Wikipedia and the Columbia Encyclopaedia 2008</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
@@ -3807,25 +4130,26 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Geographic Data</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr"/>
+          <t>Geolocation Information</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>- core
+description: Information used to determine geographic Location.</t>
+        </is>
+      </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Data with implicit or explicit Reference to a Location relative to the Earth.</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>- Geographic Information is also used as a term for Information concerning phenomena implicitly or explicitly associated with a Location relative to the Earth.</t>
-        </is>
-      </c>
+          <t>Information used to determine geographic Location.</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>- ISO 19109:2015, 4.13; ISO 19109:2005</t>
+          <t>- ISO 19130-1:2018, 3.34</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
@@ -3848,36 +4172,59 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Metadata</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
+          <t>Verification</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>- core
+description: Provision of objective evidence that a given item fulfils specified requirements.</t>
+        </is>
+      </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Data about data, which provides an understanding of the content and utility of a product or collection</t>
+          <t>Provision of objective evidence that a given item fulfils specified requirements.</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>- Metadata may be used to select on data for a particular scientific investigation. 
-- Metadata is intended as information describing significant aspects of a resource (Earth Observation space data in this context). They are created for the purposes of data search, discovery and access management and may exist at various levels, typically from data collection through to the individual variables of each product in a collection.</t>
+          <t>- When applicable, measurement uncertainty should be taken into consideration.
+- The item may be, e.g. a Process, measurement procedure, material, compound, or measuring system.
+- The specified requirements may be, e.g. that a manufacturer's specifications are met.
+- Verification should not be confused with Calibration. Not every verification is a Validation.</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>- ISO/IEC Guide 99:2007, 2.44</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Evaluation of whether or not a product, service, or system complies with a regulation requirement, specification, or imposed condition. Often an internal Process.</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>- EU-US Land Imaging EO Collaboration</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Means to evaluate the reliability of the data in the absence of a reference dataset, allowing for an assessment of its standalone performance. Involves confirming the consistency and internal coherence of the data without direct comparison to external reference sources.</t>
+        </is>
+      </c>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
@@ -3890,21 +4237,26 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Measurement uncertainty</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
+          <t>Property</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>- base
+description: Observable Trait.</t>
+        </is>
+      </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Uncertainty associated with the method of Measurement.</t>
+          <t>Observable Trait.</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>- CEOS Wiki adopted from JCGM GUM</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
@@ -3927,32 +4279,26 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Temporal Revisit</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>- base
+description: Entity with a well-defined boundary and identity that encapsulates state and behaviour.</t>
+        </is>
+      </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>The interval between successive observations.</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>- In Remote Sensing it is also called repeat cycle.
-- More generally it is known as temporal sampling interval.</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>| Entry format example | Valid unit                    |
-|----------------------|-------------------------------|
-| 1 s, 2 h             | second, hour, day, month, year |</t>
-        </is>
-      </c>
+          <t>Entity with a well-defined boundary and identity that encapsulates state and behaviour.</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO/IEC 19501:2005</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
@@ -3975,67 +4321,43 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Test term</t>
+          <t>Time of Day</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>- base</t>
+          <t>- core
+description: Time of the day at which the variable or parameter is observed or simulated by a model.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Definition_goes_here.</t>
+          <t>Time of the day at which the variable or parameter is observed or simulated by a model.</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>- here should be bullets
-- like this</t>
+          <t>- In Remote Sensing it is also known as time of overpass.</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>- this is also bullets
-- like this</t>
+          <t>| Type      | Entry format example | Valid unit |
+|-----------|----------------------|------------|
+| timestamp | 18:00 h (0–24)       | Hours      |
+| timerange | 18:00 – 20:00 h      | Hours      |</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>- KCEO (no link included, so no brackets)
-- [Website](https://en.wikipedia.org/wiki/Thai_script) ( if you have web references, just add the term goes into square [] brackets and the url into () normal brackets
-in case that there is more than one definition, just add three underscores to separate the definition, rest remains identical 
-# Test term</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Second_definition_goes_here.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>- here should be bullets
-- like this</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>- this is also bullets
-- like this</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>- KCEO (no link included, so no brackets)
-- [Website](https://en.wikipedia.org/wiki/Thai_script) ( if you have web references, just add the term goes into square [] brackets and the url into () normal brackets
-```
----
-References: 
-1. Strobl, P. A., Woolliams, E. R., &amp; Molch, K. (2024). Lost in Translation: The Need for Common Vocabularies and an Interoperable Thesaurus in Earth Observation Sciences. Surveys in Geophysics, 1-29.</t>
-        </is>
-      </c>
+          <t>- KCEO</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
@@ -4052,23 +4374,26 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Quality indicator</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr"/>
+          <t>Obsolete Product or Collection</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>- core
+description: Products or collections which have been superseded by later versions of a product or collection.</t>
+        </is>
+      </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>A quality indicator shall provide sufficient Information to allow all users to readily evaluate 
-the “fitness for purpose” of the Data or derived product. A Quality Indicator may be a number, 
-set of numbers, graph, Uncertainty budget, or a simple “flag”.</t>
+          <t>Products or collections which have been superseded by later versions of a product or collection.</t>
         </is>
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>- CEOS Wiki</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
@@ -4091,14 +4416,19 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Temporal Consistency</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr"/>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>- core
+- approved</t>
+        </is>
+      </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>It indicates that the temporal statistical properties of the Sample depend only on the underlying physical processes and don’t depend on other factors such as fusing different products or sensors.</t>
+          <t>Reference Period, time or measure against which the Information is assessed or compared.</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -4108,10 +4438,18 @@
           <t>- KCEO</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Source data that has been processed to a common set of requirements and organised into a form that allows immediate analysis and interoperability through time and with other collections.</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
@@ -4128,21 +4466,31 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Confidence interval</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr"/>
+          <t>Earth Observation</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>- high-impact
+description: Science domain dealing with technologies and methods of collecting and analyzing observations about the different Earth spheres.</t>
+        </is>
+      </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>The probability that the Quantity lies in the interval, conditioned on the measuring or modelling assumptions.</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr"/>
+          <t>Science domain dealing with technologies and methods of collecting and analyzing observations about the different Earth spheres.</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>- Earth Observation (EO) can be categorised by location of the sensor into space-borne, air-borne, sea-borne, ground-based, underwater and underground EO.
+- Earth Observation (EO) includes Remote Sensing, such as satellite imagery, as well as in-situ observations, e.g., with ground-based devices.</t>
+        </is>
+      </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Modified GEO definition [GEO (earthobservations.org)](https://earthobservations.org/resources#key)</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
@@ -4165,25 +4513,23 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Time of Year</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr"/>
+          <t>Spectral Resolution</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>- core
+description: Measure of the ability to resolve features in the electromagnetic spectrum.</t>
+        </is>
+      </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>The time of the year that the variable is observed or simulated by a Model.</t>
+          <t>Measure of the ability to resolve features in the electromagnetic spectrum.</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>| Type      | Entry format example | Valid unit       |
-|-----------|----------------------|------------------|
-| timestamp | m/d                  | Not Applicable   |
-| timerange | m/d - m/d            | Not Applicable   |</t>
-        </is>
-      </c>
+      <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
           <t>- KCEO</t>
@@ -4209,21 +4555,26 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Obsolete Product or Collection</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
+          <t>Near Real Time Data</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>- high-impact
+description: Data available for use with a specified (small and application dependent) latency, typically 3 hours for meteorological applications.</t>
+        </is>
+      </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Products or collections which have been superseded by later versions of a product or collection.</t>
+          <t>Data available for use with a specified (small and application dependent) latency, typically 3 hours for meteorological applications.</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
@@ -4246,21 +4597,38 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Minimum Mapping Unit</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
+          <t>Measurand</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>- core
+description: Particular Quantity subject to Measurement.</t>
+        </is>
+      </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>The area of the smallest Feature that is still represented on a map.</t>
+          <t>Particular Quantity subject to Measurement.</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>| Step | Process description |
+| :----- | :--------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------- |
+| (Raw) | The complete and unaltered/unprocessed set of Data acquired by one or several sensors on a platform |
+| M/0 uncalibrated | Unaltered/unprocessed Level 0 (main) Sensor Data annotated with processed Ancillary Data and supplemented by Auxiliary Data (including radiometric and geometric Calibration coefficients and geo-referencing parameters) allowing further processing to higher Levels. |
+| M/1 Sensor-calibrated | Level M/0 Sensor Data which have been calibrated (ideally traceable to SI) and spatially aligned (co-located, eventually co-gridded) to represent at-Sensor measurements (Value and Uncertainty) in Sensor nominal spatiotemporal sampling, supplemented by appropriate ancillary data. |
+| M/2 target-calibrated | Level M/1 Data processed to represent geophysical Property values (and uncertainties) for a specified target (Object, Feature of interest, e.g. surface reflectance, apparent temperature) derived from M/1 Sensor Data, as much as possible maintaining the sensors nominal spatial and temporal sampling (Observation preserving). |
+| M/3 homogenised | Level M/1 or M/2 Data which have been generalised and integrated across one or several platforms and acquisitions to achieve an increased, more regular or in any other form enhanced spatial or temporal coverage in which states geophysical values agnostic of the originally acquiring Sensor and Observation condition and thus directly comparable. This homogenisation and fusion may include measurand re-Calibration to external standards and references including use of modelling, aggregation and interpolation. |
+| M/4 derived/inferred | Model output or results from analyses of Level M/3 (or lower level) Data i.e., attributes that might not be directly observable by the Sensor(s) but are derived from observations in combination with other external incl. non-observational Data using techniques like modelling or machine learning (AI). |
+From http://doi.org/10.2760/46796</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>- CGLS</t>
+          <t>- VIM: 1993, 2.6</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
@@ -4283,21 +4651,26 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Location error</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
+          <t>Latency</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>- core
+description: Period between the end of sensing of a Phenomenon to the beginning of availability of a specific product.</t>
+        </is>
+      </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Indicate the agreement between the represented Location of an Object and the true Location.</t>
+          <t>Period between the end of sensing of a Phenomenon to the beginning of availability of a specific product.</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ?</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
@@ -4320,24 +4693,23 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Vertical Levels</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr"/>
+          <t>Policy Target</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>- high-impact
+description: Specific level or rate set for the Policy Objective.</t>
+        </is>
+      </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Levels of a vertical discretization. Examples may be pressure levels in an atmospheric Model reanalysis or height levels in a forest biomass EO product.</t>
+          <t>Specific level or rate set for the Policy Objective.</t>
         </is>
       </c>
       <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>| Entry format example               | Valid unit        |
-|------------------------------------|-------------------|
-| 1, 5, 10 meter; 1000, 850, 500 hPa  | meter, hPa, unitless |</t>
-        </is>
-      </c>
+      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
           <t>- KCEO</t>
@@ -4363,39 +4735,32 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Quantity</t>
+          <t>Policy Objective</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>- base</t>
+          <t>- high-impact
+description: Desired outcome that policymakers wish to achieve.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Property having a magnitude that can be expressed as a number from a continuous and contiguous range and a Reference.</t>
+          <t>Desired outcome that policymakers wish to achieve.</t>
         </is>
       </c>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>- ISO/IEC Guide 99:2007, 1.1, modified – Notes omitted</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Property whose instances can be compared by ratio or only by order.</t>
-        </is>
-      </c>
+          <t>- KCEO</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>- gEOGlos(VIM4 Notes omitted)</t>
-        </is>
-      </c>
+      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
@@ -4412,14 +4777,19 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr"/>
+          <t>Forecast Range</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>- core
+description: The forecast period.</t>
+        </is>
+      </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>The Reference Period, time or measure against which the Information is assessed or compared</t>
+          <t>The forecast period.</t>
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
@@ -4429,18 +4799,10 @@
           <t>- KCEO</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Source data that has been processed to a common set of requirements and organised into a form that allows immediate analysis and interoperability through time and with other collections.</t>
-        </is>
-      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data)</t>
-        </is>
-      </c>
+      <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
@@ -4457,28 +4819,26 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Duration</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr"/>
+          <t>Quality Indicator</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>- core
+description: Indicator providing sufficient information to allow all users to readily evaluate the fitness for purpose of the data or derived product.</t>
+        </is>
+      </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Non-negative interval Quantity of time equal to the difference between the final and initial instants of a time.</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>- The duration is one of the base quantities in the International System of Quantities (ISQ) on which the International System of Units (SI) is based. The term “time” instead of “duration” is often used in this context and also for an infinitesimal duration.
-- For the term “duration”, expressions such as “time” or “time interval” are often used, but the term “time” is not recommended in this sense and the term “time interval” is deprecated in this sense to avoid confusion with the concept of “time interval”.
-- The exact duration of a time scale unit depends on the time scale used. For example, the durations of a year, month, week, day, hour or minute, may depend on when they occur [in a Gregorian calendar, a calendar month can have a duration of 28, 29, 30, or 31 days; in a 24-hour clock, a clock minute can have a duration of 59, 60, or 61 seconds, etc.]. Therefore, the exact duration can only be evaluated if the exact duration of each is known.
-- This definition is closely related to NOTE 1 of the terminological entry “duration” in IEC 60050-113:2011, 113–01–13.</t>
-        </is>
-      </c>
+          <t>Indicator providing sufficient information to allow all users to readily evaluate the fitness for purpose of the data or derived product. May be a number, set of numbers, graph, Uncertainty budget, or a simple flag.</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>- ISO 8601-1:2019, 3.1.1.8</t>
+          <t>- CEOS Wiki</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
@@ -4501,21 +4861,26 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Collection Upgrade</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr"/>
+          <t>User Interface</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>- core
+description: Set of all the components of an interactive system that provide information and controls for the user to accomplish specific tasks with the interactive system.</t>
+        </is>
+      </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>A new and improved major version of all products within a collection due to comprehensive reprocessing.</t>
+          <t>Set of all the components of an interactive system that provide information and controls for the User to accomplish specific tasks with the interactive system.</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- ISO 9241-110:2020, 3.10</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
@@ -4538,30 +4903,30 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Stability</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>- core</t>
+          <t>- core
+description: Maximum acceptable change in Uncertainty per decade.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>act of determining the Value of a Property by interacting in a reproducible way with the Phenomenon using a Sensor</t>
+          <t>Maximum acceptable change in Uncertainty per decade.</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>- the result of an observation is a Value complemented by an Uncertainty, often itself being referred to as 'observation'
-- an observation (result) represents a Sample of the Phenomenon (otherwise it would be identical with the Phenomenon)</t>
+          <t>- GCOS uses bias or systematic errors instead of Uncertainty.</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Modified from GCOS 2022</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
@@ -4584,14 +4949,19 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data access</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr"/>
+          <t>Classification System</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>- core
+- approved</t>
+        </is>
+      </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>The service to disseminate Data</t>
+          <t>Nomenclature used to classify Information into categorical thematic classes (e.g., EUNIS, MAES ecosystems, Corine Land Cover, LCCS).</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
@@ -4621,14 +4991,19 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Policy objective</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr"/>
+          <t>Spatial Consistency</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>- core
+description: Condition where the spatial statistical properties of the data depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
+        </is>
+      </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Desired Outcome that policymakers wish to achieve.</t>
+          <t>Condition where the spatial statistical properties of the data depend only on the underlying physical processes and not on other factors such as fusing different products or sensors. Also, the validity of the assumptions of the procedure to produce information holds true across the whole spatial range.</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
@@ -4658,25 +5033,26 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Cell</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr"/>
+          <t>Expanded Uncertainty</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>- core
+description: Standard Uncertainty multiplied by a coverage factor k, chosen to obtain a desired level of confidence.</t>
+        </is>
+      </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Spatial, spatio-temporal zone or temporal unit of geometry with dimensionality greater than 0, associated with a zone.</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>- Cells are the unit of geometry in a DGGS, and the geometry of the region of space-time occupied by a zone is a cell.</t>
-        </is>
-      </c>
+          <t>Standard Uncertainty multiplied by a coverage factor, k. The coverage factor is chosen to obtain a desired level of confidence. Most commonly a 95% confidence interval is chosen. For a Gaussian distribution, this is achieved with a coverage factor k = 2. (Note that strictly this provides a 95.45% confidence interval.)</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>- ISO 19170:2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
@@ -4699,21 +5075,32 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Policy making</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr"/>
+          <t>Sensor</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>- core
+description: Device or instrument suited (through physical/chemical interaction) to measure one or more properties of a Phenomenon and thus collect factual/objective data.</t>
+        </is>
+      </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>The Process by which governments translate their political vision into programmes and actions to deliver 'outcomes' - desired change in the real world.</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr"/>
+          <t>Device or instrument suited (through physical/chemical interaction) to measure one or more properties of a Phenomenon and thus collect factual/objective data.</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>- Sensing is therefore a synonym for Observation (the Process).
+- As by their definition, sensors perform sampling.
+- Sensors used to obtain measurements must be calibrated and provide uncertainties.</t>
+        </is>
+      </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>- [ESA/CEOS?, modified](https://digital-strategy.ec.europa.eu/en/library/quality-public-administration-toolbox-practitioners )</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
@@ -4736,21 +5123,26 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Biosphere</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr"/>
+          <t>Minimum Mapping Width</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>- core
+description: The width of the smallest linear Feature that is still represented on a map.</t>
+        </is>
+      </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>masses of living organisms, such as vegetation and animals, including dead but still connected parts such as roots, trunks or branches</t>
+          <t>The width of the smallest linear Feature that is still represented on a map.</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- CGLS</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
@@ -4773,21 +5165,30 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Spectral band</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr"/>
+          <t>Backup</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>- core
+- approved</t>
+        </is>
+      </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Part of the electromagnetic spectrum of specific wavelengths. In Remote Sensing usually described by central wavelength and bandwidth.</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr"/>
+          <t>General practice of making copies of current baseline and derived products of EO Collections at specified time intervals, and storing those copies in a manner that will not affect the data if the primary distribution environment is compromised.</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>- The emphasis is on the ability to retrieve a copy of the entire EO Collection on demand if the original data is lost or compromised.</t>
+        </is>
+      </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
@@ -4810,21 +5211,36 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Replicability</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr"/>
+          <t>Temporal Resolution</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>- core
+description: Observation or model output representing regular intervals, specifying the length of the interval that determines the smallest event or process that can be resolved.</t>
+        </is>
+      </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Enables other researchers to conduct an independent study with different Data and similar but not identical methods, yet arriving at results that confirm the original study’s hypothesis.</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
+          <t>Observation or model output representing regular intervals, specifying the length of the interval that determines the smallest event or Process that can be resolved (e.g., the Period between observations, the time steps in a model).</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>- WIGOS 2019 distinguishes between sampling time Period, as the Period over which a Measurement is taken, and temporal sampling interval as the time Period between the beginning of consecutive sampling periods. Temporal Resolution in this Glossary is equivalent to sampling time Period as used by WIGOS.</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>| Entry format example | Valid unit                     |
+|----------------------|-------------------------------|
+| 1 s, 2 h, 1 m        | second, hour, day, month, year |</t>
+        </is>
+      </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>- Craglia, M., ei al,. (2018).</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
@@ -4847,29 +5263,26 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Trait</t>
+          <t>Place</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>- base</t>
+          <t>- base
+description: Part of any space referenced by an identifier.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>characteristic belonging to an Entity and referenced by an identifier.</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>- Traits can be objective (inherent?) in which case they are also observable and called properties. Traits which are not observable (directly or indirectly) need to be assigned.</t>
-        </is>
-      </c>
+          <t>Part of any space referenced by an identifier.</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>- Based on ISO 19143:2010, 4.21, ISO/IEC 2382:2015, 2121440, significantly modified, Note 1 added</t>
+          <t>- ISO 19155:2012, 4.8</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
@@ -4892,27 +5305,45 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Classification system levels</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr"/>
+          <t>Ancillary Data</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>- core
+- approved</t>
+        </is>
+      </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>The levels in a hierarchical Classification System.</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr"/>
+          <t>Data acquired on the same platform but not obtained from the main Sensor itself (usually provided as part of Level 0 Data), with the primary purpose of serving the processing of main instrument Data (e.g. Position and velocity of platform).</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>This can be divided into data referred to as spacecraft 'engineering', 'core housekeeping' or 'subsystem' data obtained from other parts of the platform, and includes parameters such as orbit position and velocity, attitude and its range of change, time, temperatures, pressures, jet firings, water dumps, internally produced magnetic fields, and other environmental measurements. Ancillary refers to data that exist purely to serve the data processing.</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr"/>
+          <t>- ESA/CEOS?, modified
+- EO Data Stewardship Glossary</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Data other than instrument measurements, originating in the instrument itself or from the satellite, required to perform processing of the Data. Includes orbit Data, attitude Data, time Information, and spacecraft engineering Data, Calibration Data, Data quality Information, and Data from other instruments or earth system models.</t>
+        </is>
+      </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>- CEOS-ARD PFS template 20220302</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
@@ -4929,21 +5360,31 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Source Data</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr"/>
+          <t>Observation</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>- controversial
+description: Act of determining the Value of a Property by interacting in a reproducible way with the Phenomenon using a Sensor.</t>
+        </is>
+      </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Data required for production of an EO Collection (e.g., unenhanced satellite mission data) as well as further processed Level-1 data (precision geometrically and radiometrically corrected radiance at the sensor), or any other pre-processed format that suppliers are providing access to that meets program requirements.</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr"/>
+          <t>Act of determining the Value of a Property by interacting in a reproducible way with the Phenomenon using a Sensor.</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>- The result of an Observation is a Value complemented by an Uncertainty, often itself being referred to as 'observation'.
+- An Observation result represents a Sample of the Phenomenon (otherwise it would be identical with the Phenomenon).</t>
+        </is>
+      </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
@@ -4966,26 +5407,31 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Earth Observation</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr"/>
+          <t>Grid</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>- core
+description: Network composed of two or more sets of curves in which the members of each set intersect the members of the other sets in an algorithmic way.</t>
+        </is>
+      </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>science domain dealing with technologies and methods of collecting and analyzing observations about the different Earth spheres</t>
+          <t>Network composed of two or more sets of curves in which the members of each set intersect the members of the other sets in an algorithmic way.</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>- Earth Observation (EO) can be categorised by Location of the Sensor into space-borne, air-borne, sea-borne, ground-based, underwater and underground EO.
-- Earth Observation (EO) includes Remote Sensing, such as satellite imagery, as well as in-situ observations, e.g., with ground-based devices.</t>
+          <t>- The curves partition a space into grid cells or zones.
+- The intersection points of the curves are called nodes.</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>- Modified GEO definition [GEO (earthobservations.org)](https://earthobservations.org/resources#key)</t>
+          <t>- ISO 19123:2005, 4.1.23; Note 1 modified; Note 2 added</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
@@ -5008,27 +5454,44 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Business Continuity</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr"/>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>- core
+description: Entity (person, organization, institution, etc.) that is requesting data or information with certain characteristics described by needs and/or requirements.</t>
+        </is>
+      </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>An organization's readiness to continue functioning during times of disruption.</t>
+          <t>In the context of the KCEO, entity (person, organization, institution, etc.) that is requesting data or information with certain characteristics described by needs and/or requirements.</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
+          <t>- KCEO</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>External person, institution or system that consumes provided services.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>- Includes Data Access or Science and Service Exploitation Platforms provided by a payload data ground segment.</t>
+        </is>
+      </c>
       <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>- EO Data Stewardship Glossary</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
@@ -5045,21 +5508,35 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Provisional Product</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr"/>
-      <c r="C110" t="inlineStr"/>
+          <t>Remote Sensing</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>- controversial
+description: Type of Observation performed at a significant distance from a Phenomenon.</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Remote Observation</t>
+        </is>
+      </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Products in a research and development phase not yet been published into a standardized collection.</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr"/>
+          <t>Type of Observation performed at a significant distance from a Phenomenon.</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>- 'Significant' in this context means that the distance has, or may have, a non-negligible impact on the Value of the Property observed.
+- The effect of the distance on the acquired data is the main distinction criterion between 'remote' and 'in-situ' observations.</t>
+        </is>
+      </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
@@ -5082,18 +5559,28 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Spectral resolution</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr"/>
+          <t>Earth Observation Product</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>- core
+description: Direct output from standardized satellite data processing chains (indicative levels 2 and 3), representing fundamental geophysical and biophysical variables.</t>
+        </is>
+      </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Measure of the ability to resolve features in the electromagnetic spectrum.</t>
+          <t>Direct output from standardized satellite data processing chains (indicative levels 2 and 3), representing fundamental geophysical and biophysical variables. These products demonstrate direct Traceability to original satellite measurements through rigorous Calibration and Validation processes. The processing methodology prioritizes the conversion of raw sensor data into quantifiable physical measurements, maintaining strict adherence to standardized processing protocols and Validation requirements.</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>- Soil moisture from microwave sensors
+- Forest canopy height from LiDAR data</t>
+        </is>
+      </c>
       <c r="G111" t="inlineStr">
         <is>
           <t>- KCEO</t>
@@ -5119,25 +5606,30 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>EO Space Data</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr"/>
+          <t>Trait</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>- base
+description: Characteristic belonging to an entity and referenced by an identifier.</t>
+        </is>
+      </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Earth Observation Data generated by spaceborne missions or instruments owned by public or private organizations.</t>
+          <t>Characteristic belonging to an entity and referenced by an identifier.</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>- See also Instrument data.</t>
+          <t>- Traits can be objective (inherent?) in which case they are also observable and called properties. Traits which are not observable (directly or indirectly) need to be assigned.</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- Based on ISO 19143:2010, 4.21, ISO/IEC 2382:2015, 2121440, significantly modified, Note 1 added</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
@@ -5160,22 +5652,30 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Dwell time</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr"/>
+          <t>Time of Year</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>- core
+description: Time of the year at which the variable is observed or simulated by a model.</t>
+        </is>
+      </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>The time that an antenna beam spends on a target.</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>- in the context of radar sensing</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr"/>
+          <t>Time of the year at which the variable is observed or simulated by a model.</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>| Type      | Entry format example | Valid unit     |
+|-----------|----------------------|----------------|
+| timestamp | m/d                  | Not Applicable |
+| timerange | m/d - m/d            | Not Applicable |</t>
+        </is>
+      </c>
       <c r="G113" t="inlineStr">
         <is>
           <t>- KCEO</t>
@@ -5201,19 +5701,25 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Representativeness</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr"/>
+          <t>In-Situ Observation</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>- controversial
+description: Observations performed in the same Place where a Phenomenon occurs, normally without isolating it from other systems or altering its pre-Observation state.</t>
+        </is>
+      </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>The quality or Characteristic of a Measurement or Observation to accurately represent a specific geographic Location, time Period, or environmental condition.</t>
+          <t>Observations performed in the same Place where a Phenomenon occurs, normally without isolating it from other systems (its environment) or altering its pre-Observation state.</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>- WIGOS metadata standard defines representativeness as the extent of the region around the Observation of which it is representative.</t>
+          <t>- The main Characteristic of such observations is that distance has no or only negligible (within Uncertainty) influence on the Value of the Property observed. In-Situ Observations therefore often require either direct physical contact or small distances between a Sensor and the observed Phenomenon.
+- Observations not fulfilling these conditions are considered Remote Sensing.</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
@@ -5242,38 +5748,56 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Time of Day</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr"/>
+          <t>Characteristic</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>- base
+- approved</t>
+        </is>
+      </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>The time of the day that the variable or parameter is observed or simulated by a Model.</t>
+          <t>Distinguishing Feature.</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>- In Remote Sensing it is also known as time of overpass.</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>| Type      | Entry format example | Valid unit       |
-|-----------|----------------------|------------------|
-| timestamp | 18:00 h (0-24)       | Hours            |
-| timerange | 18:00 – 20:00 h      | Hours            |</t>
-        </is>
-      </c>
+          <t>- A Characteristic can be inherent or assigned.
+- A Characteristic can be qualitative or quantitative.
+- There are various classes of Characteristics, such as the following:
+  - physical (e.g. mechanical, electrical, chemical, biological);
+  - sensory (e.g. relating to smell, touch, taste, sight, hearing);
+  - behavioural (e.g. courtesy, honesty, veracity);
+  - temporal (e.g. punctuality, reliability, availability);
+  - ergonomic (e.g. physiological characteristic or related to human safety);
+  - functional (e.g. maximum speed of an aircraft).</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
+          <t>- ISO 9000:2005, 3.5.1</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Abstraction of a Property of an Object or of a set of objects.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>- Characteristics are used for describing Concepts.</t>
+        </is>
+      </c>
       <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>- ISO 1087-1:2000, 3.2.4; ISO 19146:2010(E); https://www.iso.org/standard/20057.html</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
@@ -5290,51 +5814,36 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Measurement</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>- core</t>
+          <t>- core
+description: Observation of a Quantity.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Value and possibly Uncertainty of a Trait of a specific Entity.</t>
+          <t>Observation of a Quantity.</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>- Data simply describe entities using certain traits and are not targeted at a particular use or audience.</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Data can be categorised into:
-- factual (i.e. obtained by Observation) or fictional (obtained e.g. through modelling, estimating or assigning)
-- quantitative (continuous) or qualitative (categorical)
-- analogue or digital
-(list not exhaustive!)</t>
-        </is>
-      </c>
+          <t>- The Process of collecting a measurement is called measuring.</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Scientific or technical measurements, values calculated therefrom, observations, or facts that can be represented by numbers, tables, graphs, models, text, or symbols which are used as a basis for reasoning and further calculation.</t>
-        </is>
-      </c>
+          <t>- GEOGlos (VIM ?, modified)</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data)</t>
-        </is>
-      </c>
+      <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
@@ -5351,59 +5860,41 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Validation</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr"/>
+          <t>Preservation</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>- core
+description: Processes and operations used to ensure data technical and intellectual survival through time.</t>
+        </is>
+      </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Process of assessing, by independent means, the quality of the Data products derived from the system outputs.</t>
+          <t>Processes and operations used to ensure data technical and intellectual survival through time.</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of Calibration Data in order to control their change over time.</t>
+          <t>- Grants data integrity, discoverability and accessibility, and facilitates its (re-)use in the long term.
+- Preservation is one of the tasks of data curation.</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>- ISO/TS 19101‑2:2008, 4.41</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Validation aims to verify that the specified requirements are achieved or compliant. This involves comparing  mission products with representative Reference Data, considering various Observation conditions, ensuring the quality and Traceability of the Reference Data used.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of Calibration Data in order to control their change over time.</t>
-        </is>
-      </c>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>- BIPM; QA4EO; ESA ?, modified</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>The assurance that a product, service, or system meets the needs of the customer and other identified stakeholders. It often involves acceptance and suitability with external customers.</t>
-        </is>
-      </c>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of Calibration Data in order to control their change over time.</t>
-        </is>
-      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr">
-        <is>
-          <t>- EU-US Land Imaging EO Collaboration</t>
-        </is>
-      </c>
+      <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr"/>
       <c r="R117" t="inlineStr"/>
@@ -5416,39 +5907,32 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>User</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr"/>
+          <t>Provisional Product</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>- core
+description: Products in a research and development phase not yet published into a standardized collection.</t>
+        </is>
+      </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>In the context of the KCEO, an Entity (person, organization, institution, etc.) that is requesting Data or Information with certain characteristics described by needs and/or requirements.</t>
+          <t>Products in a research and development phase not yet published into a standardized collection.</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>External person, institution or system that consumes provided services.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>Includes Data Access or Science and Service Exploitation Platforms provided by a payload data ground segment.</t>
-        </is>
-      </c>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>- EO Data Stewardship Glossary)</t>
-        </is>
-      </c>
+      <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
@@ -5465,28 +5949,20 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Derivative Product</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr"/>
+          <t>Outcome</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>- core
+description: ""</t>
+        </is>
+      </c>
       <c r="C119" t="inlineStr"/>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>Additionally processed from baseline or unenhanced mission data.</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>- Generally are either a compilation of time-series data (e.g., all time, annual, monthly or seasonal summary data, &gt; Level 3) or thematic versions of each individual data tile of baseline data
-- Derived products are citable via a Digital Object Identifier (DOI).</t>
-        </is>
-      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
-        </is>
-      </c>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
@@ -5507,30 +5983,26 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>- base</t>
+          <t>- high-impact
+description: Deliberate system of guidelines to guide decisions and achieve rational outcomes, implemented as a procedure or protocol and typically promulgated through official written documents.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
-          <t>element of a type domain</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>- A value may consider a possible state of an Object within a class or type (domain).
-- A Data value is an instance of a Data type, a value without identity</t>
-        </is>
-      </c>
+          <t>Deliberate system of guidelines to guide decisions and achieve rational outcomes. Statement of intent implemented as a procedure or protocol. Typically promulgated through official written documents.</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>[SOURCE: ISO/IEC 19501:2005, 0000_5]</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
@@ -5553,21 +6025,30 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Classification System</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr"/>
+          <t>Geographic Identifier</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>- core
+description: Spatial reference in the form of a label or code that identifies a Location.</t>
+        </is>
+      </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>The nomenclature used to classify Information into categorical thematic classes (e.g., EUNIS, MAES ecosystems, Corine Land Cover, LCCS).</t>
+          <t>Spatial reference in the form of a label or code that identifies a Location.</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>- "Spain" is an example of a label (country name); "SW1-3AD" is an example of a code (postcode).</t>
+        </is>
+      </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO 19112:2019, 3.1.2</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
@@ -5590,19 +6071,39 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Environmental process</t>
+          <t>Earth Spheres</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>- to be defined</t>
+          <t>- core
+description: Spheres dividing planet Earth into subsystems, which are collectives of (physical) matter sharing specific traits.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Spheres dividing planet Earth into subsystems, which are collectives of (physical) matter sharing specific traits.</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>- Atmosphere
+- Hydrosphere
+- Cryosphere
+- Biosphere
+- Lithosphere
+- Anthroposphere</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>- Hugget, R., et al., 2024, DOI: 10.1177/03091333241275465
+- Guth, P., et al., 2021, https://doi.org/10.3390/rs13183581
+- Martin, Y.E., et al., 2012</t>
+        </is>
+      </c>
       <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
@@ -5623,25 +6124,26 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Geographic Identifier</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr"/>
+          <t>Deprecated Product</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>- core
+description: Products and collections that have been superseded by a newer version and are still available, but whose use is discouraged since they will be decommissioned in the future.</t>
+        </is>
+      </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Spatial Reference in the form of a label or code that identifies a Location.</t>
+          <t>Products and collections that have been superseded by a newer version and are still available, but whose use is discouraged since they will be decommissioned in the future.</t>
         </is>
       </c>
       <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>- “Spain” is an example of a label (country name); “SW1-3AD” is an example of a code (postcode).</t>
-        </is>
-      </c>
+      <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>- ISO 19112:2019, 3.1.2</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
@@ -5664,21 +6166,26 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Collection</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr"/>
+          <t>Replicability</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>- core
+description: Property enabling other researchers to conduct an independent study with different data and similar but not identical methods, yet arriving at results that confirm the original study's hypothesis.</t>
+        </is>
+      </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>A group of products that have been processed using a consistent radiometric calibration, geometric registration base, data / metadata format, and version of processing algorithms.</t>
+          <t>Property enabling other researchers to conduct an independent study with different data and similar but not identical methods, yet arriving at results that confirm the original study's hypothesis.</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- Craglia, M., et al. (2018).</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
@@ -5701,25 +6208,30 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Spatial completeness</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr"/>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>- base
+description: Abstraction of real-world phenomena.</t>
+        </is>
+      </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>The presence or absence of gaps, which are missing values in an otherwise continuous spatial Data series.</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>- surface soil moisture retrieved from microwave satellite sensors may present gaps in mountainous terrains.</t>
-        </is>
-      </c>
+          <t>Abstraction of real-world phenomena.</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>- A feature may occur as a type or an instance.</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO 19101-1:2014, 4.1.11, modified</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
@@ -5742,25 +6254,30 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Stability</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr"/>
+          <t>Final Product Version</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>- core
+description: Product within an EO Collection that is not expected to be updated.</t>
+        </is>
+      </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>The maximum acceptable change in Uncertainty per decade.</t>
+          <t>Product within an EO Collection that is not expected to be updated.</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>- GCOS uses bias or systematic errors instead of Uncertainty</t>
+          <t>- In its production, all of the prerequisite auxiliary data were used as input.</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>- modified from GCOS 2022</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
@@ -5783,21 +6300,35 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Thematic Resolution</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr"/>
+          <t>Spatial Extent</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>- core
+description: Zone or region of space described by a geographic identifier in the form of a label or code, or by a bounding box, representing the maximum spatial boundary within which the user is requesting data.</t>
+        </is>
+      </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>The level of categorical detail of Information expressed by the number of classes.</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
+          <t>Zone or region of space described by a geographic identifier in the form of a label or code, or by a bounding box. Represents the maximum extent (the spatial boundary or limits) within which the User is requesting data.
+The attribute represents the maximum spatial extent of the AOI, and in case the AOI is made of many discontinuous zones then it represents the maximum extent of the union of all the zones.</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>- WIGOS metadata standard defines it as the typical spatial georeferenced volume covered by the observations.</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>- If a User is requesting information about degradation of African protected sites, then the AOIs are the protected sites, and the spatial extent is the African continent.</t>
+        </is>
+      </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>- CGLS</t>
+          <t>- Adapted from ISO 19170-1:2021</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
@@ -5820,21 +6351,26 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>User Interface</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr"/>
+          <t>Policy Cycle</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>- high-impact
+description: Well-established concept typically taught as the rational model of policy decision-making, representing an idealised view of the policy process.</t>
+        </is>
+      </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Set of all the components of an interactive system that provide Information and controls for the User to accomplish specific tasks with the interactive system.</t>
+          <t>Well-established concept, typically taught as the rational model of policy decision-making. Idealised view of the policy process.</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>- ISO 9241-110:2020, 3.10</t>
+          <t>- [ESA/CEOS?, modified](https://digital-strategy.ec.europa.eu/en/library/quality-public-administration-toolbox-practitioners)</t>
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
@@ -5857,25 +6393,26 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Update frequency</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr"/>
+          <t>Data Licencing</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>- core
+description: Legal instrument by which a copyright holder may grant rights over the protected work.</t>
+        </is>
+      </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>The frequency at which the product is available to users.</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>- Also known in product catalogues as dissemination frequency</t>
-        </is>
-      </c>
+          <t>Legal instrument by which a copyright holder may grant rights over the protected work. Data and content is open if it is subject to an explicitly-applied licence that conforms to the Open Definition. A range of standard open licences are available, such as the Creative Commons CC-BY licence, which requires only attribution.</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- CEOS Wiki</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
@@ -5898,25 +6435,24 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Representativeness</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>- core</t>
+          <t>- core
+description: Quality or characteristic of a measurement or observation to accurately represent a specific geographic location, time period, or environmental condition.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>A (technical?) device or instrument suited (through physical/chemical interaction) to measure one or more properties of a Phenomenon and thus collect factual/objective Data.</t>
+          <t>Quality or characteristic of a measurement or Observation to accurately represent a specific geographic location, time Period, or environmental condition.</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>- Sensing is therefore a synonym for Observation (the Process).
-- As by their definition, sensors perform sampling.
-- Sensors used to obtain measurements must be calibrated and provide uncertainties.</t>
+          <t>- WIGOS metadata standard defines representativeness as the extent of the region around the Observation of which it is representative.</t>
         </is>
       </c>
       <c r="F130" t="inlineStr"/>
@@ -5945,33 +6481,26 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Measurand</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr"/>
+          <t>Reproducibility</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>- core
+description: Concerned with the validity of the results of a particular study, enabling readers to check whether results have been manipulated by reproducing exactly the same study using the same data and methods.</t>
+        </is>
+      </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Particular Quantity subject to Measurement.</t>
+          <t>Concerned with the validity of the results of a particular study, i.e., the possibility for readers to check whether results have been manipulated, by reproducing exactly the same study using the same data and methods.</t>
         </is>
       </c>
       <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>| Step   | Process description                                                                                                                                                                                                                                                              |
-| :----- | :--------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------- |
-| (Raw) | The complete and unaltered/unprocessed set of Data acquired by one or several sensors on a platform                                                                                                                                                                             |
-| M/0 uncalibrated  | Unaltered/unprocessed Level 0 (main) Sensor Data annotated with processed Ancillary Data and supplemented by Auxiliary Data (including radiometric and geometric Calibration coefficients and geo-referencing parameters) allowing further processing to higher Levels. |
-| M/1 Sensor-calibrated | Level M/0 Sensor Data which have been calibrated (ideally traceable to SI) and spatially aligned (co-located, eventually co-gridded) to represent at-Sensor measurements (Value and Uncertainty) in Sensor nominal spatiotemporal sampling, supplemented by appropriate anc |
-| M/2 target-calibrated| Level M/1 Data processed to represent geophysical Property values (and uncertainties) for a specified target (Object, Feature of interest, e.g. surface reflectance, apparent temperature) derived from M/1 Sensor Data, as much as possible maintaining the sensors nominal spatial and temporal sampling (Observation preserving).   |
-| M/3 homogenised   | Level M/1 or M/2 Data which have been generalised and integrated across one or several platforms and acquisitions to achieve an increased, more regular or in any other form enhanced spatial or temporal coverage in which states geophysical values agnostic of the originally acquiring Sensor and Observation condition and thus directly comparable. This homogenisation and fusion may include measurand re-Calibration to external standards and references including use of modelling, aggregation and interpolation.                                                                   |
-| M/4 derived/infered | Model output or results from analyses of Level M/3 (or lower level) Data i.e., attributes that might not be directly observable by the Sensor(s) but are derived from observations in combination with other external incl. non-observational Data using techniques like modelling or machine learning (AI).        |
-From http://doi.org/10.2760/46796</t>
-        </is>
-      </c>
+      <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>- VIM: 1993, 2.6</t>
+          <t>- Ostermann and Granell (2015)</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
@@ -5994,15 +6523,32 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Cartographic projection</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr"/>
+          <t>Custodian</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>- core
+description: Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
+        </is>
+      </c>
       <c r="C132" t="inlineStr"/>
-      <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>- See also Steward.</t>
+        </is>
+      </c>
       <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+        </is>
+      </c>
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
@@ -6023,25 +6569,26 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Geographic Coordinate Reference System</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr"/>
+          <t>Geosphere</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>- core
+description: The masses of minerals that constitute planet Earth.</t>
+        </is>
+      </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Geographic coordinate Reference system (CRS) that has a geodetic Reference frame and an ellipsoidal coordinate system.</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>- Also known as geographic CRS.</t>
-        </is>
-      </c>
+          <t>The masses of minerals that constitute planet Earth.</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>- ISO 19111:2019, 3.1.35</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
@@ -6064,21 +6611,30 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Cryosphere</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr"/>
+          <t>Cell</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>- core
+- approved</t>
+        </is>
+      </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
-          <t>The masses of frozen water, such as sea ice, ice shields, glaciers, and snow.</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr"/>
+          <t>Spatial, spatio-temporal zone or temporal unit of geometry with dimensionality greater than 0, associated with a zone.</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>- Cells are the unit of geometry in a DGGS, and the geometry of the region of space-time occupied by a zone is a Cell.</t>
+        </is>
+      </c>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- ISO 19170:2021</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
@@ -6101,21 +6657,30 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Lithosphere</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr"/>
+          <t>Geographic Coordinate Reference System</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>- core
+description: Coordinate Reference System (CRS) that has a geodetic Reference frame and an ellipsoidal coordinate system.</t>
+        </is>
+      </c>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>The solid, inanimate outer layer of the Geosphere.  For the purposes of Earth Observation, the lithosphere is considered to include soils (‘pedosphere’)</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr"/>
+          <t>Coordinate Reference System (CRS) that has a geodetic Reference frame and an ellipsoidal coordinate system.</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>- Also known as geographic CRS.</t>
+        </is>
+      </c>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- ISO 19111:2019, 3.1.35</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
@@ -6138,21 +6703,32 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Near Real Time Data</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr"/>
+          <t>Vertical Levels</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>- core
+description: Levels of a vertical discretization, e.g. pressure levels in an atmospheric model reanalysis or height levels in a forest biomass EO product.</t>
+        </is>
+      </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Data that is available for use with a specified (small and application dependent) latency, typically 3 hours for meteorological applications.</t>
+          <t>Levels of a vertical discretization. Examples may be pressure levels in an atmospheric model reanalysis or height levels in a forest biomass EO product.</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>| Entry format example                | Valid unit           |
+|------------------------------------|----------------------|
+| 1, 5, 10 meter; 1000, 850, 500 hPa | meter, hPa, unitless |</t>
+        </is>
+      </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
@@ -6175,21 +6751,26 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Traceability</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr"/>
+          <t>Anthroposphere</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>- core
+- approved</t>
+        </is>
+      </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Property of a Measurement result whereby the result can be related to a Reference through a documented unbroken chain of calibrations each contributing to the Measurement uncertainty.</t>
+          <t>One of the Earth spheres consisting predominantly of matter processed by humans, such as construction wood, bricks, concrete, asphalt, glass, or plastics.</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>- https://www.isobudgets.com/Measurement-traceability-complying-iso-17025-requirements/</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
@@ -6212,30 +6793,30 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Temporal extent</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr"/>
+          <t>Dwell Time</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>- core
+description: Time that an antenna beam spends on a target.</t>
+        </is>
+      </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
-          <t>The Period during which Data was collected, observations were made, or for which the Model was run.</t>
+          <t>Time that an antenna beam spends on a target.</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>- In W3C is the definition of temporal coverage 
-- Time Period covered by a series of observations inclusive of the specified date/time indications (Measurement history). Defined based on the beginning and end dates of observations.</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>- WIGOS Metadata</t>
-        </is>
-      </c>
+          <t>- In the context of radar sensing.</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>- adapted from W3C</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
@@ -6258,26 +6839,33 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Long Term Preservation</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr"/>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>- core
+description: Non-negative interval Quantity of time equal to the difference between the final and initial instants of a time interval.</t>
+        </is>
+      </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>The act of maintaining information in a correct and independently understandable form over the long term</t>
+          <t>Non-negative interval Quantity of time equal to the difference between the final and initial instants of a time interval.</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>- Long term refers to a period of time long enough to be concerned with the impact which changing technologies, including support for media and data formats, and changing user communities will have on the information being held in a repository.
-- See also preservation</t>
+          <t>- Duration is one of the base quantities in the International System of Quantities (ISQ) on which the International System of Units (SI) is based. The term "time" instead of "duration" is often used in this context and also for an infinitesimal duration.
+- For the term "duration", expressions such as "time" or "time interval" are often used, but the term "time" is not recommended in this sense and the term "time interval" is deprecated in this sense to avoid confusion with the concept of "time interval".
+- The exact duration of a time scale unit depends on the time scale used. For example, the durations of a year, month, week, day, hour or minute may depend on when they occur (in a Gregorian calendar, a calendar month can have a duration of 28, 29, 30, or 31 days; in a 24-hour clock, a clock minute can have a duration of 59, 60, or 61 seconds, etc.). Therefore, the exact duration can only be evaluated if the exact duration of each is known.
+- This definition is closely related to NOTE 1 of the terminological entry "duration" in IEC 60050-113:2011, 113-01-13.</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- ISO 8601-1:2019, 3.1.1.8</t>
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
@@ -6300,21 +6888,22 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Path</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr"/>
+          <t>Lead Time</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>- core
+description: Minimum time of interval between an Observation being tasked and being performed.</t>
+        </is>
+      </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
-          <t>A line defined in an algorithmic way using at least two positions. (could be open ended) Alternative: A line connecting two positions in an algorithmic way. (limited by end points)</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>- A path is a 1-dimensional Place</t>
-        </is>
-      </c>
+          <t>Minimum time of interval between an Observation being tasked and being performed.</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
@@ -6341,25 +6930,30 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Final Product Version</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr"/>
+          <t>EO Space Data</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>- core
+description: Earth Observation data generated by spaceborne missions or instruments owned by public or private organizations.</t>
+        </is>
+      </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>A product that is not expected to be updated within an EO Collection.</t>
+          <t>Earth Observation data generated by spaceborne missions or instruments owned by public or private organizations.</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>- In its production, all of the prerequisite auxiliary data were input.</t>
+          <t>- See also Instrument data.</t>
         </is>
       </c>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
@@ -6382,21 +6976,30 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Hydrosphere</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr"/>
+          <t>Spatial Completeness</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>- core
+description: Presence or absence of gaps, which are missing values in an otherwise continuous spatial data series.</t>
+        </is>
+      </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>The masses of liquid water, such as oceans, lakes, and rivers.</t>
+          <t>Presence or absence of gaps, which are missing values in an otherwise continuous spatial data series.</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>- Surface soil moisture retrieved from microwave satellite sensors may present gaps in mountainous terrains.</t>
+        </is>
+      </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
@@ -6419,54 +7022,41 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Auxiliary Data</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr"/>
+          <t>Derivative Product</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>- core
+description: Product additionally processed from baseline or unenhanced mission data.</t>
+        </is>
+      </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Data, which enhance processing, and utilization of main Sensor Data. The auxiliary Data are usually not captured by the same Data collection Process or on the same platform as the main Sensor Data. Examples are e.g. meteorological Data received from ECWMF/Met or DEMs. Offices. Auxiliary Data help in Data processing, but are also Data sets in their own right.</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr"/>
+          <t>Product additionally processed from baseline or unenhanced mission data.</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>- Generally either a compilation of time-series data (e.g., all time, annual, monthly or seasonal summary data, &gt; Level 3) or thematic versions of each individual data tile of baseline data.
+- Derived products are citable via a Digital Object Identifier (DOI).</t>
+        </is>
+      </c>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
-          <t>- ESA/CEOS?, modified
-- ENMAP Glossary of Terms, https://www.enmap.org/Data/doc/EnMAP_Terms.pdf, 20210624
-- EO Data Stewardship Glossary</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>Data required to perform processing of Sensor Data which is not obtained from the Sensor itself. Include: (a) Data provided by the spacecraft (e.g. orbit Position and velocity, attitude, instrument house-keeping Data, on-board time), (b) Data not available from on-board sources.</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>For EnMAP, this includes (a) Orbit files, attitude files, Calibration Data, instrument house-keeping Data, (b) atmospheric parameters, Reference images.</t>
-        </is>
-      </c>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>- ENMAP Glossary of Terms, https://www.enmap.org/Data/doc/EnMAP_Terms.pdf, 20210624
-- EO Data Stewardship Glossary)</t>
-        </is>
-      </c>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t>The Data required for instrument processing, which does not originate in the instrument itself or from the satellite. Some auxiliary Data will be generated in the ground segment, whilst other Data will be provided from external sources.</t>
-        </is>
-      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr"/>
-      <c r="O143" t="inlineStr">
-        <is>
-          <t>- CEOS-ARD PFS template 20220302</t>
-        </is>
-      </c>
+      <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr"/>
       <c r="Q143" t="inlineStr"/>
       <c r="R143" t="inlineStr"/>
@@ -6482,7 +7072,12 @@
           <t>Geopositioning</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr"/>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>- core
+description: Determination of the geographic Position of a point (0D) or linear (1D) Feature.</t>
+        </is>
+      </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
@@ -6516,22 +7111,26 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Geospatial Data</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr"/>
+          <t>Spectral Band</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>- core
+description: Part of the electromagnetic spectrum of specific wavelengths, in remote sensing usually described by central wavelength and bandwidth.</t>
+        </is>
+      </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Consisting of, derived from, or relating to Data that is directly linked to specific geographical locations.</t>
+          <t>Part of the electromagnetic spectrum of specific wavelengths. In Remote Sensing, usually described by central wavelength and bandwidth.</t>
         </is>
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
-          <t>- https://www.merriam-webster.com/dictionary/geospatial
-- https://isotc211.geolexica.org/Concepts/202/, accessed 20221010</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
@@ -6554,21 +7153,30 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Climate projection</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr"/>
+          <t>Geographic Data</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>- core
+description: Data with implicit or explicit reference to a Location relative to the Earth.</t>
+        </is>
+      </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>A climate projection is the simulated response of the climate system to a scenario of future emission or concentration of greenhouse gases (GHGs) and aerosols, generally derived using climate models. Climate projections are distinguished from climate predictions by their dependence on the emission/concentration/radiative forcing scenario used, which is in turn based on assumptions concerning, for example, future socioeconomic and technological developments that may or may not be realized.</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr"/>
+          <t>Data with implicit or explicit reference to a Location relative to the Earth.</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>- Geographic Information is also used as a term for information concerning phenomena implicitly or explicitly associated with a Location relative to the Earth.</t>
+        </is>
+      </c>
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
-          <t>- IPCC</t>
+          <t>- ISO 19109:2015, 4.13; ISO 19109:2005</t>
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
@@ -6591,29 +7199,26 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Measurement</t>
+          <t>Business Continuity</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>- core</t>
+          <t>- core
+- approved</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Observation of a Quantity.</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>- The Process of collecting a measurement is called measuring.</t>
-        </is>
-      </c>
+          <t>An organisation's readiness to continue functioning during times of disruption.</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
-          <t>- GEOGlos (VIM ?, modified)</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
@@ -6633,43 +7238,6 @@
       <c r="V147" t="inlineStr"/>
       <c r="W147" t="inlineStr"/>
     </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Forecast range</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr"/>
-      <c r="C148" t="inlineStr"/>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>The forecast Period.</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
-      <c r="O148" t="inlineStr"/>
-      <c r="P148" t="inlineStr"/>
-      <c r="Q148" t="inlineStr"/>
-      <c r="R148" t="inlineStr"/>
-      <c r="S148" t="inlineStr"/>
-      <c r="T148" t="inlineStr"/>
-      <c r="U148" t="inlineStr"/>
-      <c r="V148" t="inlineStr"/>
-      <c r="W148" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/exports/xlsx/terms.xlsx
+++ b/exports/xlsx/terms.xlsx
@@ -536,40 +536,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Geolocating</t>
+          <t>Geographic Grid</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>- core
-description: Geopositioning of an Object using a Physical Sensor Model or a True Replacement Model.</t>
+description: Regular grid based on a Geographic Coordinate Reference System (CRS).</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Geopositioning of an Object using a Physical Sensor Model or a True Replacement Model.</t>
+          <t>Regular grid based on a Geographic Coordinate Reference System (CRS).</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>- ISO 19115-2:2009, 4.11</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Determination of the geographic location of a feature of two or more dimensions.</t>
-        </is>
-      </c>
+          <t>- KCEO</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>- ISO 19130-1:2018, 3.36 ('geopositioning'), modified</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -586,22 +578,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Spectral Bandwidth</t>
+          <t>Representativeness</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>- core
-description: Range of the Spectral Band.</t>
+description: Quality or characteristic of a measurement or observation to accurately represent a specific geographic location, time period, or environmental condition.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Range of the Spectral Band.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>Quality or characteristic of a measurement or Observation to accurately represent a specific geographic location, time Period, or environmental condition.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>- WIGOS metadata standard defines representativeness as the extent of the region around the Observation of which it is representative.</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
@@ -628,24 +624,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Instrument Data</t>
+          <t>EO Space Data</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>- core
-description: Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
+description: Earth Observation data generated by spaceborne missions or instruments owned by public or private organizations.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
+          <t>Earth Observation data generated by spaceborne missions or instruments owned by public or private organizations.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>- These data consist of instrument science and engineering data, and possibly ancillary data. Instrument engineering data is produced by engineering sensor(s) of an instrument, used either for operating the instrument or for processing the science data generated by the instrument. Instrument science data is produced by the science sensor(s) of an instrument, usually constituting the basic reason for existence of an instrument.</t>
+          <t>- See also Instrument data.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -654,30 +650,14 @@
           <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Data created by an instrument including scientific measurements and any engineering or ancillary data which may be included in the data packets.</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Data produced and transmitted by the science and engineering sensors of an instrument, and, in the spacecraft environment, any additional data packaged with the instrument's sensor data by virtue of services provided.</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
-        </is>
-      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
@@ -690,59 +670,40 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Auxiliary Data</t>
+          <t>Granule</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: The smallest aggregation of data which is independently managed (i.e. described, inventoried, retrievable).</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Data that enhance the processing and utilisation of main Sensor Data. Auxiliary Data are usually not captured by the same Data collection Process or on the same platform as the main Sensor Data. Examples include meteorological Data received from ECMWF/Met Offices or DEMs. Auxiliary Data help in Data processing, but are also Data sets in their own right.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>The smallest aggregation of data which is independently managed (i.e. described, inventoried, retrievable). Granules may be managed as logical granules and/or physical granules.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>- See also product.</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>- ESA/CEOS?, modified
-- ENMAP Glossary of Terms, https://www.enmap.org/Data/doc/EnMAP_Terms.pdf, 20210624
-- EO Data Stewardship Glossary</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Data required to perform processing of Sensor Data which is not obtained from the Sensor itself. Includes: (a) Data provided by the spacecraft (e.g. orbit Position and velocity, attitude, instrument house-keeping Data, on-board time); (b) Data not available from on-board sources.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>For EnMAP, this includes (a) orbit files, attitude files, Calibration Data, instrument house-keeping Data; (b) atmospheric parameters, reference images.</t>
-        </is>
-      </c>
+          <t>- [NASA EarthData](https://www.earthdata.nasa.gov/learn/glossary)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>- ENMAP Glossary of Terms, https://www.enmap.org/Data/doc/EnMAP_Terms.pdf, 20210624
-- EO Data Stewardship Glossary</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Data required for instrument processing that does not originate in the instrument itself or from the satellite. Some Auxiliary Data will be generated in the ground segment, whilst other Data will be provided from external sources.</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>- CEOS-ARD PFS template 20220302</t>
-        </is>
-      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
@@ -755,26 +716,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dispose</t>
+          <t>Temporal Revisit</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>- core
-description: Action of permanently and irrecoverably removing all copies of data held by an organization.</t>
+description: Interval between successive observations.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Action of permanently and irrecoverably removing all copies of data held by an organization.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>Interval between successive observations.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>- In Remote Sensing it is also called repeat cycle.
+- More generally it is known as temporal sampling interval.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>| Entry format example | Valid unit                     |
+|----------------------|-------------------------------|
+| 1 s, 2 h             | second, hour, day, month, year |</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -797,31 +769,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Dispose</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>- base
-- controversial
-description: Place referenced by a single set of coordinates within a coordinate reference system.</t>
+          <t>- core
+description: Action of permanently and irrecoverably removing all copies of data held by an organization.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Place referenced by a single set of coordinates within a coordinate reference system.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>- Opposite to (previous) ISO definition, Position shall be used only for 0-dimensional primitives (points).</t>
-        </is>
-      </c>
+          <t>Action of permanently and irrecoverably removing all copies of data held by an organization.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>- ISO 19133:2005, modified to cover only points, also called 'direct position'</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -844,34 +811,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Remote Sensing</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>- core
-description: Electronic data package distributable to users; content is derived from instrument data via processing involving ancillary and auxiliary data.</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>- controversial
+description: Type of Observation performed at a significant distance from a Phenomenon.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Remote Observation</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Electronic data package distributable to users; content is derived from instrument data via processing involving ancillary and auxiliary data.</t>
+          <t>Type of Observation performed at a significant distance from a Phenomenon.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>- Products may be accompanied by metadata and browse images.
-- A Product may be part of a collection — a distinction useful for archiving and cataloguing purposes.
-- The term Product may be used to denote a product type, such as e.g. ENVISAT_ASAR_L1B_PRI data products.
-- End users may distinguish between (input, "raw") data and products, i.e., the derived geophysical parameters.
-- See also granule.</t>
+          <t>- 'Significant' in this context means that the distance has, or may have, a non-negligible impact on the Value of the Property observed.
+- The effect of the distance on the acquired data is the main distinction criterion between 'remote' and 'in-situ' observations.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -894,30 +862,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Near Real Time Data</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>- base
-description: Series of activities that interact to produce a result.</t>
+          <t>- high-impact
+description: Data available for use with a specified (small and application dependent) latency, typically 3 hours for meteorological applications.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Series of activities that interact to produce a result.</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>- A Process may occur once-only or be recurrent or periodic.</t>
-        </is>
-      </c>
+          <t>Data available for use with a specified (small and application dependent) latency, typically 3 hours for meteorological applications.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>- [Wikipedia](https://en.wikipedia.org/wiki/Process)</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -940,34 +904,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>- core
-description: Phenomenon whose values for specific properties are known and understood with an Uncertainty significantly lower than that of the Observation with which it is compared.</t>
+          <t>- base
+description: Value and possibly Uncertainty of a Trait of a specific Entity.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Phenomenon whose values for specific properties are known and understood with an Uncertainty significantly lower (quantify?) than that of the Observation with which it is compared.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+          <t>Value and possibly Uncertainty of a Trait of a specific Entity.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>- Data simply describe entities using certain traits and are not targeted at a particular use or audience.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Data can be categorised into:
+- factual (i.e. obtained by Observation) or fictional (obtained e.g. through modelling, estimating or assigning)
+- quantitative (continuous) or qualitative (categorical)
+- analogue or digital
+(list not exhaustive!)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sort of data acquired with an Uncertainty significantly lower (quantify?) than that of the data it is being compared with.</t>
+          <t>Scientific or technical measurements, values calculated therefrom, observations, or facts that can be represented by numbers, tables, graphs, models, text, or symbols which are used as a basis for reasoning and further calculation.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>- VIM?, modified</t>
+          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -986,29 +966,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Earth Observation Based Output</t>
+          <t>Geographic Coordinate Reference System</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>- core
-description: Higher-level processing and integration output (indicative level 4 and beyond) that goes beyond basic data processing, often designed for policy or decision-making needs.</t>
+description: Coordinate Reference System (CRS) that has a geodetic Reference frame and an ellipsoidal coordinate system.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Higher-level processing and integration output (indicative level 4 and beyond) that goes beyond basic data processing. These outputs are often designed specifically for policy or decision-making needs, and can be categorized into sub-categories:
-- Outputs from models/model integration: use of EO products as inputs in numerical models or combining them with other data sources in modelling frameworks.
-- Indicator-based outputs: EO products transformed through specialized algorithms (including statistical methods, machine learning, and pattern recognition) to create meaningful metrics based on spatio-temporal analysis.
-- Outputs from reanalysis: merging of EO products with other observations and models, creating consistent long-term records of past atmospheric, oceanic, and land surface conditions, and filling gaps through data assimilation techniques.</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>Coordinate Reference System (CRS) that has a geodetic Reference frame and an ellipsoidal coordinate system.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>- Also known as geographic CRS.</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO 19111:2019, 3.1.35</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -1031,44 +1012,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Entity</t>
+          <t>Long Term Preservation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>- base
-description: Something that has separate and distinct existence and objective or conceptual reality.</t>
+          <t>- core
+description: The act of maintaining information in a correct and independently understandable form over the long term.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Something that has separate and distinct existence and objective or conceptual reality.</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+          <t>The act of maintaining information in a correct and independently understandable form over the long term.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>- Long term refers to a period of time long enough to be concerned with the impact which changing technologies, including support for media and data formats, and changing user communities will have on the information being held in a repository.
+- See also preservation.</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>- ISO 19119:2016, 4.1.6</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Government or business organization that is formed to conduct business or represent the government of the day.</t>
-        </is>
-      </c>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>CEOS Entities include Working Groups, Virtual Constellations, etc.</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1085,26 +1059,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>Preservation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Processes and operations used to ensure data technical and intellectual survival through time.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Group of products that have been processed using a consistent radiometric calibration, geometric registration base, data/metadata format, and version of processing algorithms.</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>Processes and operations used to ensure data technical and intellectual survival through time.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>- Grants data integrity, discoverability and accessibility, and facilitates its (re-)use in the long term.
+- Preservation is one of the tasks of data curation.</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1127,26 +1106,26 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Geographic Grid</t>
+          <t>Version Control</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>- core
-description: Regular grid based on a Geographic Coordinate Reference System (CRS).</t>
+description: Method of working with collections, similar to version control systems used in traditional software development but optimized to allow better processing of data and collaboration in data analytics and research contexts.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Regular grid based on a Geographic Coordinate Reference System (CRS).</t>
+          <t>Method of working with collections, similar to the version control systems used in traditional software development but optimized to allow better processing of data and collaboration in the context of data analytics, research, and any other form of data analysis.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [Wikipedia](https://en.wikipedia.org/wiki/Data_version_control)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -1169,30 +1148,26 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Archive</t>
+          <t>Thematic Resolution</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Level of categorical detail of information expressed by the number of classes.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>System that stores data products, guaranteeing their preservation for future use.</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>- This function includes all operations to identify, store and retrieve the data and ensure their integrity.</t>
-        </is>
-      </c>
+          <t>Level of categorical detail of information expressed by the number of classes.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- CGLS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1215,30 +1190,26 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Steward</t>
+          <t>Copernicus Service Provider</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>- core
-description: Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
+- approved</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>- See also Custodian.</t>
-        </is>
-      </c>
+          <t>Institutional body, organisation or programme that provides reliable, trusted (authoritative?) EO Information and that has the financial resources to sustain the provision. It utilises satellite Data, ground-based measurements, and other sources to generate accurate and timely Data products related to various aspects of the Earth's environment, such as land, Atmosphere, oceans, and climate.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -1261,32 +1232,26 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sample</t>
+          <t>Replicability</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>- controversial
-description: Subset of one or more entities.</t>
+          <t>- core
+description: Property enabling other researchers to conduct an independent study with different data and similar but not identical methods, yet arriving at results that confirm the original study's hypothesis.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Subset of one or more entities.</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>- A Sample may be spatial, temporal, spectral, or in any other dimension or Trait.
-- Each Sample is contiguous, i.e. it does not consist of more than one discontinuous geometry in any dimension.
-- The Process of obtaining a Sample is called sampling.</t>
-        </is>
-      </c>
+          <t>Property enabling other researchers to conduct an independent study with different data and similar but not identical methods, yet arriving at results that confirm the original study's hypothesis.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Craglia, M., et al. (2018).</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -1309,35 +1274,30 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Temporal Extent</t>
+          <t>Coverage Interval</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>- core
-description: Period during which data was collected, observations were made, or for which the model was run.</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+- approved</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Coverage extent</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Period during which data was collected, observations were made, or for which the model was run.</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>- In W3C this is the definition of temporal coverage.
-- Time Period covered by a series of observations inclusive of the specified date/time indications (measurement history). Defined based on the beginning and end dates of observations.</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>- WIGOS Metadata</t>
-        </is>
-      </c>
+          <t>Range or specific subset of values associated with a coverage dataset.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>- Adapted from W3C</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -1407,7 +1367,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cryosphere</t>
+          <t>Band Central Wavelength</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1419,14 +1379,20 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Masses of frozen water, such as sea ice, ice shields, glaciers, and snow.</t>
+          <t>Single wavelength Value within the sensitivity interval of a spectroradiometric Sensor which represents the respective band. It could be either the mean, the median, the maximum sensitivity, or any other reasonable Value chosen to be representative.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>| Entry format example | Valid unit                                        |
+|----------------------|---------------------------------------------------|
+| 0.545 μm             | micrometre (μm), millimetre (mm), centimetre (cm) |</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -1449,24 +1415,24 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Spatial Reporting Unit</t>
+          <t>Update Frequency</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>- core
-description: Smallest spatial object of interest that may be used for reporting and for which the information should be aggregated.</t>
+description: Frequency at which the product is available to users.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Smallest spatial object of interest that may be used for reporting and for which the information should be aggregated.</t>
+          <t>Frequency at which the product is available to users.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>- WIGOS 2019 uses 'spatial reporting interval', probably assuming observations are reported on a grid with regular spacing/intervals.</t>
+          <t>- Also known in product catalogues as dissemination frequency.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -1495,36 +1461,44 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Decommissioned Product</t>
+          <t>Entity</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>- core
-description: Products and collections that have been superseded by new versions and are no longer available.</t>
+          <t>- base
+description: Something that has separate and distinct existence and objective or conceptual reality.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Products and collections that have been superseded by new versions and are no longer available.</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>- Decommissioned products are no longer supported, i.e. corrections will not be made, new data will not be added, and support is not available.</t>
-        </is>
-      </c>
+          <t>Something that has separate and distinct existence and objective or conceptual reality.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>- ISO 19119:2016, 4.1.6</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Government or business organization that is formed to conduct business or represent the government of the day.</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>CEOS Entities include Working Groups, Virtual Constellations, etc.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -1541,36 +1515,26 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Place</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>- base
-description: Particular Place referenced by an identifier.</t>
+description: Part of any space referenced by an identifier.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Particular Place referenced by an identifier.</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>- While a (geo)location identifies a geographic Place, it may also be associated with objects other than the Earth.
-- While Location in principle covers 0- to 3-dimensional spatial geometries, it should not be used for 0- and 1-dimensional geometries (positions and paths).</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>- Madrid
-- California</t>
-        </is>
-      </c>
+          <t>Part of any space referenced by an identifier.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>- [ISO 19112:2019](https://www.iso.org/standard/70742.html), (E), 3.1.3, modified, note 2 added</t>
+          <t>- ISO 19155:2012, 4.8</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -1593,30 +1557,33 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Period</t>
+          <t>Duration</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>- base
-description: Particular era or span of time.</t>
+          <t>- core
+description: Non-negative interval Quantity of time equal to the difference between the final and initial instants of a time interval.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Particular era or span of time.</t>
+          <t>Non-negative interval Quantity of time equal to the difference between the final and initial instants of a time interval.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>- Periods are intervals named with a Period Identifier.</t>
+          <t>- Duration is one of the base quantities in the International System of Quantities (ISQ) on which the International System of Units (SI) is based. The term "time" instead of "duration" is often used in this context and also for an infinitesimal duration.
+- For the term "duration", expressions such as "time" or "time interval" are often used, but the term "time" is not recommended in this sense and the term "time interval" is deprecated in this sense to avoid confusion with the concept of "time interval".
+- The exact duration of a time scale unit depends on the time scale used. For example, the durations of a year, month, week, day, hour or minute may depend on when they occur (in a Gregorian calendar, a calendar month can have a duration of 28, 29, 30, or 31 days; in a 24-hour clock, a clock minute can have a duration of 59, 60, or 61 seconds, etc.). Therefore, the exact duration can only be evaluated if the exact duration of each is known.
+- This definition is closely related to NOTE 1 of the terminological entry "duration" in IEC 60050-113:2011, 113-01-13.</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>- ISO 19170:2021</t>
+          <t>- ISO 8601-1:2019, 3.1.1.8</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -1639,27 +1606,37 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Geospatial Data</t>
+          <t>Time of Day</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>- core
-description: Data consisting of, derived from, or relating to information that is directly linked to specific geographical locations.</t>
+description: Time of the day at which the variable or parameter is observed or simulated by a model.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Data consisting of, derived from, or relating to information that is directly linked to specific geographical locations.</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+          <t>Time of the day at which the variable or parameter is observed or simulated by a model.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>- In Remote Sensing it is also known as time of overpass.</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>| Type      | Entry format example | Valid unit |
+|-----------|----------------------|------------|
+| timestamp | 18:00 h (0–24)       | Hours      |
+| timerange | 18:00 – 20:00 h      | Hours      |</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>- https://www.merriam-webster.com/dictionary/geospatial
-- https://isotc211.geolexica.org/Concepts/202/, accessed 20221010</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -1682,23 +1659,29 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Confidence Interval</t>
+          <t>Vertical Levels</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>- controversial
-- approved</t>
+          <t>- core
+description: Levels of a vertical discretization, e.g. pressure levels in an atmospheric model reanalysis or height levels in a forest biomass EO product.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Probability that the Quantity lies in the interval, conditioned on the measuring or modelling assumptions.</t>
+          <t>Levels of a vertical discretization. Examples may be pressure levels in an atmospheric model reanalysis or height levels in a forest biomass EO product.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>| Entry format example                | Valid unit           |
+|------------------------------------|----------------------|
+| 1, 5, 10 meter; 1000, 850, 500 hPa | meter, hPa, unitless |</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>- KCEO</t>
@@ -1724,30 +1707,34 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Granule</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>- core
-description: The smallest aggregation of data which is independently managed (i.e. described, inventoried, retrievable).</t>
+description: Electronic data package distributable to users; content is derived from instrument data via processing involving ancillary and auxiliary data.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>The smallest aggregation of data which is independently managed (i.e. described, inventoried, retrievable). Granules may be managed as logical granules and/or physical granules.</t>
+          <t>Electronic data package distributable to users; content is derived from instrument data via processing involving ancillary and auxiliary data.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>- See also product.</t>
+          <t>- Products may be accompanied by metadata and browse images.
+- A Product may be part of a collection — a distinction useful for archiving and cataloguing purposes.
+- The term Product may be used to denote a product type, such as e.g. ENVISAT_ASAR_L1B_PRI data products.
+- End users may distinguish between (input, "raw") data and products, i.e., the derived geophysical parameters.
+- See also granule.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>- [NASA EarthData](https://www.earthdata.nasa.gov/learn/glossary)</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -1770,24 +1757,24 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>- controversial
-description: An, often numeric, theoretical (or otherwise abstract) representation of an Entity intended to generate Data describing one or more of its traits.</t>
+          <t>- base
+description: The result of organisation, interpretation, categorisation, classification, or some other form of processing of Data attaching to it a certain meaning that can be understood by the addressee.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>An, often numeric, theoretical (or otherwise abstract) representation of an Entity intended to generate Data describing one or more of its traits (as a result of pre-set conditions).</t>
+          <t>The result of organisation, interpretation, categorisation, classification, or some other form of processing of Data attaching to it a certain meaning that can be understood by the addressee.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>- The Process of generating Data using a model is called modelling.</t>
+          <t>- Information depends on Data and is targeted.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -1816,44 +1803,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Georectifying</t>
+          <t>Lithosphere</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>- core
-description: Correcting for positional displacement with respect to the surface of the Earth.</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Orthorectifying</t>
-        </is>
-      </c>
+description: The solid, inanimate outer layer of the Geosphere. For the purposes of Earth Observation, includes soils ('pedosphere').</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Correcting for positional displacement with respect to the surface of the Earth.</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>- Source: ISO 19115-2:2019, 3.11; ISO 19115-2:2009(E); https://www.iso.org/standard/67039.html, modified</t>
-        </is>
-      </c>
+          <t>The solid, inanimate outer layer of the Geosphere. For the purposes of Earth Observation, the Lithosphere is considered to include soils ('pedosphere').</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>The correction of sample locations to achieve some sort of geometric regularity, e.g., a regular 2D geographic grid.</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>- Guth et al. 2021</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
@@ -1870,32 +1845,45 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Policy Making</t>
+          <t>Ancillary Data</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>- high-impact
-description: Process by which governments translate their political vision into programmes and actions to deliver outcomes — desired change in the real world.</t>
+          <t>- core
+- approved</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Process by which governments translate their political vision into programmes and actions to deliver outcomes — desired change in the real world.</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>Data acquired on the same platform but not obtained from the main Sensor itself (usually provided as part of Level 0 Data), with the primary purpose of serving the processing of main instrument Data (e.g. Position and velocity of platform).</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>This can be divided into data referred to as spacecraft 'engineering', 'core housekeeping' or 'subsystem' data obtained from other parts of the platform, and includes parameters such as orbit position and velocity, attitude and its range of change, time, temperatures, pressures, jet firings, water dumps, internally produced magnetic fields, and other environmental measurements. Ancillary refers to data that exist purely to serve the data processing.</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>- [ESA/CEOS?, modified](https://digital-strategy.ec.europa.eu/en/library/quality-public-administration-toolbox-practitioners)</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>- ESA/CEOS?, modified
+- EO Data Stewardship Glossary</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Data other than instrument measurements, originating in the instrument itself or from the satellite, required to perform processing of the Data. Includes orbit Data, attitude Data, time Information, and spacecraft engineering Data, Calibration Data, Data quality Information, and Data from other instruments or earth system models.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>- CEOS-ARD PFS template 20220302</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
@@ -1912,109 +1900,72 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Uncertainty</t>
+          <t>Quality Indicator</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>- core
-description: Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
+description: Indicator providing sufficient information to allow all users to readily evaluate the fitness for purpose of the data or derived product.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
+          <t>Indicator providing sufficient information to allow all users to readily evaluate the fitness for purpose of the data or derived product. May be a number, set of numbers, graph, Uncertainty budget, or a simple flag.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>- GUM</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Non-negative parameter, associated with data, which characterizes the dispersion of the values of a Trait that could reasonably be attributed to a Phenomenon by means of sensing or modelling.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>- In case of quantitative (continuous) data the uncertainty may be, for example, a standard deviation (or a given multiple of it), or the half-width of an interval having a stated level of confidence (see e.g. Standard and Expanded Uncertainty).
-- For qualitative (categorical?) data, uncertainty may be expressed by commission and omission ('confusion matrix') or overall errors.</t>
-        </is>
-      </c>
+          <t>- CEOS Wiki</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>- Modified from GUM, VIM4:3.1, FIDUCEO, Notes added</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Measure of the spread of the distribution of possible values.</t>
-        </is>
-      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>- [FIDUCEO Glossary](https://research.reading.ac.uk/fiduceo/glossary/), VIM?, modified</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Parameter, associated with the result of measurement, that characterizes the dispersion of values that could reasonably be attributed to the measurand.</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>- When the quality of accuracy or precision of measured values, such as coordinates, is to be characterized quantitatively, the quality parameter is an estimate of the uncertainty of the measurement results. Because accuracy is a qualitative concept, one should not use it quantitatively, that is associate numbers with it; numbers should be associated with measures of uncertainty instead.</t>
-        </is>
-      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>- ISO 19116:2004(E)</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Parameter characterizing the dispersion of the values being attributed to a measurand, based on the information used.</t>
-        </is>
-      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>- VIM4: 3.1</t>
-        </is>
-      </c>
+      <c r="W31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Climate Projection</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>- core
-- approved</t>
+          <t>- base
+description: Series of activities that interact to produce a result.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Simulated response of the climate system to a scenario of future emission or concentration of greenhouse gases (GHGs) and aerosols, generally derived using climate models. Climate Projections are distinguished from climate predictions by their dependence on the emission/concentration/radiative forcing scenario used, which is in turn based on assumptions concerning, for example, future socioeconomic and technological developments that may or may not be realised.</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
+          <t>Series of activities that interact to produce a result.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>- A Process may occur once-only or be recurrent or periodic.</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>- IPCC</t>
+          <t>- [Wikipedia](https://en.wikipedia.org/wiki/Process)</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -2037,26 +1988,26 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Format</t>
+          <t>Standard Uncertainty</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>- core
-description: Structured Data that is machine readable and can be automatically read and processed by a computer, such as HDF, NetCDF, CSV, JSON, XML, etc.</t>
+description: Standard deviation of the probability distribution describing the spread of possible values in quantitative/continuous data.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Structured Data that is machine readable and can be automatically read and processed by a computer, such as HDF, NetCDF, CSV, JSON, XML, etc.</t>
+          <t>Standard deviation of the probability distribution describing the spread of possible values in quantitative/continuous data.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>- CEOS Wiki</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -2079,26 +2030,26 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Classification System Levels</t>
+          <t>Minimum Mapping Width</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: The width of the smallest linear Feature that is still represented on a map.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Levels in a hierarchical Classification System.</t>
+          <t>The width of the smallest linear Feature that is still represented on a map.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- CGLS</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -2121,30 +2072,26 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Geocoding</t>
+          <t>Deprecated Product</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>- core
-description: Translation of one form of Location into another.</t>
+description: Products and collections that have been superseded by a newer version and are still available, but whose use is discouraged since they will be decommissioned in the future.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Translation of one form of Location into another.</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>- Geocoding usually refers to the translation of "address" or "intersection" to "direct Position." Many service providers also include a "reverse geocoding" interface to their geocoder, thus extending the definition of the service as a general translator of Location. Because routing services use internal Location encodings not usually available to others, a geocoder is an integral part of the internals of such a service.</t>
-        </is>
-      </c>
+          <t>Products and collections that have been superseded by a newer version and are still available, but whose use is discouraged since they will be decommissioned in the future.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>- ISO 19133:2005; https://www.iso.org/standard/32551.html</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -2167,32 +2114,30 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Band Central Wavelength</t>
+          <t>Period Identifier</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Temporal reference in the form of a label or code that identifies a Period.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Single wavelength Value within the sensitivity interval of a spectroradiometric Sensor which represents the respective band. It could be either the mean, the median, the maximum sensitivity, or any other reasonable Value chosen to be representative.</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>| Entry format example | Valid unit                                        |
-|----------------------|---------------------------------------------------|
-| 0.545 μm             | micrometre (μm), millimetre (mm), centimetre (cm) |</t>
-        </is>
-      </c>
+          <t>Temporal reference in the form of a label or code that identifies a Period.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>- Period Identifiers are the temporal equivalent of geographic identifiers as specified in ISO 19912.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO 19170:2021</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -2215,19 +2160,28 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cartographic Projection</t>
+          <t>Lead Time</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>- core</t>
+          <t>- core
+description: Minimum time of interval between an Observation being tasked and being performed.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Minimum time of interval between an Observation being tasked and being performed.</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
@@ -2248,7 +2202,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Copernicus Service Provider</t>
+          <t>Calibration</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2260,16 +2214,12 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Institutional body, organisation or programme that provides reliable, trusted (authoritative?) EO Information and that has the financial resources to sustain the provision. It utilises satellite Data, ground-based measurements, and other sources to generate accurate and timely Data products related to various aspects of the Earth's environment, such as land, Atmosphere, oceans, and climate.</t>
+          <t>Process of quantitatively defining a system's (e.g. a Sensor or Model's) response to known, controlled inputs produced for example by references. In Remote Sensing, it implies the collection of pre-flight and in-flight calibration measurements and in-situ Data that is to be used in the Data calibration processing routine.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
@@ -2290,26 +2240,26 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Location Error</t>
+          <t>Climate Projection</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>- core
-description: Measure of the agreement between the represented Location of an Object and the true Location.</t>
+- approved</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Measure of the agreement between the represented Location of an Object and the true Location.</t>
+          <t>Simulated response of the climate system to a scenario of future emission or concentration of greenhouse gases (GHGs) and aerosols, generally derived using climate models. Climate Projections are distinguished from climate predictions by their dependence on the emission/concentration/radiative forcing scenario used, which is in turn based on assumptions concerning, for example, future socioeconomic and technological developments that may or may not be realised.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- IPCC</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -2332,26 +2282,30 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Version Control</t>
+          <t>Spatial Reporting Unit</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>- core
-description: Method of working with collections, similar to version control systems used in traditional software development but optimized to allow better processing of data and collaboration in data analytics and research contexts.</t>
+description: Smallest spatial object of interest that may be used for reporting and for which the information should be aggregated.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Method of working with collections, similar to the version control systems used in traditional software development but optimized to allow better processing of data and collaboration in the context of data analytics, research, and any other form of data analysis.</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
+          <t>Smallest spatial object of interest that may be used for reporting and for which the information should be aggregated.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>- WIGOS 2019 uses 'spatial reporting interval', probably assuming observations are reported on a grid with regular spacing/intervals.</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>- [Wikipedia](https://en.wikipedia.org/wiki/Data_version_control)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -2374,26 +2328,26 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Access</t>
+          <t>Source Data</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>- core
-description: Service to disseminate Data.</t>
+description: Data required for production of an EO Collection (e.g., unenhanced satellite mission data) as well as further processed Level-1 data, or any other pre-processed format meeting program requirements.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Service to disseminate Data.</t>
+          <t>Data required for production of an EO Collection (e.g., unenhanced satellite mission data) as well as further processed Level-1 data (precision geometrically and radiometrically corrected radiance at the sensor), or any other pre-processed format that suppliers are providing access to that meets program requirements.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -2416,7 +2370,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Collection Upgrade</t>
+          <t>Accuracy</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2428,14 +2382,18 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>New and improved major version of all products within a collection due to comprehensive reprocessing.</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+          <t>Proximity of Measurement results to the accepted Value; precision is the degree to which repeated or reproducible measurements under unchanged conditions show the same results.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>- In essence, Accuracy reflects how close measurements are to the accepted Value, while precision gauges the reliability and consistency of those measurements.</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- BS ISO 5725-1</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -2458,26 +2416,26 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Thematic Resolution</t>
+          <t>Policy Making</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>- core
-description: Level of categorical detail of information expressed by the number of classes.</t>
+          <t>- high-impact
+description: Process by which governments translate their political vision into programmes and actions to deliver outcomes — desired change in the real world.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Level of categorical detail of information expressed by the number of classes.</t>
+          <t>Process by which governments translate their political vision into programmes and actions to deliver outcomes — desired change in the real world.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>- CGLS</t>
+          <t>- [ESA/CEOS?, modified](https://digital-strategy.ec.europa.eu/en/library/quality-public-administration-toolbox-practitioners)</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -2500,26 +2458,31 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Standard Uncertainty</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>- core
-description: Standard deviation of the probability distribution describing the spread of possible values in quantitative/continuous data.</t>
+          <t>- base
+- controversial
+description: Place referenced by a single set of coordinates within a coordinate reference system.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Standard deviation of the probability distribution describing the spread of possible values in quantitative/continuous data.</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
+          <t>Place referenced by a single set of coordinates within a coordinate reference system.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>- Opposite to (previous) ISO definition, Position shall be used only for 0-dimensional primitives (points).</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO 19133:2005, modified to cover only points, also called 'direct position'</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -2542,30 +2505,26 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Coverage Interval</t>
+          <t>Minimum Mapping Unit</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Coverage extent</t>
-        </is>
-      </c>
+description: The area of the smallest Feature that is still represented on a map.</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Range or specific subset of values associated with a coverage dataset.</t>
+          <t>The area of the smallest Feature that is still represented on a map.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- CGLS</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -2588,26 +2547,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Path</t>
+          <t>Spectral Band</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>- base
-description: "Line defined in an algorithmic way using at least two positions (can be open-ended). Alternative: line connecting two positions in an algorithmic way (limited by end points)."</t>
+          <t>- core
+description: Part of the electromagnetic spectrum of specific wavelengths, in remote sensing usually described by central wavelength and bandwidth.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Line defined in an algorithmic way using at least two positions (can be open-ended). Alternative: line connecting two positions in an algorithmic way (limited by end points).</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>- A Path is a 1-dimensional Place.</t>
-        </is>
-      </c>
+          <t>Part of the electromagnetic spectrum of specific wavelengths. In Remote Sensing, usually described by central wavelength and bandwidth.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
@@ -2634,28 +2589,28 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Source Data</t>
+          <t>Geopositioning</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>- core
-description: Data required for production of an EO Collection (e.g., unenhanced satellite mission data) as well as further processed Level-1 data, or any other pre-processed format meeting program requirements.</t>
+description: Determination of the geographic Position of a point (0D) or linear (1D) Feature.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Data required for production of an EO Collection (e.g., unenhanced satellite mission data) as well as further processed Level-1 data (precision geometrically and radiometrically corrected radiance at the sensor), or any other pre-processed format that suppliers are providing access to that meets program requirements.</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
+          <t>Determination of the geographic Position of a point (0D) or linear (1D) Feature.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>- Modified from: ISO 19130-1:2018, 3.36</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
-        </is>
-      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
@@ -2676,7 +2631,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Atmosphere</t>
+          <t>Collection Update</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2688,14 +2643,14 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Layer of gases, commonly known as air, including suspended liquid and solid particles known as aerosols (incl. dust, clouds, snow and ice).</t>
+          <t>Minor revisions to a relatively small number of products within a collection for the purpose of correcting errors and maintaining consistent quality.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -2718,62 +2673,57 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Verification</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>- core
-description: Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
+description: Provision of objective evidence that a given item fulfils specified requirements.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
+          <t>Provision of objective evidence that a given item fulfils specified requirements.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
+          <t>- When applicable, measurement uncertainty should be taken into consideration.
+- The item may be, e.g. a Process, measurement procedure, material, compound, or measuring system.
+- The specified requirements may be, e.g. that a manufacturer's specifications are met.
+- Verification should not be confused with Calibration. Not every verification is a Validation.</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>- ISO/TS 19101‑2:2008, 4.41</t>
+          <t>- ISO/IEC Guide 99:2007, 2.44</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Process aimed at verifying that the specified requirements are achieved or compliant. Involves comparing mission products with representative reference data, considering various observation conditions, ensuring the quality and traceability of the reference data used.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
-        </is>
-      </c>
+          <t>Evaluation of whether or not a product, service, or system complies with a regulation requirement, specification, or imposed condition. Often an internal Process.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>- BIPM; QA4EO; ESA?, modified</t>
+          <t>- EU-US Land Imaging EO Collaboration</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Assurance that a product, service, or system meets the needs of the customer and other identified stakeholders. Often involves acceptance and suitability with external customers.</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
-        </is>
-      </c>
+          <t>Means to evaluate the reliability of the data in the absence of a reference dataset, allowing for an assessment of its standalone performance. Involves confirming the consistency and internal coherence of the data without direct comparison to external reference sources.</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
-          <t>- EU-US Land Imaging EO Collaboration</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="P49" t="inlineStr"/>
@@ -2788,31 +2738,29 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Long Term Preservation</t>
+          <t>Earth Observation Based Output</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>- core
-description: The act of maintaining information in a correct and independently understandable form over the long term.</t>
+description: Higher-level processing and integration output (indicative level 4 and beyond) that goes beyond basic data processing, often designed for policy or decision-making needs.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>The act of maintaining information in a correct and independently understandable form over the long term.</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>- Long term refers to a period of time long enough to be concerned with the impact which changing technologies, including support for media and data formats, and changing user communities will have on the information being held in a repository.
-- See also preservation.</t>
-        </is>
-      </c>
+          <t>Higher-level processing and integration output (indicative level 4 and beyond) that goes beyond basic data processing. These outputs are often designed specifically for policy or decision-making needs, and can be categorized into sub-categories:
+- Outputs from models/model integration: use of EO products as inputs in numerical models or combining them with other data sources in modelling frameworks.
+- Indicator-based outputs: EO products transformed through specialized algorithms (including statistical methods, machine learning, and pattern recognition) to create meaningful metrics based on spatio-temporal analysis.
+- Outputs from reanalysis: merging of EO products with other observations and models, creating consistent long-term records of past atmospheric, oceanic, and land surface conditions, and filling gaps through data assimilation techniques.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
@@ -2835,32 +2783,19 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Catalogue</t>
+          <t>Cartographic Projection</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>- core
-- approved</t>
+          <t>- core</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>System that provides users with discovery of information on which EO products can be obtained.</t>
-        </is>
-      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>- A 'Product Catalogue' can organise products and collections with varying access levels depending on product and user type.</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
-        </is>
-      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
@@ -2881,26 +2816,32 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Minimum Mapping Unit</t>
+          <t>Temporal Reporting Period</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>- core
-description: The area of the smallest Feature that is still represented on a map.</t>
+description: Time period used for reporting and for which the information should be aggregated from the native temporal resolution.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>The area of the smallest Feature that is still represented on a map.</t>
+          <t>Time Period used for reporting and for which the information should be aggregated from the native Temporal Resolution.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>| Entry format example | Valid unit                     |
+|----------------------|-------------------------------|
+| 1 s, 2 h, 1 d        | second, hour, day, month, year |</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>- CGLS</t>
+          <t>- Modified WIGOS Metadata Standard 2019</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
@@ -2923,32 +2864,26 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Temporal Reporting Period</t>
+          <t>Reproducibility</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>- core
-description: Time period used for reporting and for which the information should be aggregated from the native temporal resolution.</t>
+description: Concerned with the validity of the results of a particular study, enabling readers to check whether results have been manipulated by reproducing exactly the same study using the same data and methods.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Time Period used for reporting and for which the information should be aggregated from the native Temporal Resolution.</t>
+          <t>Concerned with the validity of the results of a particular study, i.e., the possibility for readers to check whether results have been manipulated, by reproducing exactly the same study using the same data and methods.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>| Entry format example | Valid unit                     |
-|----------------------|-------------------------------|
-| 1 s, 2 h, 1 d        | second, hour, day, month, year |</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>- Modified WIGOS Metadata Standard 2019</t>
+          <t>- Ostermann and Granell (2015)</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
@@ -2971,26 +2906,26 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Policy File</t>
+          <t>Atmosphere</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>- high-impact
-description: Policy documents that represent the official written reference for a given Policy.</t>
+          <t>- core
+- approved</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Policy documents that represent the official written reference for a given Policy.</t>
+          <t>Layer of gases, commonly known as air, including suspended liquid and solid particles known as aerosols (incl. dust, clouds, snow and ice).</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
@@ -3013,32 +2948,40 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Impact</t>
+          <t>Geolocating</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>- core
-description: Regarded long-term according to X. However, in the Horizon Europe Missions terminology, regarded short-term.</t>
+description: Geopositioning of an Object using a Physical Sensor Model or a True Replacement Model.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Regarded long-term according to X. However, in the Horizon Europe Missions terminology, regarded short-term.</t>
+          <t>Geopositioning of an Object using a Physical Sensor Model or a True Replacement Model.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>- ISO 19115-2:2009, 4.11</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Determination of the geographic location of a feature of two or more dimensions.</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>- ISO 19130-1:2018, 3.36 ('geopositioning'), modified</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
@@ -3055,24 +2998,28 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Calibration</t>
+          <t>Confidence Interval</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>- core
+          <t>- controversial
 - approved</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Process of quantitatively defining a system's (e.g. a Sensor or Model's) response to known, controlled inputs produced for example by references. In Remote Sensing, it implies the collection of pre-flight and in-flight calibration measurements and in-situ Data that is to be used in the Data calibration processing routine.</t>
+          <t>Probability that the Quantity lies in the interval, conditioned on the measuring or modelling assumptions.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
@@ -3093,35 +3040,23 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Baseline</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>- base
-description: Value and possibly Uncertainty of a Trait of a specific Entity.</t>
+          <t>- core
+- approved</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Value and possibly Uncertainty of a Trait of a specific Entity.</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>- Data simply describe entities using certain traits and are not targeted at a particular use or audience.</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Data can be categorised into:
-- factual (i.e. obtained by Observation) or fictional (obtained e.g. through modelling, estimating or assigning)
-- quantitative (continuous) or qualitative (categorical)
-- analogue or digital
-(list not exhaustive!)</t>
-        </is>
-      </c>
+          <t>Reference Period, time or measure against which the Information is assessed or compared.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
           <t>- KCEO</t>
@@ -3129,7 +3064,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Scientific or technical measurements, values calculated therefrom, observations, or facts that can be represented by numbers, tables, graphs, models, text, or symbols which are used as a basis for reasoning and further calculation.</t>
+          <t>Source data that has been processed to a common set of requirements and organised into a form that allows immediate analysis and interoperability through time and with other collections.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -3155,40 +3090,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Quantity</t>
+          <t>Classification System Levels</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>- base
-description: Property having a magnitude that can be expressed as a number from a continuous and contiguous range and a reference.</t>
+          <t>- core
+- approved</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Property having a magnitude that can be expressed as a number from a continuous and contiguous range and a reference.</t>
+          <t>Levels in a hierarchical Classification System.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>- ISO/IEC Guide 99:2007, 1.1, modified — Notes omitted</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Property whose instances can be compared by ratio or only by order.</t>
-        </is>
-      </c>
+          <t>- KCEO</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>- gEOGlos (VIM4 Notes omitted)</t>
-        </is>
-      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
@@ -3205,26 +3132,26 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Policy Milestone</t>
+          <t>Latency</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>- high-impact
-description: Markers of significant progress in addressing specific issues, or crucial decision points where significant choices are made within a policy process.</t>
+          <t>- core
+description: Period between the end of sensing of a Phenomenon to the beginning of availability of a specific product.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Markers of significant progress in addressing specific issues, or crucial decision points where significant choices are made. Concrete examples include: policy planning and proposing, impact assessment, implementation, or implementation cycles (e.g., Water Framework Directive, Marine Strategy Framework Directive), achievement of Policy Objectives and Policy Targets, and evaluating and improving existing laws.</t>
+          <t>Period between the end of sensing of a Phenomenon to the beginning of availability of a specific product.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ?</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -3247,31 +3174,26 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Data Access</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>- base
-description: Element of a type domain.</t>
+          <t>- core
+description: Service to disseminate Data.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Element of a type domain.</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>- A Value may consider a possible state of an object within a class or type (domain).
-- A data value is an instance of a data type, a value without identity.</t>
-        </is>
-      </c>
+          <t>Service to disseminate Data.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>- ISO/IEC 19501:2005, 0000_5</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -3294,26 +3216,26 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Collection Update</t>
+          <t>Phenomenon</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>- core
-- approved</t>
+          <t>- base
+description: Entity with at least one Property referenced by an identifier.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Minor revisions to a relatively small number of products within a collection for the purpose of correcting errors and maintaining consistent quality.</t>
+          <t>Entity with at least one Property referenced by an identifier.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- KCEO, modified after Wikipedia and the Columbia Encyclopaedia 2008</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -3336,30 +3258,37 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Laboratory Observation</t>
+          <t>Earth Spheres</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>- core
-description: Usually in-situ observations in which the Object or Phenomenon is isolated from other systems or altered in its original conditions or environment.</t>
+description: Spheres dividing planet Earth into subsystems, which are collectives of (physical) matter sharing specific traits.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Usually in-situ observations in which the Object or Phenomenon is isolated from other systems or altered in its original conditions or environment.</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>- It is important to consider that Laboratory Observations are typically conducted in controlled conditions, allowing for isolation or alteration of the Object or Phenomenon from its natural environment or other systems.</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr"/>
+          <t>Spheres dividing planet Earth into subsystems, which are collectives of (physical) matter sharing specific traits.</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>- Atmosphere
+- Hydrosphere
+- Cryosphere
+- Biosphere
+- Lithosphere
+- Anthroposphere</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Hugget, R., et al., 2024, DOI: 10.1177/03091333241275465
+- Guth, P., et al., 2021, https://doi.org/10.3390/rs13183581
+- Martin, Y.E., et al., 2012</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
@@ -3382,20 +3311,33 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Environmental Process</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>- core
-description: ""</t>
+          <t>- base
+description: Element of a type domain.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Element of a type domain.</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>- A Value may consider a possible state of an object within a class or type (domain).
+- A data value is an instance of a data type, a value without identity.</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>- ISO/IEC 19501:2005, 0000_5</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
@@ -3416,26 +3358,34 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Measurement Uncertainty</t>
+          <t>Timeliness</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>- core
-description: Uncertainty associated with the method of Measurement.</t>
+description: Period between the moment of requesting information and the moment of availability of information.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Uncertainty associated with the method of Measurement.</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr"/>
+          <t>Period between the moment of requesting information and the moment of availability of information.
+- Near Real-Time (NRT): delivered less than 3 hours after requesting information.
+- Slow-Time Critical (STC): delivered within 48 hours after requesting information.
+- Non-Time Critical (NTC): typically delivered within 1 month after requesting information.</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>- In some contexts also known as delivery time.
+- C3S URDB describes timeliness as "the ability of the publish/subscribe middleware to provide the expected service within known time bounds".</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>- CEOS Wiki adopted from JCGM GUM</t>
+          <t>- Adapted from ESA S3 User Guide</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
@@ -3458,47 +3408,59 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Temporal Revisit</t>
+          <t>Auxiliary Data</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>- core
-description: Interval between successive observations.</t>
+- approved</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Interval between successive observations.</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>- In Remote Sensing it is also called repeat cycle.
-- More generally it is known as temporal sampling interval.</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>| Entry format example | Valid unit                     |
-|----------------------|-------------------------------|
-| 1 s, 2 h             | second, hour, day, month, year |</t>
-        </is>
-      </c>
+          <t>Data that enhance the processing and utilisation of main Sensor Data. Auxiliary Data are usually not captured by the same Data collection Process or on the same platform as the main Sensor Data. Examples include meteorological Data received from ECMWF/Met Offices or DEMs. Auxiliary Data help in Data processing, but are also Data sets in their own right.</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
+          <t>- ESA/CEOS?, modified
+- ENMAP Glossary of Terms, https://www.enmap.org/Data/doc/EnMAP_Terms.pdf, 20210624
+- EO Data Stewardship Glossary</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Data required to perform processing of Sensor Data which is not obtained from the Sensor itself. Includes: (a) Data provided by the spacecraft (e.g. orbit Position and velocity, attitude, instrument house-keeping Data, on-board time); (b) Data not available from on-board sources.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>For EnMAP, this includes (a) orbit files, attitude files, Calibration Data, instrument house-keeping Data; (b) atmospheric parameters, reference images.</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>- ENMAP Glossary of Terms, https://www.enmap.org/Data/doc/EnMAP_Terms.pdf, 20210624
+- EO Data Stewardship Glossary</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Data required for instrument processing that does not originate in the instrument itself or from the satellite. Some Auxiliary Data will be generated in the ground segment, whilst other Data will be provided from external sources.</t>
+        </is>
+      </c>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>- CEOS-ARD PFS template 20220302</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
@@ -3511,30 +3473,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Period Identifier</t>
+          <t>Area of Interest</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>- core
-description: Temporal reference in the form of a label or code that identifies a Period.</t>
+- approved</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Temporal reference in the form of a label or code that identifies a Period.</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>- Period Identifiers are the temporal equivalent of geographic identifiers as specified in ISO 19912.</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
+          <t>Zone in 2D or 3D for which the Information or Data is requested. It can be discontinuous in space — in other words it can consist of the union of many separate zones (e.g., Natural Reserves in Africa, Urban environments, etc.). The attribute indicates a request for spatially complete Data within the AOI zone(s).</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>| Type                                    | Entry format example              | Valid units |
+|-----------------------------------------|-----------------------------------|-------------|
+| Geographical/administrative identifier  | NUTS3, LAU, Natura 2000 site      | unitless    |</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>- ISO 19170:2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
@@ -3557,38 +3521,40 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Area of Interest</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>- core
-- approved</t>
+          <t>- base
+description: Property having a magnitude that can be expressed as a number from a continuous and contiguous range and a reference.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Zone in 2D or 3D for which the Information or Data is requested. It can be discontinuous in space — in other words it can consist of the union of many separate zones (e.g., Natural Reserves in Africa, Urban environments, etc.). The attribute indicates a request for spatially complete Data within the AOI zone(s).</t>
+          <t>Property having a magnitude that can be expressed as a number from a continuous and contiguous range and a reference.</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>| Type                                    | Entry format example              | Valid units |
-|-----------------------------------------|-----------------------------------|-------------|
-| Geographical/administrative identifier  | NUTS3, LAU, Natura 2000 site      | unitless    |</t>
-        </is>
-      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>- ISO/IEC Guide 99:2007, 1.1, modified — Notes omitted</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Property whose instances can be compared by ratio or only by order.</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>- gEOGlos (VIM4 Notes omitted)</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
@@ -3605,34 +3571,30 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Timeliness</t>
+          <t>Final Product Version</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>- core
-description: Period between the moment of requesting information and the moment of availability of information.</t>
+description: Product within an EO Collection that is not expected to be updated.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Period between the moment of requesting information and the moment of availability of information.
-- Near Real-Time (NRT): delivered less than 3 hours after requesting information.
-- Slow-Time Critical (STC): delivered within 48 hours after requesting information.
-- Non-Time Critical (NTC): typically delivered within 1 month after requesting information.</t>
+          <t>Product within an EO Collection that is not expected to be updated.</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>- In some contexts also known as delivery time.
-- C3S URDB describes timeliness as "the ability of the publish/subscribe middleware to provide the expected service within known time bounds".</t>
+          <t>- In its production, all of the prerequisite auxiliary data were used as input.</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>- Adapted from ESA S3 User Guide</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
@@ -3655,26 +3617,31 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Hydrosphere</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>- core
-description: The masses of liquid water, such as oceans, lakes, and rivers.</t>
+          <t>- controversial
+description: Act of determining the Value of a Property by interacting in a reproducible way with the Phenomenon using a Sensor.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>The masses of liquid water, such as oceans, lakes, and rivers.</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr"/>
+          <t>Act of determining the Value of a Property by interacting in a reproducible way with the Phenomenon using a Sensor.</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>- The result of an Observation is a Value complemented by an Uncertainty, often itself being referred to as 'observation'.
+- An Observation result represents a Sample of the Phenomenon (otherwise it would be identical with the Phenomenon).</t>
+        </is>
+      </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
@@ -3697,36 +3664,56 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>Characteristic</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>- core
+          <t>- base
 - approved</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Proximity of Measurement results to the accepted Value; precision is the degree to which repeated or reproducible measurements under unchanged conditions show the same results.</t>
+          <t>Distinguishing Feature.</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>- In essence, Accuracy reflects how close measurements are to the accepted Value, while precision gauges the reliability and consistency of those measurements.</t>
+          <t>- A Characteristic can be inherent or assigned.
+- A Characteristic can be qualitative or quantitative.
+- There are various classes of Characteristics, such as the following:
+  - physical (e.g. mechanical, electrical, chemical, biological);
+  - sensory (e.g. relating to smell, touch, taste, sight, hearing);
+  - behavioural (e.g. courtesy, honesty, veracity);
+  - temporal (e.g. punctuality, reliability, availability);
+  - ergonomic (e.g. physiological characteristic or related to human safety);
+  - functional (e.g. maximum speed of an aircraft).</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>- BS ISO 5725-1</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
+          <t>- ISO 9000:2005, 3.5.1</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Abstraction of a Property of an Object or of a set of objects.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>- Characteristics are used for describing Concepts.</t>
+        </is>
+      </c>
       <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>- ISO 1087-1:2000, 3.2.4; ISO 19146:2010(E); https://www.iso.org/standard/20057.html</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
@@ -3743,26 +3730,26 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Traceability</t>
+          <t>Geosphere</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>- core
-description: Property of a measurement result whereby the result can be related to a reference through a documented unbroken chain of calibrations each contributing to the measurement uncertainty.</t>
+description: The masses of minerals that constitute planet Earth.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Property of a measurement result whereby the result can be related to a Reference through a documented unbroken chain of calibrations, each contributing to the measurement uncertainty.</t>
+          <t>The masses of minerals that constitute planet Earth.</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>- https://www.isobudgets.com/Measurement-traceability-complying-iso-17025-requirements/</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
@@ -3785,26 +3772,26 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Biosphere</t>
+          <t>Spectral Resolution</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Measure of the ability to resolve features in the electromagnetic spectrum.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Masses of living organisms, such as vegetation and animals, including dead but still connected parts such as roots, trunks or branches.</t>
+          <t>Measure of the ability to resolve features in the electromagnetic spectrum.</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
@@ -3827,30 +3814,26 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Update Frequency</t>
+          <t>Hydrosphere</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>- core
-description: Frequency at which the product is available to users.</t>
+description: The masses of liquid water, such as oceans, lakes, and rivers.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Frequency at which the product is available to users.</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>- Also known in product catalogues as dissemination frequency.</t>
-        </is>
-      </c>
+          <t>The masses of liquid water, such as oceans, lakes, and rivers.</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
@@ -3873,26 +3856,33 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Lithosphere</t>
+          <t>Time of Year</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>- core
-description: The solid, inanimate outer layer of the Geosphere. For the purposes of Earth Observation, includes soils ('pedosphere').</t>
+description: Time of the year at which the variable is observed or simulated by a model.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>The solid, inanimate outer layer of the Geosphere. For the purposes of Earth Observation, the Lithosphere is considered to include soils ('pedosphere').</t>
+          <t>Time of the year at which the variable is observed or simulated by a model.</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>| Type      | Entry format example | Valid unit     |
+|-----------|----------------------|----------------|
+| timestamp | m/d                  | Not Applicable |
+| timerange | m/d - m/d            | Not Applicable |</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -3915,24 +3905,24 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Path</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>- base
-description: The result of organisation, interpretation, categorisation, classification, or some other form of processing of Data attaching to it a certain meaning that can be understood by the addressee.</t>
+description: "Line defined in an algorithmic way using at least two positions (can be open-ended). Alternative: line connecting two positions in an algorithmic way (limited by end points)."</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>The result of organisation, interpretation, categorisation, classification, or some other form of processing of Data attaching to it a certain meaning that can be understood by the addressee.</t>
+          <t>Line defined in an algorithmic way using at least two positions (can be open-ended). Alternative: line connecting two positions in an algorithmic way (limited by end points).</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>- Information depends on Data and is targeted.</t>
+          <t>- A Path is a 1-dimensional Place.</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
@@ -3961,19 +3951,19 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Temporal Consistency</t>
+          <t>Spatial Consistency</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>- core
-description: Condition where the temporal statistical properties of the sample depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
+description: Condition where the spatial statistical properties of the data depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Condition where the temporal statistical properties of the Sample depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
+          <t>Condition where the spatial statistical properties of the data depend only on the underlying physical processes and not on other factors such as fusing different products or sensors. Also, the validity of the assumptions of the procedure to produce information holds true across the whole spatial range.</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -4003,31 +3993,30 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Metadata</t>
+          <t>Cell</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>- core
-description: Data describing other data, providing an understanding of the content and utility of a product or collection.</t>
+- approved</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Data describing other data, providing an understanding of the content and utility of a product or collection.</t>
+          <t>Spatial, spatio-temporal zone or temporal unit of geometry with dimensionality greater than 0, associated with a zone.</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>- Metadata may be used to select data for a particular scientific investigation.
-- Metadata is intended as information describing significant aspects of a resource (Earth Observation space data in this context). They are created for the purposes of data search, discovery and access management and may exist at various levels, typically from data collection through to the individual variables of each product in a collection.</t>
+          <t>- Cells are the unit of geometry in a DGGS, and the geometry of the region of space-time occupied by a zone is a Cell.</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- ISO 19170:2021</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
@@ -4050,22 +4039,26 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Spatial Resolution</t>
+          <t>Business Continuity</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>- core
-description: ''</t>
+- approved</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>An organisation's readiness to continue functioning during times of disruption.</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
@@ -4088,26 +4081,31 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Phenomenon</t>
+          <t>Derivative Product</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>- base
-description: Entity with at least one Property referenced by an identifier.</t>
+          <t>- core
+description: Product additionally processed from baseline or unenhanced mission data.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Entity with at least one Property referenced by an identifier.</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr"/>
+          <t>Product additionally processed from baseline or unenhanced mission data.</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>- Generally either a compilation of time-series data (e.g., all time, annual, monthly or seasonal summary data, &gt; Level 3) or thematic versions of each individual data tile of baseline data.
+- Derived products are citable via a Digital Object Identifier (DOI).</t>
+        </is>
+      </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>- KCEO, modified after Wikipedia and the Columbia Encyclopaedia 2008</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
@@ -4130,26 +4128,26 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Geolocation Information</t>
+          <t>Policy Objective</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>- core
-description: Information used to determine geographic Location.</t>
+          <t>- high-impact
+description: Desired outcome that policymakers wish to achieve.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Information used to determine geographic Location.</t>
+          <t>Desired outcome that policymakers wish to achieve.</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>- ISO 19130-1:2018, 3.34</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
@@ -4172,57 +4170,62 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Verification</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>- core
-description: Provision of objective evidence that a given item fulfils specified requirements.</t>
+description: Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Provision of objective evidence that a given item fulfils specified requirements.</t>
+          <t>Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>- When applicable, measurement uncertainty should be taken into consideration.
-- The item may be, e.g. a Process, measurement procedure, material, compound, or measuring system.
-- The specified requirements may be, e.g. that a manufacturer's specifications are met.
-- Verification should not be confused with Calibration. Not every verification is a Validation.</t>
+          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>- ISO/IEC Guide 99:2007, 2.44</t>
+          <t>- ISO/TS 19101‑2:2008, 4.41</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Evaluation of whether or not a product, service, or system complies with a regulation requirement, specification, or imposed condition. Often an internal Process.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>Process aimed at verifying that the specified requirements are achieved or compliant. Involves comparing mission products with representative reference data, considering various observation conditions, ensuring the quality and traceability of the reference data used.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
+        </is>
+      </c>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
-          <t>- EU-US Land Imaging EO Collaboration</t>
+          <t>- BIPM; QA4EO; ESA?, modified</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Means to evaluate the reliability of the data in the absence of a reference dataset, allowing for an assessment of its standalone performance. Involves confirming the consistency and internal coherence of the data without direct comparison to external reference sources.</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr"/>
+          <t>Assurance that a product, service, or system meets the needs of the customer and other identified stakeholders. Often involves acceptance and suitability with external customers.</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
+        </is>
+      </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- EU-US Land Imaging EO Collaboration</t>
         </is>
       </c>
       <c r="P81" t="inlineStr"/>
@@ -4237,26 +4240,35 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Property</t>
+          <t>Temporal Extent</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>- base
-description: Observable Trait.</t>
+          <t>- core
+description: Period during which data was collected, observations were made, or for which the model was run.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Observable Trait.</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
+          <t>Period during which data was collected, observations were made, or for which the model was run.</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>- In W3C this is the definition of temporal coverage.
+- Time Period covered by a series of observations inclusive of the specified date/time indications (measurement history). Defined based on the beginning and end dates of observations.</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>- WIGOS Metadata</t>
+        </is>
+      </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Adapted from W3C</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
@@ -4279,26 +4291,26 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Object</t>
+          <t>Traceability</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>- base
-description: Entity with a well-defined boundary and identity that encapsulates state and behaviour.</t>
+          <t>- core
+description: Property of a measurement result whereby the result can be related to a reference through a documented unbroken chain of calibrations each contributing to the measurement uncertainty.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Entity with a well-defined boundary and identity that encapsulates state and behaviour.</t>
+          <t>Property of a measurement result whereby the result can be related to a Reference through a documented unbroken chain of calibrations, each contributing to the measurement uncertainty.</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>- ISO/IEC 19501:2005</t>
+          <t>- https://www.isobudgets.com/Measurement-traceability-complying-iso-17025-requirements/</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
@@ -4321,37 +4333,30 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Time of Day</t>
+          <t>Decommissioned Product</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>- core
-description: Time of the day at which the variable or parameter is observed or simulated by a model.</t>
+description: Products and collections that have been superseded by new versions and are no longer available.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Time of the day at which the variable or parameter is observed or simulated by a model.</t>
+          <t>Products and collections that have been superseded by new versions and are no longer available.</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>- In Remote Sensing it is also known as time of overpass.</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>| Type      | Entry format example | Valid unit |
-|-----------|----------------------|------------|
-| timestamp | 18:00 h (0–24)       | Hours      |
-| timerange | 18:00 – 20:00 h      | Hours      |</t>
-        </is>
-      </c>
+          <t>- Decommissioned products are no longer supported, i.e. corrections will not be made, new data will not be added, and support is not available.</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
@@ -4374,26 +4379,31 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Obsolete Product or Collection</t>
+          <t>Grid</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>- core
-description: Products or collections which have been superseded by later versions of a product or collection.</t>
+description: Network composed of two or more sets of curves in which the members of each set intersect the members of the other sets in an algorithmic way.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Products or collections which have been superseded by later versions of a product or collection.</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr"/>
+          <t>Network composed of two or more sets of curves in which the members of each set intersect the members of the other sets in an algorithmic way.</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>- The curves partition a space into grid cells or zones.
+- The intersection points of the curves are called nodes.</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- ISO 19123:2005, 4.1.23; Note 1 modified; Note 2 added</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
@@ -4416,40 +4426,36 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Baseline</t>
+          <t>Measurement</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Observation of a Quantity.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Reference Period, time or measure against which the Information is assessed or compared.</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr"/>
+          <t>Observation of a Quantity.</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>- The Process of collecting a measurement is called measuring.</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Source data that has been processed to a common set of requirements and organised into a form that allows immediate analysis and interoperability through time and with other collections.</t>
-        </is>
-      </c>
+          <t>- GEOGlos (VIM ?, modified)</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
-        </is>
-      </c>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
@@ -4466,31 +4472,30 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Earth Observation</t>
+          <t>Catalogue</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>- high-impact
-description: Science domain dealing with technologies and methods of collecting and analyzing observations about the different Earth spheres.</t>
+          <t>- core
+- approved</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Science domain dealing with technologies and methods of collecting and analyzing observations about the different Earth spheres.</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>- Earth Observation (EO) can be categorised by location of the sensor into space-borne, air-borne, sea-borne, ground-based, underwater and underground EO.
-- Earth Observation (EO) includes Remote Sensing, such as satellite imagery, as well as in-situ observations, e.g., with ground-based devices.</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr"/>
+          <t>System that provides users with discovery of information on which EO products can be obtained.</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>- A 'Product Catalogue' can organise products and collections with varying access levels depending on product and user type.</t>
+        </is>
+      </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>- Modified GEO definition [GEO (earthobservations.org)](https://earthobservations.org/resources#key)</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
@@ -4513,32 +4518,36 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Spectral Resolution</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>- core
-description: Measure of the ability to resolve features in the electromagnetic spectrum.</t>
+description: Phenomenon whose values for specific properties are known and understood with an Uncertainty significantly lower than that of the Observation with which it is compared.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Measure of the ability to resolve features in the electromagnetic spectrum.</t>
+          <t>Phenomenon whose values for specific properties are known and understood with an Uncertainty significantly lower (quantify?) than that of the Observation with which it is compared.</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Sort of data acquired with an Uncertainty significantly lower (quantify?) than that of the data it is being compared with.</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>- VIM?, modified</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
@@ -4555,26 +4564,30 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Near Real Time Data</t>
+          <t>Laboratory Observation</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>- high-impact
-description: Data available for use with a specified (small and application dependent) latency, typically 3 hours for meteorological applications.</t>
+          <t>- core
+description: Usually in-situ observations in which the Object or Phenomenon is isolated from other systems or altered in its original conditions or environment.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Data available for use with a specified (small and application dependent) latency, typically 3 hours for meteorological applications.</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr"/>
+          <t>Usually in-situ observations in which the Object or Phenomenon is isolated from other systems or altered in its original conditions or environment.</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>- It is important to consider that Laboratory Observations are typically conducted in controlled conditions, allowing for isolation or alteration of the Object or Phenomenon from its natural environment or other systems.</t>
+        </is>
+      </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
@@ -4597,38 +4610,32 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Measurand</t>
+          <t>Sample</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>- core
-description: Particular Quantity subject to Measurement.</t>
+          <t>- controversial
+description: Subset of one or more entities.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Particular Quantity subject to Measurement.</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>| Step | Process description |
-| :----- | :--------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------- |
-| (Raw) | The complete and unaltered/unprocessed set of Data acquired by one or several sensors on a platform |
-| M/0 uncalibrated | Unaltered/unprocessed Level 0 (main) Sensor Data annotated with processed Ancillary Data and supplemented by Auxiliary Data (including radiometric and geometric Calibration coefficients and geo-referencing parameters) allowing further processing to higher Levels. |
-| M/1 Sensor-calibrated | Level M/0 Sensor Data which have been calibrated (ideally traceable to SI) and spatially aligned (co-located, eventually co-gridded) to represent at-Sensor measurements (Value and Uncertainty) in Sensor nominal spatiotemporal sampling, supplemented by appropriate ancillary data. |
-| M/2 target-calibrated | Level M/1 Data processed to represent geophysical Property values (and uncertainties) for a specified target (Object, Feature of interest, e.g. surface reflectance, apparent temperature) derived from M/1 Sensor Data, as much as possible maintaining the sensors nominal spatial and temporal sampling (Observation preserving). |
-| M/3 homogenised | Level M/1 or M/2 Data which have been generalised and integrated across one or several platforms and acquisitions to achieve an increased, more regular or in any other form enhanced spatial or temporal coverage in which states geophysical values agnostic of the originally acquiring Sensor and Observation condition and thus directly comparable. This homogenisation and fusion may include measurand re-Calibration to external standards and references including use of modelling, aggregation and interpolation. |
-| M/4 derived/inferred | Model output or results from analyses of Level M/3 (or lower level) Data i.e., attributes that might not be directly observable by the Sensor(s) but are derived from observations in combination with other external incl. non-observational Data using techniques like modelling or machine learning (AI). |
-From http://doi.org/10.2760/46796</t>
-        </is>
-      </c>
+          <t>Subset of one or more entities.</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>- A Sample may be spatial, temporal, spectral, or in any other dimension or Trait.
+- Each Sample is contiguous, i.e. it does not consist of more than one discontinuous geometry in any dimension.
+- The Process of obtaining a Sample is called sampling.</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>- VIM: 1993, 2.6</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
@@ -4651,26 +4658,30 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Latency</t>
+          <t>Trait</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>- core
-description: Period between the end of sensing of a Phenomenon to the beginning of availability of a specific product.</t>
+          <t>- base
+description: Characteristic belonging to an entity and referenced by an identifier.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Period between the end of sensing of a Phenomenon to the beginning of availability of a specific product.</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr"/>
+          <t>Characteristic belonging to an entity and referenced by an identifier.</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>- Traits can be objective (inherent?) in which case they are also observable and called properties. Traits which are not observable (directly or indirectly) need to be assigned.</t>
+        </is>
+      </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>- ?</t>
+          <t>- Based on ISO 19143:2010, 4.21, ISO/IEC 2382:2015, 2121440, significantly modified, Note 1 added</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
@@ -4693,26 +4704,31 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Policy Target</t>
+          <t>Metadata</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>- high-impact
-description: Specific level or rate set for the Policy Objective.</t>
+          <t>- core
+description: Data describing other data, providing an understanding of the content and utility of a product or collection.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Specific level or rate set for the Policy Objective.</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr"/>
+          <t>Data describing other data, providing an understanding of the content and utility of a product or collection.</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>- Metadata may be used to select data for a particular scientific investigation.
+- Metadata is intended as information describing significant aspects of a resource (Earth Observation space data in this context). They are created for the purposes of data search, discovery and access management and may exist at various levels, typically from data collection through to the individual variables of each product in a collection.</t>
+        </is>
+      </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
@@ -4735,26 +4751,30 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Policy Objective</t>
+          <t>Backup</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>- high-impact
-description: Desired outcome that policymakers wish to achieve.</t>
+          <t>- core
+- approved</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Desired outcome that policymakers wish to achieve.</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr"/>
+          <t>General practice of making copies of current baseline and derived products of EO Collections at specified time intervals, and storing those copies in a manner that will not affect the data if the primary distribution environment is compromised.</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>- The emphasis is on the ability to retrieve a copy of the entire EO Collection on demand if the original data is lost or compromised.</t>
+        </is>
+      </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
@@ -4777,26 +4797,30 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Forecast Range</t>
+          <t>Archive</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>- core
-description: The forecast period.</t>
+- approved</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>The forecast period.</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr"/>
+          <t>System that stores data products, guaranteeing their preservation for future use.</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>- This function includes all operations to identify, store and retrieve the data and ensure their integrity.</t>
+        </is>
+      </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
@@ -4819,26 +4843,26 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Quality Indicator</t>
+          <t>Biosphere</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>- core
-description: Indicator providing sufficient information to allow all users to readily evaluate the fitness for purpose of the data or derived product.</t>
+- approved</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Indicator providing sufficient information to allow all users to readily evaluate the fitness for purpose of the data or derived product. May be a number, set of numbers, graph, Uncertainty budget, or a simple flag.</t>
+          <t>Masses of living organisms, such as vegetation and animals, including dead but still connected parts such as roots, trunks or branches.</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>- CEOS Wiki</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
@@ -4861,26 +4885,26 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>User Interface</t>
+          <t>Impact</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>- core
-description: Set of all the components of an interactive system that provide information and controls for the user to accomplish specific tasks with the interactive system.</t>
+description: Regarded long-term according to X. However, in the Horizon Europe Missions terminology, regarded short-term.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Set of all the components of an interactive system that provide information and controls for the User to accomplish specific tasks with the interactive system.</t>
+          <t>Regarded long-term according to X. However, in the Horizon Europe Missions terminology, regarded short-term.</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>- ISO 9241-110:2020, 3.10</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
@@ -4903,30 +4927,26 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Obsolete Product or Collection</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>- core
-description: Maximum acceptable change in Uncertainty per decade.</t>
+description: Products or collections which have been superseded by later versions of a product or collection.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Maximum acceptable change in Uncertainty per decade.</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>- GCOS uses bias or systematic errors instead of Uncertainty.</t>
-        </is>
-      </c>
+          <t>Products or collections which have been superseded by later versions of a product or collection.</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>- Modified from GCOS 2022</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
@@ -4949,26 +4969,26 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Classification System</t>
+          <t>Measurement Uncertainty</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Uncertainty associated with the method of Measurement.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Nomenclature used to classify Information into categorical thematic classes (e.g., EUNIS, MAES ecosystems, Corine Land Cover, LCCS).</t>
+          <t>Uncertainty associated with the method of Measurement.</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- CEOS Wiki adopted from JCGM GUM</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
@@ -4991,21 +5011,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Spatial Consistency</t>
+          <t>Spatial Resolution</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>- core
-description: Condition where the spatial statistical properties of the data depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
+description: ''</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Condition where the spatial statistical properties of the data depend only on the underlying physical processes and not on other factors such as fusing different products or sensors. Also, the validity of the assumptions of the procedure to produce information holds true across the whole spatial range.</t>
-        </is>
-      </c>
+      <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
@@ -5033,22 +5049,27 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Expanded Uncertainty</t>
+          <t>In-Situ Observation</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>- core
-description: Standard Uncertainty multiplied by a coverage factor k, chosen to obtain a desired level of confidence.</t>
+          <t>- controversial
+description: Observations performed in the same Place where a Phenomenon occurs, normally without isolating it from other systems or altering its pre-Observation state.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Standard Uncertainty multiplied by a coverage factor, k. The coverage factor is chosen to obtain a desired level of confidence. Most commonly a 95% confidence interval is chosen. For a Gaussian distribution, this is achieved with a coverage factor k = 2. (Note that strictly this provides a 95.45% confidence interval.)</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr"/>
+          <t>Observations performed in the same Place where a Phenomenon occurs, normally without isolating it from other systems (its environment) or altering its pre-Observation state.</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>- The main Characteristic of such observations is that distance has no or only negligible (within Uncertainty) influence on the Value of the Property observed. In-Situ Observations therefore often require either direct physical contact or small distances between a Sensor and the observed Phenomenon.
+- Observations not fulfilling these conditions are considered Remote Sensing.</t>
+        </is>
+      </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
@@ -5075,29 +5096,28 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Earth Observation Product</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>- core
-description: Device or instrument suited (through physical/chemical interaction) to measure one or more properties of a Phenomenon and thus collect factual/objective data.</t>
+description: Direct output from standardized satellite data processing chains (indicative levels 2 and 3), representing fundamental geophysical and biophysical variables.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Device or instrument suited (through physical/chemical interaction) to measure one or more properties of a Phenomenon and thus collect factual/objective data.</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>- Sensing is therefore a synonym for Observation (the Process).
-- As by their definition, sensors perform sampling.
-- Sensors used to obtain measurements must be calibrated and provide uncertainties.</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr"/>
+          <t>Direct output from standardized satellite data processing chains (indicative levels 2 and 3), representing fundamental geophysical and biophysical variables. These products demonstrate direct Traceability to original satellite measurements through rigorous Calibration and Validation processes. The processing methodology prioritizes the conversion of raw sensor data into quantifiable physical measurements, maintaining strict adherence to standardized processing protocols and Validation requirements.</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>- Soil moisture from microwave sensors
+- Forest canopy height from LiDAR data</t>
+        </is>
+      </c>
       <c r="G101" t="inlineStr">
         <is>
           <t>- KCEO</t>
@@ -5123,26 +5143,30 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Minimum Mapping Width</t>
+          <t>Spatial Completeness</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>- core
-description: The width of the smallest linear Feature that is still represented on a map.</t>
+description: Presence or absence of gaps, which are missing values in an otherwise continuous spatial data series.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>The width of the smallest linear Feature that is still represented on a map.</t>
+          <t>Presence or absence of gaps, which are missing values in an otherwise continuous spatial data series.</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>- Surface soil moisture retrieved from microwave satellite sensors may present gaps in mountainous terrains.</t>
+        </is>
+      </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>- CGLS</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
@@ -5165,30 +5189,30 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Backup</t>
+          <t>Geocoding</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Translation of one form of Location into another.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>General practice of making copies of current baseline and derived products of EO Collections at specified time intervals, and storing those copies in a manner that will not affect the data if the primary distribution environment is compromised.</t>
+          <t>Translation of one form of Location into another.</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>- The emphasis is on the ability to retrieve a copy of the entire EO Collection on demand if the original data is lost or compromised.</t>
+          <t>- Geocoding usually refers to the translation of "address" or "intersection" to "direct Position." Many service providers also include a "reverse geocoding" interface to their geocoder, thus extending the definition of the service as a general translator of Location. Because routing services use internal Location encodings not usually available to others, a geocoder is an integral part of the internals of such a service.</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- ISO 19133:2005; https://www.iso.org/standard/32551.html</t>
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
@@ -5211,42 +5235,44 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Temporal Resolution</t>
+          <t>Georectifying</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>- core
-description: Observation or model output representing regular intervals, specifying the length of the interval that determines the smallest event or process that can be resolved.</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr"/>
+description: Correcting for positional displacement with respect to the surface of the Earth.</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Orthorectifying</t>
+        </is>
+      </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Observation or model output representing regular intervals, specifying the length of the interval that determines the smallest event or Process that can be resolved (e.g., the Period between observations, the time steps in a model).</t>
+          <t>Correcting for positional displacement with respect to the surface of the Earth.</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>- WIGOS 2019 distinguishes between sampling time Period, as the Period over which a Measurement is taken, and temporal sampling interval as the time Period between the beginning of consecutive sampling periods. Temporal Resolution in this Glossary is equivalent to sampling time Period as used by WIGOS.</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>| Entry format example | Valid unit                     |
-|----------------------|-------------------------------|
-| 1 s, 2 h, 1 m        | second, hour, day, month, year |</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr"/>
+          <t>- Source: ISO 19115-2:2019, 3.11; ISO 19115-2:2009(E); https://www.iso.org/standard/67039.html, modified</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>The correction of sample locations to achieve some sort of geometric regularity, e.g., a regular 2D geographic grid.</t>
+        </is>
+      </c>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
@@ -5263,26 +5289,26 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Place</t>
+          <t>Data Licencing</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>- base
-description: Part of any space referenced by an identifier.</t>
+          <t>- core
+description: Legal instrument by which a copyright holder may grant rights over the protected work.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Part of any space referenced by an identifier.</t>
+          <t>Legal instrument by which a copyright holder may grant rights over the protected work. Data and content is open if it is subject to an explicitly-applied licence that conforms to the Open Definition. A range of standard open licences are available, such as the Creative Commons CC-BY licence, which requires only attribution.</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>- ISO 19155:2012, 4.8</t>
+          <t>- CEOS Wiki</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
@@ -5305,45 +5331,36 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Ancillary Data</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>- core
-- approved</t>
+          <t>- base
+description: Particular era or span of time.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Data acquired on the same platform but not obtained from the main Sensor itself (usually provided as part of Level 0 Data), with the primary purpose of serving the processing of main instrument Data (e.g. Position and velocity of platform).</t>
+          <t>Particular era or span of time.</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>This can be divided into data referred to as spacecraft 'engineering', 'core housekeeping' or 'subsystem' data obtained from other parts of the platform, and includes parameters such as orbit position and velocity, attitude and its range of change, time, temperatures, pressures, jet firings, water dumps, internally produced magnetic fields, and other environmental measurements. Ancillary refers to data that exist purely to serve the data processing.</t>
+          <t>- Periods are intervals named with a Period Identifier.</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>- ESA/CEOS?, modified
-- EO Data Stewardship Glossary</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Data other than instrument measurements, originating in the instrument itself or from the satellite, required to perform processing of the Data. Includes orbit Data, attitude Data, time Information, and spacecraft engineering Data, Calibration Data, Data quality Information, and Data from other instruments or earth system models.</t>
-        </is>
-      </c>
+          <t>- ISO 19170:2021</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>- CEOS-ARD PFS template 20220302</t>
-        </is>
-      </c>
+      <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
@@ -5360,31 +5377,26 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Collection Upgrade</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>- controversial
-description: Act of determining the Value of a Property by interacting in a reproducible way with the Phenomenon using a Sensor.</t>
+          <t>- core
+- approved</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Act of determining the Value of a Property by interacting in a reproducible way with the Phenomenon using a Sensor.</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>- The result of an Observation is a Value complemented by an Uncertainty, often itself being referred to as 'observation'.
-- An Observation result represents a Sample of the Phenomenon (otherwise it would be identical with the Phenomenon).</t>
-        </is>
-      </c>
+          <t>New and improved major version of all products within a collection due to comprehensive reprocessing.</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
@@ -5407,31 +5419,30 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Grid</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>- core
-description: Network composed of two or more sets of curves in which the members of each set intersect the members of the other sets in an algorithmic way.</t>
+          <t>- base
+description: Abstraction of real-world phenomena.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Network composed of two or more sets of curves in which the members of each set intersect the members of the other sets in an algorithmic way.</t>
+          <t>Abstraction of real-world phenomena.</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>- The curves partition a space into grid cells or zones.
-- The intersection points of the curves are called nodes.</t>
+          <t>- A feature may occur as a type or an instance.</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>- ISO 19123:2005, 4.1.23; Note 1 modified; Note 2 added</t>
+          <t>- ISO 19101-1:2014, 4.1.11, modified</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
@@ -5454,44 +5465,36 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>Custodian</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>- core
-description: Entity (person, organization, institution, etc.) that is requesting data or information with certain characteristics described by needs and/or requirements.</t>
+description: Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>In the context of the KCEO, entity (person, organization, institution, etc.) that is requesting data or information with certain characteristics described by needs and/or requirements.</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr"/>
+          <t>Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>- See also Steward.</t>
+        </is>
+      </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>External person, institution or system that consumes provided services.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>- Includes Data Access or Science and Service Exploitation Platforms provided by a payload data ground segment.</t>
-        </is>
-      </c>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
       <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>- EO Data Stewardship Glossary</t>
-        </is>
-      </c>
+      <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
@@ -5508,35 +5511,26 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Remote Sensing</t>
+          <t>Anthroposphere</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>- controversial
-description: Type of Observation performed at a significant distance from a Phenomenon.</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Remote Observation</t>
-        </is>
-      </c>
+          <t>- core
+- approved</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Type of Observation performed at a significant distance from a Phenomenon.</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>- 'Significant' in this context means that the distance has, or may have, a non-negligible impact on the Value of the Property observed.
-- The effect of the distance on the acquired data is the main distinction criterion between 'remote' and 'in-situ' observations.</t>
-        </is>
-      </c>
+          <t>One of the Earth spheres consisting predominantly of matter processed by humans, such as construction wood, bricks, concrete, asphalt, glass, or plastics.</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
@@ -5559,37 +5553,44 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Earth Observation Product</t>
+          <t>User</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>- core
-description: Direct output from standardized satellite data processing chains (indicative levels 2 and 3), representing fundamental geophysical and biophysical variables.</t>
+description: Entity (person, organization, institution, etc.) that is requesting data or information with certain characteristics described by needs and/or requirements.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Direct output from standardized satellite data processing chains (indicative levels 2 and 3), representing fundamental geophysical and biophysical variables. These products demonstrate direct Traceability to original satellite measurements through rigorous Calibration and Validation processes. The processing methodology prioritizes the conversion of raw sensor data into quantifiable physical measurements, maintaining strict adherence to standardized processing protocols and Validation requirements.</t>
+          <t>In the context of the KCEO, entity (person, organization, institution, etc.) that is requesting data or information with certain characteristics described by needs and/or requirements.</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>- Soil moisture from microwave sensors
-- Forest canopy height from LiDAR data</t>
-        </is>
-      </c>
+      <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
           <t>- KCEO</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>External person, institution or system that consumes provided services.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>- Includes Data Access or Science and Service Exploitation Platforms provided by a payload data ground segment.</t>
+        </is>
+      </c>
       <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>- EO Data Stewardship Glossary</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
@@ -5606,30 +5607,30 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Trait</t>
+          <t>Steward</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>- base
-description: Characteristic belonging to an entity and referenced by an identifier.</t>
+          <t>- core
+description: Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Characteristic belonging to an entity and referenced by an identifier.</t>
+          <t>Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>- Traits can be objective (inherent?) in which case they are also observable and called properties. Traits which are not observable (directly or indirectly) need to be assigned.</t>
+          <t>- See also Custodian.</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>- Based on ISO 19143:2010, 4.21, ISO/IEC 2382:2015, 2121440, significantly modified, Note 1 added</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
@@ -5652,30 +5653,23 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Time of Year</t>
+          <t>Temporal Consistency</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>- core
-description: Time of the year at which the variable is observed or simulated by a model.</t>
+description: Condition where the temporal statistical properties of the sample depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Time of the year at which the variable is observed or simulated by a model.</t>
+          <t>Condition where the temporal statistical properties of the Sample depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>| Type      | Entry format example | Valid unit     |
-|-----------|----------------------|----------------|
-| timestamp | m/d                  | Not Applicable |
-| timerange | m/d - m/d            | Not Applicable |</t>
-        </is>
-      </c>
+      <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
           <t>- KCEO</t>
@@ -5701,31 +5695,27 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>In-Situ Observation</t>
+          <t>Geospatial Data</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>- controversial
-description: Observations performed in the same Place where a Phenomenon occurs, normally without isolating it from other systems or altering its pre-Observation state.</t>
+          <t>- core
+description: Data consisting of, derived from, or relating to information that is directly linked to specific geographical locations.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Observations performed in the same Place where a Phenomenon occurs, normally without isolating it from other systems (its environment) or altering its pre-Observation state.</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>- The main Characteristic of such observations is that distance has no or only negligible (within Uncertainty) influence on the Value of the Property observed. In-Situ Observations therefore often require either direct physical contact or small distances between a Sensor and the observed Phenomenon.
-- Observations not fulfilling these conditions are considered Remote Sensing.</t>
-        </is>
-      </c>
+          <t>Data consisting of, derived from, or relating to information that is directly linked to specific geographical locations.</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- https://www.merriam-webster.com/dictionary/geospatial
+- https://isotc211.geolexica.org/Concepts/202/, accessed 20221010</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
@@ -5748,56 +5738,36 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Characteristic</t>
+          <t>Stability</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>- base
-- approved</t>
+          <t>- core
+description: Maximum acceptable change in Uncertainty per decade.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Distinguishing Feature.</t>
+          <t>Maximum acceptable change in Uncertainty per decade.</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>- A Characteristic can be inherent or assigned.
-- A Characteristic can be qualitative or quantitative.
-- There are various classes of Characteristics, such as the following:
-  - physical (e.g. mechanical, electrical, chemical, biological);
-  - sensory (e.g. relating to smell, touch, taste, sight, hearing);
-  - behavioural (e.g. courtesy, honesty, veracity);
-  - temporal (e.g. punctuality, reliability, availability);
-  - ergonomic (e.g. physiological characteristic or related to human safety);
-  - functional (e.g. maximum speed of an aircraft).</t>
+          <t>- GCOS uses bias or systematic errors instead of Uncertainty.</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>- ISO 9000:2005, 3.5.1</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Abstraction of a Property of an Object or of a set of objects.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>- Characteristics are used for describing Concepts.</t>
-        </is>
-      </c>
+          <t>- Modified from GCOS 2022</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>- ISO 1087-1:2000, 3.2.4; ISO 19146:2010(E); https://www.iso.org/standard/20057.html</t>
-        </is>
-      </c>
+      <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
@@ -5814,30 +5784,26 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Measurement</t>
+          <t>Property</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>- core
-description: Observation of a Quantity.</t>
+          <t>- base
+description: Observable Trait.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Observation of a Quantity.</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>- The Process of collecting a measurement is called measuring.</t>
-        </is>
-      </c>
+          <t>Observable Trait.</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>- GEOGlos (VIM ?, modified)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
@@ -5860,31 +5826,30 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Preservation</t>
+          <t>Geographic Data</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>- core
-description: Processes and operations used to ensure data technical and intellectual survival through time.</t>
+description: Data with implicit or explicit reference to a Location relative to the Earth.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Processes and operations used to ensure data technical and intellectual survival through time.</t>
+          <t>Data with implicit or explicit reference to a Location relative to the Earth.</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>- Grants data integrity, discoverability and accessibility, and facilitates its (re-)use in the long term.
-- Preservation is one of the tasks of data curation.</t>
+          <t>- Geographic Information is also used as a term for information concerning phenomena implicitly or explicitly associated with a Location relative to the Earth.</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- ISO 19109:2015, 4.13; ISO 19109:2005</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
@@ -5907,62 +5872,111 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Provisional Product</t>
+          <t>Uncertainty</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>- core
-description: Products in a research and development phase not yet published into a standardized collection.</t>
+description: Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Products in a research and development phase not yet published into a standardized collection.</t>
+          <t>Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
+          <t>- GUM</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Non-negative parameter, associated with data, which characterizes the dispersion of the values of a Trait that could reasonably be attributed to a Phenomenon by means of sensing or modelling.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>- In case of quantitative (continuous) data the uncertainty may be, for example, a standard deviation (or a given multiple of it), or the half-width of an interval having a stated level of confidence (see e.g. Standard and Expanded Uncertainty).
+- For qualitative (categorical?) data, uncertainty may be expressed by commission and omission ('confusion matrix') or overall errors.</t>
+        </is>
+      </c>
       <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>- Modified from GUM, VIM4:3.1, FIDUCEO, Notes added</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Measure of the spread of the distribution of possible values.</t>
+        </is>
+      </c>
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
-      <c r="O118" t="inlineStr"/>
-      <c r="P118" t="inlineStr"/>
-      <c r="Q118" t="inlineStr"/>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>- [FIDUCEO Glossary](https://research.reading.ac.uk/fiduceo/glossary/), VIM?, modified</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Parameter, associated with the result of measurement, that characterizes the dispersion of values that could reasonably be attributed to the measurand.</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>- When the quality of accuracy or precision of measured values, such as coordinates, is to be characterized quantitatively, the quality parameter is an estimate of the uncertainty of the measurement results. Because accuracy is a qualitative concept, one should not use it quantitatively, that is associate numbers with it; numbers should be associated with measures of uncertainty instead.</t>
+        </is>
+      </c>
       <c r="R118" t="inlineStr"/>
-      <c r="S118" t="inlineStr"/>
-      <c r="T118" t="inlineStr"/>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>- ISO 19116:2004(E)</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Parameter characterizing the dispersion of the values being attributed to a measurand, based on the information used.</t>
+        </is>
+      </c>
       <c r="U118" t="inlineStr"/>
       <c r="V118" t="inlineStr"/>
-      <c r="W118" t="inlineStr"/>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>- VIM4: 3.1</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>User Interface</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>- core
-description: ""</t>
+description: Set of all the components of an interactive system that provide information and controls for the user to accomplish specific tasks with the interactive system.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Set of all the components of an interactive system that provide information and controls for the User to accomplish specific tasks with the interactive system.</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>- ISO 9241-110:2020, 3.10</t>
+        </is>
+      </c>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
@@ -5983,36 +5997,56 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Instrument Data</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>- high-impact
-description: Deliberate system of guidelines to guide decisions and achieve rational outcomes, implemented as a procedure or protocol and typically promulgated through official written documents.</t>
+          <t>- core
+description: Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Deliberate system of guidelines to guide decisions and achieve rational outcomes. Statement of intent implemented as a procedure or protocol. Typically promulgated through official written documents.</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>- These data consist of instrument science and engineering data, and possibly ancillary data. Instrument engineering data is produced by engineering sensor(s) of an instrument, used either for operating the instrument or for processing the science data generated by the instrument. Instrument science data is produced by the science sensor(s) of an instrument, usually constituting the basic reason for existence of an instrument.</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr"/>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Data created by an instrument including scientific measurements and any engineering or ancillary data which may be included in the data packets.</t>
+        </is>
+      </c>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Data produced and transmitted by the science and engineering sensors of an instrument, and, in the spacecraft environment, any additional data packaged with the instrument's sensor data by virtue of services provided.</t>
+        </is>
+      </c>
       <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr"/>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr"/>
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr"/>
@@ -6025,30 +6059,38 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Geographic Identifier</t>
+          <t>Measurand</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>- core
-description: Spatial reference in the form of a label or code that identifies a Location.</t>
+description: Particular Quantity subject to Measurement.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Spatial reference in the form of a label or code that identifies a Location.</t>
+          <t>Particular Quantity subject to Measurement.</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>- "Spain" is an example of a label (country name); "SW1-3AD" is an example of a code (postcode).</t>
+          <t>| Step | Process description |
+| :----- | :--------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------- |
+| (Raw) | The complete and unaltered/unprocessed set of Data acquired by one or several sensors on a platform |
+| M/0 uncalibrated | Unaltered/unprocessed Level 0 (main) Sensor Data annotated with processed Ancillary Data and supplemented by Auxiliary Data (including radiometric and geometric Calibration coefficients and geo-referencing parameters) allowing further processing to higher Levels. |
+| M/1 Sensor-calibrated | Level M/0 Sensor Data which have been calibrated (ideally traceable to SI) and spatially aligned (co-located, eventually co-gridded) to represent at-Sensor measurements (Value and Uncertainty) in Sensor nominal spatiotemporal sampling, supplemented by appropriate ancillary data. |
+| M/2 target-calibrated | Level M/1 Data processed to represent geophysical Property values (and uncertainties) for a specified target (Object, Feature of interest, e.g. surface reflectance, apparent temperature) derived from M/1 Sensor Data, as much as possible maintaining the sensors nominal spatial and temporal sampling (Observation preserving). |
+| M/3 homogenised | Level M/1 or M/2 Data which have been generalised and integrated across one or several platforms and acquisitions to achieve an increased, more regular or in any other form enhanced spatial or temporal coverage in which states geophysical values agnostic of the originally acquiring Sensor and Observation condition and thus directly comparable. This homogenisation and fusion may include measurand re-Calibration to external standards and references including use of modelling, aggregation and interpolation. |
+| M/4 derived/inferred | Model output or results from analyses of Level M/3 (or lower level) Data i.e., attributes that might not be directly observable by the Sensor(s) but are derived from observations in combination with other external incl. non-observational Data using techniques like modelling or machine learning (AI). |
+From http://doi.org/10.2760/46796</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>- ISO 19112:2019, 3.1.2</t>
+          <t>- VIM: 1993, 2.6</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
@@ -6071,37 +6113,26 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Earth Spheres</t>
+          <t>Policy Target</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>- core
-description: Spheres dividing planet Earth into subsystems, which are collectives of (physical) matter sharing specific traits.</t>
+          <t>- high-impact
+description: Specific level or rate set for the Policy Objective.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Spheres dividing planet Earth into subsystems, which are collectives of (physical) matter sharing specific traits.</t>
+          <t>Specific level or rate set for the Policy Objective.</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>- Atmosphere
-- Hydrosphere
-- Cryosphere
-- Biosphere
-- Lithosphere
-- Anthroposphere</t>
-        </is>
-      </c>
+      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>- Hugget, R., et al., 2024, DOI: 10.1177/03091333241275465
-- Guth, P., et al., 2021, https://doi.org/10.3390/rs13183581
-- Martin, Y.E., et al., 2012</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
@@ -6124,26 +6155,35 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Deprecated Product</t>
+          <t>Spatial Extent</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>- core
-description: Products and collections that have been superseded by a newer version and are still available, but whose use is discouraged since they will be decommissioned in the future.</t>
+description: Zone or region of space described by a geographic identifier in the form of a label or code, or by a bounding box, representing the maximum spatial boundary within which the user is requesting data.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Products and collections that have been superseded by a newer version and are still available, but whose use is discouraged since they will be decommissioned in the future.</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
+          <t>Zone or region of space described by a geographic identifier in the form of a label or code, or by a bounding box. Represents the maximum extent (the spatial boundary or limits) within which the User is requesting data.
+The attribute represents the maximum spatial extent of the AOI, and in case the AOI is made of many discontinuous zones then it represents the maximum extent of the union of all the zones.</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>- WIGOS metadata standard defines it as the typical spatial georeferenced volume covered by the observations.</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>- If a User is requesting information about degradation of African protected sites, then the AOIs are the protected sites, and the spatial extent is the African continent.</t>
+        </is>
+      </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- Adapted from ISO 19170-1:2021</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
@@ -6166,26 +6206,26 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Replicability</t>
+          <t>Provisional Product</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>- core
-description: Property enabling other researchers to conduct an independent study with different data and similar but not identical methods, yet arriving at results that confirm the original study's hypothesis.</t>
+description: Products in a research and development phase not yet published into a standardized collection.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Property enabling other researchers to conduct an independent study with different data and similar but not identical methods, yet arriving at results that confirm the original study's hypothesis.</t>
+          <t>Products in a research and development phase not yet published into a standardized collection.</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>- Craglia, M., et al. (2018).</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
@@ -6208,30 +6248,26 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>- base
-description: Abstraction of real-world phenomena.</t>
+description: Entity with a well-defined boundary and identity that encapsulates state and behaviour.</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Abstraction of real-world phenomena.</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>- A feature may occur as a type or an instance.</t>
-        </is>
-      </c>
+          <t>Entity with a well-defined boundary and identity that encapsulates state and behaviour.</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>- ISO 19101-1:2014, 4.1.11, modified</t>
+          <t>- ISO/IEC 19501:2005</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
@@ -6254,30 +6290,26 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Final Product Version</t>
+          <t>Forecast Range</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>- core
-description: Product within an EO Collection that is not expected to be updated.</t>
+description: The forecast period.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Product within an EO Collection that is not expected to be updated.</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>- In its production, all of the prerequisite auxiliary data were used as input.</t>
-        </is>
-      </c>
+          <t>The forecast period.</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
@@ -6300,35 +6332,26 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Spatial Extent</t>
+          <t>Policy Milestone</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>- core
-description: Zone or region of space described by a geographic identifier in the form of a label or code, or by a bounding box, representing the maximum spatial boundary within which the user is requesting data.</t>
+          <t>- high-impact
+description: Markers of significant progress in addressing specific issues, or crucial decision points where significant choices are made within a policy process.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Zone or region of space described by a geographic identifier in the form of a label or code, or by a bounding box. Represents the maximum extent (the spatial boundary or limits) within which the User is requesting data.
-The attribute represents the maximum spatial extent of the AOI, and in case the AOI is made of many discontinuous zones then it represents the maximum extent of the union of all the zones.</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>- WIGOS metadata standard defines it as the typical spatial georeferenced volume covered by the observations.</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>- If a User is requesting information about degradation of African protected sites, then the AOIs are the protected sites, and the spatial extent is the African continent.</t>
-        </is>
-      </c>
+          <t>Markers of significant progress in addressing specific issues, or crucial decision points where significant choices are made. Concrete examples include: policy planning and proposing, impact assessment, implementation, or implementation cycles (e.g., Water Framework Directive, Marine Strategy Framework Directive), achievement of Policy Objectives and Policy Targets, and evaluating and improving existing laws.</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>- Adapted from ISO 19170-1:2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
@@ -6351,26 +6374,30 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Policy Cycle</t>
+          <t>Dwell Time</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>- high-impact
-description: Well-established concept typically taught as the rational model of policy decision-making, representing an idealised view of the policy process.</t>
+          <t>- core
+description: Time that an antenna beam spends on a target.</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Well-established concept, typically taught as the rational model of policy decision-making. Idealised view of the policy process.</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr"/>
+          <t>Time that an antenna beam spends on a target.</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>- In the context of radar sensing.</t>
+        </is>
+      </c>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>- [ESA/CEOS?, modified](https://digital-strategy.ec.europa.eu/en/library/quality-public-administration-toolbox-practitioners)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
@@ -6393,26 +6420,26 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Data Licencing</t>
+          <t>Location Error</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>- core
-description: Legal instrument by which a copyright holder may grant rights over the protected work.</t>
+description: Measure of the agreement between the represented Location of an Object and the true Location.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Legal instrument by which a copyright holder may grant rights over the protected work. Data and content is open if it is subject to an explicitly-applied licence that conforms to the Open Definition. A range of standard open licences are available, such as the Creative Commons CC-BY licence, which requires only attribution.</t>
+          <t>Measure of the agreement between the represented Location of an Object and the true Location.</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>- CEOS Wiki</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
@@ -6435,26 +6462,22 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Representativeness</t>
+          <t>Expanded Uncertainty</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>- core
-description: Quality or characteristic of a measurement or observation to accurately represent a specific geographic location, time period, or environmental condition.</t>
+description: Standard Uncertainty multiplied by a coverage factor k, chosen to obtain a desired level of confidence.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Quality or characteristic of a measurement or Observation to accurately represent a specific geographic location, time Period, or environmental condition.</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>- WIGOS metadata standard defines representativeness as the extent of the region around the Observation of which it is representative.</t>
-        </is>
-      </c>
+          <t>Standard Uncertainty multiplied by a coverage factor, k. The coverage factor is chosen to obtain a desired level of confidence. Most commonly a 95% confidence interval is chosen. For a Gaussian distribution, this is achieved with a coverage factor k = 2. (Note that strictly this provides a 95.45% confidence interval.)</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
@@ -6481,28 +6504,20 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Reproducibility</t>
+          <t>Environmental Process</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>- core
-description: Concerned with the validity of the results of a particular study, enabling readers to check whether results have been manipulated by reproducing exactly the same study using the same data and methods.</t>
+description: ""</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>Concerned with the validity of the results of a particular study, i.e., the possibility for readers to check whether results have been manipulated, by reproducing exactly the same study using the same data and methods.</t>
-        </is>
-      </c>
+      <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>- Ostermann and Granell (2015)</t>
-        </is>
-      </c>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr"/>
@@ -6523,30 +6538,30 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Custodian</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>- core
-description: Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
+          <t>- controversial
+description: An, often numeric, theoretical (or otherwise abstract) representation of an Entity intended to generate Data describing one or more of its traits.</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
+          <t>An, often numeric, theoretical (or otherwise abstract) representation of an Entity intended to generate Data describing one or more of its traits (as a result of pre-set conditions).</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>- See also Steward.</t>
+          <t>- The Process of generating Data using a model is called modelling.</t>
         </is>
       </c>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
@@ -6569,26 +6584,26 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Geosphere</t>
+          <t>Classification System</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>- core
-description: The masses of minerals that constitute planet Earth.</t>
+- approved</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>The masses of minerals that constitute planet Earth.</t>
+          <t>Nomenclature used to classify Information into categorical thematic classes (e.g., EUNIS, MAES ecosystems, Corine Land Cover, LCCS).</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
@@ -6611,30 +6626,26 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Cell</t>
+          <t>Spectral Bandwidth</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Range of the Spectral Band.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Spatial, spatio-temporal zone or temporal unit of geometry with dimensionality greater than 0, associated with a zone.</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>- Cells are the unit of geometry in a DGGS, and the geometry of the region of space-time occupied by a zone is a Cell.</t>
-        </is>
-      </c>
+          <t>Range of the Spectral Band.</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>- ISO 19170:2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
@@ -6657,30 +6668,26 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Geographic Coordinate Reference System</t>
+          <t>Collection</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>- core
-description: Coordinate Reference System (CRS) that has a geodetic Reference frame and an ellipsoidal coordinate system.</t>
+- approved</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Coordinate Reference System (CRS) that has a geodetic Reference frame and an ellipsoidal coordinate system.</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>- Also known as geographic CRS.</t>
-        </is>
-      </c>
+          <t>Group of products that have been processed using a consistent radiometric calibration, geometric registration base, data/metadata format, and version of processing algorithms.</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>- ISO 19111:2019, 3.1.35</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
@@ -6703,29 +6710,23 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Vertical Levels</t>
+          <t>Policy File</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>- core
-description: Levels of a vertical discretization, e.g. pressure levels in an atmospheric model reanalysis or height levels in a forest biomass EO product.</t>
+          <t>- high-impact
+description: Policy documents that represent the official written reference for a given Policy.</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Levels of a vertical discretization. Examples may be pressure levels in an atmospheric model reanalysis or height levels in a forest biomass EO product.</t>
+          <t>Policy documents that represent the official written reference for a given Policy.</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>| Entry format example                | Valid unit           |
-|------------------------------------|----------------------|
-| 1, 5, 10 meter; 1000, 850, 500 hPa | meter, hPa, unitless |</t>
-        </is>
-      </c>
+      <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
           <t>- KCEO</t>
@@ -6751,26 +6752,26 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Anthroposphere</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>- core
-- approved</t>
+          <t>- high-impact
+description: Deliberate system of guidelines to guide decisions and achieve rational outcomes, implemented as a procedure or protocol and typically promulgated through official written documents.</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>One of the Earth spheres consisting predominantly of matter processed by humans, such as construction wood, bricks, concrete, asphalt, glass, or plastics.</t>
+          <t>Deliberate system of guidelines to guide decisions and achieve rational outcomes. Statement of intent implemented as a procedure or protocol. Typically promulgated through official written documents.</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
@@ -6793,30 +6794,30 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Dwell Time</t>
+          <t>Geographic Identifier</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>- core
-description: Time that an antenna beam spends on a target.</t>
+description: Spatial reference in the form of a label or code that identifies a Location.</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Time that an antenna beam spends on a target.</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>- In the context of radar sensing.</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr"/>
+          <t>Spatial reference in the form of a label or code that identifies a Location.</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>- "Spain" is an example of a label (country name); "SW1-3AD" is an example of a code (postcode).</t>
+        </is>
+      </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO 19112:2019, 3.1.2</t>
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
@@ -6839,33 +6840,31 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Duration</t>
+          <t>Earth Observation</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>- core
-description: Non-negative interval Quantity of time equal to the difference between the final and initial instants of a time interval.</t>
+          <t>- high-impact
+description: Science domain dealing with technologies and methods of collecting and analyzing observations about the different Earth spheres.</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Non-negative interval Quantity of time equal to the difference between the final and initial instants of a time interval.</t>
+          <t>Science domain dealing with technologies and methods of collecting and analyzing observations about the different Earth spheres.</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>- Duration is one of the base quantities in the International System of Quantities (ISQ) on which the International System of Units (SI) is based. The term "time" instead of "duration" is often used in this context and also for an infinitesimal duration.
-- For the term "duration", expressions such as "time" or "time interval" are often used, but the term "time" is not recommended in this sense and the term "time interval" is deprecated in this sense to avoid confusion with the concept of "time interval".
-- The exact duration of a time scale unit depends on the time scale used. For example, the durations of a year, month, week, day, hour or minute may depend on when they occur (in a Gregorian calendar, a calendar month can have a duration of 28, 29, 30, or 31 days; in a 24-hour clock, a clock minute can have a duration of 59, 60, or 61 seconds, etc.). Therefore, the exact duration can only be evaluated if the exact duration of each is known.
-- This definition is closely related to NOTE 1 of the terminological entry "duration" in IEC 60050-113:2011, 113-01-13.</t>
+          <t>- Earth Observation (EO) can be categorised by location of the sensor into space-borne, air-borne, sea-borne, ground-based, underwater and underground EO.
+- Earth Observation (EO) includes Remote Sensing, such as satellite imagery, as well as in-situ observations, e.g., with ground-based devices.</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>- ISO 8601-1:2019, 3.1.1.8</t>
+          <t>- Modified GEO definition [GEO (earthobservations.org)](https://earthobservations.org/resources#key)</t>
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
@@ -6888,26 +6887,26 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Lead Time</t>
+          <t>Data Format</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>- core
-description: Minimum time of interval between an Observation being tasked and being performed.</t>
+description: Structured Data that is machine readable and can be automatically read and processed by a computer, such as HDF, NetCDF, CSV, JSON, XML, etc.</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Minimum time of interval between an Observation being tasked and being performed.</t>
+          <t>Structured Data that is machine readable and can be automatically read and processed by a computer, such as HDF, NetCDF, CSV, JSON, XML, etc.</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- CEOS Wiki</t>
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
@@ -6930,30 +6929,26 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>EO Space Data</t>
+          <t>Geolocation Information</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>- core
-description: Earth Observation data generated by spaceborne missions or instruments owned by public or private organizations.</t>
+description: Information used to determine geographic Location.</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Earth Observation data generated by spaceborne missions or instruments owned by public or private organizations.</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>- See also Instrument data.</t>
-        </is>
-      </c>
+          <t>Information used to determine geographic Location.</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- ISO 19130-1:2018, 3.34</t>
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
@@ -6976,30 +6971,26 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Spatial Completeness</t>
+          <t>Cryosphere</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>- core
-description: Presence or absence of gaps, which are missing values in an otherwise continuous spatial data series.</t>
+- approved</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Presence or absence of gaps, which are missing values in an otherwise continuous spatial data series.</t>
+          <t>Masses of frozen water, such as sea ice, ice shields, glaciers, and snow.</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>- Surface soil moisture retrieved from microwave satellite sensors may present gaps in mountainous terrains.</t>
-        </is>
-      </c>
+      <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
@@ -7022,33 +7013,20 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Derivative Product</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
           <t>- core
-description: Product additionally processed from baseline or unenhanced mission data.</t>
+description: ""</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>Product additionally processed from baseline or unenhanced mission data.</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>- Generally either a compilation of time-series data (e.g., all time, annual, monthly or seasonal summary data, &gt; Level 3) or thematic versions of each individual data tile of baseline data.
-- Derived products are citable via a Digital Object Identifier (DOI).</t>
-        </is>
-      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
-        </is>
-      </c>
+      <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
@@ -7069,28 +7047,38 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Geopositioning</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>- core
-description: Determination of the geographic Position of a point (0D) or linear (1D) Feature.</t>
+          <t>- base
+description: Particular Place referenced by an identifier.</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Determination of the geographic Position of a point (0D) or linear (1D) Feature.</t>
+          <t>Particular Place referenced by an identifier.</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>- Modified from: ISO 19130-1:2018, 3.36</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
+          <t>- While a (geo)location identifies a geographic Place, it may also be associated with objects other than the Earth.
+- While Location in principle covers 0- to 3-dimensional spatial geometries, it should not be used for 0- and 1-dimensional geometries (positions and paths).</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>- Madrid
+- California</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>- [ISO 19112:2019](https://www.iso.org/standard/70742.html), (E), 3.1.3, modified, note 2 added</t>
+        </is>
+      </c>
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr"/>
@@ -7111,22 +7099,28 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Spectral Band</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>- core
-description: Part of the electromagnetic spectrum of specific wavelengths, in remote sensing usually described by central wavelength and bandwidth.</t>
+description: Device or instrument suited (through physical/chemical interaction) to measure one or more properties of a Phenomenon and thus collect factual/objective data.</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Part of the electromagnetic spectrum of specific wavelengths. In Remote Sensing, usually described by central wavelength and bandwidth.</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr"/>
+          <t>Device or instrument suited (through physical/chemical interaction) to measure one or more properties of a Phenomenon and thus collect factual/objective data.</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>- Sensing is therefore a synonym for Observation (the Process).
+- As by their definition, sensors perform sampling.
+- Sensors used to obtain measurements must be calibrated and provide uncertainties.</t>
+        </is>
+      </c>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
@@ -7153,30 +7147,36 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Geographic Data</t>
+          <t>Temporal Resolution</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>- core
-description: Data with implicit or explicit reference to a Location relative to the Earth.</t>
+description: Observation or model output representing regular intervals, specifying the length of the interval that determines the smallest event or process that can be resolved.</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Data with implicit or explicit reference to a Location relative to the Earth.</t>
+          <t>Observation or model output representing regular intervals, specifying the length of the interval that determines the smallest event or Process that can be resolved (e.g., the Period between observations, the time steps in a model).</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>- Geographic Information is also used as a term for information concerning phenomena implicitly or explicitly associated with a Location relative to the Earth.</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr"/>
+          <t>- WIGOS 2019 distinguishes between sampling time Period, as the Period over which a Measurement is taken, and temporal sampling interval as the time Period between the beginning of consecutive sampling periods. Temporal Resolution in this Glossary is equivalent to sampling time Period as used by WIGOS.</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>| Entry format example | Valid unit                     |
+|----------------------|-------------------------------|
+| 1 s, 2 h, 1 m        | second, hour, day, month, year |</t>
+        </is>
+      </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>- ISO 19109:2015, 4.13; ISO 19109:2005</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
@@ -7199,26 +7199,26 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Business Continuity</t>
+          <t>Policy Cycle</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>- core
-- approved</t>
+          <t>- high-impact
+description: Well-established concept typically taught as the rational model of policy decision-making, representing an idealised view of the policy process.</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>An organisation's readiness to continue functioning during times of disruption.</t>
+          <t>Well-established concept, typically taught as the rational model of policy decision-making. Idealised view of the policy process.</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- [ESA/CEOS?, modified](https://digital-strategy.ec.europa.eu/en/library/quality-public-administration-toolbox-practitioners)</t>
         </is>
       </c>
       <c r="H147" t="inlineStr"/>

--- a/exports/xlsx/terms.xlsx
+++ b/exports/xlsx/terms.xlsx
@@ -536,32 +536,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Geographic Grid</t>
+          <t>Geolocating</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>- core
-description: Regular grid based on a Geographic Coordinate Reference System (CRS).</t>
+description: Geopositioning of an Object using a Physical Sensor Model or a True Replacement Model.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Regular grid based on a Geographic Coordinate Reference System (CRS).</t>
+          <t>Geopositioning of an Object using a Physical Sensor Model or a True Replacement Model.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>- ISO 19115-2:2009, 4.11</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Determination of the geographic location of a feature of two or more dimensions.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>- ISO 19130-1:2018, 3.36 ('geopositioning'), modified</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -578,26 +586,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Representativeness</t>
+          <t>Spectral Bandwidth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>- core
-description: Quality or characteristic of a measurement or observation to accurately represent a specific geographic location, time period, or environmental condition.</t>
+description: Range of the Spectral Band.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Quality or characteristic of a measurement or Observation to accurately represent a specific geographic location, time Period, or environmental condition.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>- WIGOS metadata standard defines representativeness as the extent of the region around the Observation of which it is representative.</t>
-        </is>
-      </c>
+          <t>Range of the Spectral Band.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
@@ -624,24 +628,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EO Space Data</t>
+          <t>Instrument Data</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>- core
-description: Earth Observation data generated by spaceborne missions or instruments owned by public or private organizations.</t>
+description: Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Earth Observation data generated by spaceborne missions or instruments owned by public or private organizations.</t>
+          <t>Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>- See also Instrument data.</t>
+          <t>- These data consist of instrument science and engineering data, and possibly ancillary data. Instrument engineering data is produced by engineering sensor(s) of an instrument, used either for operating the instrument or for processing the science data generated by the instrument. Instrument science data is produced by the science sensor(s) of an instrument, usually constituting the basic reason for existence of an instrument.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -650,14 +654,30 @@
           <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Data created by an instrument including scientific measurements and any engineering or ancillary data which may be included in the data packets.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Data produced and transmitted by the science and engineering sensors of an instrument, and, in the spacecraft environment, any additional data packaged with the instrument's sensor data by virtue of services provided.</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
@@ -670,40 +690,59 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Granule</t>
+          <t>Auxiliary Data</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>- core
-description: The smallest aggregation of data which is independently managed (i.e. described, inventoried, retrievable).</t>
+- approved</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>The smallest aggregation of data which is independently managed (i.e. described, inventoried, retrievable). Granules may be managed as logical granules and/or physical granules.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>- See also product.</t>
-        </is>
-      </c>
+          <t>Data that enhance the processing and utilisation of main Sensor Data. Auxiliary Data are usually not captured by the same Data collection Process or on the same platform as the main Sensor Data. Examples include meteorological Data received from ECMWF/Met Offices or DEMs. Auxiliary Data help in Data processing, but are also Data sets in their own right.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>- [NASA EarthData](https://www.earthdata.nasa.gov/learn/glossary)</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+          <t>- ESA/CEOS?, modified
+- ENMAP Glossary of Terms, https://www.enmap.org/Data/doc/EnMAP_Terms.pdf, 20210624
+- EO Data Stewardship Glossary</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Data required to perform processing of Sensor Data which is not obtained from the Sensor itself. Includes: (a) Data provided by the spacecraft (e.g. orbit Position and velocity, attitude, instrument house-keeping Data, on-board time); (b) Data not available from on-board sources.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>For EnMAP, this includes (a) orbit files, attitude files, Calibration Data, instrument house-keeping Data; (b) atmospheric parameters, reference images.</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>- ENMAP Glossary of Terms, https://www.enmap.org/Data/doc/EnMAP_Terms.pdf, 20210624
+- EO Data Stewardship Glossary</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Data required for instrument processing that does not originate in the instrument itself or from the satellite. Some Auxiliary Data will be generated in the ground segment, whilst other Data will be provided from external sources.</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>- CEOS-ARD PFS template 20220302</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
@@ -716,37 +755,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Temporal Revisit</t>
+          <t>Dispose</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>- core
-description: Interval between successive observations.</t>
+description: Action of permanently and irrecoverably removing all copies of data held by an organization.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Interval between successive observations.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>- In Remote Sensing it is also called repeat cycle.
-- More generally it is known as temporal sampling interval.</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>| Entry format example | Valid unit                     |
-|----------------------|-------------------------------|
-| 1 s, 2 h             | second, hour, day, month, year |</t>
-        </is>
-      </c>
+          <t>Action of permanently and irrecoverably removing all copies of data held by an organization.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -769,26 +797,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dispose</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>- core
-description: Action of permanently and irrecoverably removing all copies of data held by an organization.</t>
+          <t>- base
+- controversial
+description: Place referenced by a single set of coordinates within a coordinate reference system.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Action of permanently and irrecoverably removing all copies of data held by an organization.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>Place referenced by a single set of coordinates within a coordinate reference system.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>- Opposite to (previous) ISO definition, Position shall be used only for 0-dimensional primitives (points).</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- ISO 19133:2005, modified to cover only points, also called 'direct position'</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -811,35 +844,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Remote Sensing</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>- controversial
-description: Type of Observation performed at a significant distance from a Phenomenon.</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Remote Observation</t>
-        </is>
-      </c>
+          <t>- core
+description: Electronic data package distributable to users; content is derived from instrument data via processing involving ancillary and auxiliary data.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Type of Observation performed at a significant distance from a Phenomenon.</t>
+          <t>Electronic data package distributable to users; content is derived from instrument data via processing involving ancillary and auxiliary data.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>- 'Significant' in this context means that the distance has, or may have, a non-negligible impact on the Value of the Property observed.
-- The effect of the distance on the acquired data is the main distinction criterion between 'remote' and 'in-situ' observations.</t>
+          <t>- Products may be accompanied by metadata and browse images.
+- A Product may be part of a collection — a distinction useful for archiving and cataloguing purposes.
+- The term Product may be used to denote a product type, such as e.g. ENVISAT_ASAR_L1B_PRI data products.
+- End users may distinguish between (input, "raw") data and products, i.e., the derived geophysical parameters.
+- See also granule.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -862,26 +894,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Near Real Time Data</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>- high-impact
-description: Data available for use with a specified (small and application dependent) latency, typically 3 hours for meteorological applications.</t>
+          <t>- base
+description: Series of activities that interact to produce a result.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Data available for use with a specified (small and application dependent) latency, typically 3 hours for meteorological applications.</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>Series of activities that interact to produce a result.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>- A Process may occur once-only or be recurrent or periodic.</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- [Wikipedia](https://en.wikipedia.org/wiki/Process)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -904,50 +940,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>- base
-description: Value and possibly Uncertainty of a Trait of a specific Entity.</t>
+          <t>- core
+description: Phenomenon whose values for specific properties are known and understood with an Uncertainty significantly lower than that of the Observation with which it is compared.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Value and possibly Uncertainty of a Trait of a specific Entity.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>- Data simply describe entities using certain traits and are not targeted at a particular use or audience.</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Data can be categorised into:
-- factual (i.e. obtained by Observation) or fictional (obtained e.g. through modelling, estimating or assigning)
-- quantitative (continuous) or qualitative (categorical)
-- analogue or digital
-(list not exhaustive!)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
+          <t>Phenomenon whose values for specific properties are known and understood with an Uncertainty significantly lower (quantify?) than that of the Observation with which it is compared.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Scientific or technical measurements, values calculated therefrom, observations, or facts that can be represented by numbers, tables, graphs, models, text, or symbols which are used as a basis for reasoning and further calculation.</t>
+          <t>Sort of data acquired with an Uncertainty significantly lower (quantify?) than that of the data it is being compared with.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
+          <t>- VIM?, modified</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -966,30 +986,29 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Geographic Coordinate Reference System</t>
+          <t>Earth Observation Based Output</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>- core
-description: Coordinate Reference System (CRS) that has a geodetic Reference frame and an ellipsoidal coordinate system.</t>
+description: Higher-level processing and integration output (indicative level 4 and beyond) that goes beyond basic data processing, often designed for policy or decision-making needs.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Coordinate Reference System (CRS) that has a geodetic Reference frame and an ellipsoidal coordinate system.</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>- Also known as geographic CRS.</t>
-        </is>
-      </c>
+          <t>Higher-level processing and integration output (indicative level 4 and beyond) that goes beyond basic data processing. These outputs are often designed specifically for policy or decision-making needs, and can be categorized into sub-categories:
+- Outputs from models/model integration: use of EO products as inputs in numerical models or combining them with other data sources in modelling frameworks.
+- Indicator-based outputs: EO products transformed through specialized algorithms (including statistical methods, machine learning, and pattern recognition) to create meaningful metrics based on spatio-temporal analysis.
+- Outputs from reanalysis: merging of EO products with other observations and models, creating consistent long-term records of past atmospheric, oceanic, and land surface conditions, and filling gaps through data assimilation techniques.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>- ISO 19111:2019, 3.1.35</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -1012,37 +1031,44 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Long Term Preservation</t>
+          <t>Entity</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>- core
-description: The act of maintaining information in a correct and independently understandable form over the long term.</t>
+          <t>- base
+description: Something that has separate and distinct existence and objective or conceptual reality.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>The act of maintaining information in a correct and independently understandable form over the long term.</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>- Long term refers to a period of time long enough to be concerned with the impact which changing technologies, including support for media and data formats, and changing user communities will have on the information being held in a repository.
-- See also preservation.</t>
-        </is>
-      </c>
+          <t>Something that has separate and distinct existence and objective or conceptual reality.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>- ISO 19119:2016, 4.1.6</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Government or business organization that is formed to conduct business or represent the government of the day.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>CEOS Entities include Working Groups, Virtual Constellations, etc.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1059,31 +1085,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Preservation</t>
+          <t>Collection</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>- core
-description: Processes and operations used to ensure data technical and intellectual survival through time.</t>
+- approved</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Processes and operations used to ensure data technical and intellectual survival through time.</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>- Grants data integrity, discoverability and accessibility, and facilitates its (re-)use in the long term.
-- Preservation is one of the tasks of data curation.</t>
-        </is>
-      </c>
+          <t>Group of products that have been processed using a consistent radiometric calibration, geometric registration base, data/metadata format, and version of processing algorithms.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1106,26 +1127,26 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Version Control</t>
+          <t>Geographic Grid</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>- core
-description: Method of working with collections, similar to version control systems used in traditional software development but optimized to allow better processing of data and collaboration in data analytics and research contexts.</t>
+description: Regular grid based on a Geographic Coordinate Reference System (CRS).</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Method of working with collections, similar to the version control systems used in traditional software development but optimized to allow better processing of data and collaboration in the context of data analytics, research, and any other form of data analysis.</t>
+          <t>Regular grid based on a Geographic Coordinate Reference System (CRS).</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>- [Wikipedia](https://en.wikipedia.org/wiki/Data_version_control)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -1148,26 +1169,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Thematic Resolution</t>
+          <t>Archive</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>- core
-description: Level of categorical detail of information expressed by the number of classes.</t>
+- approved</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Level of categorical detail of information expressed by the number of classes.</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>System that stores data products, guaranteeing their preservation for future use.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>- This function includes all operations to identify, store and retrieve the data and ensure their integrity.</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>- CGLS</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1190,26 +1215,30 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Copernicus Service Provider</t>
+          <t>Steward</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Institutional body, organisation or programme that provides reliable, trusted (authoritative?) EO Information and that has the financial resources to sustain the provision. It utilises satellite Data, ground-based measurements, and other sources to generate accurate and timely Data products related to various aspects of the Earth's environment, such as land, Atmosphere, oceans, and climate.</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>- See also Custodian.</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -1232,26 +1261,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Replicability</t>
+          <t>Sample</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>- core
-description: Property enabling other researchers to conduct an independent study with different data and similar but not identical methods, yet arriving at results that confirm the original study's hypothesis.</t>
+          <t>- controversial
+description: Subset of one or more entities.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Property enabling other researchers to conduct an independent study with different data and similar but not identical methods, yet arriving at results that confirm the original study's hypothesis.</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+          <t>Subset of one or more entities.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>- A Sample may be spatial, temporal, spectral, or in any other dimension or Trait.
+- Each Sample is contiguous, i.e. it does not consist of more than one discontinuous geometry in any dimension.
+- The Process of obtaining a Sample is called sampling.</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>- Craglia, M., et al. (2018).</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -1274,30 +1309,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Coverage Interval</t>
+          <t>Temporal Extent</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Coverage extent</t>
-        </is>
-      </c>
+description: Period during which data was collected, observations were made, or for which the model was run.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Range or specific subset of values associated with a coverage dataset.</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+          <t>Period during which data was collected, observations were made, or for which the model was run.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>- In W3C this is the definition of temporal coverage.
+- Time Period covered by a series of observations inclusive of the specified date/time indications (measurement history). Defined based on the beginning and end dates of observations.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>- WIGOS Metadata</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Adapted from W3C</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -1367,7 +1407,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Band Central Wavelength</t>
+          <t>Cryosphere</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1379,20 +1419,14 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Single wavelength Value within the sensitivity interval of a spectroradiometric Sensor which represents the respective band. It could be either the mean, the median, the maximum sensitivity, or any other reasonable Value chosen to be representative.</t>
+          <t>Masses of frozen water, such as sea ice, ice shields, glaciers, and snow.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>| Entry format example | Valid unit                                        |
-|----------------------|---------------------------------------------------|
-| 0.545 μm             | micrometre (μm), millimetre (mm), centimetre (cm) |</t>
-        </is>
-      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -1415,24 +1449,24 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Update Frequency</t>
+          <t>Spatial Reporting Unit</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>- core
-description: Frequency at which the product is available to users.</t>
+description: Smallest spatial object of interest that may be used for reporting and for which the information should be aggregated.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Frequency at which the product is available to users.</t>
+          <t>Smallest spatial object of interest that may be used for reporting and for which the information should be aggregated.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>- Also known in product catalogues as dissemination frequency.</t>
+          <t>- WIGOS 2019 uses 'spatial reporting interval', probably assuming observations are reported on a grid with regular spacing/intervals.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -1461,44 +1495,36 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Entity</t>
+          <t>Decommissioned Product</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>- base
-description: Something that has separate and distinct existence and objective or conceptual reality.</t>
+          <t>- core
+description: Products and collections that have been superseded by new versions and are no longer available.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Something that has separate and distinct existence and objective or conceptual reality.</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+          <t>Products and collections that have been superseded by new versions and are no longer available.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>- Decommissioned products are no longer supported, i.e. corrections will not be made, new data will not be added, and support is not available.</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>- ISO 19119:2016, 4.1.6</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Government or business organization that is formed to conduct business or represent the government of the day.</t>
-        </is>
-      </c>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>CEOS Entities include Working Groups, Virtual Constellations, etc.</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
-        </is>
-      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -1515,26 +1541,36 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Place</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>- base
-description: Part of any space referenced by an identifier.</t>
+description: Particular Place referenced by an identifier.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Part of any space referenced by an identifier.</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+          <t>Particular Place referenced by an identifier.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>- While a (geo)location identifies a geographic Place, it may also be associated with objects other than the Earth.
+- While Location in principle covers 0- to 3-dimensional spatial geometries, it should not be used for 0- and 1-dimensional geometries (positions and paths).</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>- Madrid
+- California</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>- ISO 19155:2012, 4.8</t>
+          <t>- [ISO 19112:2019](https://www.iso.org/standard/70742.html), (E), 3.1.3, modified, note 2 added</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -1557,33 +1593,30 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Duration</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>- core
-description: Non-negative interval Quantity of time equal to the difference between the final and initial instants of a time interval.</t>
+          <t>- base
+description: Particular era or span of time.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Non-negative interval Quantity of time equal to the difference between the final and initial instants of a time interval.</t>
+          <t>Particular era or span of time.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>- Duration is one of the base quantities in the International System of Quantities (ISQ) on which the International System of Units (SI) is based. The term "time" instead of "duration" is often used in this context and also for an infinitesimal duration.
-- For the term "duration", expressions such as "time" or "time interval" are often used, but the term "time" is not recommended in this sense and the term "time interval" is deprecated in this sense to avoid confusion with the concept of "time interval".
-- The exact duration of a time scale unit depends on the time scale used. For example, the durations of a year, month, week, day, hour or minute may depend on when they occur (in a Gregorian calendar, a calendar month can have a duration of 28, 29, 30, or 31 days; in a 24-hour clock, a clock minute can have a duration of 59, 60, or 61 seconds, etc.). Therefore, the exact duration can only be evaluated if the exact duration of each is known.
-- This definition is closely related to NOTE 1 of the terminological entry "duration" in IEC 60050-113:2011, 113-01-13.</t>
+          <t>- Periods are intervals named with a Period Identifier.</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>- ISO 8601-1:2019, 3.1.1.8</t>
+          <t>- ISO 19170:2021</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -1606,37 +1639,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Time of Day</t>
+          <t>Geospatial Data</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>- core
-description: Time of the day at which the variable or parameter is observed or simulated by a model.</t>
+description: Data consisting of, derived from, or relating to information that is directly linked to specific geographical locations.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Time of the day at which the variable or parameter is observed or simulated by a model.</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>- In Remote Sensing it is also known as time of overpass.</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>| Type      | Entry format example | Valid unit |
-|-----------|----------------------|------------|
-| timestamp | 18:00 h (0–24)       | Hours      |
-| timerange | 18:00 – 20:00 h      | Hours      |</t>
-        </is>
-      </c>
+          <t>Data consisting of, derived from, or relating to information that is directly linked to specific geographical locations.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- https://www.merriam-webster.com/dictionary/geospatial
+- https://isotc211.geolexica.org/Concepts/202/, accessed 20221010</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -1659,29 +1682,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Vertical Levels</t>
+          <t>Confidence Interval</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>- core
-description: Levels of a vertical discretization, e.g. pressure levels in an atmospheric model reanalysis or height levels in a forest biomass EO product.</t>
+          <t>- controversial
+- approved</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Levels of a vertical discretization. Examples may be pressure levels in an atmospheric model reanalysis or height levels in a forest biomass EO product.</t>
+          <t>Probability that the Quantity lies in the interval, conditioned on the measuring or modelling assumptions.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>| Entry format example                | Valid unit           |
-|------------------------------------|----------------------|
-| 1, 5, 10 meter; 1000, 850, 500 hPa | meter, hPa, unitless |</t>
-        </is>
-      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>- KCEO</t>
@@ -1707,34 +1724,30 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Granule</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>- core
-description: Electronic data package distributable to users; content is derived from instrument data via processing involving ancillary and auxiliary data.</t>
+description: The smallest aggregation of data which is independently managed (i.e. described, inventoried, retrievable).</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Electronic data package distributable to users; content is derived from instrument data via processing involving ancillary and auxiliary data.</t>
+          <t>The smallest aggregation of data which is independently managed (i.e. described, inventoried, retrievable). Granules may be managed as logical granules and/or physical granules.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>- Products may be accompanied by metadata and browse images.
-- A Product may be part of a collection — a distinction useful for archiving and cataloguing purposes.
-- The term Product may be used to denote a product type, such as e.g. ENVISAT_ASAR_L1B_PRI data products.
-- End users may distinguish between (input, "raw") data and products, i.e., the derived geophysical parameters.
-- See also granule.</t>
+          <t>- See also product.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- [NASA EarthData](https://www.earthdata.nasa.gov/learn/glossary)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -1757,24 +1770,24 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>- base
-description: The result of organisation, interpretation, categorisation, classification, or some other form of processing of Data attaching to it a certain meaning that can be understood by the addressee.</t>
+          <t>- controversial
+description: An, often numeric, theoretical (or otherwise abstract) representation of an Entity intended to generate Data describing one or more of its traits.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>The result of organisation, interpretation, categorisation, classification, or some other form of processing of Data attaching to it a certain meaning that can be understood by the addressee.</t>
+          <t>An, often numeric, theoretical (or otherwise abstract) representation of an Entity intended to generate Data describing one or more of its traits (as a result of pre-set conditions).</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>- Information depends on Data and is targeted.</t>
+          <t>- The Process of generating Data using a model is called modelling.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
@@ -1803,32 +1816,44 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Lithosphere</t>
+          <t>Georectifying</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>- core
-description: The solid, inanimate outer layer of the Geosphere. For the purposes of Earth Observation, includes soils ('pedosphere').</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+description: Correcting for positional displacement with respect to the surface of the Earth.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Orthorectifying</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>The solid, inanimate outer layer of the Geosphere. For the purposes of Earth Observation, the Lithosphere is considered to include soils ('pedosphere').</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>Correcting for positional displacement with respect to the surface of the Earth.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>- Source: ISO 19115-2:2019, 3.11; ISO 19115-2:2009(E); https://www.iso.org/standard/67039.html, modified</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>- Guth et al. 2021</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>The correction of sample locations to achieve some sort of geometric regularity, e.g., a regular 2D geographic grid.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
@@ -1845,45 +1870,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ancillary Data</t>
+          <t>Policy Making</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>- core
-- approved</t>
+          <t>- high-impact
+description: Process by which governments translate their political vision into programmes and actions to deliver outcomes — desired change in the real world.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Data acquired on the same platform but not obtained from the main Sensor itself (usually provided as part of Level 0 Data), with the primary purpose of serving the processing of main instrument Data (e.g. Position and velocity of platform).</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>This can be divided into data referred to as spacecraft 'engineering', 'core housekeeping' or 'subsystem' data obtained from other parts of the platform, and includes parameters such as orbit position and velocity, attitude and its range of change, time, temperatures, pressures, jet firings, water dumps, internally produced magnetic fields, and other environmental measurements. Ancillary refers to data that exist purely to serve the data processing.</t>
-        </is>
-      </c>
+          <t>Process by which governments translate their political vision into programmes and actions to deliver outcomes — desired change in the real world.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>- ESA/CEOS?, modified
-- EO Data Stewardship Glossary</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Data other than instrument measurements, originating in the instrument itself or from the satellite, required to perform processing of the Data. Includes orbit Data, attitude Data, time Information, and spacecraft engineering Data, Calibration Data, Data quality Information, and Data from other instruments or earth system models.</t>
-        </is>
-      </c>
+          <t>- [ESA/CEOS?, modified](https://digital-strategy.ec.europa.eu/en/library/quality-public-administration-toolbox-practitioners)</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>- CEOS-ARD PFS template 20220302</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
@@ -1900,72 +1912,109 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Quality Indicator</t>
+          <t>Uncertainty</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>- core
-description: Indicator providing sufficient information to allow all users to readily evaluate the fitness for purpose of the data or derived product.</t>
+description: Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Indicator providing sufficient information to allow all users to readily evaluate the fitness for purpose of the data or derived product. May be a number, set of numbers, graph, Uncertainty budget, or a simple flag.</t>
+          <t>Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>- CEOS Wiki</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
+          <t>- GUM</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Non-negative parameter, associated with data, which characterizes the dispersion of the values of a Trait that could reasonably be attributed to a Phenomenon by means of sensing or modelling.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>- In case of quantitative (continuous) data the uncertainty may be, for example, a standard deviation (or a given multiple of it), or the half-width of an interval having a stated level of confidence (see e.g. Standard and Expanded Uncertainty).
+- For qualitative (categorical?) data, uncertainty may be expressed by commission and omission ('confusion matrix') or overall errors.</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>- Modified from GUM, VIM4:3.1, FIDUCEO, Notes added</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Measure of the spread of the distribution of possible values.</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>- [FIDUCEO Glossary](https://research.reading.ac.uk/fiduceo/glossary/), VIM?, modified</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Parameter, associated with the result of measurement, that characterizes the dispersion of values that could reasonably be attributed to the measurand.</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>- When the quality of accuracy or precision of measured values, such as coordinates, is to be characterized quantitatively, the quality parameter is an estimate of the uncertainty of the measurement results. Because accuracy is a qualitative concept, one should not use it quantitatively, that is associate numbers with it; numbers should be associated with measures of uncertainty instead.</t>
+        </is>
+      </c>
       <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>- ISO 19116:2004(E)</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Parameter characterizing the dispersion of the values being attributed to a measurand, based on the information used.</t>
+        </is>
+      </c>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>- VIM4: 3.1</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Climate Projection</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>- base
-description: Series of activities that interact to produce a result.</t>
+          <t>- core
+- approved</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Series of activities that interact to produce a result.</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>- A Process may occur once-only or be recurrent or periodic.</t>
-        </is>
-      </c>
+          <t>Simulated response of the climate system to a scenario of future emission or concentration of greenhouse gases (GHGs) and aerosols, generally derived using climate models. Climate Projections are distinguished from climate predictions by their dependence on the emission/concentration/radiative forcing scenario used, which is in turn based on assumptions concerning, for example, future socioeconomic and technological developments that may or may not be realised.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>- [Wikipedia](https://en.wikipedia.org/wiki/Process)</t>
+          <t>- IPCC</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -1988,26 +2037,26 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Standard Uncertainty</t>
+          <t>Data Format</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>- core
-description: Standard deviation of the probability distribution describing the spread of possible values in quantitative/continuous data.</t>
+description: Structured Data that is machine readable and can be automatically read and processed by a computer, such as HDF, NetCDF, CSV, JSON, XML, etc.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Standard deviation of the probability distribution describing the spread of possible values in quantitative/continuous data.</t>
+          <t>Structured Data that is machine readable and can be automatically read and processed by a computer, such as HDF, NetCDF, CSV, JSON, XML, etc.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- CEOS Wiki</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -2030,26 +2079,26 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Minimum Mapping Width</t>
+          <t>Classification System Levels</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>- core
-description: The width of the smallest linear Feature that is still represented on a map.</t>
+- approved</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>The width of the smallest linear Feature that is still represented on a map.</t>
+          <t>Levels in a hierarchical Classification System.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>- CGLS</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -2072,26 +2121,30 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Deprecated Product</t>
+          <t>Geocoding</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>- core
-description: Products and collections that have been superseded by a newer version and are still available, but whose use is discouraged since they will be decommissioned in the future.</t>
+description: Translation of one form of Location into another.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Products and collections that have been superseded by a newer version and are still available, but whose use is discouraged since they will be decommissioned in the future.</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
+          <t>Translation of one form of Location into another.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>- Geocoding usually refers to the translation of "address" or "intersection" to "direct Position." Many service providers also include a "reverse geocoding" interface to their geocoder, thus extending the definition of the service as a general translator of Location. Because routing services use internal Location encodings not usually available to others, a geocoder is an integral part of the internals of such a service.</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- ISO 19133:2005; https://www.iso.org/standard/32551.html</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -2114,30 +2167,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Period Identifier</t>
+          <t>Band Central Wavelength</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>- core
-description: Temporal reference in the form of a label or code that identifies a Period.</t>
+- approved</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Temporal reference in the form of a label or code that identifies a Period.</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>- Period Identifiers are the temporal equivalent of geographic identifiers as specified in ISO 19912.</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
+          <t>Single wavelength Value within the sensitivity interval of a spectroradiometric Sensor which represents the respective band. It could be either the mean, the median, the maximum sensitivity, or any other reasonable Value chosen to be representative.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>| Entry format example | Valid unit                                        |
+|----------------------|---------------------------------------------------|
+| 0.545 μm             | micrometre (μm), millimetre (mm), centimetre (cm) |</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>- ISO 19170:2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -2160,28 +2215,19 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Lead Time</t>
+          <t>Cartographic Projection</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>- core
-description: Minimum time of interval between an Observation being tasked and being performed.</t>
+          <t>- core</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Minimum time of interval between an Observation being tasked and being performed.</t>
-        </is>
-      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
@@ -2202,7 +2248,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Calibration</t>
+          <t>Copernicus Service Provider</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2214,12 +2260,16 @@
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Process of quantitatively defining a system's (e.g. a Sensor or Model's) response to known, controlled inputs produced for example by references. In Remote Sensing, it implies the collection of pre-flight and in-flight calibration measurements and in-situ Data that is to be used in the Data calibration processing routine.</t>
+          <t>Institutional body, organisation or programme that provides reliable, trusted (authoritative?) EO Information and that has the financial resources to sustain the provision. It utilises satellite Data, ground-based measurements, and other sources to generate accurate and timely Data products related to various aspects of the Earth's environment, such as land, Atmosphere, oceans, and climate.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
@@ -2240,26 +2290,26 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Climate Projection</t>
+          <t>Location Error</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Measure of the agreement between the represented Location of an Object and the true Location.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Simulated response of the climate system to a scenario of future emission or concentration of greenhouse gases (GHGs) and aerosols, generally derived using climate models. Climate Projections are distinguished from climate predictions by their dependence on the emission/concentration/radiative forcing scenario used, which is in turn based on assumptions concerning, for example, future socioeconomic and technological developments that may or may not be realised.</t>
+          <t>Measure of the agreement between the represented Location of an Object and the true Location.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>- IPCC</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -2282,30 +2332,26 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Spatial Reporting Unit</t>
+          <t>Version Control</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>- core
-description: Smallest spatial object of interest that may be used for reporting and for which the information should be aggregated.</t>
+description: Method of working with collections, similar to version control systems used in traditional software development but optimized to allow better processing of data and collaboration in data analytics and research contexts.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Smallest spatial object of interest that may be used for reporting and for which the information should be aggregated.</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>- WIGOS 2019 uses 'spatial reporting interval', probably assuming observations are reported on a grid with regular spacing/intervals.</t>
-        </is>
-      </c>
+          <t>Method of working with collections, similar to the version control systems used in traditional software development but optimized to allow better processing of data and collaboration in the context of data analytics, research, and any other form of data analysis.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [Wikipedia](https://en.wikipedia.org/wiki/Data_version_control)</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -2328,26 +2374,26 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Source Data</t>
+          <t>Data Access</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>- core
-description: Data required for production of an EO Collection (e.g., unenhanced satellite mission data) as well as further processed Level-1 data, or any other pre-processed format meeting program requirements.</t>
+description: Service to disseminate Data.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Data required for production of an EO Collection (e.g., unenhanced satellite mission data) as well as further processed Level-1 data (precision geometrically and radiometrically corrected radiance at the sensor), or any other pre-processed format that suppliers are providing access to that meets program requirements.</t>
+          <t>Service to disseminate Data.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -2370,7 +2416,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>Collection Upgrade</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2382,18 +2428,14 @@
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Proximity of Measurement results to the accepted Value; precision is the degree to which repeated or reproducible measurements under unchanged conditions show the same results.</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>- In essence, Accuracy reflects how close measurements are to the accepted Value, while precision gauges the reliability and consistency of those measurements.</t>
-        </is>
-      </c>
+          <t>New and improved major version of all products within a collection due to comprehensive reprocessing.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>- BS ISO 5725-1</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -2416,26 +2458,26 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Policy Making</t>
+          <t>Thematic Resolution</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>- high-impact
-description: Process by which governments translate their political vision into programmes and actions to deliver outcomes — desired change in the real world.</t>
+          <t>- core
+description: Level of categorical detail of information expressed by the number of classes.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Process by which governments translate their political vision into programmes and actions to deliver outcomes — desired change in the real world.</t>
+          <t>Level of categorical detail of information expressed by the number of classes.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>- [ESA/CEOS?, modified](https://digital-strategy.ec.europa.eu/en/library/quality-public-administration-toolbox-practitioners)</t>
+          <t>- CGLS</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -2458,31 +2500,26 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Standard Uncertainty</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>- base
-- controversial
-description: Place referenced by a single set of coordinates within a coordinate reference system.</t>
+          <t>- core
+description: Standard deviation of the probability distribution describing the spread of possible values in quantitative/continuous data.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Place referenced by a single set of coordinates within a coordinate reference system.</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>- Opposite to (previous) ISO definition, Position shall be used only for 0-dimensional primitives (points).</t>
-        </is>
-      </c>
+          <t>Standard deviation of the probability distribution describing the spread of possible values in quantitative/continuous data.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>- ISO 19133:2005, modified to cover only points, also called 'direct position'</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -2505,26 +2542,30 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Minimum Mapping Unit</t>
+          <t>Coverage Interval</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>- core
-description: The area of the smallest Feature that is still represented on a map.</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+- approved</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Coverage extent</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>The area of the smallest Feature that is still represented on a map.</t>
+          <t>Range or specific subset of values associated with a coverage dataset.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>- CGLS</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -2547,22 +2588,26 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Spectral Band</t>
+          <t>Path</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>- core
-description: Part of the electromagnetic spectrum of specific wavelengths, in remote sensing usually described by central wavelength and bandwidth.</t>
+          <t>- base
+description: "Line defined in an algorithmic way using at least two positions (can be open-ended). Alternative: line connecting two positions in an algorithmic way (limited by end points)."</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Part of the electromagnetic spectrum of specific wavelengths. In Remote Sensing, usually described by central wavelength and bandwidth.</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
+          <t>Line defined in an algorithmic way using at least two positions (can be open-ended). Alternative: line connecting two positions in an algorithmic way (limited by end points).</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>- A Path is a 1-dimensional Place.</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
@@ -2589,28 +2634,28 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Geopositioning</t>
+          <t>Source Data</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>- core
-description: Determination of the geographic Position of a point (0D) or linear (1D) Feature.</t>
+description: Data required for production of an EO Collection (e.g., unenhanced satellite mission data) as well as further processed Level-1 data, or any other pre-processed format meeting program requirements.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Determination of the geographic Position of a point (0D) or linear (1D) Feature.</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>- Modified from: ISO 19130-1:2018, 3.36</t>
-        </is>
-      </c>
+          <t>Data required for production of an EO Collection (e.g., unenhanced satellite mission data) as well as further processed Level-1 data (precision geometrically and radiometrically corrected radiance at the sensor), or any other pre-processed format that suppliers are providing access to that meets program requirements.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
@@ -2631,7 +2676,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Collection Update</t>
+          <t>Atmosphere</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2643,14 +2688,14 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Minor revisions to a relatively small number of products within a collection for the purpose of correcting errors and maintaining consistent quality.</t>
+          <t>Layer of gases, commonly known as air, including suspended liquid and solid particles known as aerosols (incl. dust, clouds, snow and ice).</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -2673,57 +2718,62 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Verification</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>- core
-description: Provision of objective evidence that a given item fulfils specified requirements.</t>
+description: Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Provision of objective evidence that a given item fulfils specified requirements.</t>
+          <t>Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>- When applicable, measurement uncertainty should be taken into consideration.
-- The item may be, e.g. a Process, measurement procedure, material, compound, or measuring system.
-- The specified requirements may be, e.g. that a manufacturer's specifications are met.
-- Verification should not be confused with Calibration. Not every verification is a Validation.</t>
+          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>- ISO/IEC Guide 99:2007, 2.44</t>
+          <t>- ISO/TS 19101‑2:2008, 4.41</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Evaluation of whether or not a product, service, or system complies with a regulation requirement, specification, or imposed condition. Often an internal Process.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>Process aimed at verifying that the specified requirements are achieved or compliant. Involves comparing mission products with representative reference data, considering various observation conditions, ensuring the quality and traceability of the reference data used.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>- EU-US Land Imaging EO Collaboration</t>
+          <t>- BIPM; QA4EO; ESA?, modified</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Means to evaluate the reliability of the data in the absence of a reference dataset, allowing for an assessment of its standalone performance. Involves confirming the consistency and internal coherence of the data without direct comparison to external reference sources.</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr"/>
+          <t>Assurance that a product, service, or system meets the needs of the customer and other identified stakeholders. Often involves acceptance and suitability with external customers.</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- EU-US Land Imaging EO Collaboration</t>
         </is>
       </c>
       <c r="P49" t="inlineStr"/>
@@ -2738,29 +2788,31 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Earth Observation Based Output</t>
+          <t>Long Term Preservation</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>- core
-description: Higher-level processing and integration output (indicative level 4 and beyond) that goes beyond basic data processing, often designed for policy or decision-making needs.</t>
+description: The act of maintaining information in a correct and independently understandable form over the long term.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Higher-level processing and integration output (indicative level 4 and beyond) that goes beyond basic data processing. These outputs are often designed specifically for policy or decision-making needs, and can be categorized into sub-categories:
-- Outputs from models/model integration: use of EO products as inputs in numerical models or combining them with other data sources in modelling frameworks.
-- Indicator-based outputs: EO products transformed through specialized algorithms (including statistical methods, machine learning, and pattern recognition) to create meaningful metrics based on spatio-temporal analysis.
-- Outputs from reanalysis: merging of EO products with other observations and models, creating consistent long-term records of past atmospheric, oceanic, and land surface conditions, and filling gaps through data assimilation techniques.</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
+          <t>The act of maintaining information in a correct and independently understandable form over the long term.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>- Long term refers to a period of time long enough to be concerned with the impact which changing technologies, including support for media and data formats, and changing user communities will have on the information being held in a repository.
+- See also preservation.</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
@@ -2783,19 +2835,32 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cartographic Projection</t>
+          <t>Catalogue</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>- core</t>
+          <t>- core
+- approved</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>System that provides users with discovery of information on which EO products can be obtained.</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>- A 'Product Catalogue' can organise products and collections with varying access levels depending on product and user type.</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
@@ -2816,32 +2881,26 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Temporal Reporting Period</t>
+          <t>Minimum Mapping Unit</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>- core
-description: Time period used for reporting and for which the information should be aggregated from the native temporal resolution.</t>
+description: The area of the smallest Feature that is still represented on a map.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Time Period used for reporting and for which the information should be aggregated from the native Temporal Resolution.</t>
+          <t>The area of the smallest Feature that is still represented on a map.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>| Entry format example | Valid unit                     |
-|----------------------|-------------------------------|
-| 1 s, 2 h, 1 d        | second, hour, day, month, year |</t>
-        </is>
-      </c>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>- Modified WIGOS Metadata Standard 2019</t>
+          <t>- CGLS</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
@@ -2864,26 +2923,32 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Reproducibility</t>
+          <t>Temporal Reporting Period</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>- core
-description: Concerned with the validity of the results of a particular study, enabling readers to check whether results have been manipulated by reproducing exactly the same study using the same data and methods.</t>
+description: Time period used for reporting and for which the information should be aggregated from the native temporal resolution.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Concerned with the validity of the results of a particular study, i.e., the possibility for readers to check whether results have been manipulated, by reproducing exactly the same study using the same data and methods.</t>
+          <t>Time Period used for reporting and for which the information should be aggregated from the native Temporal Resolution.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>| Entry format example | Valid unit                     |
+|----------------------|-------------------------------|
+| 1 s, 2 h, 1 d        | second, hour, day, month, year |</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>- Ostermann and Granell (2015)</t>
+          <t>- Modified WIGOS Metadata Standard 2019</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
@@ -2906,26 +2971,26 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Atmosphere</t>
+          <t>Policy File</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>- core
-- approved</t>
+          <t>- high-impact
+description: Policy documents that represent the official written reference for a given Policy.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Layer of gases, commonly known as air, including suspended liquid and solid particles known as aerosols (incl. dust, clouds, snow and ice).</t>
+          <t>Policy documents that represent the official written reference for a given Policy.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
@@ -2948,40 +3013,32 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Geolocating</t>
+          <t>Impact</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>- core
-description: Geopositioning of an Object using a Physical Sensor Model or a True Replacement Model.</t>
+description: Regarded long-term according to X. However, in the Horizon Europe Missions terminology, regarded short-term.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Geopositioning of an Object using a Physical Sensor Model or a True Replacement Model.</t>
+          <t>Regarded long-term according to X. However, in the Horizon Europe Missions terminology, regarded short-term.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>- ISO 19115-2:2009, 4.11</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>Determination of the geographic location of a feature of two or more dimensions.</t>
-        </is>
-      </c>
+          <t>- KCEO</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>- ISO 19130-1:2018, 3.36 ('geopositioning'), modified</t>
-        </is>
-      </c>
+      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
@@ -2998,28 +3055,24 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Confidence Interval</t>
+          <t>Calibration</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>- controversial
+          <t>- core
 - approved</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Probability that the Quantity lies in the interval, conditioned on the measuring or modelling assumptions.</t>
+          <t>Process of quantitatively defining a system's (e.g. a Sensor or Model's) response to known, controlled inputs produced for example by references. In Remote Sensing, it implies the collection of pre-flight and in-flight calibration measurements and in-situ Data that is to be used in the Data calibration processing routine.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
@@ -3040,23 +3093,35 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Baseline</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>- core
-- approved</t>
+          <t>- base
+description: Value and possibly Uncertainty of a Trait of a specific Entity.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Reference Period, time or measure against which the Information is assessed or compared.</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
+          <t>Value and possibly Uncertainty of a Trait of a specific Entity.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>- Data simply describe entities using certain traits and are not targeted at a particular use or audience.</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Data can be categorised into:
+- factual (i.e. obtained by Observation) or fictional (obtained e.g. through modelling, estimating or assigning)
+- quantitative (continuous) or qualitative (categorical)
+- analogue or digital
+(list not exhaustive!)</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
           <t>- KCEO</t>
@@ -3064,7 +3129,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Source data that has been processed to a common set of requirements and organised into a form that allows immediate analysis and interoperability through time and with other collections.</t>
+          <t>Scientific or technical measurements, values calculated therefrom, observations, or facts that can be represented by numbers, tables, graphs, models, text, or symbols which are used as a basis for reasoning and further calculation.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -3090,32 +3155,40 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Classification System Levels</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>- core
-- approved</t>
+          <t>- base
+description: Property having a magnitude that can be expressed as a number from a continuous and contiguous range and a reference.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Levels in a hierarchical Classification System.</t>
+          <t>Property having a magnitude that can be expressed as a number from a continuous and contiguous range and a reference.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>- ISO/IEC Guide 99:2007, 1.1, modified — Notes omitted</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Property whose instances can be compared by ratio or only by order.</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>- gEOGlos (VIM4 Notes omitted)</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
@@ -3132,26 +3205,26 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Latency</t>
+          <t>Policy Milestone</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>- core
-description: Period between the end of sensing of a Phenomenon to the beginning of availability of a specific product.</t>
+          <t>- high-impact
+description: Markers of significant progress in addressing specific issues, or crucial decision points where significant choices are made within a policy process.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Period between the end of sensing of a Phenomenon to the beginning of availability of a specific product.</t>
+          <t>Markers of significant progress in addressing specific issues, or crucial decision points where significant choices are made. Concrete examples include: policy planning and proposing, impact assessment, implementation, or implementation cycles (e.g., Water Framework Directive, Marine Strategy Framework Directive), achievement of Policy Objectives and Policy Targets, and evaluating and improving existing laws.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>- ?</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -3174,26 +3247,31 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Access</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>- core
-description: Service to disseminate Data.</t>
+          <t>- base
+description: Element of a type domain.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Service to disseminate Data.</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
+          <t>Element of a type domain.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>- A Value may consider a possible state of an object within a class or type (domain).
+- A data value is an instance of a data type, a value without identity.</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO/IEC 19501:2005, 0000_5</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -3216,26 +3294,26 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Phenomenon</t>
+          <t>Collection Update</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>- base
-description: Entity with at least one Property referenced by an identifier.</t>
+          <t>- core
+- approved</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Entity with at least one Property referenced by an identifier.</t>
+          <t>Minor revisions to a relatively small number of products within a collection for the purpose of correcting errors and maintaining consistent quality.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>- KCEO, modified after Wikipedia and the Columbia Encyclopaedia 2008</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -3258,37 +3336,30 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Earth Spheres</t>
+          <t>Laboratory Observation</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>- core
-description: Spheres dividing planet Earth into subsystems, which are collectives of (physical) matter sharing specific traits.</t>
+description: Usually in-situ observations in which the Object or Phenomenon is isolated from other systems or altered in its original conditions or environment.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Spheres dividing planet Earth into subsystems, which are collectives of (physical) matter sharing specific traits.</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>- Atmosphere
-- Hydrosphere
-- Cryosphere
-- Biosphere
-- Lithosphere
-- Anthroposphere</t>
-        </is>
-      </c>
+          <t>Usually in-situ observations in which the Object or Phenomenon is isolated from other systems or altered in its original conditions or environment.</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>- It is important to consider that Laboratory Observations are typically conducted in controlled conditions, allowing for isolation or alteration of the Object or Phenomenon from its natural environment or other systems.</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>- Hugget, R., et al., 2024, DOI: 10.1177/03091333241275465
-- Guth, P., et al., 2021, https://doi.org/10.3390/rs13183581
-- Martin, Y.E., et al., 2012</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
@@ -3311,33 +3382,20 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Environmental Process</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>- base
-description: Element of a type domain.</t>
+          <t>- core
+description: ""</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Element of a type domain.</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>- A Value may consider a possible state of an object within a class or type (domain).
-- A data value is an instance of a data type, a value without identity.</t>
-        </is>
-      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>- ISO/IEC 19501:2005, 0000_5</t>
-        </is>
-      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
@@ -3358,34 +3416,26 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Timeliness</t>
+          <t>Measurement Uncertainty</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>- core
-description: Period between the moment of requesting information and the moment of availability of information.</t>
+description: Uncertainty associated with the method of Measurement.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Period between the moment of requesting information and the moment of availability of information.
-- Near Real-Time (NRT): delivered less than 3 hours after requesting information.
-- Slow-Time Critical (STC): delivered within 48 hours after requesting information.
-- Non-Time Critical (NTC): typically delivered within 1 month after requesting information.</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>- In some contexts also known as delivery time.
-- C3S URDB describes timeliness as "the ability of the publish/subscribe middleware to provide the expected service within known time bounds".</t>
-        </is>
-      </c>
+          <t>Uncertainty associated with the method of Measurement.</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>- Adapted from ESA S3 User Guide</t>
+          <t>- CEOS Wiki adopted from JCGM GUM</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
@@ -3408,59 +3458,47 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Auxiliary Data</t>
+          <t>Temporal Revisit</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Interval between successive observations.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Data that enhance the processing and utilisation of main Sensor Data. Auxiliary Data are usually not captured by the same Data collection Process or on the same platform as the main Sensor Data. Examples include meteorological Data received from ECMWF/Met Offices or DEMs. Auxiliary Data help in Data processing, but are also Data sets in their own right.</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
+          <t>Interval between successive observations.</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>- In Remote Sensing it is also called repeat cycle.
+- More generally it is known as temporal sampling interval.</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>| Entry format example | Valid unit                     |
+|----------------------|-------------------------------|
+| 1 s, 2 h             | second, hour, day, month, year |</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>- ESA/CEOS?, modified
-- ENMAP Glossary of Terms, https://www.enmap.org/Data/doc/EnMAP_Terms.pdf, 20210624
-- EO Data Stewardship Glossary</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>Data required to perform processing of Sensor Data which is not obtained from the Sensor itself. Includes: (a) Data provided by the spacecraft (e.g. orbit Position and velocity, attitude, instrument house-keeping Data, on-board time); (b) Data not available from on-board sources.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>For EnMAP, this includes (a) orbit files, attitude files, Calibration Data, instrument house-keeping Data; (b) atmospheric parameters, reference images.</t>
-        </is>
-      </c>
+          <t>- KCEO</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>- ENMAP Glossary of Terms, https://www.enmap.org/Data/doc/EnMAP_Terms.pdf, 20210624
-- EO Data Stewardship Glossary</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>Data required for instrument processing that does not originate in the instrument itself or from the satellite. Some Auxiliary Data will be generated in the ground segment, whilst other Data will be provided from external sources.</t>
-        </is>
-      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>- CEOS-ARD PFS template 20220302</t>
-        </is>
-      </c>
+      <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
@@ -3473,32 +3511,30 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Area of Interest</t>
+          <t>Period Identifier</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Temporal reference in the form of a label or code that identifies a Period.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Zone in 2D or 3D for which the Information or Data is requested. It can be discontinuous in space — in other words it can consist of the union of many separate zones (e.g., Natural Reserves in Africa, Urban environments, etc.). The attribute indicates a request for spatially complete Data within the AOI zone(s).</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>| Type                                    | Entry format example              | Valid units |
-|-----------------------------------------|-----------------------------------|-------------|
-| Geographical/administrative identifier  | NUTS3, LAU, Natura 2000 site      | unitless    |</t>
-        </is>
-      </c>
+          <t>Temporal reference in the form of a label or code that identifies a Period.</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>- Period Identifiers are the temporal equivalent of geographic identifiers as specified in ISO 19912.</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO 19170:2021</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
@@ -3521,40 +3557,38 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Quantity</t>
+          <t>Area of Interest</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>- base
-description: Property having a magnitude that can be expressed as a number from a continuous and contiguous range and a reference.</t>
+          <t>- core
+- approved</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Property having a magnitude that can be expressed as a number from a continuous and contiguous range and a reference.</t>
+          <t>Zone in 2D or 3D for which the Information or Data is requested. It can be discontinuous in space — in other words it can consist of the union of many separate zones (e.g., Natural Reserves in Africa, Urban environments, etc.). The attribute indicates a request for spatially complete Data within the AOI zone(s).</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>| Type                                    | Entry format example              | Valid units |
+|-----------------------------------------|-----------------------------------|-------------|
+| Geographical/administrative identifier  | NUTS3, LAU, Natura 2000 site      | unitless    |</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>- ISO/IEC Guide 99:2007, 1.1, modified — Notes omitted</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Property whose instances can be compared by ratio or only by order.</t>
-        </is>
-      </c>
+          <t>- KCEO</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>- gEOGlos (VIM4 Notes omitted)</t>
-        </is>
-      </c>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
@@ -3571,30 +3605,34 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Final Product Version</t>
+          <t>Timeliness</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>- core
-description: Product within an EO Collection that is not expected to be updated.</t>
+description: Period between the moment of requesting information and the moment of availability of information.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Product within an EO Collection that is not expected to be updated.</t>
+          <t>Period between the moment of requesting information and the moment of availability of information.
+- Near Real-Time (NRT): delivered less than 3 hours after requesting information.
+- Slow-Time Critical (STC): delivered within 48 hours after requesting information.
+- Non-Time Critical (NTC): typically delivered within 1 month after requesting information.</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>- In its production, all of the prerequisite auxiliary data were used as input.</t>
+          <t>- In some contexts also known as delivery time.
+- C3S URDB describes timeliness as "the ability of the publish/subscribe middleware to provide the expected service within known time bounds".</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- Adapted from ESA S3 User Guide</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
@@ -3617,31 +3655,26 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Hydrosphere</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>- controversial
-description: Act of determining the Value of a Property by interacting in a reproducible way with the Phenomenon using a Sensor.</t>
+          <t>- core
+description: The masses of liquid water, such as oceans, lakes, and rivers.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Act of determining the Value of a Property by interacting in a reproducible way with the Phenomenon using a Sensor.</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>- The result of an Observation is a Value complemented by an Uncertainty, often itself being referred to as 'observation'.
-- An Observation result represents a Sample of the Phenomenon (otherwise it would be identical with the Phenomenon).</t>
-        </is>
-      </c>
+          <t>The masses of liquid water, such as oceans, lakes, and rivers.</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
@@ -3664,56 +3697,36 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Characteristic</t>
+          <t>Accuracy</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>- base
+          <t>- core
 - approved</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Distinguishing Feature.</t>
+          <t>Proximity of Measurement results to the accepted Value; precision is the degree to which repeated or reproducible measurements under unchanged conditions show the same results.</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>- A Characteristic can be inherent or assigned.
-- A Characteristic can be qualitative or quantitative.
-- There are various classes of Characteristics, such as the following:
-  - physical (e.g. mechanical, electrical, chemical, biological);
-  - sensory (e.g. relating to smell, touch, taste, sight, hearing);
-  - behavioural (e.g. courtesy, honesty, veracity);
-  - temporal (e.g. punctuality, reliability, availability);
-  - ergonomic (e.g. physiological characteristic or related to human safety);
-  - functional (e.g. maximum speed of an aircraft).</t>
+          <t>- In essence, Accuracy reflects how close measurements are to the accepted Value, while precision gauges the reliability and consistency of those measurements.</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>- ISO 9000:2005, 3.5.1</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Abstraction of a Property of an Object or of a set of objects.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>- Characteristics are used for describing Concepts.</t>
-        </is>
-      </c>
+          <t>- BS ISO 5725-1</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>- ISO 1087-1:2000, 3.2.4; ISO 19146:2010(E); https://www.iso.org/standard/20057.html</t>
-        </is>
-      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
@@ -3730,26 +3743,26 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Geosphere</t>
+          <t>Traceability</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>- core
-description: The masses of minerals that constitute planet Earth.</t>
+description: Property of a measurement result whereby the result can be related to a reference through a documented unbroken chain of calibrations each contributing to the measurement uncertainty.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>The masses of minerals that constitute planet Earth.</t>
+          <t>Property of a measurement result whereby the result can be related to a Reference through a documented unbroken chain of calibrations, each contributing to the measurement uncertainty.</t>
         </is>
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- https://www.isobudgets.com/Measurement-traceability-complying-iso-17025-requirements/</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
@@ -3772,26 +3785,26 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Spectral Resolution</t>
+          <t>Biosphere</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>- core
-description: Measure of the ability to resolve features in the electromagnetic spectrum.</t>
+- approved</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Measure of the ability to resolve features in the electromagnetic spectrum.</t>
+          <t>Masses of living organisms, such as vegetation and animals, including dead but still connected parts such as roots, trunks or branches.</t>
         </is>
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
@@ -3814,26 +3827,30 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Hydrosphere</t>
+          <t>Update Frequency</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>- core
-description: The masses of liquid water, such as oceans, lakes, and rivers.</t>
+description: Frequency at which the product is available to users.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>The masses of liquid water, such as oceans, lakes, and rivers.</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr"/>
+          <t>Frequency at which the product is available to users.</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>- Also known in product catalogues as dissemination frequency.</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
@@ -3856,33 +3873,26 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Time of Year</t>
+          <t>Lithosphere</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>- core
-description: Time of the year at which the variable is observed or simulated by a model.</t>
+description: The solid, inanimate outer layer of the Geosphere. For the purposes of Earth Observation, includes soils ('pedosphere').</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Time of the year at which the variable is observed or simulated by a model.</t>
+          <t>The solid, inanimate outer layer of the Geosphere. For the purposes of Earth Observation, the Lithosphere is considered to include soils ('pedosphere').</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>| Type      | Entry format example | Valid unit     |
-|-----------|----------------------|----------------|
-| timestamp | m/d                  | Not Applicable |
-| timerange | m/d - m/d            | Not Applicable |</t>
-        </is>
-      </c>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -3905,24 +3915,24 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Path</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>- base
-description: "Line defined in an algorithmic way using at least two positions (can be open-ended). Alternative: line connecting two positions in an algorithmic way (limited by end points)."</t>
+description: The result of organisation, interpretation, categorisation, classification, or some other form of processing of Data attaching to it a certain meaning that can be understood by the addressee.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Line defined in an algorithmic way using at least two positions (can be open-ended). Alternative: line connecting two positions in an algorithmic way (limited by end points).</t>
+          <t>The result of organisation, interpretation, categorisation, classification, or some other form of processing of Data attaching to it a certain meaning that can be understood by the addressee.</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>- A Path is a 1-dimensional Place.</t>
+          <t>- Information depends on Data and is targeted.</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
@@ -3951,19 +3961,19 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Spatial Consistency</t>
+          <t>Temporal Consistency</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>- core
-description: Condition where the spatial statistical properties of the data depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
+description: Condition where the temporal statistical properties of the sample depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Condition where the spatial statistical properties of the data depend only on the underlying physical processes and not on other factors such as fusing different products or sensors. Also, the validity of the assumptions of the procedure to produce information holds true across the whole spatial range.</t>
+          <t>Condition where the temporal statistical properties of the Sample depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -3993,30 +4003,31 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cell</t>
+          <t>Metadata</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Data describing other data, providing an understanding of the content and utility of a product or collection.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Spatial, spatio-temporal zone or temporal unit of geometry with dimensionality greater than 0, associated with a zone.</t>
+          <t>Data describing other data, providing an understanding of the content and utility of a product or collection.</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>- Cells are the unit of geometry in a DGGS, and the geometry of the region of space-time occupied by a zone is a Cell.</t>
+          <t>- Metadata may be used to select data for a particular scientific investigation.
+- Metadata is intended as information describing significant aspects of a resource (Earth Observation space data in this context). They are created for the purposes of data search, discovery and access management and may exist at various levels, typically from data collection through to the individual variables of each product in a collection.</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>- ISO 19170:2021</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
@@ -4039,26 +4050,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Business Continuity</t>
+          <t>Spatial Resolution</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: ''</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>An organisation's readiness to continue functioning during times of disruption.</t>
-        </is>
-      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
@@ -4081,31 +4088,26 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Derivative Product</t>
+          <t>Phenomenon</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>- core
-description: Product additionally processed from baseline or unenhanced mission data.</t>
+          <t>- base
+description: Entity with at least one Property referenced by an identifier.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Product additionally processed from baseline or unenhanced mission data.</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>- Generally either a compilation of time-series data (e.g., all time, annual, monthly or seasonal summary data, &gt; Level 3) or thematic versions of each individual data tile of baseline data.
-- Derived products are citable via a Digital Object Identifier (DOI).</t>
-        </is>
-      </c>
+          <t>Entity with at least one Property referenced by an identifier.</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- KCEO, modified after Wikipedia and the Columbia Encyclopaedia 2008</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
@@ -4128,26 +4130,26 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Policy Objective</t>
+          <t>Geolocation Information</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>- high-impact
-description: Desired outcome that policymakers wish to achieve.</t>
+          <t>- core
+description: Information used to determine geographic Location.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Desired outcome that policymakers wish to achieve.</t>
+          <t>Information used to determine geographic Location.</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO 19130-1:2018, 3.34</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
@@ -4170,62 +4172,57 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Verification</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>- core
-description: Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
+description: Provision of objective evidence that a given item fulfils specified requirements.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
+          <t>Provision of objective evidence that a given item fulfils specified requirements.</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
+          <t>- When applicable, measurement uncertainty should be taken into consideration.
+- The item may be, e.g. a Process, measurement procedure, material, compound, or measuring system.
+- The specified requirements may be, e.g. that a manufacturer's specifications are met.
+- Verification should not be confused with Calibration. Not every verification is a Validation.</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>- ISO/TS 19101‑2:2008, 4.41</t>
+          <t>- ISO/IEC Guide 99:2007, 2.44</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Process aimed at verifying that the specified requirements are achieved or compliant. Involves comparing mission products with representative reference data, considering various observation conditions, ensuring the quality and traceability of the reference data used.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
-        </is>
-      </c>
+          <t>Evaluation of whether or not a product, service, or system complies with a regulation requirement, specification, or imposed condition. Often an internal Process.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
-          <t>- BIPM; QA4EO; ESA?, modified</t>
+          <t>- EU-US Land Imaging EO Collaboration</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Assurance that a product, service, or system meets the needs of the customer and other identified stakeholders. Often involves acceptance and suitability with external customers.</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
-        </is>
-      </c>
+          <t>Means to evaluate the reliability of the data in the absence of a reference dataset, allowing for an assessment of its standalone performance. Involves confirming the consistency and internal coherence of the data without direct comparison to external reference sources.</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr">
         <is>
-          <t>- EU-US Land Imaging EO Collaboration</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="P81" t="inlineStr"/>
@@ -4240,35 +4237,26 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Temporal Extent</t>
+          <t>Property</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>- core
-description: Period during which data was collected, observations were made, or for which the model was run.</t>
+          <t>- base
+description: Observable Trait.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Period during which data was collected, observations were made, or for which the model was run.</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>- In W3C this is the definition of temporal coverage.
-- Time Period covered by a series of observations inclusive of the specified date/time indications (measurement history). Defined based on the beginning and end dates of observations.</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>- WIGOS Metadata</t>
-        </is>
-      </c>
+          <t>Observable Trait.</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>- Adapted from W3C</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
@@ -4291,26 +4279,26 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Traceability</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>- core
-description: Property of a measurement result whereby the result can be related to a reference through a documented unbroken chain of calibrations each contributing to the measurement uncertainty.</t>
+          <t>- base
+description: Entity with a well-defined boundary and identity that encapsulates state and behaviour.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Property of a measurement result whereby the result can be related to a Reference through a documented unbroken chain of calibrations, each contributing to the measurement uncertainty.</t>
+          <t>Entity with a well-defined boundary and identity that encapsulates state and behaviour.</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>- https://www.isobudgets.com/Measurement-traceability-complying-iso-17025-requirements/</t>
+          <t>- ISO/IEC 19501:2005</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
@@ -4333,30 +4321,37 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Decommissioned Product</t>
+          <t>Time of Day</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>- core
-description: Products and collections that have been superseded by new versions and are no longer available.</t>
+description: Time of the day at which the variable or parameter is observed or simulated by a model.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Products and collections that have been superseded by new versions and are no longer available.</t>
+          <t>Time of the day at which the variable or parameter is observed or simulated by a model.</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>- Decommissioned products are no longer supported, i.e. corrections will not be made, new data will not be added, and support is not available.</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr"/>
+          <t>- In Remote Sensing it is also known as time of overpass.</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>| Type      | Entry format example | Valid unit |
+|-----------|----------------------|------------|
+| timestamp | 18:00 h (0–24)       | Hours      |
+| timerange | 18:00 – 20:00 h      | Hours      |</t>
+        </is>
+      </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
@@ -4379,31 +4374,26 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Grid</t>
+          <t>Obsolete Product or Collection</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>- core
-description: Network composed of two or more sets of curves in which the members of each set intersect the members of the other sets in an algorithmic way.</t>
+description: Products or collections which have been superseded by later versions of a product or collection.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Network composed of two or more sets of curves in which the members of each set intersect the members of the other sets in an algorithmic way.</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>- The curves partition a space into grid cells or zones.
-- The intersection points of the curves are called nodes.</t>
-        </is>
-      </c>
+          <t>Products or collections which have been superseded by later versions of a product or collection.</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>- ISO 19123:2005, 4.1.23; Note 1 modified; Note 2 added</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
@@ -4426,36 +4416,40 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Measurement</t>
+          <t>Baseline</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>- core
-description: Observation of a Quantity.</t>
+- approved</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Observation of a Quantity.</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>- The Process of collecting a measurement is called measuring.</t>
-        </is>
-      </c>
+          <t>Reference Period, time or measure against which the Information is assessed or compared.</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>- GEOGlos (VIM ?, modified)</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>- KCEO</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Source data that has been processed to a common set of requirements and organised into a form that allows immediate analysis and interoperability through time and with other collections.</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
@@ -4472,30 +4466,31 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Catalogue</t>
+          <t>Earth Observation</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>- core
-- approved</t>
+          <t>- high-impact
+description: Science domain dealing with technologies and methods of collecting and analyzing observations about the different Earth spheres.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>System that provides users with discovery of information on which EO products can be obtained.</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>- A 'Product Catalogue' can organise products and collections with varying access levels depending on product and user type.</t>
-        </is>
-      </c>
+          <t>Science domain dealing with technologies and methods of collecting and analyzing observations about the different Earth spheres.</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>- Earth Observation (EO) can be categorised by location of the sensor into space-borne, air-borne, sea-borne, ground-based, underwater and underground EO.
+- Earth Observation (EO) includes Remote Sensing, such as satellite imagery, as well as in-situ observations, e.g., with ground-based devices.</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- Modified GEO definition [GEO (earthobservations.org)](https://earthobservations.org/resources#key)</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
@@ -4518,36 +4513,32 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Spectral Resolution</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>- core
-description: Phenomenon whose values for specific properties are known and understood with an Uncertainty significantly lower than that of the Observation with which it is compared.</t>
+description: Measure of the ability to resolve features in the electromagnetic spectrum.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Phenomenon whose values for specific properties are known and understood with an Uncertainty significantly lower (quantify?) than that of the Observation with which it is compared.</t>
+          <t>Measure of the ability to resolve features in the electromagnetic spectrum.</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Sort of data acquired with an Uncertainty significantly lower (quantify?) than that of the data it is being compared with.</t>
-        </is>
-      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>- VIM?, modified</t>
-        </is>
-      </c>
+      <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
@@ -4564,30 +4555,26 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Laboratory Observation</t>
+          <t>Near Real Time Data</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>- core
-description: Usually in-situ observations in which the Object or Phenomenon is isolated from other systems or altered in its original conditions or environment.</t>
+          <t>- high-impact
+description: Data available for use with a specified (small and application dependent) latency, typically 3 hours for meteorological applications.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Usually in-situ observations in which the Object or Phenomenon is isolated from other systems or altered in its original conditions or environment.</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>- It is important to consider that Laboratory Observations are typically conducted in controlled conditions, allowing for isolation or alteration of the Object or Phenomenon from its natural environment or other systems.</t>
-        </is>
-      </c>
+          <t>Data available for use with a specified (small and application dependent) latency, typically 3 hours for meteorological applications.</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
@@ -4610,32 +4597,38 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sample</t>
+          <t>Measurand</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>- controversial
-description: Subset of one or more entities.</t>
+          <t>- core
+description: Particular Quantity subject to Measurement.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Subset of one or more entities.</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>- A Sample may be spatial, temporal, spectral, or in any other dimension or Trait.
-- Each Sample is contiguous, i.e. it does not consist of more than one discontinuous geometry in any dimension.
-- The Process of obtaining a Sample is called sampling.</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr"/>
+          <t>Particular Quantity subject to Measurement.</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>| Step | Process description |
+| :----- | :--------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------- |
+| (Raw) | The complete and unaltered/unprocessed set of Data acquired by one or several sensors on a platform |
+| M/0 uncalibrated | Unaltered/unprocessed Level 0 (main) Sensor Data annotated with processed Ancillary Data and supplemented by Auxiliary Data (including radiometric and geometric Calibration coefficients and geo-referencing parameters) allowing further processing to higher Levels. |
+| M/1 Sensor-calibrated | Level M/0 Sensor Data which have been calibrated (ideally traceable to SI) and spatially aligned (co-located, eventually co-gridded) to represent at-Sensor measurements (Value and Uncertainty) in Sensor nominal spatiotemporal sampling, supplemented by appropriate ancillary data. |
+| M/2 target-calibrated | Level M/1 Data processed to represent geophysical Property values (and uncertainties) for a specified target (Object, Feature of interest, e.g. surface reflectance, apparent temperature) derived from M/1 Sensor Data, as much as possible maintaining the sensors nominal spatial and temporal sampling (Observation preserving). |
+| M/3 homogenised | Level M/1 or M/2 Data which have been generalised and integrated across one or several platforms and acquisitions to achieve an increased, more regular or in any other form enhanced spatial or temporal coverage in which states geophysical values agnostic of the originally acquiring Sensor and Observation condition and thus directly comparable. This homogenisation and fusion may include measurand re-Calibration to external standards and references including use of modelling, aggregation and interpolation. |
+| M/4 derived/inferred | Model output or results from analyses of Level M/3 (or lower level) Data i.e., attributes that might not be directly observable by the Sensor(s) but are derived from observations in combination with other external incl. non-observational Data using techniques like modelling or machine learning (AI). |
+From http://doi.org/10.2760/46796</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- VIM: 1993, 2.6</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
@@ -4658,30 +4651,26 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Trait</t>
+          <t>Latency</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>- base
-description: Characteristic belonging to an entity and referenced by an identifier.</t>
+          <t>- core
+description: Period between the end of sensing of a Phenomenon to the beginning of availability of a specific product.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Characteristic belonging to an entity and referenced by an identifier.</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>- Traits can be objective (inherent?) in which case they are also observable and called properties. Traits which are not observable (directly or indirectly) need to be assigned.</t>
-        </is>
-      </c>
+          <t>Period between the end of sensing of a Phenomenon to the beginning of availability of a specific product.</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>- Based on ISO 19143:2010, 4.21, ISO/IEC 2382:2015, 2121440, significantly modified, Note 1 added</t>
+          <t>- ?</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
@@ -4704,31 +4693,26 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Metadata</t>
+          <t>Policy Target</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>- core
-description: Data describing other data, providing an understanding of the content and utility of a product or collection.</t>
+          <t>- high-impact
+description: Specific level or rate set for the Policy Objective.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Data describing other data, providing an understanding of the content and utility of a product or collection.</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>- Metadata may be used to select data for a particular scientific investigation.
-- Metadata is intended as information describing significant aspects of a resource (Earth Observation space data in this context). They are created for the purposes of data search, discovery and access management and may exist at various levels, typically from data collection through to the individual variables of each product in a collection.</t>
-        </is>
-      </c>
+          <t>Specific level or rate set for the Policy Objective.</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
@@ -4751,30 +4735,26 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Backup</t>
+          <t>Policy Objective</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>- core
-- approved</t>
+          <t>- high-impact
+description: Desired outcome that policymakers wish to achieve.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>General practice of making copies of current baseline and derived products of EO Collections at specified time intervals, and storing those copies in a manner that will not affect the data if the primary distribution environment is compromised.</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>- The emphasis is on the ability to retrieve a copy of the entire EO Collection on demand if the original data is lost or compromised.</t>
-        </is>
-      </c>
+          <t>Desired outcome that policymakers wish to achieve.</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
@@ -4797,30 +4777,26 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Archive</t>
+          <t>Forecast Range</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: The forecast period.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>System that stores data products, guaranteeing their preservation for future use.</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>- This function includes all operations to identify, store and retrieve the data and ensure their integrity.</t>
-        </is>
-      </c>
+          <t>The forecast period.</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
@@ -4843,26 +4819,26 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Biosphere</t>
+          <t>Quality Indicator</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Indicator providing sufficient information to allow all users to readily evaluate the fitness for purpose of the data or derived product.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Masses of living organisms, such as vegetation and animals, including dead but still connected parts such as roots, trunks or branches.</t>
+          <t>Indicator providing sufficient information to allow all users to readily evaluate the fitness for purpose of the data or derived product. May be a number, set of numbers, graph, Uncertainty budget, or a simple flag.</t>
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- CEOS Wiki</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
@@ -4885,26 +4861,26 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Impact</t>
+          <t>User Interface</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>- core
-description: Regarded long-term according to X. However, in the Horizon Europe Missions terminology, regarded short-term.</t>
+description: Set of all the components of an interactive system that provide information and controls for the user to accomplish specific tasks with the interactive system.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Regarded long-term according to X. However, in the Horizon Europe Missions terminology, regarded short-term.</t>
+          <t>Set of all the components of an interactive system that provide information and controls for the User to accomplish specific tasks with the interactive system.</t>
         </is>
       </c>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO 9241-110:2020, 3.10</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
@@ -4927,26 +4903,30 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Obsolete Product or Collection</t>
+          <t>Stability</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>- core
-description: Products or collections which have been superseded by later versions of a product or collection.</t>
+description: Maximum acceptable change in Uncertainty per decade.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Products or collections which have been superseded by later versions of a product or collection.</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr"/>
+          <t>Maximum acceptable change in Uncertainty per decade.</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>- GCOS uses bias or systematic errors instead of Uncertainty.</t>
+        </is>
+      </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- Modified from GCOS 2022</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
@@ -4969,26 +4949,26 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Measurement Uncertainty</t>
+          <t>Classification System</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>- core
-description: Uncertainty associated with the method of Measurement.</t>
+- approved</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Uncertainty associated with the method of Measurement.</t>
+          <t>Nomenclature used to classify Information into categorical thematic classes (e.g., EUNIS, MAES ecosystems, Corine Land Cover, LCCS).</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>- CEOS Wiki adopted from JCGM GUM</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
@@ -5011,17 +4991,21 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Spatial Resolution</t>
+          <t>Spatial Consistency</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>- core
-description: ''</t>
+description: Condition where the spatial statistical properties of the data depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Condition where the spatial statistical properties of the data depend only on the underlying physical processes and not on other factors such as fusing different products or sensors. Also, the validity of the assumptions of the procedure to produce information holds true across the whole spatial range.</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
@@ -5049,27 +5033,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>In-Situ Observation</t>
+          <t>Expanded Uncertainty</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>- controversial
-description: Observations performed in the same Place where a Phenomenon occurs, normally without isolating it from other systems or altering its pre-Observation state.</t>
+          <t>- core
+description: Standard Uncertainty multiplied by a coverage factor k, chosen to obtain a desired level of confidence.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Observations performed in the same Place where a Phenomenon occurs, normally without isolating it from other systems (its environment) or altering its pre-Observation state.</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>- The main Characteristic of such observations is that distance has no or only negligible (within Uncertainty) influence on the Value of the Property observed. In-Situ Observations therefore often require either direct physical contact or small distances between a Sensor and the observed Phenomenon.
-- Observations not fulfilling these conditions are considered Remote Sensing.</t>
-        </is>
-      </c>
+          <t>Standard Uncertainty multiplied by a coverage factor, k. The coverage factor is chosen to obtain a desired level of confidence. Most commonly a 95% confidence interval is chosen. For a Gaussian distribution, this is achieved with a coverage factor k = 2. (Note that strictly this provides a 95.45% confidence interval.)</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
@@ -5096,28 +5075,29 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Earth Observation Product</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>- core
-description: Direct output from standardized satellite data processing chains (indicative levels 2 and 3), representing fundamental geophysical and biophysical variables.</t>
+description: Device or instrument suited (through physical/chemical interaction) to measure one or more properties of a Phenomenon and thus collect factual/objective data.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Direct output from standardized satellite data processing chains (indicative levels 2 and 3), representing fundamental geophysical and biophysical variables. These products demonstrate direct Traceability to original satellite measurements through rigorous Calibration and Validation processes. The processing methodology prioritizes the conversion of raw sensor data into quantifiable physical measurements, maintaining strict adherence to standardized processing protocols and Validation requirements.</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>- Soil moisture from microwave sensors
-- Forest canopy height from LiDAR data</t>
-        </is>
-      </c>
+          <t>Device or instrument suited (through physical/chemical interaction) to measure one or more properties of a Phenomenon and thus collect factual/objective data.</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>- Sensing is therefore a synonym for Observation (the Process).
+- As by their definition, sensors perform sampling.
+- Sensors used to obtain measurements must be calibrated and provide uncertainties.</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
           <t>- KCEO</t>
@@ -5143,30 +5123,26 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Spatial Completeness</t>
+          <t>Minimum Mapping Width</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>- core
-description: Presence or absence of gaps, which are missing values in an otherwise continuous spatial data series.</t>
+description: The width of the smallest linear Feature that is still represented on a map.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Presence or absence of gaps, which are missing values in an otherwise continuous spatial data series.</t>
+          <t>The width of the smallest linear Feature that is still represented on a map.</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>- Surface soil moisture retrieved from microwave satellite sensors may present gaps in mountainous terrains.</t>
-        </is>
-      </c>
+      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- CGLS</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
@@ -5189,30 +5165,30 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Geocoding</t>
+          <t>Backup</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>- core
-description: Translation of one form of Location into another.</t>
+- approved</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Translation of one form of Location into another.</t>
+          <t>General practice of making copies of current baseline and derived products of EO Collections at specified time intervals, and storing those copies in a manner that will not affect the data if the primary distribution environment is compromised.</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>- Geocoding usually refers to the translation of "address" or "intersection" to "direct Position." Many service providers also include a "reverse geocoding" interface to their geocoder, thus extending the definition of the service as a general translator of Location. Because routing services use internal Location encodings not usually available to others, a geocoder is an integral part of the internals of such a service.</t>
+          <t>- The emphasis is on the ability to retrieve a copy of the entire EO Collection on demand if the original data is lost or compromised.</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>- ISO 19133:2005; https://www.iso.org/standard/32551.html</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
@@ -5235,44 +5211,42 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Georectifying</t>
+          <t>Temporal Resolution</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>- core
-description: Correcting for positional displacement with respect to the surface of the Earth.</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Orthorectifying</t>
-        </is>
-      </c>
+description: Observation or model output representing regular intervals, specifying the length of the interval that determines the smallest event or process that can be resolved.</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Correcting for positional displacement with respect to the surface of the Earth.</t>
+          <t>Observation or model output representing regular intervals, specifying the length of the interval that determines the smallest event or Process that can be resolved (e.g., the Period between observations, the time steps in a model).</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>- Source: ISO 19115-2:2019, 3.11; ISO 19115-2:2009(E); https://www.iso.org/standard/67039.html, modified</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>The correction of sample locations to achieve some sort of geometric regularity, e.g., a regular 2D geographic grid.</t>
-        </is>
-      </c>
+          <t>- WIGOS 2019 distinguishes between sampling time Period, as the Period over which a Measurement is taken, and temporal sampling interval as the time Period between the beginning of consecutive sampling periods. Temporal Resolution in this Glossary is equivalent to sampling time Period as used by WIGOS.</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>| Entry format example | Valid unit                     |
+|----------------------|-------------------------------|
+| 1 s, 2 h, 1 m        | second, hour, day, month, year |</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
+      <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
@@ -5289,26 +5263,26 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data Licencing</t>
+          <t>Place</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>- core
-description: Legal instrument by which a copyright holder may grant rights over the protected work.</t>
+          <t>- base
+description: Part of any space referenced by an identifier.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Legal instrument by which a copyright holder may grant rights over the protected work. Data and content is open if it is subject to an explicitly-applied licence that conforms to the Open Definition. A range of standard open licences are available, such as the Creative Commons CC-BY licence, which requires only attribution.</t>
+          <t>Part of any space referenced by an identifier.</t>
         </is>
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>- CEOS Wiki</t>
+          <t>- ISO 19155:2012, 4.8</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
@@ -5331,36 +5305,45 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Period</t>
+          <t>Ancillary Data</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>- base
-description: Particular era or span of time.</t>
+          <t>- core
+- approved</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Particular era or span of time.</t>
+          <t>Data acquired on the same platform but not obtained from the main Sensor itself (usually provided as part of Level 0 Data), with the primary purpose of serving the processing of main instrument Data (e.g. Position and velocity of platform).</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>- Periods are intervals named with a Period Identifier.</t>
+          <t>This can be divided into data referred to as spacecraft 'engineering', 'core housekeeping' or 'subsystem' data obtained from other parts of the platform, and includes parameters such as orbit position and velocity, attitude and its range of change, time, temperatures, pressures, jet firings, water dumps, internally produced magnetic fields, and other environmental measurements. Ancillary refers to data that exist purely to serve the data processing.</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>- ISO 19170:2021</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr"/>
+          <t>- ESA/CEOS?, modified
+- EO Data Stewardship Glossary</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Data other than instrument measurements, originating in the instrument itself or from the satellite, required to perform processing of the Data. Includes orbit Data, attitude Data, time Information, and spacecraft engineering Data, Calibration Data, Data quality Information, and Data from other instruments or earth system models.</t>
+        </is>
+      </c>
       <c r="I106" t="inlineStr"/>
       <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>- CEOS-ARD PFS template 20220302</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
@@ -5377,26 +5360,31 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Collection Upgrade</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>- core
-- approved</t>
+          <t>- controversial
+description: Act of determining the Value of a Property by interacting in a reproducible way with the Phenomenon using a Sensor.</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>New and improved major version of all products within a collection due to comprehensive reprocessing.</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr"/>
+          <t>Act of determining the Value of a Property by interacting in a reproducible way with the Phenomenon using a Sensor.</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>- The result of an Observation is a Value complemented by an Uncertainty, often itself being referred to as 'observation'.
+- An Observation result represents a Sample of the Phenomenon (otherwise it would be identical with the Phenomenon).</t>
+        </is>
+      </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
@@ -5419,30 +5407,31 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Grid</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>- base
-description: Abstraction of real-world phenomena.</t>
+          <t>- core
+description: Network composed of two or more sets of curves in which the members of each set intersect the members of the other sets in an algorithmic way.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Abstraction of real-world phenomena.</t>
+          <t>Network composed of two or more sets of curves in which the members of each set intersect the members of the other sets in an algorithmic way.</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>- A feature may occur as a type or an instance.</t>
+          <t>- The curves partition a space into grid cells or zones.
+- The intersection points of the curves are called nodes.</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>- ISO 19101-1:2014, 4.1.11, modified</t>
+          <t>- ISO 19123:2005, 4.1.23; Note 1 modified; Note 2 added</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
@@ -5465,36 +5454,44 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Custodian</t>
+          <t>User</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>- core
-description: Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
+description: Entity (person, organization, institution, etc.) that is requesting data or information with certain characteristics described by needs and/or requirements.</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>- See also Steward.</t>
-        </is>
-      </c>
+          <t>In the context of the KCEO, entity (person, organization, institution, etc.) that is requesting data or information with certain characteristics described by needs and/or requirements.</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
+          <t>- KCEO</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>External person, institution or system that consumes provided services.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>- Includes Data Access or Science and Service Exploitation Platforms provided by a payload data ground segment.</t>
+        </is>
+      </c>
       <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>- EO Data Stewardship Glossary</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
@@ -5511,26 +5508,35 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Anthroposphere</t>
+          <t>Remote Sensing</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>- core
-- approved</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr"/>
+          <t>- controversial
+description: Type of Observation performed at a significant distance from a Phenomenon.</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Remote Observation</t>
+        </is>
+      </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>One of the Earth spheres consisting predominantly of matter processed by humans, such as construction wood, bricks, concrete, asphalt, glass, or plastics.</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr"/>
+          <t>Type of Observation performed at a significant distance from a Phenomenon.</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>- 'Significant' in this context means that the distance has, or may have, a non-negligible impact on the Value of the Property observed.
+- The effect of the distance on the acquired data is the main distinction criterion between 'remote' and 'in-situ' observations.</t>
+        </is>
+      </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
@@ -5553,44 +5559,37 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>Earth Observation Product</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>- core
-description: Entity (person, organization, institution, etc.) that is requesting data or information with certain characteristics described by needs and/or requirements.</t>
+description: Direct output from standardized satellite data processing chains (indicative levels 2 and 3), representing fundamental geophysical and biophysical variables.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>In the context of the KCEO, entity (person, organization, institution, etc.) that is requesting data or information with certain characteristics described by needs and/or requirements.</t>
+          <t>Direct output from standardized satellite data processing chains (indicative levels 2 and 3), representing fundamental geophysical and biophysical variables. These products demonstrate direct Traceability to original satellite measurements through rigorous Calibration and Validation processes. The processing methodology prioritizes the conversion of raw sensor data into quantifiable physical measurements, maintaining strict adherence to standardized processing protocols and Validation requirements.</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>- Soil moisture from microwave sensors
+- Forest canopy height from LiDAR data</t>
+        </is>
+      </c>
       <c r="G111" t="inlineStr">
         <is>
           <t>- KCEO</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>External person, institution or system that consumes provided services.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>- Includes Data Access or Science and Service Exploitation Platforms provided by a payload data ground segment.</t>
-        </is>
-      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>- EO Data Stewardship Glossary</t>
-        </is>
-      </c>
+      <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
@@ -5607,30 +5606,30 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Steward</t>
+          <t>Trait</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>- core
-description: Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
+          <t>- base
+description: Characteristic belonging to an entity and referenced by an identifier.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
+          <t>Characteristic belonging to an entity and referenced by an identifier.</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>- See also Custodian.</t>
+          <t>- Traits can be objective (inherent?) in which case they are also observable and called properties. Traits which are not observable (directly or indirectly) need to be assigned.</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- Based on ISO 19143:2010, 4.21, ISO/IEC 2382:2015, 2121440, significantly modified, Note 1 added</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
@@ -5653,23 +5652,30 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Temporal Consistency</t>
+          <t>Time of Year</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>- core
-description: Condition where the temporal statistical properties of the sample depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
+description: Time of the year at which the variable is observed or simulated by a model.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Condition where the temporal statistical properties of the Sample depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
+          <t>Time of the year at which the variable is observed or simulated by a model.</t>
         </is>
       </c>
       <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>| Type      | Entry format example | Valid unit     |
+|-----------|----------------------|----------------|
+| timestamp | m/d                  | Not Applicable |
+| timerange | m/d - m/d            | Not Applicable |</t>
+        </is>
+      </c>
       <c r="G113" t="inlineStr">
         <is>
           <t>- KCEO</t>
@@ -5695,27 +5701,31 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Geospatial Data</t>
+          <t>In-Situ Observation</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>- core
-description: Data consisting of, derived from, or relating to information that is directly linked to specific geographical locations.</t>
+          <t>- controversial
+description: Observations performed in the same Place where a Phenomenon occurs, normally without isolating it from other systems or altering its pre-Observation state.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Data consisting of, derived from, or relating to information that is directly linked to specific geographical locations.</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr"/>
+          <t>Observations performed in the same Place where a Phenomenon occurs, normally without isolating it from other systems (its environment) or altering its pre-Observation state.</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>- The main Characteristic of such observations is that distance has no or only negligible (within Uncertainty) influence on the Value of the Property observed. In-Situ Observations therefore often require either direct physical contact or small distances between a Sensor and the observed Phenomenon.
+- Observations not fulfilling these conditions are considered Remote Sensing.</t>
+        </is>
+      </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>- https://www.merriam-webster.com/dictionary/geospatial
-- https://isotc211.geolexica.org/Concepts/202/, accessed 20221010</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
@@ -5738,36 +5748,56 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Characteristic</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>- core
-description: Maximum acceptable change in Uncertainty per decade.</t>
+          <t>- base
+- approved</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Maximum acceptable change in Uncertainty per decade.</t>
+          <t>Distinguishing Feature.</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>- GCOS uses bias or systematic errors instead of Uncertainty.</t>
+          <t>- A Characteristic can be inherent or assigned.
+- A Characteristic can be qualitative or quantitative.
+- There are various classes of Characteristics, such as the following:
+  - physical (e.g. mechanical, electrical, chemical, biological);
+  - sensory (e.g. relating to smell, touch, taste, sight, hearing);
+  - behavioural (e.g. courtesy, honesty, veracity);
+  - temporal (e.g. punctuality, reliability, availability);
+  - ergonomic (e.g. physiological characteristic or related to human safety);
+  - functional (e.g. maximum speed of an aircraft).</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>- Modified from GCOS 2022</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
+          <t>- ISO 9000:2005, 3.5.1</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Abstraction of a Property of an Object or of a set of objects.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>- Characteristics are used for describing Concepts.</t>
+        </is>
+      </c>
       <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>- ISO 1087-1:2000, 3.2.4; ISO 19146:2010(E); https://www.iso.org/standard/20057.html</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
@@ -5784,26 +5814,30 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Property</t>
+          <t>Measurement</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>- base
-description: Observable Trait.</t>
+          <t>- core
+description: Observation of a Quantity.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Observable Trait.</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
+          <t>Observation of a Quantity.</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>- The Process of collecting a measurement is called measuring.</t>
+        </is>
+      </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- GEOGlos (VIM ?, modified)</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
@@ -5826,30 +5860,31 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Geographic Data</t>
+          <t>Preservation</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>- core
-description: Data with implicit or explicit reference to a Location relative to the Earth.</t>
+description: Processes and operations used to ensure data technical and intellectual survival through time.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Data with implicit or explicit reference to a Location relative to the Earth.</t>
+          <t>Processes and operations used to ensure data technical and intellectual survival through time.</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>- Geographic Information is also used as a term for information concerning phenomena implicitly or explicitly associated with a Location relative to the Earth.</t>
+          <t>- Grants data integrity, discoverability and accessibility, and facilitates its (re-)use in the long term.
+- Preservation is one of the tasks of data curation.</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>- ISO 19109:2015, 4.13; ISO 19109:2005</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
@@ -5872,111 +5907,62 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Uncertainty</t>
+          <t>Provisional Product</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>- core
-description: Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
+description: Products in a research and development phase not yet published into a standardized collection.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
+          <t>Products in a research and development phase not yet published into a standardized collection.</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>- GUM</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Non-negative parameter, associated with data, which characterizes the dispersion of the values of a Trait that could reasonably be attributed to a Phenomenon by means of sensing or modelling.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>- In case of quantitative (continuous) data the uncertainty may be, for example, a standard deviation (or a given multiple of it), or the half-width of an interval having a stated level of confidence (see e.g. Standard and Expanded Uncertainty).
-- For qualitative (categorical?) data, uncertainty may be expressed by commission and omission ('confusion matrix') or overall errors.</t>
-        </is>
-      </c>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>- Modified from GUM, VIM4:3.1, FIDUCEO, Notes added</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>Measure of the spread of the distribution of possible values.</t>
-        </is>
-      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
-      <c r="O118" t="inlineStr">
-        <is>
-          <t>- [FIDUCEO Glossary](https://research.reading.ac.uk/fiduceo/glossary/), VIM?, modified</t>
-        </is>
-      </c>
-      <c r="P118" t="inlineStr">
-        <is>
-          <t>Parameter, associated with the result of measurement, that characterizes the dispersion of values that could reasonably be attributed to the measurand.</t>
-        </is>
-      </c>
-      <c r="Q118" t="inlineStr">
-        <is>
-          <t>- When the quality of accuracy or precision of measured values, such as coordinates, is to be characterized quantitatively, the quality parameter is an estimate of the uncertainty of the measurement results. Because accuracy is a qualitative concept, one should not use it quantitatively, that is associate numbers with it; numbers should be associated with measures of uncertainty instead.</t>
-        </is>
-      </c>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr"/>
       <c r="R118" t="inlineStr"/>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>- ISO 19116:2004(E)</t>
-        </is>
-      </c>
-      <c r="T118" t="inlineStr">
-        <is>
-          <t>Parameter characterizing the dispersion of the values being attributed to a measurand, based on the information used.</t>
-        </is>
-      </c>
+      <c r="S118" t="inlineStr"/>
+      <c r="T118" t="inlineStr"/>
       <c r="U118" t="inlineStr"/>
       <c r="V118" t="inlineStr"/>
-      <c r="W118" t="inlineStr">
-        <is>
-          <t>- VIM4: 3.1</t>
-        </is>
-      </c>
+      <c r="W118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>User Interface</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>- core
-description: Set of all the components of an interactive system that provide information and controls for the user to accomplish specific tasks with the interactive system.</t>
+description: ""</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>Set of all the components of an interactive system that provide information and controls for the User to accomplish specific tasks with the interactive system.</t>
-        </is>
-      </c>
+      <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>- ISO 9241-110:2020, 3.10</t>
-        </is>
-      </c>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
@@ -5997,56 +5983,36 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Instrument Data</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>- core
-description: Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
+          <t>- high-impact
+description: Deliberate system of guidelines to guide decisions and achieve rational outcomes, implemented as a procedure or protocol and typically promulgated through official written documents.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>- These data consist of instrument science and engineering data, and possibly ancillary data. Instrument engineering data is produced by engineering sensor(s) of an instrument, used either for operating the instrument or for processing the science data generated by the instrument. Instrument science data is produced by the science sensor(s) of an instrument, usually constituting the basic reason for existence of an instrument.</t>
-        </is>
-      </c>
+          <t>Deliberate system of guidelines to guide decisions and achieve rational outcomes. Statement of intent implemented as a procedure or protocol. Typically promulgated through official written documents.</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>Data created by an instrument including scientific measurements and any engineering or ancillary data which may be included in the data packets.</t>
-        </is>
-      </c>
+          <t>- KCEO</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr"/>
       <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
-        </is>
-      </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>Data produced and transmitted by the science and engineering sensors of an instrument, and, in the spacecraft environment, any additional data packaged with the instrument's sensor data by virtue of services provided.</t>
-        </is>
-      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr">
-        <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
-        </is>
-      </c>
+      <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr"/>
       <c r="Q120" t="inlineStr"/>
       <c r="R120" t="inlineStr"/>
@@ -6059,38 +6025,30 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Measurand</t>
+          <t>Geographic Identifier</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>- core
-description: Particular Quantity subject to Measurement.</t>
+description: Spatial reference in the form of a label or code that identifies a Location.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Particular Quantity subject to Measurement.</t>
+          <t>Spatial reference in the form of a label or code that identifies a Location.</t>
         </is>
       </c>
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>| Step | Process description |
-| :----- | :--------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------- |
-| (Raw) | The complete and unaltered/unprocessed set of Data acquired by one or several sensors on a platform |
-| M/0 uncalibrated | Unaltered/unprocessed Level 0 (main) Sensor Data annotated with processed Ancillary Data and supplemented by Auxiliary Data (including radiometric and geometric Calibration coefficients and geo-referencing parameters) allowing further processing to higher Levels. |
-| M/1 Sensor-calibrated | Level M/0 Sensor Data which have been calibrated (ideally traceable to SI) and spatially aligned (co-located, eventually co-gridded) to represent at-Sensor measurements (Value and Uncertainty) in Sensor nominal spatiotemporal sampling, supplemented by appropriate ancillary data. |
-| M/2 target-calibrated | Level M/1 Data processed to represent geophysical Property values (and uncertainties) for a specified target (Object, Feature of interest, e.g. surface reflectance, apparent temperature) derived from M/1 Sensor Data, as much as possible maintaining the sensors nominal spatial and temporal sampling (Observation preserving). |
-| M/3 homogenised | Level M/1 or M/2 Data which have been generalised and integrated across one or several platforms and acquisitions to achieve an increased, more regular or in any other form enhanced spatial or temporal coverage in which states geophysical values agnostic of the originally acquiring Sensor and Observation condition and thus directly comparable. This homogenisation and fusion may include measurand re-Calibration to external standards and references including use of modelling, aggregation and interpolation. |
-| M/4 derived/inferred | Model output or results from analyses of Level M/3 (or lower level) Data i.e., attributes that might not be directly observable by the Sensor(s) but are derived from observations in combination with other external incl. non-observational Data using techniques like modelling or machine learning (AI). |
-From http://doi.org/10.2760/46796</t>
+          <t>- "Spain" is an example of a label (country name); "SW1-3AD" is an example of a code (postcode).</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>- VIM: 1993, 2.6</t>
+          <t>- ISO 19112:2019, 3.1.2</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
@@ -6113,26 +6071,37 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Policy Target</t>
+          <t>Earth Spheres</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>- high-impact
-description: Specific level or rate set for the Policy Objective.</t>
+          <t>- core
+description: Spheres dividing planet Earth into subsystems, which are collectives of (physical) matter sharing specific traits.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Specific level or rate set for the Policy Objective.</t>
+          <t>Spheres dividing planet Earth into subsystems, which are collectives of (physical) matter sharing specific traits.</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>- Atmosphere
+- Hydrosphere
+- Cryosphere
+- Biosphere
+- Lithosphere
+- Anthroposphere</t>
+        </is>
+      </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Hugget, R., et al., 2024, DOI: 10.1177/03091333241275465
+- Guth, P., et al., 2021, https://doi.org/10.3390/rs13183581
+- Martin, Y.E., et al., 2012</t>
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
@@ -6155,35 +6124,26 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Spatial Extent</t>
+          <t>Deprecated Product</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>- core
-description: Zone or region of space described by a geographic identifier in the form of a label or code, or by a bounding box, representing the maximum spatial boundary within which the user is requesting data.</t>
+description: Products and collections that have been superseded by a newer version and are still available, but whose use is discouraged since they will be decommissioned in the future.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Zone or region of space described by a geographic identifier in the form of a label or code, or by a bounding box. Represents the maximum extent (the spatial boundary or limits) within which the User is requesting data.
-The attribute represents the maximum spatial extent of the AOI, and in case the AOI is made of many discontinuous zones then it represents the maximum extent of the union of all the zones.</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>- WIGOS metadata standard defines it as the typical spatial georeferenced volume covered by the observations.</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>- If a User is requesting information about degradation of African protected sites, then the AOIs are the protected sites, and the spatial extent is the African continent.</t>
-        </is>
-      </c>
+          <t>Products and collections that have been superseded by a newer version and are still available, but whose use is discouraged since they will be decommissioned in the future.</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
-          <t>- Adapted from ISO 19170-1:2021</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
@@ -6206,26 +6166,26 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Provisional Product</t>
+          <t>Replicability</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>- core
-description: Products in a research and development phase not yet published into a standardized collection.</t>
+description: Property enabling other researchers to conduct an independent study with different data and similar but not identical methods, yet arriving at results that confirm the original study's hypothesis.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Products in a research and development phase not yet published into a standardized collection.</t>
+          <t>Property enabling other researchers to conduct an independent study with different data and similar but not identical methods, yet arriving at results that confirm the original study's hypothesis.</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- Craglia, M., et al. (2018).</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
@@ -6248,26 +6208,30 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Object</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>- base
-description: Entity with a well-defined boundary and identity that encapsulates state and behaviour.</t>
+description: Abstraction of real-world phenomena.</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Entity with a well-defined boundary and identity that encapsulates state and behaviour.</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr"/>
+          <t>Abstraction of real-world phenomena.</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>- A feature may occur as a type or an instance.</t>
+        </is>
+      </c>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>- ISO/IEC 19501:2005</t>
+          <t>- ISO 19101-1:2014, 4.1.11, modified</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
@@ -6290,26 +6254,30 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Forecast Range</t>
+          <t>Final Product Version</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>- core
-description: The forecast period.</t>
+description: Product within an EO Collection that is not expected to be updated.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>The forecast period.</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr"/>
+          <t>Product within an EO Collection that is not expected to be updated.</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>- In its production, all of the prerequisite auxiliary data were used as input.</t>
+        </is>
+      </c>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
@@ -6332,26 +6300,35 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Policy Milestone</t>
+          <t>Spatial Extent</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>- high-impact
-description: Markers of significant progress in addressing specific issues, or crucial decision points where significant choices are made within a policy process.</t>
+          <t>- core
+description: Zone or region of space described by a geographic identifier in the form of a label or code, or by a bounding box, representing the maximum spatial boundary within which the user is requesting data.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Markers of significant progress in addressing specific issues, or crucial decision points where significant choices are made. Concrete examples include: policy planning and proposing, impact assessment, implementation, or implementation cycles (e.g., Water Framework Directive, Marine Strategy Framework Directive), achievement of Policy Objectives and Policy Targets, and evaluating and improving existing laws.</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
+          <t>Zone or region of space described by a geographic identifier in the form of a label or code, or by a bounding box. Represents the maximum extent (the spatial boundary or limits) within which the User is requesting data.
+The attribute represents the maximum spatial extent of the AOI, and in case the AOI is made of many discontinuous zones then it represents the maximum extent of the union of all the zones.</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>- WIGOS metadata standard defines it as the typical spatial georeferenced volume covered by the observations.</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>- If a User is requesting information about degradation of African protected sites, then the AOIs are the protected sites, and the spatial extent is the African continent.</t>
+        </is>
+      </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Adapted from ISO 19170-1:2021</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
@@ -6374,30 +6351,26 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Dwell Time</t>
+          <t>Policy Cycle</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>- core
-description: Time that an antenna beam spends on a target.</t>
+          <t>- high-impact
+description: Well-established concept typically taught as the rational model of policy decision-making, representing an idealised view of the policy process.</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Time that an antenna beam spends on a target.</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>- In the context of radar sensing.</t>
-        </is>
-      </c>
+          <t>Well-established concept, typically taught as the rational model of policy decision-making. Idealised view of the policy process.</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [ESA/CEOS?, modified](https://digital-strategy.ec.europa.eu/en/library/quality-public-administration-toolbox-practitioners)</t>
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
@@ -6420,26 +6393,26 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Location Error</t>
+          <t>Data Licencing</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>- core
-description: Measure of the agreement between the represented Location of an Object and the true Location.</t>
+description: Legal instrument by which a copyright holder may grant rights over the protected work.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Measure of the agreement between the represented Location of an Object and the true Location.</t>
+          <t>Legal instrument by which a copyright holder may grant rights over the protected work. Data and content is open if it is subject to an explicitly-applied licence that conforms to the Open Definition. A range of standard open licences are available, such as the Creative Commons CC-BY licence, which requires only attribution.</t>
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- CEOS Wiki</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
@@ -6462,22 +6435,26 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Expanded Uncertainty</t>
+          <t>Representativeness</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>- core
-description: Standard Uncertainty multiplied by a coverage factor k, chosen to obtain a desired level of confidence.</t>
+description: Quality or characteristic of a measurement or observation to accurately represent a specific geographic location, time period, or environmental condition.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Standard Uncertainty multiplied by a coverage factor, k. The coverage factor is chosen to obtain a desired level of confidence. Most commonly a 95% confidence interval is chosen. For a Gaussian distribution, this is achieved with a coverage factor k = 2. (Note that strictly this provides a 95.45% confidence interval.)</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr"/>
+          <t>Quality or characteristic of a measurement or Observation to accurately represent a specific geographic location, time Period, or environmental condition.</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>- WIGOS metadata standard defines representativeness as the extent of the region around the Observation of which it is representative.</t>
+        </is>
+      </c>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
@@ -6504,20 +6481,28 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Environmental Process</t>
+          <t>Reproducibility</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>- core
-description: ""</t>
+description: Concerned with the validity of the results of a particular study, enabling readers to check whether results have been manipulated by reproducing exactly the same study using the same data and methods.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Concerned with the validity of the results of a particular study, i.e., the possibility for readers to check whether results have been manipulated, by reproducing exactly the same study using the same data and methods.</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>- Ostermann and Granell (2015)</t>
+        </is>
+      </c>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="inlineStr"/>
@@ -6538,30 +6523,30 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Custodian</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>- controversial
-description: An, often numeric, theoretical (or otherwise abstract) representation of an Entity intended to generate Data describing one or more of its traits.</t>
+          <t>- core
+description: Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>An, often numeric, theoretical (or otherwise abstract) representation of an Entity intended to generate Data describing one or more of its traits (as a result of pre-set conditions).</t>
+          <t>Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>- The Process of generating Data using a model is called modelling.</t>
+          <t>- See also Steward.</t>
         </is>
       </c>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
@@ -6584,26 +6569,26 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Classification System</t>
+          <t>Geosphere</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: The masses of minerals that constitute planet Earth.</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Nomenclature used to classify Information into categorical thematic classes (e.g., EUNIS, MAES ecosystems, Corine Land Cover, LCCS).</t>
+          <t>The masses of minerals that constitute planet Earth.</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
@@ -6626,26 +6611,30 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Spectral Bandwidth</t>
+          <t>Cell</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
           <t>- core
-description: Range of the Spectral Band.</t>
+- approved</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Range of the Spectral Band.</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr"/>
+          <t>Spatial, spatio-temporal zone or temporal unit of geometry with dimensionality greater than 0, associated with a zone.</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>- Cells are the unit of geometry in a DGGS, and the geometry of the region of space-time occupied by a zone is a Cell.</t>
+        </is>
+      </c>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO 19170:2021</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
@@ -6668,26 +6657,30 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>Geographic Coordinate Reference System</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Coordinate Reference System (CRS) that has a geodetic Reference frame and an ellipsoidal coordinate system.</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Group of products that have been processed using a consistent radiometric calibration, geometric registration base, data/metadata format, and version of processing algorithms.</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr"/>
+          <t>Coordinate Reference System (CRS) that has a geodetic Reference frame and an ellipsoidal coordinate system.</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>- Also known as geographic CRS.</t>
+        </is>
+      </c>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- ISO 19111:2019, 3.1.35</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
@@ -6710,23 +6703,29 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Policy File</t>
+          <t>Vertical Levels</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>- high-impact
-description: Policy documents that represent the official written reference for a given Policy.</t>
+          <t>- core
+description: Levels of a vertical discretization, e.g. pressure levels in an atmospheric model reanalysis or height levels in a forest biomass EO product.</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Policy documents that represent the official written reference for a given Policy.</t>
+          <t>Levels of a vertical discretization. Examples may be pressure levels in an atmospheric model reanalysis or height levels in a forest biomass EO product.</t>
         </is>
       </c>
       <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>| Entry format example                | Valid unit           |
+|------------------------------------|----------------------|
+| 1, 5, 10 meter; 1000, 850, 500 hPa | meter, hPa, unitless |</t>
+        </is>
+      </c>
       <c r="G136" t="inlineStr">
         <is>
           <t>- KCEO</t>
@@ -6752,26 +6751,26 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Anthroposphere</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>- high-impact
-description: Deliberate system of guidelines to guide decisions and achieve rational outcomes, implemented as a procedure or protocol and typically promulgated through official written documents.</t>
+          <t>- core
+- approved</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Deliberate system of guidelines to guide decisions and achieve rational outcomes. Statement of intent implemented as a procedure or protocol. Typically promulgated through official written documents.</t>
+          <t>One of the Earth spheres consisting predominantly of matter processed by humans, such as construction wood, bricks, concrete, asphalt, glass, or plastics.</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
@@ -6794,30 +6793,30 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Geographic Identifier</t>
+          <t>Dwell Time</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>- core
-description: Spatial reference in the form of a label or code that identifies a Location.</t>
+description: Time that an antenna beam spends on a target.</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Spatial reference in the form of a label or code that identifies a Location.</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>- "Spain" is an example of a label (country name); "SW1-3AD" is an example of a code (postcode).</t>
-        </is>
-      </c>
+          <t>Time that an antenna beam spends on a target.</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>- In the context of radar sensing.</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>- ISO 19112:2019, 3.1.2</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
@@ -6840,31 +6839,33 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Earth Observation</t>
+          <t>Duration</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>- high-impact
-description: Science domain dealing with technologies and methods of collecting and analyzing observations about the different Earth spheres.</t>
+          <t>- core
+description: Non-negative interval Quantity of time equal to the difference between the final and initial instants of a time interval.</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Science domain dealing with technologies and methods of collecting and analyzing observations about the different Earth spheres.</t>
+          <t>Non-negative interval Quantity of time equal to the difference between the final and initial instants of a time interval.</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>- Earth Observation (EO) can be categorised by location of the sensor into space-borne, air-borne, sea-borne, ground-based, underwater and underground EO.
-- Earth Observation (EO) includes Remote Sensing, such as satellite imagery, as well as in-situ observations, e.g., with ground-based devices.</t>
+          <t>- Duration is one of the base quantities in the International System of Quantities (ISQ) on which the International System of Units (SI) is based. The term "time" instead of "duration" is often used in this context and also for an infinitesimal duration.
+- For the term "duration", expressions such as "time" or "time interval" are often used, but the term "time" is not recommended in this sense and the term "time interval" is deprecated in this sense to avoid confusion with the concept of "time interval".
+- The exact duration of a time scale unit depends on the time scale used. For example, the durations of a year, month, week, day, hour or minute may depend on when they occur (in a Gregorian calendar, a calendar month can have a duration of 28, 29, 30, or 31 days; in a 24-hour clock, a clock minute can have a duration of 59, 60, or 61 seconds, etc.). Therefore, the exact duration can only be evaluated if the exact duration of each is known.
+- This definition is closely related to NOTE 1 of the terminological entry "duration" in IEC 60050-113:2011, 113-01-13.</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>- Modified GEO definition [GEO (earthobservations.org)](https://earthobservations.org/resources#key)</t>
+          <t>- ISO 8601-1:2019, 3.1.1.8</t>
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
@@ -6887,26 +6888,26 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Data Format</t>
+          <t>Lead Time</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>- core
-description: Structured Data that is machine readable and can be automatically read and processed by a computer, such as HDF, NetCDF, CSV, JSON, XML, etc.</t>
+description: Minimum time of interval between an Observation being tasked and being performed.</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Structured Data that is machine readable and can be automatically read and processed by a computer, such as HDF, NetCDF, CSV, JSON, XML, etc.</t>
+          <t>Minimum time of interval between an Observation being tasked and being performed.</t>
         </is>
       </c>
       <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
-          <t>- CEOS Wiki</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
@@ -6929,26 +6930,30 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Geolocation Information</t>
+          <t>EO Space Data</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>- core
-description: Information used to determine geographic Location.</t>
+description: Earth Observation data generated by spaceborne missions or instruments owned by public or private organizations.</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Information used to determine geographic Location.</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr"/>
+          <t>Earth Observation data generated by spaceborne missions or instruments owned by public or private organizations.</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>- See also Instrument data.</t>
+        </is>
+      </c>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
-          <t>- ISO 19130-1:2018, 3.34</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
@@ -6971,26 +6976,30 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Cryosphere</t>
+          <t>Spatial Completeness</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Presence or absence of gaps, which are missing values in an otherwise continuous spatial data series.</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Masses of frozen water, such as sea ice, ice shields, glaciers, and snow.</t>
+          <t>Presence or absence of gaps, which are missing values in an otherwise continuous spatial data series.</t>
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>- Surface soil moisture retrieved from microwave satellite sensors may present gaps in mountainous terrains.</t>
+        </is>
+      </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
@@ -7013,20 +7022,33 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Derivative Product</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
           <t>- core
-description: ""</t>
+description: Product additionally processed from baseline or unenhanced mission data.</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Product additionally processed from baseline or unenhanced mission data.</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>- Generally either a compilation of time-series data (e.g., all time, annual, monthly or seasonal summary data, &gt; Level 3) or thematic versions of each individual data tile of baseline data.
+- Derived products are citable via a Digital Object Identifier (DOI).</t>
+        </is>
+      </c>
       <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+        </is>
+      </c>
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
@@ -7047,38 +7069,28 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Geopositioning</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>- base
-description: Particular Place referenced by an identifier.</t>
+          <t>- core
+description: Determination of the geographic Position of a point (0D) or linear (1D) Feature.</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Particular Place referenced by an identifier.</t>
+          <t>Determination of the geographic Position of a point (0D) or linear (1D) Feature.</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>- While a (geo)location identifies a geographic Place, it may also be associated with objects other than the Earth.
-- While Location in principle covers 0- to 3-dimensional spatial geometries, it should not be used for 0- and 1-dimensional geometries (positions and paths).</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>- Madrid
-- California</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>- [ISO 19112:2019](https://www.iso.org/standard/70742.html), (E), 3.1.3, modified, note 2 added</t>
-        </is>
-      </c>
+          <t>- Modified from: ISO 19130-1:2018, 3.36</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr"/>
@@ -7099,28 +7111,22 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Spectral Band</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>- core
-description: Device or instrument suited (through physical/chemical interaction) to measure one or more properties of a Phenomenon and thus collect factual/objective data.</t>
+description: Part of the electromagnetic spectrum of specific wavelengths, in remote sensing usually described by central wavelength and bandwidth.</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Device or instrument suited (through physical/chemical interaction) to measure one or more properties of a Phenomenon and thus collect factual/objective data.</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>- Sensing is therefore a synonym for Observation (the Process).
-- As by their definition, sensors perform sampling.
-- Sensors used to obtain measurements must be calibrated and provide uncertainties.</t>
-        </is>
-      </c>
+          <t>Part of the electromagnetic spectrum of specific wavelengths. In Remote Sensing, usually described by central wavelength and bandwidth.</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
@@ -7147,36 +7153,30 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Temporal Resolution</t>
+          <t>Geographic Data</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>- core
-description: Observation or model output representing regular intervals, specifying the length of the interval that determines the smallest event or process that can be resolved.</t>
+description: Data with implicit or explicit reference to a Location relative to the Earth.</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Observation or model output representing regular intervals, specifying the length of the interval that determines the smallest event or Process that can be resolved (e.g., the Period between observations, the time steps in a model).</t>
+          <t>Data with implicit or explicit reference to a Location relative to the Earth.</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>- WIGOS 2019 distinguishes between sampling time Period, as the Period over which a Measurement is taken, and temporal sampling interval as the time Period between the beginning of consecutive sampling periods. Temporal Resolution in this Glossary is equivalent to sampling time Period as used by WIGOS.</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>| Entry format example | Valid unit                     |
-|----------------------|-------------------------------|
-| 1 s, 2 h, 1 m        | second, hour, day, month, year |</t>
-        </is>
-      </c>
+          <t>- Geographic Information is also used as a term for information concerning phenomena implicitly or explicitly associated with a Location relative to the Earth.</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO 19109:2015, 4.13; ISO 19109:2005</t>
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
@@ -7199,26 +7199,26 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Policy Cycle</t>
+          <t>Business Continuity</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>- high-impact
-description: Well-established concept typically taught as the rational model of policy decision-making, representing an idealised view of the policy process.</t>
+          <t>- core
+- approved</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Well-established concept, typically taught as the rational model of policy decision-making. Idealised view of the policy process.</t>
+          <t>An organisation's readiness to continue functioning during times of disruption.</t>
         </is>
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
-          <t>- [ESA/CEOS?, modified](https://digital-strategy.ec.europa.eu/en/library/quality-public-administration-toolbox-practitioners)</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H147" t="inlineStr"/>

--- a/exports/xlsx/terms.xlsx
+++ b/exports/xlsx/terms.xlsx
@@ -536,32 +536,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Geographic Grid</t>
+          <t>Geolocating</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>- core
-description: Regular grid based on a Geographic Coordinate Reference System (CRS).</t>
+description: Geopositioning of an Object using a Physical Sensor Model or a True Replacement Model.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Regular grid based on a Geographic Coordinate Reference System (CRS).</t>
+          <t>Geopositioning of an Object using a Physical Sensor Model or a True Replacement Model.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>- ISO 19115-2:2009, 4.11</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Determination of the geographic location of a feature of two or more dimensions.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>- ISO 19130-1:2018, 3.36 ('geopositioning'), modified</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -578,26 +586,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Representativeness</t>
+          <t>Spectral Bandwidth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>- core
-description: Quality or characteristic of a measurement or observation to accurately represent a specific geographic location, time period, or environmental condition.</t>
+description: Range of the Spectral Band.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Quality or characteristic of a measurement or Observation to accurately represent a specific geographic location, time Period, or environmental condition.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>- WIGOS metadata standard defines representativeness as the extent of the region around the Observation of which it is representative.</t>
-        </is>
-      </c>
+          <t>Range of the Spectral Band.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
@@ -624,24 +628,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EO Space Data</t>
+          <t>Instrument Data</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>- core
-description: Earth Observation data generated by spaceborne missions or instruments owned by public or private organizations.</t>
+description: Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Earth Observation data generated by spaceborne missions or instruments owned by public or private organizations.</t>
+          <t>Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>- See also Instrument data.</t>
+          <t>- These data consist of instrument science and engineering data, and possibly ancillary data. Instrument engineering data is produced by engineering sensor(s) of an instrument, used either for operating the instrument or for processing the science data generated by the instrument. Instrument science data is produced by the science sensor(s) of an instrument, usually constituting the basic reason for existence of an instrument.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -650,14 +654,30 @@
           <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Data created by an instrument including scientific measurements and any engineering or ancillary data which may be included in the data packets.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Data produced and transmitted by the science and engineering sensors of an instrument, and, in the spacecraft environment, any additional data packaged with the instrument's sensor data by virtue of services provided.</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
@@ -670,40 +690,59 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Granule</t>
+          <t>Auxiliary Data</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>- core
-description: The smallest aggregation of data which is independently managed (i.e. described, inventoried, retrievable).</t>
+- approved</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>The smallest aggregation of data which is independently managed (i.e. described, inventoried, retrievable). Granules may be managed as logical granules and/or physical granules.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>- See also product.</t>
-        </is>
-      </c>
+          <t>Data that enhance the processing and utilisation of main Sensor Data. Auxiliary Data are usually not captured by the same Data collection Process or on the same platform as the main Sensor Data. Examples include meteorological Data received from ECMWF/Met Offices or DEMs. Auxiliary Data help in Data processing, but are also Data sets in their own right.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>- [NASA EarthData](https://www.earthdata.nasa.gov/learn/glossary)</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+          <t>- ESA/CEOS?, modified
+- ENMAP Glossary of Terms, https://www.enmap.org/Data/doc/EnMAP_Terms.pdf, 20210624
+- EO Data Stewardship Glossary</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Data required to perform processing of Sensor Data which is not obtained from the Sensor itself. Includes: (a) Data provided by the spacecraft (e.g. orbit Position and velocity, attitude, instrument house-keeping Data, on-board time); (b) Data not available from on-board sources.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>For EnMAP, this includes (a) orbit files, attitude files, Calibration Data, instrument house-keeping Data; (b) atmospheric parameters, reference images.</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>- ENMAP Glossary of Terms, https://www.enmap.org/Data/doc/EnMAP_Terms.pdf, 20210624
+- EO Data Stewardship Glossary</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Data required for instrument processing that does not originate in the instrument itself or from the satellite. Some Auxiliary Data will be generated in the ground segment, whilst other Data will be provided from external sources.</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>- CEOS-ARD PFS template 20220302</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
@@ -716,37 +755,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Temporal Revisit</t>
+          <t>Dispose</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>- core
-description: Interval between successive observations.</t>
+description: Action of permanently and irrecoverably removing all copies of data held by an organization.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Interval between successive observations.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>- In Remote Sensing it is also called repeat cycle.
-- More generally it is known as temporal sampling interval.</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>| Entry format example | Valid unit                     |
-|----------------------|-------------------------------|
-| 1 s, 2 h             | second, hour, day, month, year |</t>
-        </is>
-      </c>
+          <t>Action of permanently and irrecoverably removing all copies of data held by an organization.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -769,26 +797,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dispose</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>- core
-description: Action of permanently and irrecoverably removing all copies of data held by an organization.</t>
+          <t>- base
+- controversial
+description: Place referenced by a single set of coordinates within a coordinate reference system.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Action of permanently and irrecoverably removing all copies of data held by an organization.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>Place referenced by a single set of coordinates within a coordinate reference system.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>- Opposite to (previous) ISO definition, Position shall be used only for 0-dimensional primitives (points).</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- ISO 19133:2005, modified to cover only points, also called 'direct position'</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -811,35 +844,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Remote Sensing</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>- controversial
-description: Type of Observation performed at a significant distance from a Phenomenon.</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Remote Observation</t>
-        </is>
-      </c>
+          <t>- core
+description: Electronic data package distributable to users; content is derived from instrument data via processing involving ancillary and auxiliary data.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Type of Observation performed at a significant distance from a Phenomenon.</t>
+          <t>Electronic data package distributable to users; content is derived from instrument data via processing involving ancillary and auxiliary data.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>- 'Significant' in this context means that the distance has, or may have, a non-negligible impact on the Value of the Property observed.
-- The effect of the distance on the acquired data is the main distinction criterion between 'remote' and 'in-situ' observations.</t>
+          <t>- Products may be accompanied by metadata and browse images.
+- A Product may be part of a collection — a distinction useful for archiving and cataloguing purposes.
+- The term Product may be used to denote a product type, such as e.g. ENVISAT_ASAR_L1B_PRI data products.
+- End users may distinguish between (input, "raw") data and products, i.e., the derived geophysical parameters.
+- See also granule.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -862,26 +894,30 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Near Real Time Data</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>- high-impact
-description: Data available for use with a specified (small and application dependent) latency, typically 3 hours for meteorological applications.</t>
+          <t>- base
+description: Series of activities that interact to produce a result.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Data available for use with a specified (small and application dependent) latency, typically 3 hours for meteorological applications.</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>Series of activities that interact to produce a result.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>- A Process may occur once-only or be recurrent or periodic.</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- [Wikipedia](https://en.wikipedia.org/wiki/Process)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -904,50 +940,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>- base
-description: Value and possibly Uncertainty of a Trait of a specific Entity.</t>
+          <t>- core
+description: Phenomenon whose values for specific properties are known and understood with an Uncertainty significantly lower than that of the Observation with which it is compared.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Value and possibly Uncertainty of a Trait of a specific Entity.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>- Data simply describe entities using certain traits and are not targeted at a particular use or audience.</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Data can be categorised into:
-- factual (i.e. obtained by Observation) or fictional (obtained e.g. through modelling, estimating or assigning)
-- quantitative (continuous) or qualitative (categorical)
-- analogue or digital
-(list not exhaustive!)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
+          <t>Phenomenon whose values for specific properties are known and understood with an Uncertainty significantly lower (quantify?) than that of the Observation with which it is compared.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Scientific or technical measurements, values calculated therefrom, observations, or facts that can be represented by numbers, tables, graphs, models, text, or symbols which are used as a basis for reasoning and further calculation.</t>
+          <t>Sort of data acquired with an Uncertainty significantly lower (quantify?) than that of the data it is being compared with.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
+          <t>- VIM?, modified</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -966,30 +986,29 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Geographic Coordinate Reference System</t>
+          <t>Earth Observation Based Output</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>- core
-description: Coordinate Reference System (CRS) that has a geodetic Reference frame and an ellipsoidal coordinate system.</t>
+description: Higher-level processing and integration output (indicative level 4 and beyond) that goes beyond basic data processing, often designed for policy or decision-making needs.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Coordinate Reference System (CRS) that has a geodetic Reference frame and an ellipsoidal coordinate system.</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>- Also known as geographic CRS.</t>
-        </is>
-      </c>
+          <t>Higher-level processing and integration output (indicative level 4 and beyond) that goes beyond basic data processing. These outputs are often designed specifically for policy or decision-making needs, and can be categorized into sub-categories:
+- Outputs from models/model integration: use of EO products as inputs in numerical models or combining them with other data sources in modelling frameworks.
+- Indicator-based outputs: EO products transformed through specialized algorithms (including statistical methods, machine learning, and pattern recognition) to create meaningful metrics based on spatio-temporal analysis.
+- Outputs from reanalysis: merging of EO products with other observations and models, creating consistent long-term records of past atmospheric, oceanic, and land surface conditions, and filling gaps through data assimilation techniques.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>- ISO 19111:2019, 3.1.35</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -1012,37 +1031,44 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Long Term Preservation</t>
+          <t>Entity</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>- core
-description: The act of maintaining information in a correct and independently understandable form over the long term.</t>
+          <t>- base
+description: Something that has separate and distinct existence and objective or conceptual reality.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>The act of maintaining information in a correct and independently understandable form over the long term.</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>- Long term refers to a period of time long enough to be concerned with the impact which changing technologies, including support for media and data formats, and changing user communities will have on the information being held in a repository.
-- See also preservation.</t>
-        </is>
-      </c>
+          <t>Something that has separate and distinct existence and objective or conceptual reality.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>- ISO 19119:2016, 4.1.6</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Government or business organization that is formed to conduct business or represent the government of the day.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>CEOS Entities include Working Groups, Virtual Constellations, etc.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1059,31 +1085,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Preservation</t>
+          <t>Collection</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>- core
-description: Processes and operations used to ensure data technical and intellectual survival through time.</t>
+- approved</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Processes and operations used to ensure data technical and intellectual survival through time.</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>- Grants data integrity, discoverability and accessibility, and facilitates its (re-)use in the long term.
-- Preservation is one of the tasks of data curation.</t>
-        </is>
-      </c>
+          <t>Group of products that have been processed using a consistent radiometric calibration, geometric registration base, data/metadata format, and version of processing algorithms.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1106,26 +1127,26 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Version Control</t>
+          <t>Geographic Grid</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>- core
-description: Method of working with collections, similar to version control systems used in traditional software development but optimized to allow better processing of data and collaboration in data analytics and research contexts.</t>
+description: Regular grid based on a Geographic Coordinate Reference System (CRS).</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Method of working with collections, similar to the version control systems used in traditional software development but optimized to allow better processing of data and collaboration in the context of data analytics, research, and any other form of data analysis.</t>
+          <t>Regular grid based on a Geographic Coordinate Reference System (CRS).</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>- [Wikipedia](https://en.wikipedia.org/wiki/Data_version_control)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -1148,26 +1169,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Thematic Resolution</t>
+          <t>Archive</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>- core
-description: Level of categorical detail of information expressed by the number of classes.</t>
+- approved</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Level of categorical detail of information expressed by the number of classes.</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>System that stores data products, guaranteeing their preservation for future use.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>- This function includes all operations to identify, store and retrieve the data and ensure their integrity.</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>- CGLS</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1190,26 +1215,30 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Copernicus Service Provider</t>
+          <t>Steward</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Institutional body, organisation or programme that provides reliable, trusted (authoritative?) EO Information and that has the financial resources to sustain the provision. It utilises satellite Data, ground-based measurements, and other sources to generate accurate and timely Data products related to various aspects of the Earth's environment, such as land, Atmosphere, oceans, and climate.</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>- See also Custodian.</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -1232,26 +1261,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Replicability</t>
+          <t>Sample</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>- core
-description: Property enabling other researchers to conduct an independent study with different data and similar but not identical methods, yet arriving at results that confirm the original study's hypothesis.</t>
+          <t>- controversial
+description: Subset of one or more entities.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Property enabling other researchers to conduct an independent study with different data and similar but not identical methods, yet arriving at results that confirm the original study's hypothesis.</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+          <t>Subset of one or more entities.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>- A Sample may be spatial, temporal, spectral, or in any other dimension or Trait.
+- Each Sample is contiguous, i.e. it does not consist of more than one discontinuous geometry in any dimension.
+- The Process of obtaining a Sample is called sampling.</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>- Craglia, M., et al. (2018).</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -1274,30 +1309,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Coverage Interval</t>
+          <t>Temporal Extent</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Coverage extent</t>
-        </is>
-      </c>
+description: Period during which data was collected, observations were made, or for which the model was run.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Range or specific subset of values associated with a coverage dataset.</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+          <t>Period during which data was collected, observations were made, or for which the model was run.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>- In W3C this is the definition of temporal coverage.
+- Time Period covered by a series of observations inclusive of the specified date/time indications (measurement history). Defined based on the beginning and end dates of observations.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>- WIGOS Metadata</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Adapted from W3C</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -1367,20 +1407,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Equivalence</t>
+          <t>Cryosphere</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>- core
-  - to be defined</t>
+- approved</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Masses of frozen water, such as sea ice, ice shields, glaciers, and snow.</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>- Guth et al. 2021</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
@@ -1401,29 +1449,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Band Central Wavelength</t>
+          <t>Spatial Reporting Unit</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Smallest spatial object of interest that may be used for reporting and for which the information should be aggregated.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Single wavelength Value within the sensitivity interval of a spectroradiometric Sensor which represents the respective band. It could be either the mean, the median, the maximum sensitivity, or any other reasonable Value chosen to be representative.</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>| Entry format example | Valid unit                                        |
-|----------------------|---------------------------------------------------|
-| 0.545 μm             | micrometre (μm), millimetre (mm), centimetre (cm) |</t>
-        </is>
-      </c>
+          <t>Smallest spatial object of interest that may be used for reporting and for which the information should be aggregated.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>- WIGOS 2019 uses 'spatial reporting interval', probably assuming observations are reported on a grid with regular spacing/intervals.</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>- KCEO</t>
@@ -1449,30 +1495,30 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Update Frequency</t>
+          <t>Decommissioned Product</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>- core
-description: Frequency at which the product is available to users.</t>
+description: Products and collections that have been superseded by new versions and are no longer available.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Frequency at which the product is available to users.</t>
+          <t>Products and collections that have been superseded by new versions and are no longer available.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>- Also known in product catalogues as dissemination frequency.</t>
+          <t>- Decommissioned products are no longer supported, i.e. corrections will not be made, new data will not be added, and support is not available.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -1495,44 +1541,42 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Entity</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>- base
-description: Something that has separate and distinct existence and objective or conceptual reality.</t>
+description: Particular Place referenced by an identifier.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Something that has separate and distinct existence and objective or conceptual reality.</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+          <t>Particular Place referenced by an identifier.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>- While a (geo)location identifies a geographic Place, it may also be associated with objects other than the Earth.
+- While Location in principle covers 0- to 3-dimensional spatial geometries, it should not be used for 0- and 1-dimensional geometries (positions and paths).</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>- Madrid
+- California</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>- ISO 19119:2016, 4.1.6</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Government or business organization that is formed to conduct business or represent the government of the day.</t>
-        </is>
-      </c>
+          <t>- [ISO 19112:2019](https://www.iso.org/standard/70742.html), (E), 3.1.3, modified, note 2 added</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>CEOS Entities include Working Groups, Virtual Constellations, etc.</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
-        </is>
-      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -1549,26 +1593,30 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Place</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>- base
-description: Part of any space referenced by an identifier.</t>
+description: Particular era or span of time.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Part of any space referenced by an identifier.</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
+          <t>Particular era or span of time.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>- Periods are intervals named with a Period Identifier.</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>- ISO 19155:2012, 4.8</t>
+          <t>- ISO 19170:2021</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -1591,33 +1639,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Duration</t>
+          <t>Geospatial Data</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>- core
-description: Non-negative interval Quantity of time equal to the difference between the final and initial instants of a time interval.</t>
+description: Data consisting of, derived from, or relating to information that is directly linked to specific geographical locations.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Non-negative interval Quantity of time equal to the difference between the final and initial instants of a time interval.</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>- Duration is one of the base quantities in the International System of Quantities (ISQ) on which the International System of Units (SI) is based. The term "time" instead of "duration" is often used in this context and also for an infinitesimal duration.
-- For the term "duration", expressions such as "time" or "time interval" are often used, but the term "time" is not recommended in this sense and the term "time interval" is deprecated in this sense to avoid confusion with the concept of "time interval".
-- The exact duration of a time scale unit depends on the time scale used. For example, the durations of a year, month, week, day, hour or minute may depend on when they occur (in a Gregorian calendar, a calendar month can have a duration of 28, 29, 30, or 31 days; in a 24-hour clock, a clock minute can have a duration of 59, 60, or 61 seconds, etc.). Therefore, the exact duration can only be evaluated if the exact duration of each is known.
-- This definition is closely related to NOTE 1 of the terminological entry "duration" in IEC 60050-113:2011, 113-01-13.</t>
-        </is>
-      </c>
+          <t>Data consisting of, derived from, or relating to information that is directly linked to specific geographical locations.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>- ISO 8601-1:2019, 3.1.1.8</t>
+          <t>- https://www.merriam-webster.com/dictionary/geospatial
+- https://isotc211.geolexica.org/Concepts/202/, accessed 20221010</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -1640,34 +1682,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Time of Day</t>
+          <t>Confidence Interval</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>- core
-description: Time of the day at which the variable or parameter is observed or simulated by a model.</t>
+          <t>- controversial
+- approved</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Time of the day at which the variable or parameter is observed or simulated by a model.</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>- In Remote Sensing it is also known as time of overpass.</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>| Type      | Entry format example | Valid unit |
-|-----------|----------------------|------------|
-| timestamp | 18:00 h (0–24)       | Hours      |
-| timerange | 18:00 – 20:00 h      | Hours      |</t>
-        </is>
-      </c>
+          <t>Probability that the Quantity lies in the interval, conditioned on the measuring or modelling assumptions.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>- KCEO</t>
@@ -1693,32 +1724,30 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Vertical Levels</t>
+          <t>Granule</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>- core
-description: Levels of a vertical discretization, e.g. pressure levels in an atmospheric model reanalysis or height levels in a forest biomass EO product.</t>
+description: The smallest aggregation of data which is independently managed (i.e. described, inventoried, retrievable).</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Levels of a vertical discretization. Examples may be pressure levels in an atmospheric model reanalysis or height levels in a forest biomass EO product.</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>| Entry format example                | Valid unit           |
-|------------------------------------|----------------------|
-| 1, 5, 10 meter; 1000, 850, 500 hPa | meter, hPa, unitless |</t>
-        </is>
-      </c>
+          <t>The smallest aggregation of data which is independently managed (i.e. described, inventoried, retrievable). Granules may be managed as logical granules and/or physical granules.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>- See also product.</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [NASA EarthData](https://www.earthdata.nasa.gov/learn/glossary)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -1741,34 +1770,30 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>- core
-description: Electronic data package distributable to users; content is derived from instrument data via processing involving ancillary and auxiliary data.</t>
+          <t>- controversial
+description: An, often numeric, theoretical (or otherwise abstract) representation of an Entity intended to generate Data describing one or more of its traits.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Electronic data package distributable to users; content is derived from instrument data via processing involving ancillary and auxiliary data.</t>
+          <t>An, often numeric, theoretical (or otherwise abstract) representation of an Entity intended to generate Data describing one or more of its traits (as a result of pre-set conditions).</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>- Products may be accompanied by metadata and browse images.
-- A Product may be part of a collection — a distinction useful for archiving and cataloguing purposes.
-- The term Product may be used to denote a product type, such as e.g. ENVISAT_ASAR_L1B_PRI data products.
-- End users may distinguish between (input, "raw") data and products, i.e., the derived geophysical parameters.
-- See also granule.</t>
+          <t>- The Process of generating Data using a model is called modelling.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -1791,36 +1816,44 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Georectifying</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>- base
-description: The result of organisation, interpretation, categorisation, classification, or some other form of processing of Data attaching to it a certain meaning that can be understood by the addressee.</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>- core
+description: Correcting for positional displacement with respect to the surface of the Earth.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Orthorectifying</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>The result of organisation, interpretation, categorisation, classification, or some other form of processing of Data attaching to it a certain meaning that can be understood by the addressee.</t>
+          <t>Correcting for positional displacement with respect to the surface of the Earth.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>- Information depends on Data and is targeted.</t>
+          <t>- Source: ISO 19115-2:2019, 3.11; ISO 19115-2:2009(E); https://www.iso.org/standard/67039.html, modified</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>The correction of sample locations to achieve some sort of geometric regularity, e.g., a regular 2D geographic grid.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
@@ -1837,26 +1870,26 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Lithosphere</t>
+          <t>Policy Making</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>- core
-description: The solid, inanimate outer layer of the Geosphere. For the purposes of Earth Observation, includes soils ('pedosphere').</t>
+          <t>- high-impact
+description: Process by which governments translate their political vision into programmes and actions to deliver outcomes — desired change in the real world.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>The solid, inanimate outer layer of the Geosphere. For the purposes of Earth Observation, the Lithosphere is considered to include soils ('pedosphere').</t>
+          <t>Process by which governments translate their political vision into programmes and actions to deliver outcomes — desired change in the real world.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- [ESA/CEOS?, modified](https://digital-strategy.ec.europa.eu/en/library/quality-public-administration-toolbox-practitioners)</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -1879,75 +1912,111 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ancillary Data</t>
+          <t>Uncertainty</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Data acquired on the same platform but not obtained from the main Sensor itself (usually provided as part of Level 0 Data), with the primary purpose of serving the processing of main instrument Data (e.g. Position and velocity of platform).</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>This can be divided into data referred to as spacecraft 'engineering', 'core housekeeping' or 'subsystem' data obtained from other parts of the platform, and includes parameters such as orbit position and velocity, attitude and its range of change, time, temperatures, pressures, jet firings, water dumps, internally produced magnetic fields, and other environmental measurements. Ancillary refers to data that exist purely to serve the data processing.</t>
-        </is>
-      </c>
+          <t>Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>- ESA/CEOS?, modified
-- EO Data Stewardship Glossary</t>
+          <t>- GUM</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Data other than instrument measurements, originating in the instrument itself or from the satellite, required to perform processing of the Data. Includes orbit Data, attitude Data, time Information, and spacecraft engineering Data, Calibration Data, Data quality Information, and Data from other instruments or earth system models.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>Non-negative parameter, associated with data, which characterizes the dispersion of the values of a Trait that could reasonably be attributed to a Phenomenon by means of sensing or modelling.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>- In case of quantitative (continuous) data the uncertainty may be, for example, a standard deviation (or a given multiple of it), or the half-width of an interval having a stated level of confidence (see e.g. Standard and Expanded Uncertainty).
+- For qualitative (categorical?) data, uncertainty may be expressed by commission and omission ('confusion matrix') or overall errors.</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>- CEOS-ARD PFS template 20220302</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
+          <t>- Modified from GUM, VIM4:3.1, FIDUCEO, Notes added</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Measure of the spread of the distribution of possible values.</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>- [FIDUCEO Glossary](https://research.reading.ac.uk/fiduceo/glossary/), VIM?, modified</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Parameter, associated with the result of measurement, that characterizes the dispersion of values that could reasonably be attributed to the measurand.</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>- When the quality of accuracy or precision of measured values, such as coordinates, is to be characterized quantitatively, the quality parameter is an estimate of the uncertainty of the measurement results. Because accuracy is a qualitative concept, one should not use it quantitatively, that is associate numbers with it; numbers should be associated with measures of uncertainty instead.</t>
+        </is>
+      </c>
       <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>- ISO 19116:2004(E)</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Parameter characterizing the dispersion of the values being attributed to a measurand, based on the information used.</t>
+        </is>
+      </c>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>- VIM4: 3.1</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Consistency</t>
+          <t>Climate Projection</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>- core
-  - to be defined</t>
+- approved</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Simulated response of the climate system to a scenario of future emission or concentration of greenhouse gases (GHGs) and aerosols, generally derived using climate models. Climate Projections are distinguished from climate predictions by their dependence on the emission/concentration/radiative forcing scenario used, which is in turn based on assumptions concerning, for example, future socioeconomic and technological developments that may or may not be realised.</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>- IPCC</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
@@ -1968,19 +2037,19 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Quality Indicator</t>
+          <t>Data Format</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>- core
-description: Indicator providing sufficient information to allow all users to readily evaluate the fitness for purpose of the data or derived product.</t>
+description: Structured Data that is machine readable and can be automatically read and processed by a computer, such as HDF, NetCDF, CSV, JSON, XML, etc.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Indicator providing sufficient information to allow all users to readily evaluate the fitness for purpose of the data or derived product. May be a number, set of numbers, graph, Uncertainty budget, or a simple flag.</t>
+          <t>Structured Data that is machine readable and can be automatically read and processed by a computer, such as HDF, NetCDF, CSV, JSON, XML, etc.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -2010,30 +2079,26 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Classification System Levels</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>- base
-description: Series of activities that interact to produce a result.</t>
+          <t>- core
+- approved</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Series of activities that interact to produce a result.</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>- A Process may occur once-only or be recurrent or periodic.</t>
-        </is>
-      </c>
+          <t>Levels in a hierarchical Classification System.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>- [Wikipedia](https://en.wikipedia.org/wiki/Process)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -2056,26 +2121,30 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Standard Uncertainty</t>
+          <t>Geocoding</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>- core
-description: Standard deviation of the probability distribution describing the spread of possible values in quantitative/continuous data.</t>
+description: Translation of one form of Location into another.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Standard deviation of the probability distribution describing the spread of possible values in quantitative/continuous data.</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
+          <t>Translation of one form of Location into another.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>- Geocoding usually refers to the translation of "address" or "intersection" to "direct Position." Many service providers also include a "reverse geocoding" interface to their geocoder, thus extending the definition of the service as a general translator of Location. Because routing services use internal Location encodings not usually available to others, a geocoder is an integral part of the internals of such a service.</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO 19133:2005; https://www.iso.org/standard/32551.html</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -2098,26 +2167,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Minimum Mapping Width</t>
+          <t>Band Central Wavelength</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>- core
-description: The width of the smallest linear Feature that is still represented on a map.</t>
+- approved</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>The width of the smallest linear Feature that is still represented on a map.</t>
+          <t>Single wavelength Value within the sensitivity interval of a spectroradiometric Sensor which represents the respective band. It could be either the mean, the median, the maximum sensitivity, or any other reasonable Value chosen to be representative.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>| Entry format example | Valid unit                                        |
+|----------------------|---------------------------------------------------|
+| 0.545 μm             | micrometre (μm), millimetre (mm), centimetre (cm) |</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>- CGLS</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -2140,28 +2215,19 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Deprecated Product</t>
+          <t>Cartographic Projection</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>- core
-description: Products and collections that have been superseded by a newer version and are still available, but whose use is discouraged since they will be decommissioned in the future.</t>
+          <t>- core</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Products and collections that have been superseded by a newer version and are still available, but whose use is discouraged since they will be decommissioned in the future.</t>
-        </is>
-      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
@@ -2182,30 +2248,26 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Period Identifier</t>
+          <t>Copernicus Service Provider</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>- core
-description: Temporal reference in the form of a label or code that identifies a Period.</t>
+- approved</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Temporal reference in the form of a label or code that identifies a Period.</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>- Period Identifiers are the temporal equivalent of geographic identifiers as specified in ISO 19912.</t>
-        </is>
-      </c>
+          <t>Institutional body, organisation or programme that provides reliable, trusted (authoritative?) EO Information and that has the financial resources to sustain the provision. It utilises satellite Data, ground-based measurements, and other sources to generate accurate and timely Data products related to various aspects of the Earth's environment, such as land, Atmosphere, oceans, and climate.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>- ISO 19170:2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -2228,19 +2290,19 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Lead Time</t>
+          <t>Location Error</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>- core
-description: Minimum time of interval between an Observation being tasked and being performed.</t>
+description: Measure of the agreement between the represented Location of an Object and the true Location.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Minimum time of interval between an Observation being tasked and being performed.</t>
+          <t>Measure of the agreement between the represented Location of an Object and the true Location.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2270,24 +2332,28 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Calibration</t>
+          <t>Version Control</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Method of working with collections, similar to version control systems used in traditional software development but optimized to allow better processing of data and collaboration in data analytics and research contexts.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Process of quantitatively defining a system's (e.g. a Sensor or Model's) response to known, controlled inputs produced for example by references. In Remote Sensing, it implies the collection of pre-flight and in-flight calibration measurements and in-situ Data that is to be used in the Data calibration processing routine.</t>
+          <t>Method of working with collections, similar to the version control systems used in traditional software development but optimized to allow better processing of data and collaboration in the context of data analytics, research, and any other form of data analysis.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>- [Wikipedia](https://en.wikipedia.org/wiki/Data_version_control)</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
@@ -2308,26 +2374,26 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Climate Projection</t>
+          <t>Data Access</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Service to disseminate Data.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Simulated response of the climate system to a scenario of future emission or concentration of greenhouse gases (GHGs) and aerosols, generally derived using climate models. Climate Projections are distinguished from climate predictions by their dependence on the emission/concentration/radiative forcing scenario used, which is in turn based on assumptions concerning, for example, future socioeconomic and technological developments that may or may not be realised.</t>
+          <t>Service to disseminate Data.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>- IPCC</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -2350,30 +2416,26 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Spatial Reporting Unit</t>
+          <t>Collection Upgrade</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>- core
-description: Smallest spatial object of interest that may be used for reporting and for which the information should be aggregated.</t>
+- approved</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Smallest spatial object of interest that may be used for reporting and for which the information should be aggregated.</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>- WIGOS 2019 uses 'spatial reporting interval', probably assuming observations are reported on a grid with regular spacing/intervals.</t>
-        </is>
-      </c>
+          <t>New and improved major version of all products within a collection due to comprehensive reprocessing.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -2396,26 +2458,26 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Source Data</t>
+          <t>Thematic Resolution</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>- core
-description: Data required for production of an EO Collection (e.g., unenhanced satellite mission data) as well as further processed Level-1 data, or any other pre-processed format meeting program requirements.</t>
+description: Level of categorical detail of information expressed by the number of classes.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Data required for production of an EO Collection (e.g., unenhanced satellite mission data) as well as further processed Level-1 data (precision geometrically and radiometrically corrected radiance at the sensor), or any other pre-processed format that suppliers are providing access to that meets program requirements.</t>
+          <t>Level of categorical detail of information expressed by the number of classes.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- CGLS</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -2438,30 +2500,26 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>Standard Uncertainty</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Standard deviation of the probability distribution describing the spread of possible values in quantitative/continuous data.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Proximity of Measurement results to the accepted Value; precision is the degree to which repeated or reproducible measurements under unchanged conditions show the same results.</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>- In essence, Accuracy reflects how close measurements are to the accepted Value, while precision gauges the reliability and consistency of those measurements.</t>
-        </is>
-      </c>
+          <t>Standard deviation of the probability distribution describing the spread of possible values in quantitative/continuous data.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>- BS ISO 5725-1</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -2484,26 +2542,30 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Policy Making</t>
+          <t>Coverage Interval</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>- high-impact
-description: Process by which governments translate their political vision into programmes and actions to deliver outcomes — desired change in the real world.</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>- core
+- approved</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Coverage extent</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Process by which governments translate their political vision into programmes and actions to deliver outcomes — desired change in the real world.</t>
+          <t>Range or specific subset of values associated with a coverage dataset.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>- [ESA/CEOS?, modified](https://digital-strategy.ec.europa.eu/en/library/quality-public-administration-toolbox-practitioners)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -2526,31 +2588,30 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Path</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>- base
-- controversial
-description: Place referenced by a single set of coordinates within a coordinate reference system.</t>
+description: "Line defined in an algorithmic way using at least two positions (can be open-ended). Alternative: line connecting two positions in an algorithmic way (limited by end points)."</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Place referenced by a single set of coordinates within a coordinate reference system.</t>
+          <t>Line defined in an algorithmic way using at least two positions (can be open-ended). Alternative: line connecting two positions in an algorithmic way (limited by end points).</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>- Opposite to (previous) ISO definition, Position shall be used only for 0-dimensional primitives (points).</t>
+          <t>- A Path is a 1-dimensional Place.</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>- ISO 19133:2005, modified to cover only points, also called 'direct position'</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -2573,26 +2634,26 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Minimum Mapping Unit</t>
+          <t>Source Data</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>- core
-description: The area of the smallest Feature that is still represented on a map.</t>
+description: Data required for production of an EO Collection (e.g., unenhanced satellite mission data) as well as further processed Level-1 data, or any other pre-processed format meeting program requirements.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>The area of the smallest Feature that is still represented on a map.</t>
+          <t>Data required for production of an EO Collection (e.g., unenhanced satellite mission data) as well as further processed Level-1 data (precision geometrically and radiometrically corrected radiance at the sensor), or any other pre-processed format that suppliers are providing access to that meets program requirements.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>- CGLS</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -2615,26 +2676,26 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Spectral Band</t>
+          <t>Atmosphere</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>- core
-description: Part of the electromagnetic spectrum of specific wavelengths, in remote sensing usually described by central wavelength and bandwidth.</t>
+- approved</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Part of the electromagnetic spectrum of specific wavelengths. In Remote Sensing, usually described by central wavelength and bandwidth.</t>
+          <t>Layer of gases, commonly known as air, including suspended liquid and solid particles known as aerosols (incl. dust, clouds, snow and ice).</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -2657,36 +2718,64 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Geopositioning</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>- core
-description: Determination of the geographic Position of a point (0D) or linear (1D) Feature.</t>
+description: Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Determination of the geographic Position of a point (0D) or linear (1D) Feature.</t>
+          <t>Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>- Modified from: ISO 19130-1:2018, 3.36</t>
+          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>- ISO/TS 19101‑2:2008, 4.41</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Process aimed at verifying that the specified requirements are achieved or compliant. Involves comparing mission products with representative reference data, considering various observation conditions, ensuring the quality and traceability of the reference data used.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>- BIPM; QA4EO; ESA?, modified</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Assurance that a product, service, or system meets the needs of the customer and other identified stakeholders. Often involves acceptance and suitability with external customers.</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>- EU-US Land Imaging EO Collaboration</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
@@ -2699,26 +2788,31 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Collection Update</t>
+          <t>Long Term Preservation</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: The act of maintaining information in a correct and independently understandable form over the long term.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Minor revisions to a relatively small number of products within a collection for the purpose of correcting errors and maintaining consistent quality.</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
+          <t>The act of maintaining information in a correct and independently understandable form over the long term.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>- Long term refers to a period of time long enough to be concerned with the impact which changing technologies, including support for media and data formats, and changing user communities will have on the information being held in a repository.
+- See also preservation.</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
@@ -2741,59 +2835,40 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Verification</t>
+          <t>Catalogue</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>- core
-description: Provision of objective evidence that a given item fulfils specified requirements.</t>
+- approved</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Provision of objective evidence that a given item fulfils specified requirements.</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>- When applicable, measurement uncertainty should be taken into consideration.
-- The item may be, e.g. a Process, measurement procedure, material, compound, or measuring system.
-- The specified requirements may be, e.g. that a manufacturer's specifications are met.
-- Verification should not be confused with Calibration. Not every verification is a Validation.</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
+          <t>System that provides users with discovery of information on which EO products can be obtained.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>- A 'Product Catalogue' can organise products and collections with varying access levels depending on product and user type.</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>- ISO/IEC Guide 99:2007, 2.44</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Evaluation of whether or not a product, service, or system complies with a regulation requirement, specification, or imposed condition. Often an internal Process.</t>
-        </is>
-      </c>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>- EU-US Land Imaging EO Collaboration</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Means to evaluate the reliability of the data in the absence of a reference dataset, allowing for an assessment of its standalone performance. Involves confirming the consistency and internal coherence of the data without direct comparison to external reference sources.</t>
-        </is>
-      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
+      <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
@@ -2806,29 +2881,26 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Earth Observation Based Output</t>
+          <t>Minimum Mapping Unit</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>- core
-description: Higher-level processing and integration output (indicative level 4 and beyond) that goes beyond basic data processing, often designed for policy or decision-making needs.</t>
+description: The area of the smallest Feature that is still represented on a map.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Higher-level processing and integration output (indicative level 4 and beyond) that goes beyond basic data processing. These outputs are often designed specifically for policy or decision-making needs, and can be categorized into sub-categories:
-- Outputs from models/model integration: use of EO products as inputs in numerical models or combining them with other data sources in modelling frameworks.
-- Indicator-based outputs: EO products transformed through specialized algorithms (including statistical methods, machine learning, and pattern recognition) to create meaningful metrics based on spatio-temporal analysis.
-- Outputs from reanalysis: merging of EO products with other observations and models, creating consistent long-term records of past atmospheric, oceanic, and land surface conditions, and filling gaps through data assimilation techniques.</t>
+          <t>The area of the smallest Feature that is still represented on a map.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- CGLS</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
@@ -2851,19 +2923,34 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cartographic Projection</t>
+          <t>Temporal Reporting Period</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>- core</t>
+          <t>- core
+description: Time period used for reporting and for which the information should be aggregated from the native temporal resolution.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Time Period used for reporting and for which the information should be aggregated from the native Temporal Resolution.</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>| Entry format example | Valid unit                     |
+|----------------------|-------------------------------|
+| 1 s, 2 h, 1 d        | second, hour, day, month, year |</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>- Modified WIGOS Metadata Standard 2019</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
@@ -2884,32 +2971,26 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Temporal Reporting Period</t>
+          <t>Policy File</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>- core
-description: Time period used for reporting and for which the information should be aggregated from the native temporal resolution.</t>
+          <t>- high-impact
+description: Policy documents that represent the official written reference for a given Policy.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Time Period used for reporting and for which the information should be aggregated from the native Temporal Resolution.</t>
+          <t>Policy documents that represent the official written reference for a given Policy.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>| Entry format example | Valid unit                     |
-|----------------------|-------------------------------|
-| 1 s, 2 h, 1 d        | second, hour, day, month, year |</t>
-        </is>
-      </c>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>- Modified WIGOS Metadata Standard 2019</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
@@ -2932,26 +3013,26 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Reproducibility</t>
+          <t>Impact</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>- core
-description: Concerned with the validity of the results of a particular study, enabling readers to check whether results have been manipulated by reproducing exactly the same study using the same data and methods.</t>
+description: Regarded long-term according to X. However, in the Horizon Europe Missions terminology, regarded short-term.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Concerned with the validity of the results of a particular study, i.e., the possibility for readers to check whether results have been manipulated, by reproducing exactly the same study using the same data and methods.</t>
+          <t>Regarded long-term according to X. However, in the Horizon Europe Missions terminology, regarded short-term.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>- Ostermann and Granell (2015)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
@@ -2974,7 +3055,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Atmosphere</t>
+          <t>Calibration</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2986,16 +3067,12 @@
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Layer of gases, commonly known as air, including suspended liquid and solid particles known as aerosols (incl. dust, clouds, snow and ice).</t>
+          <t>Process of quantitatively defining a system's (e.g. a Sensor or Model's) response to known, controlled inputs produced for example by references. In Remote Sensing, it implies the collection of pre-flight and in-flight calibration measurements and in-situ Data that is to be used in the Data calibration processing routine.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>- Guth et al. 2021</t>
-        </is>
-      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
@@ -3016,38 +3093,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Geolocating</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>- core
-description: Geopositioning of an Object using a Physical Sensor Model or a True Replacement Model.</t>
+          <t>- base
+description: Value and possibly Uncertainty of a Trait of a specific Entity.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Geopositioning of an Object using a Physical Sensor Model or a True Replacement Model.</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
+          <t>Value and possibly Uncertainty of a Trait of a specific Entity.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>- Data simply describe entities using certain traits and are not targeted at a particular use or audience.</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Data can be categorised into:
+- factual (i.e. obtained by Observation) or fictional (obtained e.g. through modelling, estimating or assigning)
+- quantitative (continuous) or qualitative (categorical)
+- analogue or digital
+(list not exhaustive!)</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>- ISO 19115-2:2009, 4.11</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Determination of the geographic location of a feature of two or more dimensions.</t>
+          <t>Scientific or technical measurements, values calculated therefrom, observations, or facts that can be represented by numbers, tables, graphs, models, text, or symbols which are used as a basis for reasoning and further calculation.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>- ISO 19130-1:2018, 3.36 ('geopositioning'), modified</t>
+          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
@@ -3066,32 +3155,40 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Confidence Interval</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>- controversial
-- approved</t>
+          <t>- base
+description: Property having a magnitude that can be expressed as a number from a continuous and contiguous range and a reference.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Probability that the Quantity lies in the interval, conditioned on the measuring or modelling assumptions.</t>
+          <t>Property having a magnitude that can be expressed as a number from a continuous and contiguous range and a reference.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>- ISO/IEC Guide 99:2007, 1.1, modified — Notes omitted</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Property whose instances can be compared by ratio or only by order.</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>- gEOGlos (VIM4 Notes omitted)</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
@@ -3108,19 +3205,19 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Baseline</t>
+          <t>Policy Milestone</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>- core
-- approved</t>
+          <t>- high-impact
+description: Markers of significant progress in addressing specific issues, or crucial decision points where significant choices are made within a policy process.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Reference Period, time or measure against which the Information is assessed or compared.</t>
+          <t>Markers of significant progress in addressing specific issues, or crucial decision points where significant choices are made. Concrete examples include: policy planning and proposing, impact assessment, implementation, or implementation cycles (e.g., Water Framework Directive, Marine Strategy Framework Directive), achievement of Policy Objectives and Policy Targets, and evaluating and improving existing laws.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -3130,18 +3227,10 @@
           <t>- KCEO</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Source data that has been processed to a common set of requirements and organised into a form that allows immediate analysis and interoperability through time and with other collections.</t>
-        </is>
-      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
-        </is>
-      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
@@ -3158,26 +3247,31 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Classification System Levels</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>- core
-- approved</t>
+          <t>- base
+description: Element of a type domain.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Levels in a hierarchical Classification System.</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
+          <t>Element of a type domain.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>- A Value may consider a possible state of an object within a class or type (domain).
+- A data value is an instance of a data type, a value without identity.</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO/IEC 19501:2005, 0000_5</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -3200,26 +3294,26 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Latency</t>
+          <t>Collection Update</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>- core
-description: Period between the end of sensing of a Phenomenon to the beginning of availability of a specific product.</t>
+- approved</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Period between the end of sensing of a Phenomenon to the beginning of availability of a specific product.</t>
+          <t>Minor revisions to a relatively small number of products within a collection for the purpose of correcting errors and maintaining consistent quality.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>- ?</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -3242,20 +3336,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Laboratory Observation</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>- core
-  - to be defined</t>
+description: Usually in-situ observations in which the Object or Phenomenon is isolated from other systems or altered in its original conditions or environment.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Usually in-situ observations in which the Object or Phenomenon is isolated from other systems or altered in its original conditions or environment.</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>- It is important to consider that Laboratory Observations are typically conducted in controlled conditions, allowing for isolation or alteration of the Object or Phenomenon from its natural environment or other systems.</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
@@ -3276,28 +3382,20 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Access</t>
+          <t>Environmental Process</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>- core
-description: Service to disseminate Data.</t>
+description: ""</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Service to disseminate Data.</t>
-        </is>
-      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
@@ -3318,26 +3416,26 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Phenomenon</t>
+          <t>Measurement Uncertainty</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>- base
-description: Entity with at least one Property referenced by an identifier.</t>
+          <t>- core
+description: Uncertainty associated with the method of Measurement.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Entity with at least one Property referenced by an identifier.</t>
+          <t>Uncertainty associated with the method of Measurement.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>- KCEO, modified after Wikipedia and the Columbia Encyclopaedia 2008</t>
+          <t>- CEOS Wiki adopted from JCGM GUM</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
@@ -3360,39 +3458,20 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Earth Spheres</t>
+          <t>Continuity</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>- core
-description: Spheres dividing planet Earth into subsystems, which are collectives of (physical) matter sharing specific traits.</t>
+  - to be defined</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Spheres dividing planet Earth into subsystems, which are collectives of (physical) matter sharing specific traits.</t>
-        </is>
-      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>- Atmosphere
-- Hydrosphere
-- Cryosphere
-- Biosphere
-- Lithosphere
-- Anthroposphere</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>- Hugget, R., et al., 2024, DOI: 10.1177/03091333241275465
-- Guth, P., et al., 2021, https://doi.org/10.3390/rs13183581
-- Martin, Y.E., et al., 2012</t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
@@ -3413,31 +3492,37 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Temporal Revisit</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>- base
-description: Element of a type domain.</t>
+          <t>- core
+description: Interval between successive observations.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Element of a type domain.</t>
+          <t>Interval between successive observations.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>- A Value may consider a possible state of an object within a class or type (domain).
-- A data value is an instance of a data type, a value without identity.</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
+          <t>- In Remote Sensing it is also called repeat cycle.
+- More generally it is known as temporal sampling interval.</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>| Entry format example | Valid unit                     |
+|----------------------|-------------------------------|
+| 1 s, 2 h             | second, hour, day, month, year |</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>- ISO/IEC 19501:2005, 0000_5</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
@@ -3460,36 +3545,20 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Timeliness</t>
+          <t>Resolution</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>- core
-description: Period between the moment of requesting information and the moment of availability of information.</t>
+  - to be defined</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Period between the moment of requesting information and the moment of availability of information.
-- Near Real-Time (NRT): delivered less than 3 hours after requesting information.
-- Slow-Time Critical (STC): delivered within 48 hours after requesting information.
-- Non-Time Critical (NTC): typically delivered within 1 month after requesting information.</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>- In some contexts also known as delivery time.
-- C3S URDB describes timeliness as "the ability of the publish/subscribe middleware to provide the expected service within known time bounds".</t>
-        </is>
-      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>- Adapted from ESA S3 User Guide</t>
-        </is>
-      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
@@ -3510,59 +3579,40 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Auxiliary Data</t>
+          <t>Period Identifier</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Temporal reference in the form of a label or code that identifies a Period.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Data that enhance the processing and utilisation of main Sensor Data. Auxiliary Data are usually not captured by the same Data collection Process or on the same platform as the main Sensor Data. Examples include meteorological Data received from ECMWF/Met Offices or DEMs. Auxiliary Data help in Data processing, but are also Data sets in their own right.</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr"/>
+          <t>Temporal reference in the form of a label or code that identifies a Period.</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>- Period Identifiers are the temporal equivalent of geographic identifiers as specified in ISO 19912.</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>- ESA/CEOS?, modified
-- ENMAP Glossary of Terms, https://www.enmap.org/Data/doc/EnMAP_Terms.pdf, 20210624
-- EO Data Stewardship Glossary</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Data required to perform processing of Sensor Data which is not obtained from the Sensor itself. Includes: (a) Data provided by the spacecraft (e.g. orbit Position and velocity, attitude, instrument house-keeping Data, on-board time); (b) Data not available from on-board sources.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>For EnMAP, this includes (a) orbit files, attitude files, Calibration Data, instrument house-keeping Data; (b) atmospheric parameters, reference images.</t>
-        </is>
-      </c>
+          <t>- ISO 19170:2021</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>- ENMAP Glossary of Terms, https://www.enmap.org/Data/doc/EnMAP_Terms.pdf, 20210624
-- EO Data Stewardship Glossary</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>Data required for instrument processing that does not originate in the instrument itself or from the satellite. Some Auxiliary Data will be generated in the ground segment, whilst other Data will be provided from external sources.</t>
-        </is>
-      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>- CEOS-ARD PFS template 20220302</t>
-        </is>
-      </c>
+      <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
@@ -3623,40 +3673,40 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Quantity</t>
+          <t>Timeliness</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>- base
-description: Property having a magnitude that can be expressed as a number from a continuous and contiguous range and a reference.</t>
+          <t>- core
+description: Period between the moment of requesting information and the moment of availability of information.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Property having a magnitude that can be expressed as a number from a continuous and contiguous range and a reference.</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr"/>
+          <t>Period between the moment of requesting information and the moment of availability of information.
+- Near Real-Time (NRT): delivered less than 3 hours after requesting information.
+- Slow-Time Critical (STC): delivered within 48 hours after requesting information.
+- Non-Time Critical (NTC): typically delivered within 1 month after requesting information.</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>- In some contexts also known as delivery time.
+- C3S URDB describes timeliness as "the ability of the publish/subscribe middleware to provide the expected service within known time bounds".</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>- ISO/IEC Guide 99:2007, 1.1, modified — Notes omitted</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Property whose instances can be compared by ratio or only by order.</t>
-        </is>
-      </c>
+          <t>- Adapted from ESA S3 User Guide</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>- gEOGlos (VIM4 Notes omitted)</t>
-        </is>
-      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
@@ -3673,32 +3723,20 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Final Product Version</t>
+          <t>Equivalence</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>- core
-description: Product within an EO Collection that is not expected to be updated.</t>
+  - to be defined</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Product within an EO Collection that is not expected to be updated.</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>- In its production, all of the prerequisite auxiliary data were used as input.</t>
-        </is>
-      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
-        </is>
-      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
@@ -3719,31 +3757,26 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Hydrosphere</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>- controversial
-description: Act of determining the Value of a Property by interacting in a reproducible way with the Phenomenon using a Sensor.</t>
+          <t>- core
+description: The masses of liquid water, such as oceans, lakes, and rivers.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Act of determining the Value of a Property by interacting in a reproducible way with the Phenomenon using a Sensor.</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>- The result of an Observation is a Value complemented by an Uncertainty, often itself being referred to as 'observation'.
-- An Observation result represents a Sample of the Phenomenon (otherwise it would be identical with the Phenomenon).</t>
-        </is>
-      </c>
+          <t>The masses of liquid water, such as oceans, lakes, and rivers.</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
@@ -3766,56 +3799,36 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Characteristic</t>
+          <t>Accuracy</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>- base
+          <t>- core
 - approved</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Distinguishing Feature.</t>
+          <t>Proximity of Measurement results to the accepted Value; precision is the degree to which repeated or reproducible measurements under unchanged conditions show the same results.</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>- A Characteristic can be inherent or assigned.
-- A Characteristic can be qualitative or quantitative.
-- There are various classes of Characteristics, such as the following:
-  - physical (e.g. mechanical, electrical, chemical, biological);
-  - sensory (e.g. relating to smell, touch, taste, sight, hearing);
-  - behavioural (e.g. courtesy, honesty, veracity);
-  - temporal (e.g. punctuality, reliability, availability);
-  - ergonomic (e.g. physiological characteristic or related to human safety);
-  - functional (e.g. maximum speed of an aircraft).</t>
+          <t>- In essence, Accuracy reflects how close measurements are to the accepted Value, while precision gauges the reliability and consistency of those measurements.</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>- ISO 9000:2005, 3.5.1</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Abstraction of a Property of an Object or of a set of objects.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>- Characteristics are used for describing Concepts.</t>
-        </is>
-      </c>
+          <t>- BS ISO 5725-1</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>- ISO 1087-1:2000, 3.2.4; ISO 19146:2010(E); https://www.iso.org/standard/20057.html</t>
-        </is>
-      </c>
+      <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
@@ -3832,26 +3845,26 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Geosphere</t>
+          <t>Traceability</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>- core
-description: The masses of minerals that constitute planet Earth.</t>
+description: Property of a measurement result whereby the result can be related to a reference through a documented unbroken chain of calibrations each contributing to the measurement uncertainty.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>The masses of minerals that constitute planet Earth.</t>
+          <t>Property of a measurement result whereby the result can be related to a Reference through a documented unbroken chain of calibrations, each contributing to the measurement uncertainty.</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- https://www.isobudgets.com/Measurement-traceability-complying-iso-17025-requirements/</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -3874,26 +3887,26 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Spectral Resolution</t>
+          <t>Biosphere</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>- core
-description: Measure of the ability to resolve features in the electromagnetic spectrum.</t>
+- approved</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Measure of the ability to resolve features in the electromagnetic spectrum.</t>
+          <t>Masses of living organisms, such as vegetation and animals, including dead but still connected parts such as roots, trunks or branches.</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
@@ -3916,26 +3929,30 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Hydrosphere</t>
+          <t>Update Frequency</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>- core
-description: The masses of liquid water, such as oceans, lakes, and rivers.</t>
+description: Frequency at which the product is available to users.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>The masses of liquid water, such as oceans, lakes, and rivers.</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr"/>
+          <t>Frequency at which the product is available to users.</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>- Also known in product catalogues as dissemination frequency.</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
@@ -3958,33 +3975,26 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Time of Year</t>
+          <t>Lithosphere</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>- core
-description: Time of the year at which the variable is observed or simulated by a model.</t>
+description: The solid, inanimate outer layer of the Geosphere. For the purposes of Earth Observation, includes soils ('pedosphere').</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Time of the year at which the variable is observed or simulated by a model.</t>
+          <t>The solid, inanimate outer layer of the Geosphere. For the purposes of Earth Observation, the Lithosphere is considered to include soils ('pedosphere').</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>| Type      | Entry format example | Valid unit     |
-|-----------|----------------------|----------------|
-| timestamp | m/d                  | Not Applicable |
-| timerange | m/d - m/d            | Not Applicable |</t>
-        </is>
-      </c>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
@@ -4007,24 +4017,24 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Path</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>- base
-description: "Line defined in an algorithmic way using at least two positions (can be open-ended). Alternative: line connecting two positions in an algorithmic way (limited by end points)."</t>
+description: The result of organisation, interpretation, categorisation, classification, or some other form of processing of Data attaching to it a certain meaning that can be understood by the addressee.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Line defined in an algorithmic way using at least two positions (can be open-ended). Alternative: line connecting two positions in an algorithmic way (limited by end points).</t>
+          <t>The result of organisation, interpretation, categorisation, classification, or some other form of processing of Data attaching to it a certain meaning that can be understood by the addressee.</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>- A Path is a 1-dimensional Place.</t>
+          <t>- Information depends on Data and is targeted.</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
@@ -4053,19 +4063,19 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Spatial Consistency</t>
+          <t>Temporal Consistency</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>- core
-description: Condition where the spatial statistical properties of the data depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
+description: Condition where the temporal statistical properties of the sample depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Condition where the spatial statistical properties of the data depend only on the underlying physical processes and not on other factors such as fusing different products or sensors. Also, the validity of the assumptions of the procedure to produce information holds true across the whole spatial range.</t>
+          <t>Condition where the temporal statistical properties of the Sample depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -4095,30 +4105,31 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cell</t>
+          <t>Metadata</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Data describing other data, providing an understanding of the content and utility of a product or collection.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Spatial, spatio-temporal zone or temporal unit of geometry with dimensionality greater than 0, associated with a zone.</t>
+          <t>Data describing other data, providing an understanding of the content and utility of a product or collection.</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>- Cells are the unit of geometry in a DGGS, and the geometry of the region of space-time occupied by a zone is a Cell.</t>
+          <t>- Metadata may be used to select data for a particular scientific investigation.
+- Metadata is intended as information describing significant aspects of a resource (Earth Observation space data in this context). They are created for the purposes of data search, discovery and access management and may exist at various levels, typically from data collection through to the individual variables of each product in a collection.</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>- ISO 19170:2021</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
@@ -4141,26 +4152,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Business Continuity</t>
+          <t>Spatial Resolution</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: ''</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>An organisation's readiness to continue functioning during times of disruption.</t>
-        </is>
-      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
@@ -4183,31 +4190,26 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Derivative Product</t>
+          <t>Phenomenon</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>- core
-description: Product additionally processed from baseline or unenhanced mission data.</t>
+          <t>- base
+description: Entity with at least one Property referenced by an identifier.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Product additionally processed from baseline or unenhanced mission data.</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>- Generally either a compilation of time-series data (e.g., all time, annual, monthly or seasonal summary data, &gt; Level 3) or thematic versions of each individual data tile of baseline data.
-- Derived products are citable via a Digital Object Identifier (DOI).</t>
-        </is>
-      </c>
+          <t>Entity with at least one Property referenced by an identifier.</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- KCEO, modified after Wikipedia and the Columbia Encyclopaedia 2008</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
@@ -4230,26 +4232,26 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Policy Objective</t>
+          <t>Geolocation Information</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>- high-impact
-description: Desired outcome that policymakers wish to achieve.</t>
+          <t>- core
+description: Information used to determine geographic Location.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Desired outcome that policymakers wish to achieve.</t>
+          <t>Information used to determine geographic Location.</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO 19130-1:2018, 3.34</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
@@ -4272,62 +4274,57 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Verification</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>- core
-description: Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
+description: Provision of objective evidence that a given item fulfils specified requirements.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
+          <t>Provision of objective evidence that a given item fulfils specified requirements.</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
+          <t>- When applicable, measurement uncertainty should be taken into consideration.
+- The item may be, e.g. a Process, measurement procedure, material, compound, or measuring system.
+- The specified requirements may be, e.g. that a manufacturer's specifications are met.
+- Verification should not be confused with Calibration. Not every verification is a Validation.</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>- ISO/TS 19101‑2:2008, 4.41</t>
+          <t>- ISO/IEC Guide 99:2007, 2.44</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Process aimed at verifying that the specified requirements are achieved or compliant. Involves comparing mission products with representative reference data, considering various observation conditions, ensuring the quality and traceability of the reference data used.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
-        </is>
-      </c>
+          <t>Evaluation of whether or not a product, service, or system complies with a regulation requirement, specification, or imposed condition. Often an internal Process.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
-          <t>- BIPM; QA4EO; ESA?, modified</t>
+          <t>- EU-US Land Imaging EO Collaboration</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Assurance that a product, service, or system meets the needs of the customer and other identified stakeholders. Often involves acceptance and suitability with external customers.</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
-        </is>
-      </c>
+          <t>Means to evaluate the reliability of the data in the absence of a reference dataset, allowing for an assessment of its standalone performance. Involves confirming the consistency and internal coherence of the data without direct comparison to external reference sources.</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr">
         <is>
-          <t>- EU-US Land Imaging EO Collaboration</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="P84" t="inlineStr"/>
@@ -4342,35 +4339,26 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Temporal Extent</t>
+          <t>Property</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>- core
-description: Period during which data was collected, observations were made, or for which the model was run.</t>
+          <t>- base
+description: Observable Trait.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Period during which data was collected, observations were made, or for which the model was run.</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>- In W3C this is the definition of temporal coverage.
-- Time Period covered by a series of observations inclusive of the specified date/time indications (measurement history). Defined based on the beginning and end dates of observations.</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>- WIGOS Metadata</t>
-        </is>
-      </c>
+          <t>Observable Trait.</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>- Adapted from W3C</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
@@ -4393,26 +4381,26 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Traceability</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>- core
-description: Property of a measurement result whereby the result can be related to a reference through a documented unbroken chain of calibrations each contributing to the measurement uncertainty.</t>
+          <t>- base
+description: Entity with a well-defined boundary and identity that encapsulates state and behaviour.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Property of a measurement result whereby the result can be related to a Reference through a documented unbroken chain of calibrations, each contributing to the measurement uncertainty.</t>
+          <t>Entity with a well-defined boundary and identity that encapsulates state and behaviour.</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>- https://www.isobudgets.com/Measurement-traceability-complying-iso-17025-requirements/</t>
+          <t>- ISO/IEC 19501:2005</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
@@ -4435,30 +4423,37 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Decommissioned Product</t>
+          <t>Time of Day</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>- core
-description: Products and collections that have been superseded by new versions and are no longer available.</t>
+description: Time of the day at which the variable or parameter is observed or simulated by a model.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Products and collections that have been superseded by new versions and are no longer available.</t>
+          <t>Time of the day at which the variable or parameter is observed or simulated by a model.</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>- Decommissioned products are no longer supported, i.e. corrections will not be made, new data will not be added, and support is not available.</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr"/>
+          <t>- In Remote Sensing it is also known as time of overpass.</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>| Type      | Entry format example | Valid unit |
+|-----------|----------------------|------------|
+| timestamp | 18:00 h (0–24)       | Hours      |
+| timerange | 18:00 – 20:00 h      | Hours      |</t>
+        </is>
+      </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
@@ -4481,31 +4476,26 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Grid</t>
+          <t>Obsolete Product or Collection</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>- core
-description: Network composed of two or more sets of curves in which the members of each set intersect the members of the other sets in an algorithmic way.</t>
+description: Products or collections which have been superseded by later versions of a product or collection.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Network composed of two or more sets of curves in which the members of each set intersect the members of the other sets in an algorithmic way.</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>- The curves partition a space into grid cells or zones.
-- The intersection points of the curves are called nodes.</t>
-        </is>
-      </c>
+          <t>Products or collections which have been superseded by later versions of a product or collection.</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>- ISO 19123:2005, 4.1.23; Note 1 modified; Note 2 added</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
@@ -4528,36 +4518,40 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Measurement</t>
+          <t>Baseline</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>- core
-description: Observation of a Quantity.</t>
+- approved</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Observation of a Quantity.</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>- The Process of collecting a measurement is called measuring.</t>
-        </is>
-      </c>
+          <t>Reference Period, time or measure against which the Information is assessed or compared.</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>- GEOGlos (VIM ?, modified)</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>- KCEO</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Source data that has been processed to a common set of requirements and organised into a form that allows immediate analysis and interoperability through time and with other collections.</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
@@ -4574,30 +4568,31 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Catalogue</t>
+          <t>Earth Observation</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>- core
-- approved</t>
+          <t>- high-impact
+description: Science domain dealing with technologies and methods of collecting and analyzing observations about the different Earth spheres.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>System that provides users with discovery of information on which EO products can be obtained.</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>- A 'Product Catalogue' can organise products and collections with varying access levels depending on product and user type.</t>
-        </is>
-      </c>
+          <t>Science domain dealing with technologies and methods of collecting and analyzing observations about the different Earth spheres.</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>- Earth Observation (EO) can be categorised by location of the sensor into space-borne, air-borne, sea-borne, ground-based, underwater and underground EO.
+- Earth Observation (EO) includes Remote Sensing, such as satellite imagery, as well as in-situ observations, e.g., with ground-based devices.</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- Modified GEO definition [GEO (earthobservations.org)](https://earthobservations.org/resources#key)</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
@@ -4620,36 +4615,24 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Tolerance</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>- core
-description: Phenomenon whose values for specific properties are known and understood with an Uncertainty significantly lower than that of the Observation with which it is compared.</t>
+  - to be defined</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Phenomenon whose values for specific properties are known and understood with an Uncertainty significantly lower (quantify?) than that of the Observation with which it is compared.</t>
-        </is>
-      </c>
+      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Sort of data acquired with an Uncertainty significantly lower (quantify?) than that of the data it is being compared with.</t>
-        </is>
-      </c>
+      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>- VIM?, modified</t>
-        </is>
-      </c>
+      <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
@@ -4666,26 +4649,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Laboratory Observation</t>
+          <t>Spectral Resolution</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>- core
-description: Usually in-situ observations in which the Object or Phenomenon is isolated from other systems or altered in its original conditions or environment.</t>
+description: Measure of the ability to resolve features in the electromagnetic spectrum.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Usually in-situ observations in which the Object or Phenomenon is isolated from other systems or altered in its original conditions or environment.</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>- It is important to consider that Laboratory Observations are typically conducted in controlled conditions, allowing for isolation or alteration of the Object or Phenomenon from its natural environment or other systems.</t>
-        </is>
-      </c>
+          <t>Measure of the ability to resolve features in the electromagnetic spectrum.</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
@@ -4712,32 +4691,26 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sample</t>
+          <t>Near Real Time Data</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>- controversial
-description: Subset of one or more entities.</t>
+          <t>- high-impact
+description: Data available for use with a specified (small and application dependent) latency, typically 3 hours for meteorological applications.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Subset of one or more entities.</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>- A Sample may be spatial, temporal, spectral, or in any other dimension or Trait.
-- Each Sample is contiguous, i.e. it does not consist of more than one discontinuous geometry in any dimension.
-- The Process of obtaining a Sample is called sampling.</t>
-        </is>
-      </c>
+          <t>Data available for use with a specified (small and application dependent) latency, typically 3 hours for meteorological applications.</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
@@ -4760,30 +4733,38 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Trait</t>
+          <t>Measurand</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>- base
-description: Characteristic belonging to an entity and referenced by an identifier.</t>
+          <t>- core
+description: Particular Quantity subject to Measurement.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Characteristic belonging to an entity and referenced by an identifier.</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>- Traits can be objective (inherent?) in which case they are also observable and called properties. Traits which are not observable (directly or indirectly) need to be assigned.</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr"/>
+          <t>Particular Quantity subject to Measurement.</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>| Step | Process description |
+| :----- | :--------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------- |
+| (Raw) | The complete and unaltered/unprocessed set of Data acquired by one or several sensors on a platform |
+| M/0 uncalibrated | Unaltered/unprocessed Level 0 (main) Sensor Data annotated with processed Ancillary Data and supplemented by Auxiliary Data (including radiometric and geometric Calibration coefficients and geo-referencing parameters) allowing further processing to higher Levels. |
+| M/1 Sensor-calibrated | Level M/0 Sensor Data which have been calibrated (ideally traceable to SI) and spatially aligned (co-located, eventually co-gridded) to represent at-Sensor measurements (Value and Uncertainty) in Sensor nominal spatiotemporal sampling, supplemented by appropriate ancillary data. |
+| M/2 target-calibrated | Level M/1 Data processed to represent geophysical Property values (and uncertainties) for a specified target (Object, Feature of interest, e.g. surface reflectance, apparent temperature) derived from M/1 Sensor Data, as much as possible maintaining the sensors nominal spatial and temporal sampling (Observation preserving). |
+| M/3 homogenised | Level M/1 or M/2 Data which have been generalised and integrated across one or several platforms and acquisitions to achieve an increased, more regular or in any other form enhanced spatial or temporal coverage in which states geophysical values agnostic of the originally acquiring Sensor and Observation condition and thus directly comparable. This homogenisation and fusion may include measurand re-Calibration to external standards and references including use of modelling, aggregation and interpolation. |
+| M/4 derived/inferred | Model output or results from analyses of Level M/3 (or lower level) Data i.e., attributes that might not be directly observable by the Sensor(s) but are derived from observations in combination with other external incl. non-observational Data using techniques like modelling or machine learning (AI). |
+From http://doi.org/10.2760/46796</t>
+        </is>
+      </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>- Based on ISO 19143:2010, 4.21, ISO/IEC 2382:2015, 2121440, significantly modified, Note 1 added</t>
+          <t>- VIM: 1993, 2.6</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
@@ -4806,31 +4787,26 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Metadata</t>
+          <t>Latency</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>- core
-description: Data describing other data, providing an understanding of the content and utility of a product or collection.</t>
+description: Period between the end of sensing of a Phenomenon to the beginning of availability of a specific product.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Data describing other data, providing an understanding of the content and utility of a product or collection.</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>- Metadata may be used to select data for a particular scientific investigation.
-- Metadata is intended as information describing significant aspects of a resource (Earth Observation space data in this context). They are created for the purposes of data search, discovery and access management and may exist at various levels, typically from data collection through to the individual variables of each product in a collection.</t>
-        </is>
-      </c>
+          <t>Period between the end of sensing of a Phenomenon to the beginning of availability of a specific product.</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- ?</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
@@ -4853,30 +4829,26 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Backup</t>
+          <t>Policy Target</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>- core
-- approved</t>
+          <t>- high-impact
+description: Specific level or rate set for the Policy Objective.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>General practice of making copies of current baseline and derived products of EO Collections at specified time intervals, and storing those copies in a manner that will not affect the data if the primary distribution environment is compromised.</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>- The emphasis is on the ability to retrieve a copy of the entire EO Collection on demand if the original data is lost or compromised.</t>
-        </is>
-      </c>
+          <t>Specific level or rate set for the Policy Objective.</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
@@ -4899,20 +4871,28 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Tolerance</t>
+          <t>Policy Objective</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>- core
-  - to be defined</t>
+          <t>- high-impact
+description: Desired outcome that policymakers wish to achieve.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Desired outcome that policymakers wish to achieve.</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
@@ -4933,30 +4913,26 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Archive</t>
+          <t>Forecast Range</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: The forecast period.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>System that stores data products, guaranteeing their preservation for future use.</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>- This function includes all operations to identify, store and retrieve the data and ensure their integrity.</t>
-        </is>
-      </c>
+          <t>The forecast period.</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
@@ -4979,26 +4955,26 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Biosphere</t>
+          <t>Quality Indicator</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Indicator providing sufficient information to allow all users to readily evaluate the fitness for purpose of the data or derived product.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Masses of living organisms, such as vegetation and animals, including dead but still connected parts such as roots, trunks or branches.</t>
+          <t>Indicator providing sufficient information to allow all users to readily evaluate the fitness for purpose of the data or derived product. May be a number, set of numbers, graph, Uncertainty budget, or a simple flag.</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- CEOS Wiki</t>
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
@@ -5021,26 +4997,26 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Impact</t>
+          <t>User Interface</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>- core
-description: Regarded long-term according to X. However, in the Horizon Europe Missions terminology, regarded short-term.</t>
+description: Set of all the components of an interactive system that provide information and controls for the user to accomplish specific tasks with the interactive system.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Regarded long-term according to X. However, in the Horizon Europe Missions terminology, regarded short-term.</t>
+          <t>Set of all the components of an interactive system that provide information and controls for the User to accomplish specific tasks with the interactive system.</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO 9241-110:2020, 3.10</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
@@ -5063,26 +5039,30 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Obsolete Product or Collection</t>
+          <t>Stability</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>- core
-description: Products or collections which have been superseded by later versions of a product or collection.</t>
+description: Maximum acceptable change in Uncertainty per decade.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Products or collections which have been superseded by later versions of a product or collection.</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr"/>
+          <t>Maximum acceptable change in Uncertainty per decade.</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>- GCOS uses bias or systematic errors instead of Uncertainty.</t>
+        </is>
+      </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- Modified from GCOS 2022</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
@@ -5105,26 +5085,26 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Measurement Uncertainty</t>
+          <t>Classification System</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>- core
-description: Uncertainty associated with the method of Measurement.</t>
+- approved</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Uncertainty associated with the method of Measurement.</t>
+          <t>Nomenclature used to classify Information into categorical thematic classes (e.g., EUNIS, MAES ecosystems, Corine Land Cover, LCCS).</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>- CEOS Wiki adopted from JCGM GUM</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
@@ -5147,17 +5127,21 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Spatial Resolution</t>
+          <t>Spatial Consistency</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>- core
-description: ''</t>
+description: Condition where the spatial statistical properties of the data depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Condition where the spatial statistical properties of the data depend only on the underlying physical processes and not on other factors such as fusing different products or sensors. Also, the validity of the assumptions of the procedure to produce information holds true across the whole spatial range.</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
@@ -5185,27 +5169,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>In-Situ Observation</t>
+          <t>Expanded Uncertainty</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>- controversial
-description: Observations performed in the same Place where a Phenomenon occurs, normally without isolating it from other systems or altering its pre-Observation state.</t>
+          <t>- core
+description: Standard Uncertainty multiplied by a coverage factor k, chosen to obtain a desired level of confidence.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Observations performed in the same Place where a Phenomenon occurs, normally without isolating it from other systems (its environment) or altering its pre-Observation state.</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>- The main Characteristic of such observations is that distance has no or only negligible (within Uncertainty) influence on the Value of the Property observed. In-Situ Observations therefore often require either direct physical contact or small distances between a Sensor and the observed Phenomenon.
-- Observations not fulfilling these conditions are considered Remote Sensing.</t>
-        </is>
-      </c>
+          <t>Standard Uncertainty multiplied by a coverage factor, k. The coverage factor is chosen to obtain a desired level of confidence. Most commonly a 95% confidence interval is chosen. For a Gaussian distribution, this is achieved with a coverage factor k = 2. (Note that strictly this provides a 95.45% confidence interval.)</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
@@ -5232,28 +5211,29 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Earth Observation Product</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>- core
-description: Direct output from standardized satellite data processing chains (indicative levels 2 and 3), representing fundamental geophysical and biophysical variables.</t>
+description: Device or instrument suited (through physical/chemical interaction) to measure one or more properties of a Phenomenon and thus collect factual/objective data.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Direct output from standardized satellite data processing chains (indicative levels 2 and 3), representing fundamental geophysical and biophysical variables. These products demonstrate direct Traceability to original satellite measurements through rigorous Calibration and Validation processes. The processing methodology prioritizes the conversion of raw sensor data into quantifiable physical measurements, maintaining strict adherence to standardized processing protocols and Validation requirements.</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>- Soil moisture from microwave sensors
-- Forest canopy height from LiDAR data</t>
-        </is>
-      </c>
+          <t>Device or instrument suited (through physical/chemical interaction) to measure one or more properties of a Phenomenon and thus collect factual/objective data.</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>- Sensing is therefore a synonym for Observation (the Process).
+- As by their definition, sensors perform sampling.
+- Sensors used to obtain measurements must be calibrated and provide uncertainties.</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
           <t>- KCEO</t>
@@ -5279,30 +5259,26 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Spatial Completeness</t>
+          <t>Minimum Mapping Width</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>- core
-description: Presence or absence of gaps, which are missing values in an otherwise continuous spatial data series.</t>
+description: The width of the smallest linear Feature that is still represented on a map.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Presence or absence of gaps, which are missing values in an otherwise continuous spatial data series.</t>
+          <t>The width of the smallest linear Feature that is still represented on a map.</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>- Surface soil moisture retrieved from microwave satellite sensors may present gaps in mountainous terrains.</t>
-        </is>
-      </c>
+      <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- CGLS</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
@@ -5325,30 +5301,30 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Geocoding</t>
+          <t>Backup</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>- core
-description: Translation of one form of Location into another.</t>
+- approved</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Translation of one form of Location into another.</t>
+          <t>General practice of making copies of current baseline and derived products of EO Collections at specified time intervals, and storing those copies in a manner that will not affect the data if the primary distribution environment is compromised.</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>- Geocoding usually refers to the translation of "address" or "intersection" to "direct Position." Many service providers also include a "reverse geocoding" interface to their geocoder, thus extending the definition of the service as a general translator of Location. Because routing services use internal Location encodings not usually available to others, a geocoder is an integral part of the internals of such a service.</t>
+          <t>- The emphasis is on the ability to retrieve a copy of the entire EO Collection on demand if the original data is lost or compromised.</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>- ISO 19133:2005; https://www.iso.org/standard/32551.html</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
@@ -5371,44 +5347,42 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Georectifying</t>
+          <t>Temporal Resolution</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>- core
-description: Correcting for positional displacement with respect to the surface of the Earth.</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Orthorectifying</t>
-        </is>
-      </c>
+description: Observation or model output representing regular intervals, specifying the length of the interval that determines the smallest event or process that can be resolved.</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Correcting for positional displacement with respect to the surface of the Earth.</t>
+          <t>Observation or model output representing regular intervals, specifying the length of the interval that determines the smallest event or Process that can be resolved (e.g., the Period between observations, the time steps in a model).</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>- Source: ISO 19115-2:2019, 3.11; ISO 19115-2:2009(E); https://www.iso.org/standard/67039.html, modified</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>The correction of sample locations to achieve some sort of geometric regularity, e.g., a regular 2D geographic grid.</t>
-        </is>
-      </c>
+          <t>- WIGOS 2019 distinguishes between sampling time Period, as the Period over which a Measurement is taken, and temporal sampling interval as the time Period between the beginning of consecutive sampling periods. Temporal Resolution in this Glossary is equivalent to sampling time Period as used by WIGOS.</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>| Entry format example | Valid unit                     |
+|----------------------|-------------------------------|
+| 1 s, 2 h, 1 m        | second, hour, day, month, year |</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
+      <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
@@ -5425,26 +5399,26 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Licencing</t>
+          <t>Place</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>- core
-description: Legal instrument by which a copyright holder may grant rights over the protected work.</t>
+          <t>- base
+description: Part of any space referenced by an identifier.</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Legal instrument by which a copyright holder may grant rights over the protected work. Data and content is open if it is subject to an explicitly-applied licence that conforms to the Open Definition. A range of standard open licences are available, such as the Creative Commons CC-BY licence, which requires only attribution.</t>
+          <t>Part of any space referenced by an identifier.</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>- CEOS Wiki</t>
+          <t>- ISO 19155:2012, 4.8</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
@@ -5467,36 +5441,45 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Period</t>
+          <t>Ancillary Data</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>- base
-description: Particular era or span of time.</t>
+          <t>- core
+- approved</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Particular era or span of time.</t>
+          <t>Data acquired on the same platform but not obtained from the main Sensor itself (usually provided as part of Level 0 Data), with the primary purpose of serving the processing of main instrument Data (e.g. Position and velocity of platform).</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>- Periods are intervals named with a Period Identifier.</t>
+          <t>This can be divided into data referred to as spacecraft 'engineering', 'core housekeeping' or 'subsystem' data obtained from other parts of the platform, and includes parameters such as orbit position and velocity, attitude and its range of change, time, temperatures, pressures, jet firings, water dumps, internally produced magnetic fields, and other environmental measurements. Ancillary refers to data that exist purely to serve the data processing.</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>- ISO 19170:2021</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr"/>
+          <t>- ESA/CEOS?, modified
+- EO Data Stewardship Glossary</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Data other than instrument measurements, originating in the instrument itself or from the satellite, required to perform processing of the Data. Includes orbit Data, attitude Data, time Information, and spacecraft engineering Data, Calibration Data, Data quality Information, and Data from other instruments or earth system models.</t>
+        </is>
+      </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>- CEOS-ARD PFS template 20220302</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
@@ -5513,26 +5496,31 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Collection Upgrade</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>- core
-- approved</t>
+          <t>- controversial
+description: Act of determining the Value of a Property by interacting in a reproducible way with the Phenomenon using a Sensor.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>New and improved major version of all products within a collection due to comprehensive reprocessing.</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
+          <t>Act of determining the Value of a Property by interacting in a reproducible way with the Phenomenon using a Sensor.</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>- The result of an Observation is a Value complemented by an Uncertainty, often itself being referred to as 'observation'.
+- An Observation result represents a Sample of the Phenomenon (otherwise it would be identical with the Phenomenon).</t>
+        </is>
+      </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
@@ -5555,30 +5543,31 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Grid</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>- base
-description: Abstraction of real-world phenomena.</t>
+          <t>- core
+description: Network composed of two or more sets of curves in which the members of each set intersect the members of the other sets in an algorithmic way.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Abstraction of real-world phenomena.</t>
+          <t>Network composed of two or more sets of curves in which the members of each set intersect the members of the other sets in an algorithmic way.</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>- A feature may occur as a type or an instance.</t>
+          <t>- The curves partition a space into grid cells or zones.
+- The intersection points of the curves are called nodes.</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>- ISO 19101-1:2014, 4.1.11, modified</t>
+          <t>- ISO 19123:2005, 4.1.23; Note 1 modified; Note 2 added</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
@@ -5601,36 +5590,44 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Custodian</t>
+          <t>User</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>- core
-description: Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
+description: Entity (person, organization, institution, etc.) that is requesting data or information with certain characteristics described by needs and/or requirements.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>- See also Steward.</t>
-        </is>
-      </c>
+          <t>In the context of the KCEO, entity (person, organization, institution, etc.) that is requesting data or information with certain characteristics described by needs and/or requirements.</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
+          <t>- KCEO</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>External person, institution or system that consumes provided services.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>- Includes Data Access or Science and Service Exploitation Platforms provided by a payload data ground segment.</t>
+        </is>
+      </c>
       <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>- EO Data Stewardship Glossary</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
@@ -5647,26 +5644,35 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Anthroposphere</t>
+          <t>Remote Sensing</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>- core
-- approved</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr"/>
+          <t>- controversial
+description: Type of Observation performed at a significant distance from a Phenomenon.</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Remote Observation</t>
+        </is>
+      </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>One of the Earth spheres consisting predominantly of matter processed by humans, such as construction wood, bricks, concrete, asphalt, glass, or plastics.</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr"/>
+          <t>Type of Observation performed at a significant distance from a Phenomenon.</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>- 'Significant' in this context means that the distance has, or may have, a non-negligible impact on the Value of the Property observed.
+- The effect of the distance on the acquired data is the main distinction criterion between 'remote' and 'in-situ' observations.</t>
+        </is>
+      </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
@@ -5689,44 +5695,37 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>Earth Observation Product</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>- core
-description: Entity (person, organization, institution, etc.) that is requesting data or information with certain characteristics described by needs and/or requirements.</t>
+description: Direct output from standardized satellite data processing chains (indicative levels 2 and 3), representing fundamental geophysical and biophysical variables.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>In the context of the KCEO, entity (person, organization, institution, etc.) that is requesting data or information with certain characteristics described by needs and/or requirements.</t>
+          <t>Direct output from standardized satellite data processing chains (indicative levels 2 and 3), representing fundamental geophysical and biophysical variables. These products demonstrate direct Traceability to original satellite measurements through rigorous Calibration and Validation processes. The processing methodology prioritizes the conversion of raw sensor data into quantifiable physical measurements, maintaining strict adherence to standardized processing protocols and Validation requirements.</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>- Soil moisture from microwave sensors
+- Forest canopy height from LiDAR data</t>
+        </is>
+      </c>
       <c r="G115" t="inlineStr">
         <is>
           <t>- KCEO</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>External person, institution or system that consumes provided services.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>- Includes Data Access or Science and Service Exploitation Platforms provided by a payload data ground segment.</t>
-        </is>
-      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>- EO Data Stewardship Glossary</t>
-        </is>
-      </c>
+      <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
@@ -5743,30 +5742,30 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Steward</t>
+          <t>Trait</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>- core
-description: Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
+          <t>- base
+description: Characteristic belonging to an entity and referenced by an identifier.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
+          <t>Characteristic belonging to an entity and referenced by an identifier.</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>- See also Custodian.</t>
+          <t>- Traits can be objective (inherent?) in which case they are also observable and called properties. Traits which are not observable (directly or indirectly) need to be assigned.</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- Based on ISO 19143:2010, 4.21, ISO/IEC 2382:2015, 2121440, significantly modified, Note 1 added</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
@@ -5789,23 +5788,30 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Temporal Consistency</t>
+          <t>Time of Year</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>- core
-description: Condition where the temporal statistical properties of the sample depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
+description: Time of the year at which the variable is observed or simulated by a model.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Condition where the temporal statistical properties of the Sample depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
+          <t>Time of the year at which the variable is observed or simulated by a model.</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>| Type      | Entry format example | Valid unit     |
+|-----------|----------------------|----------------|
+| timestamp | m/d                  | Not Applicable |
+| timerange | m/d - m/d            | Not Applicable |</t>
+        </is>
+      </c>
       <c r="G117" t="inlineStr">
         <is>
           <t>- KCEO</t>
@@ -5831,27 +5837,31 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Geospatial Data</t>
+          <t>In-Situ Observation</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>- core
-description: Data consisting of, derived from, or relating to information that is directly linked to specific geographical locations.</t>
+          <t>- controversial
+description: Observations performed in the same Place where a Phenomenon occurs, normally without isolating it from other systems or altering its pre-Observation state.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Data consisting of, derived from, or relating to information that is directly linked to specific geographical locations.</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
+          <t>Observations performed in the same Place where a Phenomenon occurs, normally without isolating it from other systems (its environment) or altering its pre-Observation state.</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>- The main Characteristic of such observations is that distance has no or only negligible (within Uncertainty) influence on the Value of the Property observed. In-Situ Observations therefore often require either direct physical contact or small distances between a Sensor and the observed Phenomenon.
+- Observations not fulfilling these conditions are considered Remote Sensing.</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>- https://www.merriam-webster.com/dictionary/geospatial
-- https://isotc211.geolexica.org/Concepts/202/, accessed 20221010</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
@@ -5874,36 +5884,56 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Characteristic</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>- core
-description: Maximum acceptable change in Uncertainty per decade.</t>
+          <t>- base
+- approved</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Maximum acceptable change in Uncertainty per decade.</t>
+          <t>Distinguishing Feature.</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>- GCOS uses bias or systematic errors instead of Uncertainty.</t>
+          <t>- A Characteristic can be inherent or assigned.
+- A Characteristic can be qualitative or quantitative.
+- There are various classes of Characteristics, such as the following:
+  - physical (e.g. mechanical, electrical, chemical, biological);
+  - sensory (e.g. relating to smell, touch, taste, sight, hearing);
+  - behavioural (e.g. courtesy, honesty, veracity);
+  - temporal (e.g. punctuality, reliability, availability);
+  - ergonomic (e.g. physiological characteristic or related to human safety);
+  - functional (e.g. maximum speed of an aircraft).</t>
         </is>
       </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>- Modified from GCOS 2022</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
+          <t>- ISO 9000:2005, 3.5.1</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Abstraction of a Property of an Object or of a set of objects.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>- Characteristics are used for describing Concepts.</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>- ISO 1087-1:2000, 3.2.4; ISO 19146:2010(E); https://www.iso.org/standard/20057.html</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
@@ -5920,26 +5950,30 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Property</t>
+          <t>Measurement</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>- base
-description: Observable Trait.</t>
+          <t>- core
+description: Observation of a Quantity.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Observable Trait.</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>Observation of a Quantity.</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>- The Process of collecting a measurement is called measuring.</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- GEOGlos (VIM ?, modified)</t>
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
@@ -5962,30 +5996,31 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Geographic Data</t>
+          <t>Preservation</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>- core
-description: Data with implicit or explicit reference to a Location relative to the Earth.</t>
+description: Processes and operations used to ensure data technical and intellectual survival through time.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Data with implicit or explicit reference to a Location relative to the Earth.</t>
+          <t>Processes and operations used to ensure data technical and intellectual survival through time.</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>- Geographic Information is also used as a term for information concerning phenomena implicitly or explicitly associated with a Location relative to the Earth.</t>
+          <t>- Grants data integrity, discoverability and accessibility, and facilitates its (re-)use in the long term.
+- Preservation is one of the tasks of data curation.</t>
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>- ISO 19109:2015, 4.13; ISO 19109:2005</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
@@ -6008,111 +6043,62 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Uncertainty</t>
+          <t>Provisional Product</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>- core
-description: Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
+description: Products in a research and development phase not yet published into a standardized collection.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
+          <t>Products in a research and development phase not yet published into a standardized collection.</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>- GUM</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Non-negative parameter, associated with data, which characterizes the dispersion of the values of a Trait that could reasonably be attributed to a Phenomenon by means of sensing or modelling.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>- In case of quantitative (continuous) data the uncertainty may be, for example, a standard deviation (or a given multiple of it), or the half-width of an interval having a stated level of confidence (see e.g. Standard and Expanded Uncertainty).
-- For qualitative (categorical?) data, uncertainty may be expressed by commission and omission ('confusion matrix') or overall errors.</t>
-        </is>
-      </c>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>- Modified from GUM, VIM4:3.1, FIDUCEO, Notes added</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>Measure of the spread of the distribution of possible values.</t>
-        </is>
-      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr">
-        <is>
-          <t>- [FIDUCEO Glossary](https://research.reading.ac.uk/fiduceo/glossary/), VIM?, modified</t>
-        </is>
-      </c>
-      <c r="P122" t="inlineStr">
-        <is>
-          <t>Parameter, associated with the result of measurement, that characterizes the dispersion of values that could reasonably be attributed to the measurand.</t>
-        </is>
-      </c>
-      <c r="Q122" t="inlineStr">
-        <is>
-          <t>- When the quality of accuracy or precision of measured values, such as coordinates, is to be characterized quantitatively, the quality parameter is an estimate of the uncertainty of the measurement results. Because accuracy is a qualitative concept, one should not use it quantitatively, that is associate numbers with it; numbers should be associated with measures of uncertainty instead.</t>
-        </is>
-      </c>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr"/>
       <c r="R122" t="inlineStr"/>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>- ISO 19116:2004(E)</t>
-        </is>
-      </c>
-      <c r="T122" t="inlineStr">
-        <is>
-          <t>Parameter characterizing the dispersion of the values being attributed to a measurand, based on the information used.</t>
-        </is>
-      </c>
+      <c r="S122" t="inlineStr"/>
+      <c r="T122" t="inlineStr"/>
       <c r="U122" t="inlineStr"/>
       <c r="V122" t="inlineStr"/>
-      <c r="W122" t="inlineStr">
-        <is>
-          <t>- VIM4: 3.1</t>
-        </is>
-      </c>
+      <c r="W122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>User Interface</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>- core
-description: Set of all the components of an interactive system that provide information and controls for the user to accomplish specific tasks with the interactive system.</t>
+description: ""</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>Set of all the components of an interactive system that provide information and controls for the User to accomplish specific tasks with the interactive system.</t>
-        </is>
-      </c>
+      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>- ISO 9241-110:2020, 3.10</t>
-        </is>
-      </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
@@ -6133,56 +6119,36 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Instrument Data</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>- core
-description: Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
+          <t>- high-impact
+description: Deliberate system of guidelines to guide decisions and achieve rational outcomes, implemented as a procedure or protocol and typically promulgated through official written documents.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>- These data consist of instrument science and engineering data, and possibly ancillary data. Instrument engineering data is produced by engineering sensor(s) of an instrument, used either for operating the instrument or for processing the science data generated by the instrument. Instrument science data is produced by the science sensor(s) of an instrument, usually constituting the basic reason for existence of an instrument.</t>
-        </is>
-      </c>
+          <t>Deliberate system of guidelines to guide decisions and achieve rational outcomes. Statement of intent implemented as a procedure or protocol. Typically promulgated through official written documents.</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Data created by an instrument including scientific measurements and any engineering or ancillary data which may be included in the data packets.</t>
-        </is>
-      </c>
+          <t>- KCEO</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>Data produced and transmitted by the science and engineering sensors of an instrument, and, in the spacecraft environment, any additional data packaged with the instrument's sensor data by virtue of services provided.</t>
-        </is>
-      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr">
-        <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
-        </is>
-      </c>
+      <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr"/>
       <c r="Q124" t="inlineStr"/>
       <c r="R124" t="inlineStr"/>
@@ -6195,38 +6161,30 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Measurand</t>
+          <t>Geographic Identifier</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>- core
-description: Particular Quantity subject to Measurement.</t>
+description: Spatial reference in the form of a label or code that identifies a Location.</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Particular Quantity subject to Measurement.</t>
+          <t>Spatial reference in the form of a label or code that identifies a Location.</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>| Step | Process description |
-| :----- | :--------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------- |
-| (Raw) | The complete and unaltered/unprocessed set of Data acquired by one or several sensors on a platform |
-| M/0 uncalibrated | Unaltered/unprocessed Level 0 (main) Sensor Data annotated with processed Ancillary Data and supplemented by Auxiliary Data (including radiometric and geometric Calibration coefficients and geo-referencing parameters) allowing further processing to higher Levels. |
-| M/1 Sensor-calibrated | Level M/0 Sensor Data which have been calibrated (ideally traceable to SI) and spatially aligned (co-located, eventually co-gridded) to represent at-Sensor measurements (Value and Uncertainty) in Sensor nominal spatiotemporal sampling, supplemented by appropriate ancillary data. |
-| M/2 target-calibrated | Level M/1 Data processed to represent geophysical Property values (and uncertainties) for a specified target (Object, Feature of interest, e.g. surface reflectance, apparent temperature) derived from M/1 Sensor Data, as much as possible maintaining the sensors nominal spatial and temporal sampling (Observation preserving). |
-| M/3 homogenised | Level M/1 or M/2 Data which have been generalised and integrated across one or several platforms and acquisitions to achieve an increased, more regular or in any other form enhanced spatial or temporal coverage in which states geophysical values agnostic of the originally acquiring Sensor and Observation condition and thus directly comparable. This homogenisation and fusion may include measurand re-Calibration to external standards and references including use of modelling, aggregation and interpolation. |
-| M/4 derived/inferred | Model output or results from analyses of Level M/3 (or lower level) Data i.e., attributes that might not be directly observable by the Sensor(s) but are derived from observations in combination with other external incl. non-observational Data using techniques like modelling or machine learning (AI). |
-From http://doi.org/10.2760/46796</t>
+          <t>- "Spain" is an example of a label (country name); "SW1-3AD" is an example of a code (postcode).</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>- VIM: 1993, 2.6</t>
+          <t>- ISO 19112:2019, 3.1.2</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
@@ -6249,26 +6207,37 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Policy Target</t>
+          <t>Earth Spheres</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>- high-impact
-description: Specific level or rate set for the Policy Objective.</t>
+          <t>- core
+description: Spheres dividing planet Earth into subsystems, which are collectives of (physical) matter sharing specific traits.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Specific level or rate set for the Policy Objective.</t>
+          <t>Spheres dividing planet Earth into subsystems, which are collectives of (physical) matter sharing specific traits.</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>- Atmosphere
+- Hydrosphere
+- Cryosphere
+- Biosphere
+- Lithosphere
+- Anthroposphere</t>
+        </is>
+      </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Hugget, R., et al., 2024, DOI: 10.1177/03091333241275465
+- Guth, P., et al., 2021, https://doi.org/10.3390/rs13183581
+- Martin, Y.E., et al., 2012</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
@@ -6291,35 +6260,26 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Spatial Extent</t>
+          <t>Deprecated Product</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>- core
-description: Zone or region of space described by a geographic identifier in the form of a label or code, or by a bounding box, representing the maximum spatial boundary within which the user is requesting data.</t>
+description: Products and collections that have been superseded by a newer version and are still available, but whose use is discouraged since they will be decommissioned in the future.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Zone or region of space described by a geographic identifier in the form of a label or code, or by a bounding box. Represents the maximum extent (the spatial boundary or limits) within which the User is requesting data.
-The attribute represents the maximum spatial extent of the AOI, and in case the AOI is made of many discontinuous zones then it represents the maximum extent of the union of all the zones.</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>- WIGOS metadata standard defines it as the typical spatial georeferenced volume covered by the observations.</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>- If a User is requesting information about degradation of African protected sites, then the AOIs are the protected sites, and the spatial extent is the African continent.</t>
-        </is>
-      </c>
+          <t>Products and collections that have been superseded by a newer version and are still available, but whose use is discouraged since they will be decommissioned in the future.</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>- Adapted from ISO 19170-1:2021</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
@@ -6342,26 +6302,26 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Provisional Product</t>
+          <t>Replicability</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>- core
-description: Products in a research and development phase not yet published into a standardized collection.</t>
+description: Property enabling other researchers to conduct an independent study with different data and similar but not identical methods, yet arriving at results that confirm the original study's hypothesis.</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Products in a research and development phase not yet published into a standardized collection.</t>
+          <t>Property enabling other researchers to conduct an independent study with different data and similar but not identical methods, yet arriving at results that confirm the original study's hypothesis.</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- Craglia, M., et al. (2018).</t>
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
@@ -6384,26 +6344,30 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Object</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>- base
-description: Entity with a well-defined boundary and identity that encapsulates state and behaviour.</t>
+description: Abstraction of real-world phenomena.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Entity with a well-defined boundary and identity that encapsulates state and behaviour.</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr"/>
+          <t>Abstraction of real-world phenomena.</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>- A feature may occur as a type or an instance.</t>
+        </is>
+      </c>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>- ISO/IEC 19501:2005</t>
+          <t>- ISO 19101-1:2014, 4.1.11, modified</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
@@ -6426,26 +6390,30 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Forecast Range</t>
+          <t>Final Product Version</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>- core
-description: The forecast period.</t>
+description: Product within an EO Collection that is not expected to be updated.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>The forecast period.</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr"/>
+          <t>Product within an EO Collection that is not expected to be updated.</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>- In its production, all of the prerequisite auxiliary data were used as input.</t>
+        </is>
+      </c>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
@@ -6468,26 +6436,35 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Policy Milestone</t>
+          <t>Spatial Extent</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>- high-impact
-description: Markers of significant progress in addressing specific issues, or crucial decision points where significant choices are made within a policy process.</t>
+          <t>- core
+description: Zone or region of space described by a geographic identifier in the form of a label or code, or by a bounding box, representing the maximum spatial boundary within which the user is requesting data.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Markers of significant progress in addressing specific issues, or crucial decision points where significant choices are made. Concrete examples include: policy planning and proposing, impact assessment, implementation, or implementation cycles (e.g., Water Framework Directive, Marine Strategy Framework Directive), achievement of Policy Objectives and Policy Targets, and evaluating and improving existing laws.</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
+          <t>Zone or region of space described by a geographic identifier in the form of a label or code, or by a bounding box. Represents the maximum extent (the spatial boundary or limits) within which the User is requesting data.
+The attribute represents the maximum spatial extent of the AOI, and in case the AOI is made of many discontinuous zones then it represents the maximum extent of the union of all the zones.</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>- WIGOS metadata standard defines it as the typical spatial georeferenced volume covered by the observations.</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>- If a User is requesting information about degradation of African protected sites, then the AOIs are the protected sites, and the spatial extent is the African continent.</t>
+        </is>
+      </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Adapted from ISO 19170-1:2021</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
@@ -6510,30 +6487,26 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Dwell Time</t>
+          <t>Policy Cycle</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>- core
-description: Time that an antenna beam spends on a target.</t>
+          <t>- high-impact
+description: Well-established concept typically taught as the rational model of policy decision-making, representing an idealised view of the policy process.</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Time that an antenna beam spends on a target.</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>- In the context of radar sensing.</t>
-        </is>
-      </c>
+          <t>Well-established concept, typically taught as the rational model of policy decision-making. Idealised view of the policy process.</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [ESA/CEOS?, modified](https://digital-strategy.ec.europa.eu/en/library/quality-public-administration-toolbox-practitioners)</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
@@ -6556,26 +6529,26 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Location Error</t>
+          <t>Data Licencing</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>- core
-description: Measure of the agreement between the represented Location of an Object and the true Location.</t>
+description: Legal instrument by which a copyright holder may grant rights over the protected work.</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Measure of the agreement between the represented Location of an Object and the true Location.</t>
+          <t>Legal instrument by which a copyright holder may grant rights over the protected work. Data and content is open if it is subject to an explicitly-applied licence that conforms to the Open Definition. A range of standard open licences are available, such as the Creative Commons CC-BY licence, which requires only attribution.</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- CEOS Wiki</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
@@ -6598,22 +6571,26 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Expanded Uncertainty</t>
+          <t>Representativeness</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
           <t>- core
-description: Standard Uncertainty multiplied by a coverage factor k, chosen to obtain a desired level of confidence.</t>
+description: Quality or characteristic of a measurement or observation to accurately represent a specific geographic location, time period, or environmental condition.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Standard Uncertainty multiplied by a coverage factor, k. The coverage factor is chosen to obtain a desired level of confidence. Most commonly a 95% confidence interval is chosen. For a Gaussian distribution, this is achieved with a coverage factor k = 2. (Note that strictly this provides a 95.45% confidence interval.)</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr"/>
+          <t>Quality or characteristic of a measurement or Observation to accurately represent a specific geographic location, time Period, or environmental condition.</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>- WIGOS metadata standard defines representativeness as the extent of the region around the Observation of which it is representative.</t>
+        </is>
+      </c>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
@@ -6640,20 +6617,28 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Environmental Process</t>
+          <t>Reproducibility</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>- core
-description: ""</t>
+description: Concerned with the validity of the results of a particular study, enabling readers to check whether results have been manipulated by reproducing exactly the same study using the same data and methods.</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Concerned with the validity of the results of a particular study, i.e., the possibility for readers to check whether results have been manipulated, by reproducing exactly the same study using the same data and methods.</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>- Ostermann and Granell (2015)</t>
+        </is>
+      </c>
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
@@ -6674,30 +6659,30 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Custodian</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>- controversial
-description: An, often numeric, theoretical (or otherwise abstract) representation of an Entity intended to generate Data describing one or more of its traits.</t>
+          <t>- core
+description: Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>An, often numeric, theoretical (or otherwise abstract) representation of an Entity intended to generate Data describing one or more of its traits (as a result of pre-set conditions).</t>
+          <t>Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>- The Process of generating Data using a model is called modelling.</t>
+          <t>- See also Steward.</t>
         </is>
       </c>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
@@ -6720,26 +6705,26 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Classification System</t>
+          <t>Geosphere</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: The masses of minerals that constitute planet Earth.</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Nomenclature used to classify Information into categorical thematic classes (e.g., EUNIS, MAES ecosystems, Corine Land Cover, LCCS).</t>
+          <t>The masses of minerals that constitute planet Earth.</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
@@ -6762,26 +6747,30 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Spectral Bandwidth</t>
+          <t>Cell</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>- core
-description: Range of the Spectral Band.</t>
+- approved</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Range of the Spectral Band.</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr"/>
+          <t>Spatial, spatio-temporal zone or temporal unit of geometry with dimensionality greater than 0, associated with a zone.</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>- Cells are the unit of geometry in a DGGS, and the geometry of the region of space-time occupied by a zone is a Cell.</t>
+        </is>
+      </c>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO 19170:2021</t>
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
@@ -6804,26 +6793,30 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>Geographic Coordinate Reference System</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Coordinate Reference System (CRS) that has a geodetic Reference frame and an ellipsoidal coordinate system.</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Group of products that have been processed using a consistent radiometric calibration, geometric registration base, data/metadata format, and version of processing algorithms.</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr"/>
+          <t>Coordinate Reference System (CRS) that has a geodetic Reference frame and an ellipsoidal coordinate system.</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>- Also known as geographic CRS.</t>
+        </is>
+      </c>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- ISO 19111:2019, 3.1.35</t>
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
@@ -6846,20 +6839,34 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Continuity</t>
+          <t>Vertical Levels</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>- core
-  - to be defined</t>
+description: Levels of a vertical discretization, e.g. pressure levels in an atmospheric model reanalysis or height levels in a forest biomass EO product.</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Levels of a vertical discretization. Examples may be pressure levels in an atmospheric model reanalysis or height levels in a forest biomass EO product.</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>| Entry format example                | Valid unit           |
+|------------------------------------|----------------------|
+| 1, 5, 10 meter; 1000, 850, 500 hPa | meter, hPa, unitless |</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
@@ -6880,26 +6887,26 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Policy File</t>
+          <t>Anthroposphere</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>- high-impact
-description: Policy documents that represent the official written reference for a given Policy.</t>
+          <t>- core
+- approved</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Policy documents that represent the official written reference for a given Policy.</t>
+          <t>One of the Earth spheres consisting predominantly of matter processed by humans, such as construction wood, bricks, concrete, asphalt, glass, or plastics.</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
@@ -6922,22 +6929,26 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Dwell Time</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>- high-impact
-description: Deliberate system of guidelines to guide decisions and achieve rational outcomes, implemented as a procedure or protocol and typically promulgated through official written documents.</t>
+          <t>- core
+description: Time that an antenna beam spends on a target.</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Deliberate system of guidelines to guide decisions and achieve rational outcomes. Statement of intent implemented as a procedure or protocol. Typically promulgated through official written documents.</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr"/>
+          <t>Time that an antenna beam spends on a target.</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>- In the context of radar sensing.</t>
+        </is>
+      </c>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
@@ -6964,30 +6975,33 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Geographic Identifier</t>
+          <t>Duration</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
           <t>- core
-description: Spatial reference in the form of a label or code that identifies a Location.</t>
+description: Non-negative interval Quantity of time equal to the difference between the final and initial instants of a time interval.</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Spatial reference in the form of a label or code that identifies a Location.</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>- "Spain" is an example of a label (country name); "SW1-3AD" is an example of a code (postcode).</t>
-        </is>
-      </c>
+          <t>Non-negative interval Quantity of time equal to the difference between the final and initial instants of a time interval.</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>- Duration is one of the base quantities in the International System of Quantities (ISQ) on which the International System of Units (SI) is based. The term "time" instead of "duration" is often used in this context and also for an infinitesimal duration.
+- For the term "duration", expressions such as "time" or "time interval" are often used, but the term "time" is not recommended in this sense and the term "time interval" is deprecated in this sense to avoid confusion with the concept of "time interval".
+- The exact duration of a time scale unit depends on the time scale used. For example, the durations of a year, month, week, day, hour or minute may depend on when they occur (in a Gregorian calendar, a calendar month can have a duration of 28, 29, 30, or 31 days; in a 24-hour clock, a clock minute can have a duration of 59, 60, or 61 seconds, etc.). Therefore, the exact duration can only be evaluated if the exact duration of each is known.
+- This definition is closely related to NOTE 1 of the terminological entry "duration" in IEC 60050-113:2011, 113-01-13.</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
-          <t>- ISO 19112:2019, 3.1.2</t>
+          <t>- ISO 8601-1:2019, 3.1.1.8</t>
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
@@ -7010,31 +7024,26 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Earth Observation</t>
+          <t>Lead Time</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>- high-impact
-description: Science domain dealing with technologies and methods of collecting and analyzing observations about the different Earth spheres.</t>
+          <t>- core
+description: Minimum time of interval between an Observation being tasked and being performed.</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Science domain dealing with technologies and methods of collecting and analyzing observations about the different Earth spheres.</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>- Earth Observation (EO) can be categorised by location of the sensor into space-borne, air-borne, sea-borne, ground-based, underwater and underground EO.
-- Earth Observation (EO) includes Remote Sensing, such as satellite imagery, as well as in-situ observations, e.g., with ground-based devices.</t>
-        </is>
-      </c>
+          <t>Minimum time of interval between an Observation being tasked and being performed.</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
-          <t>- Modified GEO definition [GEO (earthobservations.org)](https://earthobservations.org/resources#key)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
@@ -7057,26 +7066,30 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Data Format</t>
+          <t>EO Space Data</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>- core
-description: Structured Data that is machine readable and can be automatically read and processed by a computer, such as HDF, NetCDF, CSV, JSON, XML, etc.</t>
+description: Earth Observation data generated by spaceborne missions or instruments owned by public or private organizations.</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Structured Data that is machine readable and can be automatically read and processed by a computer, such as HDF, NetCDF, CSV, JSON, XML, etc.</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr"/>
+          <t>Earth Observation data generated by spaceborne missions or instruments owned by public or private organizations.</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>- See also Instrument data.</t>
+        </is>
+      </c>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
-          <t>- CEOS Wiki</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
@@ -7099,26 +7112,30 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Geolocation Information</t>
+          <t>Spatial Completeness</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>- core
-description: Information used to determine geographic Location.</t>
+description: Presence or absence of gaps, which are missing values in an otherwise continuous spatial data series.</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Information used to determine geographic Location.</t>
+          <t>Presence or absence of gaps, which are missing values in an otherwise continuous spatial data series.</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>- Surface soil moisture retrieved from microwave satellite sensors may present gaps in mountainous terrains.</t>
+        </is>
+      </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>- ISO 19130-1:2018, 3.34</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
@@ -7141,26 +7158,31 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Cryosphere</t>
+          <t>Derivative Product</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Product additionally processed from baseline or unenhanced mission data.</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Masses of frozen water, such as sea ice, ice shields, glaciers, and snow.</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr"/>
+          <t>Product additionally processed from baseline or unenhanced mission data.</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>- Generally either a compilation of time-series data (e.g., all time, annual, monthly or seasonal summary data, &gt; Level 3) or thematic versions of each individual data tile of baseline data.
+- Derived products are citable via a Digital Object Identifier (DOI).</t>
+        </is>
+      </c>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
@@ -7183,18 +7205,26 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Geopositioning</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>- core
-description: ""</t>
+description: Determination of the geographic Position of a point (0D) or linear (1D) Feature.</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
-      <c r="D148" t="inlineStr"/>
-      <c r="E148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Determination of the geographic Position of a point (0D) or linear (1D) Feature.</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>- Modified from: ISO 19130-1:2018, 3.36</t>
+        </is>
+      </c>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr"/>
@@ -7217,36 +7247,26 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Spectral Band</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>- base
-description: Particular Place referenced by an identifier.</t>
+          <t>- core
+description: Part of the electromagnetic spectrum of specific wavelengths, in remote sensing usually described by central wavelength and bandwidth.</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Particular Place referenced by an identifier.</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>- While a (geo)location identifies a geographic Place, it may also be associated with objects other than the Earth.
-- While Location in principle covers 0- to 3-dimensional spatial geometries, it should not be used for 0- and 1-dimensional geometries (positions and paths).</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>- Madrid
-- California</t>
-        </is>
-      </c>
+          <t>Part of the electromagnetic spectrum of specific wavelengths. In Remote Sensing, usually described by central wavelength and bandwidth.</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr">
         <is>
-          <t>- [ISO 19112:2019](https://www.iso.org/standard/70742.html), (E), 3.1.3, modified, note 2 added</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
@@ -7269,34 +7289,20 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Consistency</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>- core
-description: Device or instrument suited (through physical/chemical interaction) to measure one or more properties of a Phenomenon and thus collect factual/objective data.</t>
+  - to be defined</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>Device or instrument suited (through physical/chemical interaction) to measure one or more properties of a Phenomenon and thus collect factual/objective data.</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>- Sensing is therefore a synonym for Observation (the Process).
-- As by their definition, sensors perform sampling.
-- Sensors used to obtain measurements must be calibrated and provide uncertainties.</t>
-        </is>
-      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
+      <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr"/>
@@ -7317,36 +7323,30 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Temporal Resolution</t>
+          <t>Geographic Data</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
           <t>- core
-description: Observation or model output representing regular intervals, specifying the length of the interval that determines the smallest event or process that can be resolved.</t>
+description: Data with implicit or explicit reference to a Location relative to the Earth.</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Observation or model output representing regular intervals, specifying the length of the interval that determines the smallest event or Process that can be resolved (e.g., the Period between observations, the time steps in a model).</t>
+          <t>Data with implicit or explicit reference to a Location relative to the Earth.</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>- WIGOS 2019 distinguishes between sampling time Period, as the Period over which a Measurement is taken, and temporal sampling interval as the time Period between the beginning of consecutive sampling periods. Temporal Resolution in this Glossary is equivalent to sampling time Period as used by WIGOS.</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>| Entry format example | Valid unit                     |
-|----------------------|-------------------------------|
-| 1 s, 2 h, 1 m        | second, hour, day, month, year |</t>
-        </is>
-      </c>
+          <t>- Geographic Information is also used as a term for information concerning phenomena implicitly or explicitly associated with a Location relative to the Earth.</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO 19109:2015, 4.13; ISO 19109:2005</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
@@ -7369,26 +7369,26 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Policy Cycle</t>
+          <t>Business Continuity</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>- high-impact
-description: Well-established concept typically taught as the rational model of policy decision-making, representing an idealised view of the policy process.</t>
+          <t>- core
+- approved</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Well-established concept, typically taught as the rational model of policy decision-making. Idealised view of the policy process.</t>
+          <t>An organisation's readiness to continue functioning during times of disruption.</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr">
         <is>
-          <t>- [ESA/CEOS?, modified](https://digital-strategy.ec.europa.eu/en/library/quality-public-administration-toolbox-practitioners)</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H152" t="inlineStr"/>

--- a/exports/xlsx/terms.xlsx
+++ b/exports/xlsx/terms.xlsx
@@ -536,40 +536,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Geolocating</t>
+          <t>Geographic Grid</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>- core
-description: Geopositioning of an Object using a Physical Sensor Model or a True Replacement Model.</t>
+description: Regular grid based on a Geographic Coordinate Reference System (CRS).</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Geopositioning of an Object using a Physical Sensor Model or a True Replacement Model.</t>
+          <t>Regular grid based on a Geographic Coordinate Reference System (CRS).</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>- ISO 19115-2:2009, 4.11</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Determination of the geographic location of a feature of two or more dimensions.</t>
-        </is>
-      </c>
+          <t>- KCEO</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>- ISO 19130-1:2018, 3.36 ('geopositioning'), modified</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -586,22 +578,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Spectral Bandwidth</t>
+          <t>Representativeness</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>- core
-description: Range of the Spectral Band.</t>
+description: Quality or characteristic of a measurement or observation to accurately represent a specific geographic location, time period, or environmental condition.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Range of the Spectral Band.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>Quality or characteristic of a measurement or Observation to accurately represent a specific geographic location, time Period, or environmental condition.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>- WIGOS metadata standard defines representativeness as the extent of the region around the Observation of which it is representative.</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
@@ -628,24 +624,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Instrument Data</t>
+          <t>EO Space Data</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>- core
-description: Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
+description: Earth Observation data generated by spaceborne missions or instruments owned by public or private organizations.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
+          <t>Earth Observation data generated by spaceborne missions or instruments owned by public or private organizations.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>- These data consist of instrument science and engineering data, and possibly ancillary data. Instrument engineering data is produced by engineering sensor(s) of an instrument, used either for operating the instrument or for processing the science data generated by the instrument. Instrument science data is produced by the science sensor(s) of an instrument, usually constituting the basic reason for existence of an instrument.</t>
+          <t>- See also Instrument data.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -654,30 +650,14 @@
           <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Data created by an instrument including scientific measurements and any engineering or ancillary data which may be included in the data packets.</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Data produced and transmitted by the science and engineering sensors of an instrument, and, in the spacecraft environment, any additional data packaged with the instrument's sensor data by virtue of services provided.</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
-        </is>
-      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
@@ -690,59 +670,40 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Auxiliary Data</t>
+          <t>Granule</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: The smallest aggregation of data which is independently managed (i.e. described, inventoried, retrievable).</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Data that enhance the processing and utilisation of main Sensor Data. Auxiliary Data are usually not captured by the same Data collection Process or on the same platform as the main Sensor Data. Examples include meteorological Data received from ECMWF/Met Offices or DEMs. Auxiliary Data help in Data processing, but are also Data sets in their own right.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>The smallest aggregation of data which is independently managed (i.e. described, inventoried, retrievable). Granules may be managed as logical granules and/or physical granules.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>- See also product.</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>- ESA/CEOS?, modified
-- ENMAP Glossary of Terms, https://www.enmap.org/Data/doc/EnMAP_Terms.pdf, 20210624
-- EO Data Stewardship Glossary</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Data required to perform processing of Sensor Data which is not obtained from the Sensor itself. Includes: (a) Data provided by the spacecraft (e.g. orbit Position and velocity, attitude, instrument house-keeping Data, on-board time); (b) Data not available from on-board sources.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>For EnMAP, this includes (a) orbit files, attitude files, Calibration Data, instrument house-keeping Data; (b) atmospheric parameters, reference images.</t>
-        </is>
-      </c>
+          <t>- [NASA EarthData](https://www.earthdata.nasa.gov/learn/glossary)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>- ENMAP Glossary of Terms, https://www.enmap.org/Data/doc/EnMAP_Terms.pdf, 20210624
-- EO Data Stewardship Glossary</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Data required for instrument processing that does not originate in the instrument itself or from the satellite. Some Auxiliary Data will be generated in the ground segment, whilst other Data will be provided from external sources.</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>- CEOS-ARD PFS template 20220302</t>
-        </is>
-      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
@@ -755,26 +716,37 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dispose</t>
+          <t>Temporal Revisit</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>- core
-description: Action of permanently and irrecoverably removing all copies of data held by an organization.</t>
+description: Interval between successive observations.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Action of permanently and irrecoverably removing all copies of data held by an organization.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>Interval between successive observations.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>- In Remote Sensing it is also called repeat cycle.
+- More generally it is known as temporal sampling interval.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>| Entry format example | Valid unit                     |
+|----------------------|-------------------------------|
+| 1 s, 2 h             | second, hour, day, month, year |</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -797,31 +769,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Dispose</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>- base
-- controversial
-description: Place referenced by a single set of coordinates within a coordinate reference system.</t>
+          <t>- core
+description: Action of permanently and irrecoverably removing all copies of data held by an organization.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Place referenced by a single set of coordinates within a coordinate reference system.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>- Opposite to (previous) ISO definition, Position shall be used only for 0-dimensional primitives (points).</t>
-        </is>
-      </c>
+          <t>Action of permanently and irrecoverably removing all copies of data held by an organization.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>- ISO 19133:2005, modified to cover only points, also called 'direct position'</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -844,34 +811,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Remote Sensing</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>- core
-description: Electronic data package distributable to users; content is derived from instrument data via processing involving ancillary and auxiliary data.</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>- controversial
+description: Type of Observation performed at a significant distance from a Phenomenon.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Remote Observation</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Electronic data package distributable to users; content is derived from instrument data via processing involving ancillary and auxiliary data.</t>
+          <t>Type of Observation performed at a significant distance from a Phenomenon.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>- Products may be accompanied by metadata and browse images.
-- A Product may be part of a collection — a distinction useful for archiving and cataloguing purposes.
-- The term Product may be used to denote a product type, such as e.g. ENVISAT_ASAR_L1B_PRI data products.
-- End users may distinguish between (input, "raw") data and products, i.e., the derived geophysical parameters.
-- See also granule.</t>
+          <t>- 'Significant' in this context means that the distance has, or may have, a non-negligible impact on the Value of the Property observed.
+- The effect of the distance on the acquired data is the main distinction criterion between 'remote' and 'in-situ' observations.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -894,30 +862,26 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Near Real Time Data</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>- base
-description: Series of activities that interact to produce a result.</t>
+          <t>- high-impact
+description: Data available for use with a specified (small and application dependent) latency, typically 3 hours for meteorological applications.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Series of activities that interact to produce a result.</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>- A Process may occur once-only or be recurrent or periodic.</t>
-        </is>
-      </c>
+          <t>Data available for use with a specified (small and application dependent) latency, typically 3 hours for meteorological applications.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>- [Wikipedia](https://en.wikipedia.org/wiki/Process)</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -940,34 +904,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>- core
-description: Phenomenon whose values for specific properties are known and understood with an Uncertainty significantly lower than that of the Observation with which it is compared.</t>
+          <t>- base
+description: Value and possibly Uncertainty of a Trait of a specific Entity.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Phenomenon whose values for specific properties are known and understood with an Uncertainty significantly lower (quantify?) than that of the Observation with which it is compared.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+          <t>Value and possibly Uncertainty of a Trait of a specific Entity.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>- Data simply describe entities using certain traits and are not targeted at a particular use or audience.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Data can be categorised into:
+- factual (i.e. obtained by Observation) or fictional (obtained e.g. through modelling, estimating or assigning)
+- quantitative (continuous) or qualitative (categorical)
+- analogue or digital
+(list not exhaustive!)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sort of data acquired with an Uncertainty significantly lower (quantify?) than that of the data it is being compared with.</t>
+          <t>Scientific or technical measurements, values calculated therefrom, observations, or facts that can be represented by numbers, tables, graphs, models, text, or symbols which are used as a basis for reasoning and further calculation.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>- VIM?, modified</t>
+          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -986,29 +966,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Earth Observation Based Output</t>
+          <t>Geographic Coordinate Reference System</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>- core
-description: Higher-level processing and integration output (indicative level 4 and beyond) that goes beyond basic data processing, often designed for policy or decision-making needs.</t>
+description: Coordinate Reference System (CRS) that has a geodetic Reference frame and an ellipsoidal coordinate system.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Higher-level processing and integration output (indicative level 4 and beyond) that goes beyond basic data processing. These outputs are often designed specifically for policy or decision-making needs, and can be categorized into sub-categories:
-- Outputs from models/model integration: use of EO products as inputs in numerical models or combining them with other data sources in modelling frameworks.
-- Indicator-based outputs: EO products transformed through specialized algorithms (including statistical methods, machine learning, and pattern recognition) to create meaningful metrics based on spatio-temporal analysis.
-- Outputs from reanalysis: merging of EO products with other observations and models, creating consistent long-term records of past atmospheric, oceanic, and land surface conditions, and filling gaps through data assimilation techniques.</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>Coordinate Reference System (CRS) that has a geodetic Reference frame and an ellipsoidal coordinate system.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>- Also known as geographic CRS.</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO 19111:2019, 3.1.35</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -1031,44 +1012,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Entity</t>
+          <t>Long Term Preservation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>- base
-description: Something that has separate and distinct existence and objective or conceptual reality.</t>
+          <t>- core
+description: The act of maintaining information in a correct and independently understandable form over the long term.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Something that has separate and distinct existence and objective or conceptual reality.</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+          <t>The act of maintaining information in a correct and independently understandable form over the long term.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>- Long term refers to a period of time long enough to be concerned with the impact which changing technologies, including support for media and data formats, and changing user communities will have on the information being held in a repository.
+- See also preservation.</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>- ISO 19119:2016, 4.1.6</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Government or business organization that is formed to conduct business or represent the government of the day.</t>
-        </is>
-      </c>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>CEOS Entities include Working Groups, Virtual Constellations, etc.</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1085,26 +1059,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>Preservation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Processes and operations used to ensure data technical and intellectual survival through time.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Group of products that have been processed using a consistent radiometric calibration, geometric registration base, data/metadata format, and version of processing algorithms.</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>Processes and operations used to ensure data technical and intellectual survival through time.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>- Grants data integrity, discoverability and accessibility, and facilitates its (re-)use in the long term.
+- Preservation is one of the tasks of data curation.</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1127,26 +1106,26 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Geographic Grid</t>
+          <t>Version Control</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>- core
-description: Regular grid based on a Geographic Coordinate Reference System (CRS).</t>
+description: Method of working with collections, similar to version control systems used in traditional software development but optimized to allow better processing of data and collaboration in data analytics and research contexts.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Regular grid based on a Geographic Coordinate Reference System (CRS).</t>
+          <t>Method of working with collections, similar to the version control systems used in traditional software development but optimized to allow better processing of data and collaboration in the context of data analytics, research, and any other form of data analysis.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [Wikipedia](https://en.wikipedia.org/wiki/Data_version_control)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -1169,30 +1148,26 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Archive</t>
+          <t>Thematic Resolution</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Level of categorical detail of information expressed by the number of classes.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>System that stores data products, guaranteeing their preservation for future use.</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>- This function includes all operations to identify, store and retrieve the data and ensure their integrity.</t>
-        </is>
-      </c>
+          <t>Level of categorical detail of information expressed by the number of classes.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- CGLS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1215,30 +1190,26 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Steward</t>
+          <t>Copernicus Service Provider</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>- core
-description: Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
+- approved</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>- See also Custodian.</t>
-        </is>
-      </c>
+          <t>Institutional body, organisation or programme that provides reliable, trusted (authoritative?) EO Information and that has the financial resources to sustain the provision. It utilises satellite Data, ground-based measurements, and other sources to generate accurate and timely Data products related to various aspects of the Earth's environment, such as land, Atmosphere, oceans, and climate.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -1261,32 +1232,26 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sample</t>
+          <t>Replicability</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>- controversial
-description: Subset of one or more entities.</t>
+          <t>- core
+description: Property enabling other researchers to conduct an independent study with different data and similar but not identical methods, yet arriving at results that confirm the original study's hypothesis.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Subset of one or more entities.</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>- A Sample may be spatial, temporal, spectral, or in any other dimension or Trait.
-- Each Sample is contiguous, i.e. it does not consist of more than one discontinuous geometry in any dimension.
-- The Process of obtaining a Sample is called sampling.</t>
-        </is>
-      </c>
+          <t>Property enabling other researchers to conduct an independent study with different data and similar but not identical methods, yet arriving at results that confirm the original study's hypothesis.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Craglia, M., et al. (2018).</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -1309,35 +1274,30 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Temporal Extent</t>
+          <t>Coverage Interval</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>- core
-description: Period during which data was collected, observations were made, or for which the model was run.</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+- approved</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Coverage extent</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Period during which data was collected, observations were made, or for which the model was run.</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>- In W3C this is the definition of temporal coverage.
-- Time Period covered by a series of observations inclusive of the specified date/time indications (measurement history). Defined based on the beginning and end dates of observations.</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>- WIGOS Metadata</t>
-        </is>
-      </c>
+          <t>Range or specific subset of values associated with a coverage dataset.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>- Adapted from W3C</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -1407,28 +1367,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cryosphere</t>
+          <t>Equivalence</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+  - to be defined</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Masses of frozen water, such as sea ice, ice shields, glaciers, and snow.</t>
-        </is>
-      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>- Guth et al. 2021</t>
-        </is>
-      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
@@ -1449,27 +1401,29 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Spatial Reporting Unit</t>
+          <t>Band Central Wavelength</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>- core
-description: Smallest spatial object of interest that may be used for reporting and for which the information should be aggregated.</t>
+- approved</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Smallest spatial object of interest that may be used for reporting and for which the information should be aggregated.</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>- WIGOS 2019 uses 'spatial reporting interval', probably assuming observations are reported on a grid with regular spacing/intervals.</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>Single wavelength Value within the sensitivity interval of a spectroradiometric Sensor which represents the respective band. It could be either the mean, the median, the maximum sensitivity, or any other reasonable Value chosen to be representative.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>| Entry format example | Valid unit                                        |
+|----------------------|---------------------------------------------------|
+| 0.545 μm             | micrometre (μm), millimetre (mm), centimetre (cm) |</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>- KCEO</t>
@@ -1495,30 +1449,30 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Decommissioned Product</t>
+          <t>Update Frequency</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>- core
-description: Products and collections that have been superseded by new versions and are no longer available.</t>
+description: Frequency at which the product is available to users.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Products and collections that have been superseded by new versions and are no longer available.</t>
+          <t>Frequency at which the product is available to users.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>- Decommissioned products are no longer supported, i.e. corrections will not be made, new data will not be added, and support is not available.</t>
+          <t>- Also known in product catalogues as dissemination frequency.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -1541,42 +1495,44 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Entity</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>- base
-description: Particular Place referenced by an identifier.</t>
+description: Something that has separate and distinct existence and objective or conceptual reality.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Particular Place referenced by an identifier.</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>- While a (geo)location identifies a geographic Place, it may also be associated with objects other than the Earth.
-- While Location in principle covers 0- to 3-dimensional spatial geometries, it should not be used for 0- and 1-dimensional geometries (positions and paths).</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>- Madrid
-- California</t>
-        </is>
-      </c>
+          <t>Something that has separate and distinct existence and objective or conceptual reality.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>- [ISO 19112:2019](https://www.iso.org/standard/70742.html), (E), 3.1.3, modified, note 2 added</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>- ISO 19119:2016, 4.1.6</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Government or business organization that is formed to conduct business or represent the government of the day.</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>CEOS Entities include Working Groups, Virtual Constellations, etc.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -1593,30 +1549,26 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Period</t>
+          <t>Place</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>- base
-description: Particular era or span of time.</t>
+description: Part of any space referenced by an identifier.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Particular era or span of time.</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>- Periods are intervals named with a Period Identifier.</t>
-        </is>
-      </c>
+          <t>Part of any space referenced by an identifier.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>- ISO 19170:2021</t>
+          <t>- ISO 19155:2012, 4.8</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -1639,27 +1591,33 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Geospatial Data</t>
+          <t>Duration</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>- core
-description: Data consisting of, derived from, or relating to information that is directly linked to specific geographical locations.</t>
+description: Non-negative interval Quantity of time equal to the difference between the final and initial instants of a time interval.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Data consisting of, derived from, or relating to information that is directly linked to specific geographical locations.</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
+          <t>Non-negative interval Quantity of time equal to the difference between the final and initial instants of a time interval.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>- Duration is one of the base quantities in the International System of Quantities (ISQ) on which the International System of Units (SI) is based. The term "time" instead of "duration" is often used in this context and also for an infinitesimal duration.
+- For the term "duration", expressions such as "time" or "time interval" are often used, but the term "time" is not recommended in this sense and the term "time interval" is deprecated in this sense to avoid confusion with the concept of "time interval".
+- The exact duration of a time scale unit depends on the time scale used. For example, the durations of a year, month, week, day, hour or minute may depend on when they occur (in a Gregorian calendar, a calendar month can have a duration of 28, 29, 30, or 31 days; in a 24-hour clock, a clock minute can have a duration of 59, 60, or 61 seconds, etc.). Therefore, the exact duration can only be evaluated if the exact duration of each is known.
+- This definition is closely related to NOTE 1 of the terminological entry "duration" in IEC 60050-113:2011, 113-01-13.</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>- https://www.merriam-webster.com/dictionary/geospatial
-- https://isotc211.geolexica.org/Concepts/202/, accessed 20221010</t>
+          <t>- ISO 8601-1:2019, 3.1.1.8</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -1682,23 +1640,34 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Confidence Interval</t>
+          <t>Time of Day</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>- controversial
-- approved</t>
+          <t>- core
+description: Time of the day at which the variable or parameter is observed or simulated by a model.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Probability that the Quantity lies in the interval, conditioned on the measuring or modelling assumptions.</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+          <t>Time of the day at which the variable or parameter is observed or simulated by a model.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>- In Remote Sensing it is also known as time of overpass.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>| Type      | Entry format example | Valid unit |
+|-----------|----------------------|------------|
+| timestamp | 18:00 h (0–24)       | Hours      |
+| timerange | 18:00 – 20:00 h      | Hours      |</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>- KCEO</t>
@@ -1724,30 +1693,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Granule</t>
+          <t>Vertical Levels</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>- core
-description: The smallest aggregation of data which is independently managed (i.e. described, inventoried, retrievable).</t>
+description: Levels of a vertical discretization, e.g. pressure levels in an atmospheric model reanalysis or height levels in a forest biomass EO product.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>The smallest aggregation of data which is independently managed (i.e. described, inventoried, retrievable). Granules may be managed as logical granules and/or physical granules.</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>- See also product.</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
+          <t>Levels of a vertical discretization. Examples may be pressure levels in an atmospheric model reanalysis or height levels in a forest biomass EO product.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>| Entry format example                | Valid unit           |
+|------------------------------------|----------------------|
+| 1, 5, 10 meter; 1000, 850, 500 hPa | meter, hPa, unitless |</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>- [NASA EarthData](https://www.earthdata.nasa.gov/learn/glossary)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -1770,30 +1741,34 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>- controversial
-description: An, often numeric, theoretical (or otherwise abstract) representation of an Entity intended to generate Data describing one or more of its traits.</t>
+          <t>- core
+description: Electronic data package distributable to users; content is derived from instrument data via processing involving ancillary and auxiliary data.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>An, often numeric, theoretical (or otherwise abstract) representation of an Entity intended to generate Data describing one or more of its traits (as a result of pre-set conditions).</t>
+          <t>Electronic data package distributable to users; content is derived from instrument data via processing involving ancillary and auxiliary data.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>- The Process of generating Data using a model is called modelling.</t>
+          <t>- Products may be accompanied by metadata and browse images.
+- A Product may be part of a collection — a distinction useful for archiving and cataloguing purposes.
+- The term Product may be used to denote a product type, such as e.g. ENVISAT_ASAR_L1B_PRI data products.
+- End users may distinguish between (input, "raw") data and products, i.e., the derived geophysical parameters.
+- See also granule.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -1816,44 +1791,36 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Georectifying</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>- core
-description: Correcting for positional displacement with respect to the surface of the Earth.</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Orthorectifying</t>
-        </is>
-      </c>
+          <t>- base
+description: The result of organisation, interpretation, categorisation, classification, or some other form of processing of Data attaching to it a certain meaning that can be understood by the addressee.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Correcting for positional displacement with respect to the surface of the Earth.</t>
+          <t>The result of organisation, interpretation, categorisation, classification, or some other form of processing of Data attaching to it a certain meaning that can be understood by the addressee.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>- Source: ISO 19115-2:2019, 3.11; ISO 19115-2:2009(E); https://www.iso.org/standard/67039.html, modified</t>
+          <t>- Information depends on Data and is targeted.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>The correction of sample locations to achieve some sort of geometric regularity, e.g., a regular 2D geographic grid.</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
@@ -1870,26 +1837,26 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Policy Making</t>
+          <t>Lithosphere</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>- high-impact
-description: Process by which governments translate their political vision into programmes and actions to deliver outcomes — desired change in the real world.</t>
+          <t>- core
+description: The solid, inanimate outer layer of the Geosphere. For the purposes of Earth Observation, includes soils ('pedosphere').</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Process by which governments translate their political vision into programmes and actions to deliver outcomes — desired change in the real world.</t>
+          <t>The solid, inanimate outer layer of the Geosphere. For the purposes of Earth Observation, the Lithosphere is considered to include soils ('pedosphere').</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>- [ESA/CEOS?, modified](https://digital-strategy.ec.europa.eu/en/library/quality-public-administration-toolbox-practitioners)</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -1912,111 +1879,75 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Uncertainty</t>
+          <t>Ancillary Data</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>- core
-description: Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
+- approved</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
+          <t>Data acquired on the same platform but not obtained from the main Sensor itself (usually provided as part of Level 0 Data), with the primary purpose of serving the processing of main instrument Data (e.g. Position and velocity of platform).</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>This can be divided into data referred to as spacecraft 'engineering', 'core housekeeping' or 'subsystem' data obtained from other parts of the platform, and includes parameters such as orbit position and velocity, attitude and its range of change, time, temperatures, pressures, jet firings, water dumps, internally produced magnetic fields, and other environmental measurements. Ancillary refers to data that exist purely to serve the data processing.</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>- GUM</t>
+          <t>- ESA/CEOS?, modified
+- EO Data Stewardship Glossary</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Non-negative parameter, associated with data, which characterizes the dispersion of the values of a Trait that could reasonably be attributed to a Phenomenon by means of sensing or modelling.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>- In case of quantitative (continuous) data the uncertainty may be, for example, a standard deviation (or a given multiple of it), or the half-width of an interval having a stated level of confidence (see e.g. Standard and Expanded Uncertainty).
-- For qualitative (categorical?) data, uncertainty may be expressed by commission and omission ('confusion matrix') or overall errors.</t>
-        </is>
-      </c>
+          <t>Data other than instrument measurements, originating in the instrument itself or from the satellite, required to perform processing of the Data. Includes orbit Data, attitude Data, time Information, and spacecraft engineering Data, Calibration Data, Data quality Information, and Data from other instruments or earth system models.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>- Modified from GUM, VIM4:3.1, FIDUCEO, Notes added</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Measure of the spread of the distribution of possible values.</t>
-        </is>
-      </c>
+          <t>- CEOS-ARD PFS template 20220302</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>- [FIDUCEO Glossary](https://research.reading.ac.uk/fiduceo/glossary/), VIM?, modified</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Parameter, associated with the result of measurement, that characterizes the dispersion of values that could reasonably be attributed to the measurand.</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>- When the quality of accuracy or precision of measured values, such as coordinates, is to be characterized quantitatively, the quality parameter is an estimate of the uncertainty of the measurement results. Because accuracy is a qualitative concept, one should not use it quantitatively, that is associate numbers with it; numbers should be associated with measures of uncertainty instead.</t>
-        </is>
-      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>- ISO 19116:2004(E)</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Parameter characterizing the dispersion of the values being attributed to a measurand, based on the information used.</t>
-        </is>
-      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>- VIM4: 3.1</t>
-        </is>
-      </c>
+      <c r="W31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Climate Projection</t>
+          <t>Consistency</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+  - to be defined</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Simulated response of the climate system to a scenario of future emission or concentration of greenhouse gases (GHGs) and aerosols, generally derived using climate models. Climate Projections are distinguished from climate predictions by their dependence on the emission/concentration/radiative forcing scenario used, which is in turn based on assumptions concerning, for example, future socioeconomic and technological developments that may or may not be realised.</t>
-        </is>
-      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>- IPCC</t>
-        </is>
-      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
@@ -2037,19 +1968,19 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Format</t>
+          <t>Quality Indicator</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>- core
-description: Structured Data that is machine readable and can be automatically read and processed by a computer, such as HDF, NetCDF, CSV, JSON, XML, etc.</t>
+description: Indicator providing sufficient information to allow all users to readily evaluate the fitness for purpose of the data or derived product.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Structured Data that is machine readable and can be automatically read and processed by a computer, such as HDF, NetCDF, CSV, JSON, XML, etc.</t>
+          <t>Indicator providing sufficient information to allow all users to readily evaluate the fitness for purpose of the data or derived product. May be a number, set of numbers, graph, Uncertainty budget, or a simple flag.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -2079,26 +2010,30 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Classification System Levels</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>- core
-- approved</t>
+          <t>- base
+description: Series of activities that interact to produce a result.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Levels in a hierarchical Classification System.</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
+          <t>Series of activities that interact to produce a result.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>- A Process may occur once-only or be recurrent or periodic.</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [Wikipedia](https://en.wikipedia.org/wiki/Process)</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -2121,30 +2056,26 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Geocoding</t>
+          <t>Standard Uncertainty</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>- core
-description: Translation of one form of Location into another.</t>
+description: Standard deviation of the probability distribution describing the spread of possible values in quantitative/continuous data.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Translation of one form of Location into another.</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>- Geocoding usually refers to the translation of "address" or "intersection" to "direct Position." Many service providers also include a "reverse geocoding" interface to their geocoder, thus extending the definition of the service as a general translator of Location. Because routing services use internal Location encodings not usually available to others, a geocoder is an integral part of the internals of such a service.</t>
-        </is>
-      </c>
+          <t>Standard deviation of the probability distribution describing the spread of possible values in quantitative/continuous data.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>- ISO 19133:2005; https://www.iso.org/standard/32551.html</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -2167,32 +2098,26 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Band Central Wavelength</t>
+          <t>Minimum Mapping Width</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: The width of the smallest linear Feature that is still represented on a map.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Single wavelength Value within the sensitivity interval of a spectroradiometric Sensor which represents the respective band. It could be either the mean, the median, the maximum sensitivity, or any other reasonable Value chosen to be representative.</t>
+          <t>The width of the smallest linear Feature that is still represented on a map.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>| Entry format example | Valid unit                                        |
-|----------------------|---------------------------------------------------|
-| 0.545 μm             | micrometre (μm), millimetre (mm), centimetre (cm) |</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- CGLS</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -2215,19 +2140,28 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cartographic Projection</t>
+          <t>Deprecated Product</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>- core</t>
+          <t>- core
+description: Products and collections that have been superseded by a newer version and are still available, but whose use is discouraged since they will be decommissioned in the future.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Products and collections that have been superseded by a newer version and are still available, but whose use is discouraged since they will be decommissioned in the future.</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
@@ -2248,26 +2182,30 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Copernicus Service Provider</t>
+          <t>Period Identifier</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Temporal reference in the form of a label or code that identifies a Period.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Institutional body, organisation or programme that provides reliable, trusted (authoritative?) EO Information and that has the financial resources to sustain the provision. It utilises satellite Data, ground-based measurements, and other sources to generate accurate and timely Data products related to various aspects of the Earth's environment, such as land, Atmosphere, oceans, and climate.</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t>Temporal reference in the form of a label or code that identifies a Period.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>- Period Identifiers are the temporal equivalent of geographic identifiers as specified in ISO 19912.</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO 19170:2021</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -2290,19 +2228,19 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Location Error</t>
+          <t>Lead Time</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>- core
-description: Measure of the agreement between the represented Location of an Object and the true Location.</t>
+description: Minimum time of interval between an Observation being tasked and being performed.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Measure of the agreement between the represented Location of an Object and the true Location.</t>
+          <t>Minimum time of interval between an Observation being tasked and being performed.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2332,28 +2270,24 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Version Control</t>
+          <t>Calibration</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>- core
-description: Method of working with collections, similar to version control systems used in traditional software development but optimized to allow better processing of data and collaboration in data analytics and research contexts.</t>
+- approved</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Method of working with collections, similar to the version control systems used in traditional software development but optimized to allow better processing of data and collaboration in the context of data analytics, research, and any other form of data analysis.</t>
+          <t>Process of quantitatively defining a system's (e.g. a Sensor or Model's) response to known, controlled inputs produced for example by references. In Remote Sensing, it implies the collection of pre-flight and in-flight calibration measurements and in-situ Data that is to be used in the Data calibration processing routine.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>- [Wikipedia](https://en.wikipedia.org/wiki/Data_version_control)</t>
-        </is>
-      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
@@ -2374,26 +2308,26 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Access</t>
+          <t>Climate Projection</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>- core
-description: Service to disseminate Data.</t>
+- approved</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Service to disseminate Data.</t>
+          <t>Simulated response of the climate system to a scenario of future emission or concentration of greenhouse gases (GHGs) and aerosols, generally derived using climate models. Climate Projections are distinguished from climate predictions by their dependence on the emission/concentration/radiative forcing scenario used, which is in turn based on assumptions concerning, for example, future socioeconomic and technological developments that may or may not be realised.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- IPCC</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -2416,26 +2350,30 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Collection Upgrade</t>
+          <t>Spatial Reporting Unit</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Smallest spatial object of interest that may be used for reporting and for which the information should be aggregated.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>New and improved major version of all products within a collection due to comprehensive reprocessing.</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+          <t>Smallest spatial object of interest that may be used for reporting and for which the information should be aggregated.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>- WIGOS 2019 uses 'spatial reporting interval', probably assuming observations are reported on a grid with regular spacing/intervals.</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -2458,26 +2396,26 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Thematic Resolution</t>
+          <t>Source Data</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>- core
-description: Level of categorical detail of information expressed by the number of classes.</t>
+description: Data required for production of an EO Collection (e.g., unenhanced satellite mission data) as well as further processed Level-1 data, or any other pre-processed format meeting program requirements.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Level of categorical detail of information expressed by the number of classes.</t>
+          <t>Data required for production of an EO Collection (e.g., unenhanced satellite mission data) as well as further processed Level-1 data (precision geometrically and radiometrically corrected radiance at the sensor), or any other pre-processed format that suppliers are providing access to that meets program requirements.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>- CGLS</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -2500,26 +2438,30 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Standard Uncertainty</t>
+          <t>Accuracy</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>- core
-description: Standard deviation of the probability distribution describing the spread of possible values in quantitative/continuous data.</t>
+- approved</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Standard deviation of the probability distribution describing the spread of possible values in quantitative/continuous data.</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
+          <t>Proximity of Measurement results to the accepted Value; precision is the degree to which repeated or reproducible measurements under unchanged conditions show the same results.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>- In essence, Accuracy reflects how close measurements are to the accepted Value, while precision gauges the reliability and consistency of those measurements.</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- BS ISO 5725-1</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -2542,30 +2484,26 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Coverage Interval</t>
+          <t>Policy Making</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>- core
-- approved</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Coverage extent</t>
-        </is>
-      </c>
+          <t>- high-impact
+description: Process by which governments translate their political vision into programmes and actions to deliver outcomes — desired change in the real world.</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Range or specific subset of values associated with a coverage dataset.</t>
+          <t>Process by which governments translate their political vision into programmes and actions to deliver outcomes — desired change in the real world.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [ESA/CEOS?, modified](https://digital-strategy.ec.europa.eu/en/library/quality-public-administration-toolbox-practitioners)</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -2588,30 +2526,31 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Path</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>- base
-description: "Line defined in an algorithmic way using at least two positions (can be open-ended). Alternative: line connecting two positions in an algorithmic way (limited by end points)."</t>
+- controversial
+description: Place referenced by a single set of coordinates within a coordinate reference system.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Line defined in an algorithmic way using at least two positions (can be open-ended). Alternative: line connecting two positions in an algorithmic way (limited by end points).</t>
+          <t>Place referenced by a single set of coordinates within a coordinate reference system.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>- A Path is a 1-dimensional Place.</t>
+          <t>- Opposite to (previous) ISO definition, Position shall be used only for 0-dimensional primitives (points).</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO 19133:2005, modified to cover only points, also called 'direct position'</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -2634,26 +2573,26 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Source Data</t>
+          <t>Minimum Mapping Unit</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>- core
-description: Data required for production of an EO Collection (e.g., unenhanced satellite mission data) as well as further processed Level-1 data, or any other pre-processed format meeting program requirements.</t>
+description: The area of the smallest Feature that is still represented on a map.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Data required for production of an EO Collection (e.g., unenhanced satellite mission data) as well as further processed Level-1 data (precision geometrically and radiometrically corrected radiance at the sensor), or any other pre-processed format that suppliers are providing access to that meets program requirements.</t>
+          <t>The area of the smallest Feature that is still represented on a map.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- CGLS</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -2676,26 +2615,26 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Atmosphere</t>
+          <t>Spectral Band</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Part of the electromagnetic spectrum of specific wavelengths, in remote sensing usually described by central wavelength and bandwidth.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Layer of gases, commonly known as air, including suspended liquid and solid particles known as aerosols (incl. dust, clouds, snow and ice).</t>
+          <t>Part of the electromagnetic spectrum of specific wavelengths. In Remote Sensing, usually described by central wavelength and bandwidth.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -2718,64 +2657,36 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Geopositioning</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>- core
-description: Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
+description: Determination of the geographic Position of a point (0D) or linear (1D) Feature.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
+          <t>Determination of the geographic Position of a point (0D) or linear (1D) Feature.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
+          <t>- Modified from: ISO 19130-1:2018, 3.36</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>- ISO/TS 19101‑2:2008, 4.41</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Process aimed at verifying that the specified requirements are achieved or compliant. Involves comparing mission products with representative reference data, considering various observation conditions, ensuring the quality and traceability of the reference data used.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
-        </is>
-      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>- BIPM; QA4EO; ESA?, modified</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Assurance that a product, service, or system meets the needs of the customer and other identified stakeholders. Often involves acceptance and suitability with external customers.</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
-        </is>
-      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>- EU-US Land Imaging EO Collaboration</t>
-        </is>
-      </c>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
@@ -2788,31 +2699,26 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Long Term Preservation</t>
+          <t>Collection Update</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>- core
-description: The act of maintaining information in a correct and independently understandable form over the long term.</t>
+- approved</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>The act of maintaining information in a correct and independently understandable form over the long term.</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>- Long term refers to a period of time long enough to be concerned with the impact which changing technologies, including support for media and data formats, and changing user communities will have on the information being held in a repository.
-- See also preservation.</t>
-        </is>
-      </c>
+          <t>Minor revisions to a relatively small number of products within a collection for the purpose of correcting errors and maintaining consistent quality.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
@@ -2835,40 +2741,59 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Catalogue</t>
+          <t>Verification</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Provision of objective evidence that a given item fulfils specified requirements.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>System that provides users with discovery of information on which EO products can be obtained.</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>- A 'Product Catalogue' can organise products and collections with varying access levels depending on product and user type.</t>
-        </is>
-      </c>
+          <t>Provision of objective evidence that a given item fulfils specified requirements.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>- When applicable, measurement uncertainty should be taken into consideration.
+- The item may be, e.g. a Process, measurement procedure, material, compound, or measuring system.
+- The specified requirements may be, e.g. that a manufacturer's specifications are met.
+- Verification should not be confused with Calibration. Not every verification is a Validation.</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>- ISO/IEC Guide 99:2007, 2.44</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Evaluation of whether or not a product, service, or system complies with a regulation requirement, specification, or imposed condition. Often an internal Process.</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>- EU-US Land Imaging EO Collaboration</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Means to evaluate the reliability of the data in the absence of a reference dataset, allowing for an assessment of its standalone performance. Involves confirming the consistency and internal coherence of the data without direct comparison to external reference sources.</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
@@ -2881,26 +2806,29 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Minimum Mapping Unit</t>
+          <t>Earth Observation Based Output</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>- core
-description: The area of the smallest Feature that is still represented on a map.</t>
+description: Higher-level processing and integration output (indicative level 4 and beyond) that goes beyond basic data processing, often designed for policy or decision-making needs.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>The area of the smallest Feature that is still represented on a map.</t>
+          <t>Higher-level processing and integration output (indicative level 4 and beyond) that goes beyond basic data processing. These outputs are often designed specifically for policy or decision-making needs, and can be categorized into sub-categories:
+- Outputs from models/model integration: use of EO products as inputs in numerical models or combining them with other data sources in modelling frameworks.
+- Indicator-based outputs: EO products transformed through specialized algorithms (including statistical methods, machine learning, and pattern recognition) to create meaningful metrics based on spatio-temporal analysis.
+- Outputs from reanalysis: merging of EO products with other observations and models, creating consistent long-term records of past atmospheric, oceanic, and land surface conditions, and filling gaps through data assimilation techniques.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>- CGLS</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
@@ -2923,34 +2851,19 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Temporal Reporting Period</t>
+          <t>Cartographic Projection</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>- core
-description: Time period used for reporting and for which the information should be aggregated from the native temporal resolution.</t>
+          <t>- core</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Time Period used for reporting and for which the information should be aggregated from the native Temporal Resolution.</t>
-        </is>
-      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>| Entry format example | Valid unit                     |
-|----------------------|-------------------------------|
-| 1 s, 2 h, 1 d        | second, hour, day, month, year |</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>- Modified WIGOS Metadata Standard 2019</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
@@ -2971,26 +2884,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Policy File</t>
+          <t>Temporal Reporting Period</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>- high-impact
-description: Policy documents that represent the official written reference for a given Policy.</t>
+          <t>- core
+description: Time period used for reporting and for which the information should be aggregated from the native temporal resolution.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Policy documents that represent the official written reference for a given Policy.</t>
+          <t>Time Period used for reporting and for which the information should be aggregated from the native Temporal Resolution.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>| Entry format example | Valid unit                     |
+|----------------------|-------------------------------|
+| 1 s, 2 h, 1 d        | second, hour, day, month, year |</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Modified WIGOS Metadata Standard 2019</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
@@ -3013,26 +2932,26 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Impact</t>
+          <t>Reproducibility</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>- core
-description: Regarded long-term according to X. However, in the Horizon Europe Missions terminology, regarded short-term.</t>
+description: Concerned with the validity of the results of a particular study, enabling readers to check whether results have been manipulated by reproducing exactly the same study using the same data and methods.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Regarded long-term according to X. However, in the Horizon Europe Missions terminology, regarded short-term.</t>
+          <t>Concerned with the validity of the results of a particular study, i.e., the possibility for readers to check whether results have been manipulated, by reproducing exactly the same study using the same data and methods.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Ostermann and Granell (2015)</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
@@ -3055,7 +2974,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Calibration</t>
+          <t>Atmosphere</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3067,12 +2986,16 @@
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Process of quantitatively defining a system's (e.g. a Sensor or Model's) response to known, controlled inputs produced for example by references. In Remote Sensing, it implies the collection of pre-flight and in-flight calibration measurements and in-situ Data that is to be used in the Data calibration processing routine.</t>
+          <t>Layer of gases, commonly known as air, including suspended liquid and solid particles known as aerosols (incl. dust, clouds, snow and ice).</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>- Guth et al. 2021</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
@@ -3093,50 +3016,38 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Geolocating</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>- base
-description: Value and possibly Uncertainty of a Trait of a specific Entity.</t>
+          <t>- core
+description: Geopositioning of an Object using a Physical Sensor Model or a True Replacement Model.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Value and possibly Uncertainty of a Trait of a specific Entity.</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>- Data simply describe entities using certain traits and are not targeted at a particular use or audience.</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Data can be categorised into:
-- factual (i.e. obtained by Observation) or fictional (obtained e.g. through modelling, estimating or assigning)
-- quantitative (continuous) or qualitative (categorical)
-- analogue or digital
-(list not exhaustive!)</t>
-        </is>
-      </c>
+          <t>Geopositioning of an Object using a Physical Sensor Model or a True Replacement Model.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO 19115-2:2009, 4.11</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Scientific or technical measurements, values calculated therefrom, observations, or facts that can be represented by numbers, tables, graphs, models, text, or symbols which are used as a basis for reasoning and further calculation.</t>
+          <t>Determination of the geographic location of a feature of two or more dimensions.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
+          <t>- ISO 19130-1:2018, 3.36 ('geopositioning'), modified</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
@@ -3155,40 +3066,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Quantity</t>
+          <t>Confidence Interval</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>- base
-description: Property having a magnitude that can be expressed as a number from a continuous and contiguous range and a reference.</t>
+          <t>- controversial
+- approved</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Property having a magnitude that can be expressed as a number from a continuous and contiguous range and a reference.</t>
+          <t>Probability that the Quantity lies in the interval, conditioned on the measuring or modelling assumptions.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>- ISO/IEC Guide 99:2007, 1.1, modified — Notes omitted</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Property whose instances can be compared by ratio or only by order.</t>
-        </is>
-      </c>
+          <t>- KCEO</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>- gEOGlos (VIM4 Notes omitted)</t>
-        </is>
-      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
@@ -3205,19 +3108,19 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Policy Milestone</t>
+          <t>Baseline</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>- high-impact
-description: Markers of significant progress in addressing specific issues, or crucial decision points where significant choices are made within a policy process.</t>
+          <t>- core
+- approved</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Markers of significant progress in addressing specific issues, or crucial decision points where significant choices are made. Concrete examples include: policy planning and proposing, impact assessment, implementation, or implementation cycles (e.g., Water Framework Directive, Marine Strategy Framework Directive), achievement of Policy Objectives and Policy Targets, and evaluating and improving existing laws.</t>
+          <t>Reference Period, time or measure against which the Information is assessed or compared.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -3227,10 +3130,18 @@
           <t>- KCEO</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Source data that has been processed to a common set of requirements and organised into a form that allows immediate analysis and interoperability through time and with other collections.</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
@@ -3247,31 +3158,26 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Classification System Levels</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>- base
-description: Element of a type domain.</t>
+          <t>- core
+- approved</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Element of a type domain.</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>- A Value may consider a possible state of an object within a class or type (domain).
-- A data value is an instance of a data type, a value without identity.</t>
-        </is>
-      </c>
+          <t>Levels in a hierarchical Classification System.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>- ISO/IEC 19501:2005, 0000_5</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -3294,26 +3200,26 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Collection Update</t>
+          <t>Latency</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Period between the end of sensing of a Phenomenon to the beginning of availability of a specific product.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Minor revisions to a relatively small number of products within a collection for the purpose of correcting errors and maintaining consistent quality.</t>
+          <t>Period between the end of sensing of a Phenomenon to the beginning of availability of a specific product.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- ?</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -3336,32 +3242,20 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Laboratory Observation</t>
+          <t>Resolution</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>- core
-description: Usually in-situ observations in which the Object or Phenomenon is isolated from other systems or altered in its original conditions or environment.</t>
+  - to be defined</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Usually in-situ observations in which the Object or Phenomenon is isolated from other systems or altered in its original conditions or environment.</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>- It is important to consider that Laboratory Observations are typically conducted in controlled conditions, allowing for isolation or alteration of the Object or Phenomenon from its natural environment or other systems.</t>
-        </is>
-      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
@@ -3382,20 +3276,28 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Environmental Process</t>
+          <t>Data Access</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>- core
-description: ""</t>
+description: Service to disseminate Data.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Service to disseminate Data.</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
@@ -3416,26 +3318,26 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Measurement Uncertainty</t>
+          <t>Phenomenon</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>- core
-description: Uncertainty associated with the method of Measurement.</t>
+          <t>- base
+description: Entity with at least one Property referenced by an identifier.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Uncertainty associated with the method of Measurement.</t>
+          <t>Entity with at least one Property referenced by an identifier.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>- CEOS Wiki adopted from JCGM GUM</t>
+          <t>- KCEO, modified after Wikipedia and the Columbia Encyclopaedia 2008</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
@@ -3458,20 +3360,39 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Continuity</t>
+          <t>Earth Spheres</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>- core
-  - to be defined</t>
+description: Spheres dividing planet Earth into subsystems, which are collectives of (physical) matter sharing specific traits.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Spheres dividing planet Earth into subsystems, which are collectives of (physical) matter sharing specific traits.</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>- Atmosphere
+- Hydrosphere
+- Cryosphere
+- Biosphere
+- Lithosphere
+- Anthroposphere</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>- Hugget, R., et al., 2024, DOI: 10.1177/03091333241275465
+- Guth, P., et al., 2021, https://doi.org/10.3390/rs13183581
+- Martin, Y.E., et al., 2012</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
@@ -3492,37 +3413,31 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Temporal Revisit</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>- core
-description: Interval between successive observations.</t>
+          <t>- base
+description: Element of a type domain.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Interval between successive observations.</t>
+          <t>Element of a type domain.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>- In Remote Sensing it is also called repeat cycle.
-- More generally it is known as temporal sampling interval.</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>| Entry format example | Valid unit                     |
-|----------------------|-------------------------------|
-| 1 s, 2 h             | second, hour, day, month, year |</t>
-        </is>
-      </c>
+          <t>- A Value may consider a possible state of an object within a class or type (domain).
+- A data value is an instance of a data type, a value without identity.</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO/IEC 19501:2005, 0000_5</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
@@ -3545,20 +3460,36 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Timeliness</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>- core
-  - to be defined</t>
+description: Period between the moment of requesting information and the moment of availability of information.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Period between the moment of requesting information and the moment of availability of information.
+- Near Real-Time (NRT): delivered less than 3 hours after requesting information.
+- Slow-Time Critical (STC): delivered within 48 hours after requesting information.
+- Non-Time Critical (NTC): typically delivered within 1 month after requesting information.</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>- In some contexts also known as delivery time.
+- C3S URDB describes timeliness as "the ability of the publish/subscribe middleware to provide the expected service within known time bounds".</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>- Adapted from ESA S3 User Guide</t>
+        </is>
+      </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
@@ -3579,40 +3510,59 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Period Identifier</t>
+          <t>Auxiliary Data</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>- core
-description: Temporal reference in the form of a label or code that identifies a Period.</t>
+- approved</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Temporal reference in the form of a label or code that identifies a Period.</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>- Period Identifiers are the temporal equivalent of geographic identifiers as specified in ISO 19912.</t>
-        </is>
-      </c>
+          <t>Data that enhance the processing and utilisation of main Sensor Data. Auxiliary Data are usually not captured by the same Data collection Process or on the same platform as the main Sensor Data. Examples include meteorological Data received from ECMWF/Met Offices or DEMs. Auxiliary Data help in Data processing, but are also Data sets in their own right.</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>- ISO 19170:2021</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
+          <t>- ESA/CEOS?, modified
+- ENMAP Glossary of Terms, https://www.enmap.org/Data/doc/EnMAP_Terms.pdf, 20210624
+- EO Data Stewardship Glossary</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Data required to perform processing of Sensor Data which is not obtained from the Sensor itself. Includes: (a) Data provided by the spacecraft (e.g. orbit Position and velocity, attitude, instrument house-keeping Data, on-board time); (b) Data not available from on-board sources.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>For EnMAP, this includes (a) orbit files, attitude files, Calibration Data, instrument house-keeping Data; (b) atmospheric parameters, reference images.</t>
+        </is>
+      </c>
       <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>- ENMAP Glossary of Terms, https://www.enmap.org/Data/doc/EnMAP_Terms.pdf, 20210624
+- EO Data Stewardship Glossary</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Data required for instrument processing that does not originate in the instrument itself or from the satellite. Some Auxiliary Data will be generated in the ground segment, whilst other Data will be provided from external sources.</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>- CEOS-ARD PFS template 20220302</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
@@ -3673,40 +3623,40 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Timeliness</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>- core
-description: Period between the moment of requesting information and the moment of availability of information.</t>
+          <t>- base
+description: Property having a magnitude that can be expressed as a number from a continuous and contiguous range and a reference.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Period between the moment of requesting information and the moment of availability of information.
-- Near Real-Time (NRT): delivered less than 3 hours after requesting information.
-- Slow-Time Critical (STC): delivered within 48 hours after requesting information.
-- Non-Time Critical (NTC): typically delivered within 1 month after requesting information.</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>- In some contexts also known as delivery time.
-- C3S URDB describes timeliness as "the ability of the publish/subscribe middleware to provide the expected service within known time bounds".</t>
-        </is>
-      </c>
+          <t>Property having a magnitude that can be expressed as a number from a continuous and contiguous range and a reference.</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>- Adapted from ESA S3 User Guide</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>- ISO/IEC Guide 99:2007, 1.1, modified — Notes omitted</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Property whose instances can be compared by ratio or only by order.</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>- gEOGlos (VIM4 Notes omitted)</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
@@ -3723,20 +3673,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Equivalence</t>
+          <t>Final Product Version</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>- core
-  - to be defined</t>
+description: Product within an EO Collection that is not expected to be updated.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Product within an EO Collection that is not expected to be updated.</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>- In its production, all of the prerequisite auxiliary data were used as input.</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
@@ -3757,26 +3719,31 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Hydrosphere</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>- core
-description: The masses of liquid water, such as oceans, lakes, and rivers.</t>
+          <t>- controversial
+description: Act of determining the Value of a Property by interacting in a reproducible way with the Phenomenon using a Sensor.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>The masses of liquid water, such as oceans, lakes, and rivers.</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr"/>
+          <t>Act of determining the Value of a Property by interacting in a reproducible way with the Phenomenon using a Sensor.</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>- The result of an Observation is a Value complemented by an Uncertainty, often itself being referred to as 'observation'.
+- An Observation result represents a Sample of the Phenomenon (otherwise it would be identical with the Phenomenon).</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
@@ -3799,36 +3766,56 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>Characteristic</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>- core
+          <t>- base
 - approved</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Proximity of Measurement results to the accepted Value; precision is the degree to which repeated or reproducible measurements under unchanged conditions show the same results.</t>
+          <t>Distinguishing Feature.</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>- In essence, Accuracy reflects how close measurements are to the accepted Value, while precision gauges the reliability and consistency of those measurements.</t>
+          <t>- A Characteristic can be inherent or assigned.
+- A Characteristic can be qualitative or quantitative.
+- There are various classes of Characteristics, such as the following:
+  - physical (e.g. mechanical, electrical, chemical, biological);
+  - sensory (e.g. relating to smell, touch, taste, sight, hearing);
+  - behavioural (e.g. courtesy, honesty, veracity);
+  - temporal (e.g. punctuality, reliability, availability);
+  - ergonomic (e.g. physiological characteristic or related to human safety);
+  - functional (e.g. maximum speed of an aircraft).</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>- BS ISO 5725-1</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
+          <t>- ISO 9000:2005, 3.5.1</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Abstraction of a Property of an Object or of a set of objects.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>- Characteristics are used for describing Concepts.</t>
+        </is>
+      </c>
       <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>- ISO 1087-1:2000, 3.2.4; ISO 19146:2010(E); https://www.iso.org/standard/20057.html</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
@@ -3845,26 +3832,26 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Traceability</t>
+          <t>Geosphere</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>- core
-description: Property of a measurement result whereby the result can be related to a reference through a documented unbroken chain of calibrations each contributing to the measurement uncertainty.</t>
+description: The masses of minerals that constitute planet Earth.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Property of a measurement result whereby the result can be related to a Reference through a documented unbroken chain of calibrations, each contributing to the measurement uncertainty.</t>
+          <t>The masses of minerals that constitute planet Earth.</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>- https://www.isobudgets.com/Measurement-traceability-complying-iso-17025-requirements/</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -3887,26 +3874,26 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Biosphere</t>
+          <t>Spectral Resolution</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Measure of the ability to resolve features in the electromagnetic spectrum.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Masses of living organisms, such as vegetation and animals, including dead but still connected parts such as roots, trunks or branches.</t>
+          <t>Measure of the ability to resolve features in the electromagnetic spectrum.</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
@@ -3929,30 +3916,26 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Update Frequency</t>
+          <t>Hydrosphere</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>- core
-description: Frequency at which the product is available to users.</t>
+description: The masses of liquid water, such as oceans, lakes, and rivers.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Frequency at which the product is available to users.</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>- Also known in product catalogues as dissemination frequency.</t>
-        </is>
-      </c>
+          <t>The masses of liquid water, such as oceans, lakes, and rivers.</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
@@ -3975,26 +3958,33 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Lithosphere</t>
+          <t>Time of Year</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>- core
-description: The solid, inanimate outer layer of the Geosphere. For the purposes of Earth Observation, includes soils ('pedosphere').</t>
+description: Time of the year at which the variable is observed or simulated by a model.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>The solid, inanimate outer layer of the Geosphere. For the purposes of Earth Observation, the Lithosphere is considered to include soils ('pedosphere').</t>
+          <t>Time of the year at which the variable is observed or simulated by a model.</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>| Type      | Entry format example | Valid unit     |
+|-----------|----------------------|----------------|
+| timestamp | m/d                  | Not Applicable |
+| timerange | m/d - m/d            | Not Applicable |</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
@@ -4017,24 +4007,24 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Path</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>- base
-description: The result of organisation, interpretation, categorisation, classification, or some other form of processing of Data attaching to it a certain meaning that can be understood by the addressee.</t>
+description: "Line defined in an algorithmic way using at least two positions (can be open-ended). Alternative: line connecting two positions in an algorithmic way (limited by end points)."</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>The result of organisation, interpretation, categorisation, classification, or some other form of processing of Data attaching to it a certain meaning that can be understood by the addressee.</t>
+          <t>Line defined in an algorithmic way using at least two positions (can be open-ended). Alternative: line connecting two positions in an algorithmic way (limited by end points).</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>- Information depends on Data and is targeted.</t>
+          <t>- A Path is a 1-dimensional Place.</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
@@ -4063,19 +4053,19 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Temporal Consistency</t>
+          <t>Spatial Consistency</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>- core
-description: Condition where the temporal statistical properties of the sample depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
+description: Condition where the spatial statistical properties of the data depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Condition where the temporal statistical properties of the Sample depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
+          <t>Condition where the spatial statistical properties of the data depend only on the underlying physical processes and not on other factors such as fusing different products or sensors. Also, the validity of the assumptions of the procedure to produce information holds true across the whole spatial range.</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -4105,31 +4095,30 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Metadata</t>
+          <t>Cell</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>- core
-description: Data describing other data, providing an understanding of the content and utility of a product or collection.</t>
+- approved</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Data describing other data, providing an understanding of the content and utility of a product or collection.</t>
+          <t>Spatial, spatio-temporal zone or temporal unit of geometry with dimensionality greater than 0, associated with a zone.</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>- Metadata may be used to select data for a particular scientific investigation.
-- Metadata is intended as information describing significant aspects of a resource (Earth Observation space data in this context). They are created for the purposes of data search, discovery and access management and may exist at various levels, typically from data collection through to the individual variables of each product in a collection.</t>
+          <t>- Cells are the unit of geometry in a DGGS, and the geometry of the region of space-time occupied by a zone is a Cell.</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- ISO 19170:2021</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
@@ -4152,22 +4141,26 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Spatial Resolution</t>
+          <t>Business Continuity</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>- core
-description: ''</t>
+- approved</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>An organisation's readiness to continue functioning during times of disruption.</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
@@ -4190,26 +4183,31 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Phenomenon</t>
+          <t>Derivative Product</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>- base
-description: Entity with at least one Property referenced by an identifier.</t>
+          <t>- core
+description: Product additionally processed from baseline or unenhanced mission data.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Entity with at least one Property referenced by an identifier.</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr"/>
+          <t>Product additionally processed from baseline or unenhanced mission data.</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>- Generally either a compilation of time-series data (e.g., all time, annual, monthly or seasonal summary data, &gt; Level 3) or thematic versions of each individual data tile of baseline data.
+- Derived products are citable via a Digital Object Identifier (DOI).</t>
+        </is>
+      </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>- KCEO, modified after Wikipedia and the Columbia Encyclopaedia 2008</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
@@ -4232,26 +4230,26 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Geolocation Information</t>
+          <t>Policy Objective</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>- core
-description: Information used to determine geographic Location.</t>
+          <t>- high-impact
+description: Desired outcome that policymakers wish to achieve.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Information used to determine geographic Location.</t>
+          <t>Desired outcome that policymakers wish to achieve.</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>- ISO 19130-1:2018, 3.34</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
@@ -4274,57 +4272,62 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Verification</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>- core
-description: Provision of objective evidence that a given item fulfils specified requirements.</t>
+description: Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Provision of objective evidence that a given item fulfils specified requirements.</t>
+          <t>Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>- When applicable, measurement uncertainty should be taken into consideration.
-- The item may be, e.g. a Process, measurement procedure, material, compound, or measuring system.
-- The specified requirements may be, e.g. that a manufacturer's specifications are met.
-- Verification should not be confused with Calibration. Not every verification is a Validation.</t>
+          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>- ISO/IEC Guide 99:2007, 2.44</t>
+          <t>- ISO/TS 19101‑2:2008, 4.41</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Evaluation of whether or not a product, service, or system complies with a regulation requirement, specification, or imposed condition. Often an internal Process.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>Process aimed at verifying that the specified requirements are achieved or compliant. Involves comparing mission products with representative reference data, considering various observation conditions, ensuring the quality and traceability of the reference data used.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
+        </is>
+      </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
-          <t>- EU-US Land Imaging EO Collaboration</t>
+          <t>- BIPM; QA4EO; ESA?, modified</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Means to evaluate the reliability of the data in the absence of a reference dataset, allowing for an assessment of its standalone performance. Involves confirming the consistency and internal coherence of the data without direct comparison to external reference sources.</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr"/>
+          <t>Assurance that a product, service, or system meets the needs of the customer and other identified stakeholders. Often involves acceptance and suitability with external customers.</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- EU-US Land Imaging EO Collaboration</t>
         </is>
       </c>
       <c r="P84" t="inlineStr"/>
@@ -4339,26 +4342,35 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Property</t>
+          <t>Temporal Extent</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>- base
-description: Observable Trait.</t>
+          <t>- core
+description: Period during which data was collected, observations were made, or for which the model was run.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Observable Trait.</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
+          <t>Period during which data was collected, observations were made, or for which the model was run.</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>- In W3C this is the definition of temporal coverage.
+- Time Period covered by a series of observations inclusive of the specified date/time indications (measurement history). Defined based on the beginning and end dates of observations.</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>- WIGOS Metadata</t>
+        </is>
+      </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Adapted from W3C</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
@@ -4381,26 +4393,26 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Object</t>
+          <t>Traceability</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>- base
-description: Entity with a well-defined boundary and identity that encapsulates state and behaviour.</t>
+          <t>- core
+description: Property of a measurement result whereby the result can be related to a reference through a documented unbroken chain of calibrations each contributing to the measurement uncertainty.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Entity with a well-defined boundary and identity that encapsulates state and behaviour.</t>
+          <t>Property of a measurement result whereby the result can be related to a Reference through a documented unbroken chain of calibrations, each contributing to the measurement uncertainty.</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>- ISO/IEC 19501:2005</t>
+          <t>- https://www.isobudgets.com/Measurement-traceability-complying-iso-17025-requirements/</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
@@ -4423,37 +4435,30 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Time of Day</t>
+          <t>Decommissioned Product</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>- core
-description: Time of the day at which the variable or parameter is observed or simulated by a model.</t>
+description: Products and collections that have been superseded by new versions and are no longer available.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Time of the day at which the variable or parameter is observed or simulated by a model.</t>
+          <t>Products and collections that have been superseded by new versions and are no longer available.</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>- In Remote Sensing it is also known as time of overpass.</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>| Type      | Entry format example | Valid unit |
-|-----------|----------------------|------------|
-| timestamp | 18:00 h (0–24)       | Hours      |
-| timerange | 18:00 – 20:00 h      | Hours      |</t>
-        </is>
-      </c>
+          <t>- Decommissioned products are no longer supported, i.e. corrections will not be made, new data will not be added, and support is not available.</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
@@ -4476,26 +4481,31 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Obsolete Product or Collection</t>
+          <t>Grid</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>- core
-description: Products or collections which have been superseded by later versions of a product or collection.</t>
+description: Network composed of two or more sets of curves in which the members of each set intersect the members of the other sets in an algorithmic way.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Products or collections which have been superseded by later versions of a product or collection.</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr"/>
+          <t>Network composed of two or more sets of curves in which the members of each set intersect the members of the other sets in an algorithmic way.</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>- The curves partition a space into grid cells or zones.
+- The intersection points of the curves are called nodes.</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- ISO 19123:2005, 4.1.23; Note 1 modified; Note 2 added</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
@@ -4518,40 +4528,36 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Baseline</t>
+          <t>Measurement</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Observation of a Quantity.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Reference Period, time or measure against which the Information is assessed or compared.</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr"/>
+          <t>Observation of a Quantity.</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>- The Process of collecting a measurement is called measuring.</t>
+        </is>
+      </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Source data that has been processed to a common set of requirements and organised into a form that allows immediate analysis and interoperability through time and with other collections.</t>
-        </is>
-      </c>
+          <t>- GEOGlos (VIM ?, modified)</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
-        </is>
-      </c>
+      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
@@ -4568,31 +4574,30 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Earth Observation</t>
+          <t>Catalogue</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>- high-impact
-description: Science domain dealing with technologies and methods of collecting and analyzing observations about the different Earth spheres.</t>
+          <t>- core
+- approved</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Science domain dealing with technologies and methods of collecting and analyzing observations about the different Earth spheres.</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>- Earth Observation (EO) can be categorised by location of the sensor into space-borne, air-borne, sea-borne, ground-based, underwater and underground EO.
-- Earth Observation (EO) includes Remote Sensing, such as satellite imagery, as well as in-situ observations, e.g., with ground-based devices.</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr"/>
+          <t>System that provides users with discovery of information on which EO products can be obtained.</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>- A 'Product Catalogue' can organise products and collections with varying access levels depending on product and user type.</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>- Modified GEO definition [GEO (earthobservations.org)](https://earthobservations.org/resources#key)</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
@@ -4615,24 +4620,36 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Tolerance</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>- core
-  - to be defined</t>
+description: Phenomenon whose values for specific properties are known and understood with an Uncertainty significantly lower than that of the Observation with which it is compared.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Phenomenon whose values for specific properties are known and understood with an Uncertainty significantly lower (quantify?) than that of the Observation with which it is compared.</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Sort of data acquired with an Uncertainty significantly lower (quantify?) than that of the data it is being compared with.</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>- VIM?, modified</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
@@ -4649,22 +4666,26 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Spectral Resolution</t>
+          <t>Laboratory Observation</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>- core
-description: Measure of the ability to resolve features in the electromagnetic spectrum.</t>
+description: Usually in-situ observations in which the Object or Phenomenon is isolated from other systems or altered in its original conditions or environment.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Measure of the ability to resolve features in the electromagnetic spectrum.</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr"/>
+          <t>Usually in-situ observations in which the Object or Phenomenon is isolated from other systems or altered in its original conditions or environment.</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>- It is important to consider that Laboratory Observations are typically conducted in controlled conditions, allowing for isolation or alteration of the Object or Phenomenon from its natural environment or other systems.</t>
+        </is>
+      </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
@@ -4691,26 +4712,32 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Near Real Time Data</t>
+          <t>Sample</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>- high-impact
-description: Data available for use with a specified (small and application dependent) latency, typically 3 hours for meteorological applications.</t>
+          <t>- controversial
+description: Subset of one or more entities.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Data available for use with a specified (small and application dependent) latency, typically 3 hours for meteorological applications.</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr"/>
+          <t>Subset of one or more entities.</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>- A Sample may be spatial, temporal, spectral, or in any other dimension or Trait.
+- Each Sample is contiguous, i.e. it does not consist of more than one discontinuous geometry in any dimension.
+- The Process of obtaining a Sample is called sampling.</t>
+        </is>
+      </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
@@ -4733,38 +4760,30 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Measurand</t>
+          <t>Trait</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>- core
-description: Particular Quantity subject to Measurement.</t>
+          <t>- base
+description: Characteristic belonging to an entity and referenced by an identifier.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Particular Quantity subject to Measurement.</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>| Step | Process description |
-| :----- | :--------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------- |
-| (Raw) | The complete and unaltered/unprocessed set of Data acquired by one or several sensors on a platform |
-| M/0 uncalibrated | Unaltered/unprocessed Level 0 (main) Sensor Data annotated with processed Ancillary Data and supplemented by Auxiliary Data (including radiometric and geometric Calibration coefficients and geo-referencing parameters) allowing further processing to higher Levels. |
-| M/1 Sensor-calibrated | Level M/0 Sensor Data which have been calibrated (ideally traceable to SI) and spatially aligned (co-located, eventually co-gridded) to represent at-Sensor measurements (Value and Uncertainty) in Sensor nominal spatiotemporal sampling, supplemented by appropriate ancillary data. |
-| M/2 target-calibrated | Level M/1 Data processed to represent geophysical Property values (and uncertainties) for a specified target (Object, Feature of interest, e.g. surface reflectance, apparent temperature) derived from M/1 Sensor Data, as much as possible maintaining the sensors nominal spatial and temporal sampling (Observation preserving). |
-| M/3 homogenised | Level M/1 or M/2 Data which have been generalised and integrated across one or several platforms and acquisitions to achieve an increased, more regular or in any other form enhanced spatial or temporal coverage in which states geophysical values agnostic of the originally acquiring Sensor and Observation condition and thus directly comparable. This homogenisation and fusion may include measurand re-Calibration to external standards and references including use of modelling, aggregation and interpolation. |
-| M/4 derived/inferred | Model output or results from analyses of Level M/3 (or lower level) Data i.e., attributes that might not be directly observable by the Sensor(s) but are derived from observations in combination with other external incl. non-observational Data using techniques like modelling or machine learning (AI). |
-From http://doi.org/10.2760/46796</t>
-        </is>
-      </c>
+          <t>Characteristic belonging to an entity and referenced by an identifier.</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>- Traits can be objective (inherent?) in which case they are also observable and called properties. Traits which are not observable (directly or indirectly) need to be assigned.</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>- VIM: 1993, 2.6</t>
+          <t>- Based on ISO 19143:2010, 4.21, ISO/IEC 2382:2015, 2121440, significantly modified, Note 1 added</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
@@ -4787,26 +4806,31 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Latency</t>
+          <t>Metadata</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>- core
-description: Period between the end of sensing of a Phenomenon to the beginning of availability of a specific product.</t>
+description: Data describing other data, providing an understanding of the content and utility of a product or collection.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Period between the end of sensing of a Phenomenon to the beginning of availability of a specific product.</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr"/>
+          <t>Data describing other data, providing an understanding of the content and utility of a product or collection.</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>- Metadata may be used to select data for a particular scientific investigation.
+- Metadata is intended as information describing significant aspects of a resource (Earth Observation space data in this context). They are created for the purposes of data search, discovery and access management and may exist at various levels, typically from data collection through to the individual variables of each product in a collection.</t>
+        </is>
+      </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>- ?</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
@@ -4829,26 +4853,30 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Policy Target</t>
+          <t>Backup</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>- high-impact
-description: Specific level or rate set for the Policy Objective.</t>
+          <t>- core
+- approved</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Specific level or rate set for the Policy Objective.</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr"/>
+          <t>General practice of making copies of current baseline and derived products of EO Collections at specified time intervals, and storing those copies in a manner that will not affect the data if the primary distribution environment is compromised.</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>- The emphasis is on the ability to retrieve a copy of the entire EO Collection on demand if the original data is lost or compromised.</t>
+        </is>
+      </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
@@ -4871,28 +4899,20 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Policy Objective</t>
+          <t>Tolerance</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>- high-impact
-description: Desired outcome that policymakers wish to achieve.</t>
+          <t>- core
+  - to be defined</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Desired outcome that policymakers wish to achieve.</t>
-        </is>
-      </c>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
@@ -4913,26 +4933,30 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Forecast Range</t>
+          <t>Archive</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>- core
-description: The forecast period.</t>
+- approved</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>The forecast period.</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr"/>
+          <t>System that stores data products, guaranteeing their preservation for future use.</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>- This function includes all operations to identify, store and retrieve the data and ensure their integrity.</t>
+        </is>
+      </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
@@ -4955,26 +4979,26 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Quality Indicator</t>
+          <t>Biosphere</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>- core
-description: Indicator providing sufficient information to allow all users to readily evaluate the fitness for purpose of the data or derived product.</t>
+- approved</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Indicator providing sufficient information to allow all users to readily evaluate the fitness for purpose of the data or derived product. May be a number, set of numbers, graph, Uncertainty budget, or a simple flag.</t>
+          <t>Masses of living organisms, such as vegetation and animals, including dead but still connected parts such as roots, trunks or branches.</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>- CEOS Wiki</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
@@ -4997,26 +5021,26 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>User Interface</t>
+          <t>Impact</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>- core
-description: Set of all the components of an interactive system that provide information and controls for the user to accomplish specific tasks with the interactive system.</t>
+description: Regarded long-term according to X. However, in the Horizon Europe Missions terminology, regarded short-term.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Set of all the components of an interactive system that provide information and controls for the User to accomplish specific tasks with the interactive system.</t>
+          <t>Regarded long-term according to X. However, in the Horizon Europe Missions terminology, regarded short-term.</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>- ISO 9241-110:2020, 3.10</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
@@ -5039,30 +5063,26 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Obsolete Product or Collection</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>- core
-description: Maximum acceptable change in Uncertainty per decade.</t>
+description: Products or collections which have been superseded by later versions of a product or collection.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Maximum acceptable change in Uncertainty per decade.</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>- GCOS uses bias or systematic errors instead of Uncertainty.</t>
-        </is>
-      </c>
+          <t>Products or collections which have been superseded by later versions of a product or collection.</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>- Modified from GCOS 2022</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
@@ -5085,26 +5105,26 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Classification System</t>
+          <t>Measurement Uncertainty</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Uncertainty associated with the method of Measurement.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Nomenclature used to classify Information into categorical thematic classes (e.g., EUNIS, MAES ecosystems, Corine Land Cover, LCCS).</t>
+          <t>Uncertainty associated with the method of Measurement.</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- CEOS Wiki adopted from JCGM GUM</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
@@ -5127,21 +5147,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Spatial Consistency</t>
+          <t>Spatial Resolution</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>- core
-description: Condition where the spatial statistical properties of the data depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
+description: ''</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Condition where the spatial statistical properties of the data depend only on the underlying physical processes and not on other factors such as fusing different products or sensors. Also, the validity of the assumptions of the procedure to produce information holds true across the whole spatial range.</t>
-        </is>
-      </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
@@ -5169,22 +5185,27 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Expanded Uncertainty</t>
+          <t>In-Situ Observation</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>- core
-description: Standard Uncertainty multiplied by a coverage factor k, chosen to obtain a desired level of confidence.</t>
+          <t>- controversial
+description: Observations performed in the same Place where a Phenomenon occurs, normally without isolating it from other systems or altering its pre-Observation state.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Standard Uncertainty multiplied by a coverage factor, k. The coverage factor is chosen to obtain a desired level of confidence. Most commonly a 95% confidence interval is chosen. For a Gaussian distribution, this is achieved with a coverage factor k = 2. (Note that strictly this provides a 95.45% confidence interval.)</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr"/>
+          <t>Observations performed in the same Place where a Phenomenon occurs, normally without isolating it from other systems (its environment) or altering its pre-Observation state.</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>- The main Characteristic of such observations is that distance has no or only negligible (within Uncertainty) influence on the Value of the Property observed. In-Situ Observations therefore often require either direct physical contact or small distances between a Sensor and the observed Phenomenon.
+- Observations not fulfilling these conditions are considered Remote Sensing.</t>
+        </is>
+      </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
@@ -5211,29 +5232,28 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Earth Observation Product</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>- core
-description: Device or instrument suited (through physical/chemical interaction) to measure one or more properties of a Phenomenon and thus collect factual/objective data.</t>
+description: Direct output from standardized satellite data processing chains (indicative levels 2 and 3), representing fundamental geophysical and biophysical variables.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Device or instrument suited (through physical/chemical interaction) to measure one or more properties of a Phenomenon and thus collect factual/objective data.</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>- Sensing is therefore a synonym for Observation (the Process).
-- As by their definition, sensors perform sampling.
-- Sensors used to obtain measurements must be calibrated and provide uncertainties.</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr"/>
+          <t>Direct output from standardized satellite data processing chains (indicative levels 2 and 3), representing fundamental geophysical and biophysical variables. These products demonstrate direct Traceability to original satellite measurements through rigorous Calibration and Validation processes. The processing methodology prioritizes the conversion of raw sensor data into quantifiable physical measurements, maintaining strict adherence to standardized processing protocols and Validation requirements.</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>- Soil moisture from microwave sensors
+- Forest canopy height from LiDAR data</t>
+        </is>
+      </c>
       <c r="G105" t="inlineStr">
         <is>
           <t>- KCEO</t>
@@ -5259,26 +5279,30 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Minimum Mapping Width</t>
+          <t>Spatial Completeness</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>- core
-description: The width of the smallest linear Feature that is still represented on a map.</t>
+description: Presence or absence of gaps, which are missing values in an otherwise continuous spatial data series.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>The width of the smallest linear Feature that is still represented on a map.</t>
+          <t>Presence or absence of gaps, which are missing values in an otherwise continuous spatial data series.</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>- Surface soil moisture retrieved from microwave satellite sensors may present gaps in mountainous terrains.</t>
+        </is>
+      </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>- CGLS</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
@@ -5301,30 +5325,30 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Backup</t>
+          <t>Geocoding</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Translation of one form of Location into another.</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>General practice of making copies of current baseline and derived products of EO Collections at specified time intervals, and storing those copies in a manner that will not affect the data if the primary distribution environment is compromised.</t>
+          <t>Translation of one form of Location into another.</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>- The emphasis is on the ability to retrieve a copy of the entire EO Collection on demand if the original data is lost or compromised.</t>
+          <t>- Geocoding usually refers to the translation of "address" or "intersection" to "direct Position." Many service providers also include a "reverse geocoding" interface to their geocoder, thus extending the definition of the service as a general translator of Location. Because routing services use internal Location encodings not usually available to others, a geocoder is an integral part of the internals of such a service.</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- ISO 19133:2005; https://www.iso.org/standard/32551.html</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
@@ -5347,42 +5371,44 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Temporal Resolution</t>
+          <t>Georectifying</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>- core
-description: Observation or model output representing regular intervals, specifying the length of the interval that determines the smallest event or process that can be resolved.</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr"/>
+description: Correcting for positional displacement with respect to the surface of the Earth.</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Orthorectifying</t>
+        </is>
+      </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Observation or model output representing regular intervals, specifying the length of the interval that determines the smallest event or Process that can be resolved (e.g., the Period between observations, the time steps in a model).</t>
+          <t>Correcting for positional displacement with respect to the surface of the Earth.</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>- WIGOS 2019 distinguishes between sampling time Period, as the Period over which a Measurement is taken, and temporal sampling interval as the time Period between the beginning of consecutive sampling periods. Temporal Resolution in this Glossary is equivalent to sampling time Period as used by WIGOS.</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>| Entry format example | Valid unit                     |
-|----------------------|-------------------------------|
-| 1 s, 2 h, 1 m        | second, hour, day, month, year |</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr"/>
+          <t>- Source: ISO 19115-2:2019, 3.11; ISO 19115-2:2009(E); https://www.iso.org/standard/67039.html, modified</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>The correction of sample locations to achieve some sort of geometric regularity, e.g., a regular 2D geographic grid.</t>
+        </is>
+      </c>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
@@ -5399,26 +5425,26 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Place</t>
+          <t>Data Licencing</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>- base
-description: Part of any space referenced by an identifier.</t>
+          <t>- core
+description: Legal instrument by which a copyright holder may grant rights over the protected work.</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Part of any space referenced by an identifier.</t>
+          <t>Legal instrument by which a copyright holder may grant rights over the protected work. Data and content is open if it is subject to an explicitly-applied licence that conforms to the Open Definition. A range of standard open licences are available, such as the Creative Commons CC-BY licence, which requires only attribution.</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>- ISO 19155:2012, 4.8</t>
+          <t>- CEOS Wiki</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
@@ -5441,45 +5467,36 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Ancillary Data</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>- core
-- approved</t>
+          <t>- base
+description: Particular era or span of time.</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Data acquired on the same platform but not obtained from the main Sensor itself (usually provided as part of Level 0 Data), with the primary purpose of serving the processing of main instrument Data (e.g. Position and velocity of platform).</t>
+          <t>Particular era or span of time.</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>This can be divided into data referred to as spacecraft 'engineering', 'core housekeeping' or 'subsystem' data obtained from other parts of the platform, and includes parameters such as orbit position and velocity, attitude and its range of change, time, temperatures, pressures, jet firings, water dumps, internally produced magnetic fields, and other environmental measurements. Ancillary refers to data that exist purely to serve the data processing.</t>
+          <t>- Periods are intervals named with a Period Identifier.</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>- ESA/CEOS?, modified
-- EO Data Stewardship Glossary</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Data other than instrument measurements, originating in the instrument itself or from the satellite, required to perform processing of the Data. Includes orbit Data, attitude Data, time Information, and spacecraft engineering Data, Calibration Data, Data quality Information, and Data from other instruments or earth system models.</t>
-        </is>
-      </c>
+          <t>- ISO 19170:2021</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>- CEOS-ARD PFS template 20220302</t>
-        </is>
-      </c>
+      <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
@@ -5496,31 +5513,26 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Collection Upgrade</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>- controversial
-description: Act of determining the Value of a Property by interacting in a reproducible way with the Phenomenon using a Sensor.</t>
+          <t>- core
+- approved</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Act of determining the Value of a Property by interacting in a reproducible way with the Phenomenon using a Sensor.</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>- The result of an Observation is a Value complemented by an Uncertainty, often itself being referred to as 'observation'.
-- An Observation result represents a Sample of the Phenomenon (otherwise it would be identical with the Phenomenon).</t>
-        </is>
-      </c>
+          <t>New and improved major version of all products within a collection due to comprehensive reprocessing.</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
@@ -5543,31 +5555,30 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Grid</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>- core
-description: Network composed of two or more sets of curves in which the members of each set intersect the members of the other sets in an algorithmic way.</t>
+          <t>- base
+description: Abstraction of real-world phenomena.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Network composed of two or more sets of curves in which the members of each set intersect the members of the other sets in an algorithmic way.</t>
+          <t>Abstraction of real-world phenomena.</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>- The curves partition a space into grid cells or zones.
-- The intersection points of the curves are called nodes.</t>
+          <t>- A feature may occur as a type or an instance.</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>- ISO 19123:2005, 4.1.23; Note 1 modified; Note 2 added</t>
+          <t>- ISO 19101-1:2014, 4.1.11, modified</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
@@ -5590,44 +5601,36 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>Custodian</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>- core
-description: Entity (person, organization, institution, etc.) that is requesting data or information with certain characteristics described by needs and/or requirements.</t>
+description: Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>In the context of the KCEO, entity (person, organization, institution, etc.) that is requesting data or information with certain characteristics described by needs and/or requirements.</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr"/>
+          <t>Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>- See also Steward.</t>
+        </is>
+      </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>External person, institution or system that consumes provided services.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>- Includes Data Access or Science and Service Exploitation Platforms provided by a payload data ground segment.</t>
-        </is>
-      </c>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>- EO Data Stewardship Glossary</t>
-        </is>
-      </c>
+      <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
@@ -5644,35 +5647,26 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Remote Sensing</t>
+          <t>Anthroposphere</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>- controversial
-description: Type of Observation performed at a significant distance from a Phenomenon.</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Remote Observation</t>
-        </is>
-      </c>
+          <t>- core
+- approved</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Type of Observation performed at a significant distance from a Phenomenon.</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>- 'Significant' in this context means that the distance has, or may have, a non-negligible impact on the Value of the Property observed.
-- The effect of the distance on the acquired data is the main distinction criterion between 'remote' and 'in-situ' observations.</t>
-        </is>
-      </c>
+          <t>One of the Earth spheres consisting predominantly of matter processed by humans, such as construction wood, bricks, concrete, asphalt, glass, or plastics.</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
@@ -5695,37 +5689,44 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Earth Observation Product</t>
+          <t>User</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>- core
-description: Direct output from standardized satellite data processing chains (indicative levels 2 and 3), representing fundamental geophysical and biophysical variables.</t>
+description: Entity (person, organization, institution, etc.) that is requesting data or information with certain characteristics described by needs and/or requirements.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Direct output from standardized satellite data processing chains (indicative levels 2 and 3), representing fundamental geophysical and biophysical variables. These products demonstrate direct Traceability to original satellite measurements through rigorous Calibration and Validation processes. The processing methodology prioritizes the conversion of raw sensor data into quantifiable physical measurements, maintaining strict adherence to standardized processing protocols and Validation requirements.</t>
+          <t>In the context of the KCEO, entity (person, organization, institution, etc.) that is requesting data or information with certain characteristics described by needs and/or requirements.</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>- Soil moisture from microwave sensors
-- Forest canopy height from LiDAR data</t>
-        </is>
-      </c>
+      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
           <t>- KCEO</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>External person, institution or system that consumes provided services.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>- Includes Data Access or Science and Service Exploitation Platforms provided by a payload data ground segment.</t>
+        </is>
+      </c>
       <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>- EO Data Stewardship Glossary</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
@@ -5742,30 +5743,30 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Trait</t>
+          <t>Steward</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>- base
-description: Characteristic belonging to an entity and referenced by an identifier.</t>
+          <t>- core
+description: Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Characteristic belonging to an entity and referenced by an identifier.</t>
+          <t>Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>- Traits can be objective (inherent?) in which case they are also observable and called properties. Traits which are not observable (directly or indirectly) need to be assigned.</t>
+          <t>- See also Custodian.</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>- Based on ISO 19143:2010, 4.21, ISO/IEC 2382:2015, 2121440, significantly modified, Note 1 added</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
@@ -5788,30 +5789,23 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Time of Year</t>
+          <t>Temporal Consistency</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>- core
-description: Time of the year at which the variable is observed or simulated by a model.</t>
+description: Condition where the temporal statistical properties of the sample depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Time of the year at which the variable is observed or simulated by a model.</t>
+          <t>Condition where the temporal statistical properties of the Sample depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>| Type      | Entry format example | Valid unit     |
-|-----------|----------------------|----------------|
-| timestamp | m/d                  | Not Applicable |
-| timerange | m/d - m/d            | Not Applicable |</t>
-        </is>
-      </c>
+      <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
           <t>- KCEO</t>
@@ -5837,31 +5831,27 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>In-Situ Observation</t>
+          <t>Geospatial Data</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>- controversial
-description: Observations performed in the same Place where a Phenomenon occurs, normally without isolating it from other systems or altering its pre-Observation state.</t>
+          <t>- core
+description: Data consisting of, derived from, or relating to information that is directly linked to specific geographical locations.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Observations performed in the same Place where a Phenomenon occurs, normally without isolating it from other systems (its environment) or altering its pre-Observation state.</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>- The main Characteristic of such observations is that distance has no or only negligible (within Uncertainty) influence on the Value of the Property observed. In-Situ Observations therefore often require either direct physical contact or small distances between a Sensor and the observed Phenomenon.
-- Observations not fulfilling these conditions are considered Remote Sensing.</t>
-        </is>
-      </c>
+          <t>Data consisting of, derived from, or relating to information that is directly linked to specific geographical locations.</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- https://www.merriam-webster.com/dictionary/geospatial
+- https://isotc211.geolexica.org/Concepts/202/, accessed 20221010</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
@@ -5884,56 +5874,36 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Characteristic</t>
+          <t>Stability</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>- base
-- approved</t>
+          <t>- core
+description: Maximum acceptable change in Uncertainty per decade.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Distinguishing Feature.</t>
+          <t>Maximum acceptable change in Uncertainty per decade.</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>- A Characteristic can be inherent or assigned.
-- A Characteristic can be qualitative or quantitative.
-- There are various classes of Characteristics, such as the following:
-  - physical (e.g. mechanical, electrical, chemical, biological);
-  - sensory (e.g. relating to smell, touch, taste, sight, hearing);
-  - behavioural (e.g. courtesy, honesty, veracity);
-  - temporal (e.g. punctuality, reliability, availability);
-  - ergonomic (e.g. physiological characteristic or related to human safety);
-  - functional (e.g. maximum speed of an aircraft).</t>
+          <t>- GCOS uses bias or systematic errors instead of Uncertainty.</t>
         </is>
       </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>- ISO 9000:2005, 3.5.1</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Abstraction of a Property of an Object or of a set of objects.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>- Characteristics are used for describing Concepts.</t>
-        </is>
-      </c>
+          <t>- Modified from GCOS 2022</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>- ISO 1087-1:2000, 3.2.4; ISO 19146:2010(E); https://www.iso.org/standard/20057.html</t>
-        </is>
-      </c>
+      <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
@@ -5950,30 +5920,26 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Measurement</t>
+          <t>Property</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>- core
-description: Observation of a Quantity.</t>
+          <t>- base
+description: Observable Trait.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Observation of a Quantity.</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>- The Process of collecting a measurement is called measuring.</t>
-        </is>
-      </c>
+          <t>Observable Trait.</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>- GEOGlos (VIM ?, modified)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
@@ -5996,31 +5962,30 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Preservation</t>
+          <t>Geographic Data</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>- core
-description: Processes and operations used to ensure data technical and intellectual survival through time.</t>
+description: Data with implicit or explicit reference to a Location relative to the Earth.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Processes and operations used to ensure data technical and intellectual survival through time.</t>
+          <t>Data with implicit or explicit reference to a Location relative to the Earth.</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>- Grants data integrity, discoverability and accessibility, and facilitates its (re-)use in the long term.
-- Preservation is one of the tasks of data curation.</t>
+          <t>- Geographic Information is also used as a term for information concerning phenomena implicitly or explicitly associated with a Location relative to the Earth.</t>
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- ISO 19109:2015, 4.13; ISO 19109:2005</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
@@ -6043,62 +6008,111 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Provisional Product</t>
+          <t>Uncertainty</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>- core
-description: Products in a research and development phase not yet published into a standardized collection.</t>
+description: Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Products in a research and development phase not yet published into a standardized collection.</t>
+          <t>Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
+          <t>- GUM</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Non-negative parameter, associated with data, which characterizes the dispersion of the values of a Trait that could reasonably be attributed to a Phenomenon by means of sensing or modelling.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>- In case of quantitative (continuous) data the uncertainty may be, for example, a standard deviation (or a given multiple of it), or the half-width of an interval having a stated level of confidence (see e.g. Standard and Expanded Uncertainty).
+- For qualitative (categorical?) data, uncertainty may be expressed by commission and omission ('confusion matrix') or overall errors.</t>
+        </is>
+      </c>
       <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>- Modified from GUM, VIM4:3.1, FIDUCEO, Notes added</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Measure of the spread of the distribution of possible values.</t>
+        </is>
+      </c>
       <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr"/>
-      <c r="P122" t="inlineStr"/>
-      <c r="Q122" t="inlineStr"/>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>- [FIDUCEO Glossary](https://research.reading.ac.uk/fiduceo/glossary/), VIM?, modified</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Parameter, associated with the result of measurement, that characterizes the dispersion of values that could reasonably be attributed to the measurand.</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>- When the quality of accuracy or precision of measured values, such as coordinates, is to be characterized quantitatively, the quality parameter is an estimate of the uncertainty of the measurement results. Because accuracy is a qualitative concept, one should not use it quantitatively, that is associate numbers with it; numbers should be associated with measures of uncertainty instead.</t>
+        </is>
+      </c>
       <c r="R122" t="inlineStr"/>
-      <c r="S122" t="inlineStr"/>
-      <c r="T122" t="inlineStr"/>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>- ISO 19116:2004(E)</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Parameter characterizing the dispersion of the values being attributed to a measurand, based on the information used.</t>
+        </is>
+      </c>
       <c r="U122" t="inlineStr"/>
       <c r="V122" t="inlineStr"/>
-      <c r="W122" t="inlineStr"/>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>- VIM4: 3.1</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>User Interface</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>- core
-description: ""</t>
+description: Set of all the components of an interactive system that provide information and controls for the user to accomplish specific tasks with the interactive system.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Set of all the components of an interactive system that provide information and controls for the User to accomplish specific tasks with the interactive system.</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>- ISO 9241-110:2020, 3.10</t>
+        </is>
+      </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
@@ -6119,36 +6133,56 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Instrument Data</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>- high-impact
-description: Deliberate system of guidelines to guide decisions and achieve rational outcomes, implemented as a procedure or protocol and typically promulgated through official written documents.</t>
+          <t>- core
+description: Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Deliberate system of guidelines to guide decisions and achieve rational outcomes. Statement of intent implemented as a procedure or protocol. Typically promulgated through official written documents.</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr"/>
+          <t>Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>- These data consist of instrument science and engineering data, and possibly ancillary data. Instrument engineering data is produced by engineering sensor(s) of an instrument, used either for operating the instrument or for processing the science data generated by the instrument. Instrument science data is produced by the science sensor(s) of an instrument, usually constituting the basic reason for existence of an instrument.</t>
+        </is>
+      </c>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr"/>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Data created by an instrument including scientific measurements and any engineering or ancillary data which may be included in the data packets.</t>
+        </is>
+      </c>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Data produced and transmitted by the science and engineering sensors of an instrument, and, in the spacecraft environment, any additional data packaged with the instrument's sensor data by virtue of services provided.</t>
+        </is>
+      </c>
       <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr"/>
       <c r="Q124" t="inlineStr"/>
       <c r="R124" t="inlineStr"/>
@@ -6161,30 +6195,38 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Geographic Identifier</t>
+          <t>Measurand</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>- core
-description: Spatial reference in the form of a label or code that identifies a Location.</t>
+description: Particular Quantity subject to Measurement.</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Spatial reference in the form of a label or code that identifies a Location.</t>
+          <t>Particular Quantity subject to Measurement.</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>- "Spain" is an example of a label (country name); "SW1-3AD" is an example of a code (postcode).</t>
+          <t>| Step | Process description |
+| :----- | :--------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------- |
+| (Raw) | The complete and unaltered/unprocessed set of Data acquired by one or several sensors on a platform |
+| M/0 uncalibrated | Unaltered/unprocessed Level 0 (main) Sensor Data annotated with processed Ancillary Data and supplemented by Auxiliary Data (including radiometric and geometric Calibration coefficients and geo-referencing parameters) allowing further processing to higher Levels. |
+| M/1 Sensor-calibrated | Level M/0 Sensor Data which have been calibrated (ideally traceable to SI) and spatially aligned (co-located, eventually co-gridded) to represent at-Sensor measurements (Value and Uncertainty) in Sensor nominal spatiotemporal sampling, supplemented by appropriate ancillary data. |
+| M/2 target-calibrated | Level M/1 Data processed to represent geophysical Property values (and uncertainties) for a specified target (Object, Feature of interest, e.g. surface reflectance, apparent temperature) derived from M/1 Sensor Data, as much as possible maintaining the sensors nominal spatial and temporal sampling (Observation preserving). |
+| M/3 homogenised | Level M/1 or M/2 Data which have been generalised and integrated across one or several platforms and acquisitions to achieve an increased, more regular or in any other form enhanced spatial or temporal coverage in which states geophysical values agnostic of the originally acquiring Sensor and Observation condition and thus directly comparable. This homogenisation and fusion may include measurand re-Calibration to external standards and references including use of modelling, aggregation and interpolation. |
+| M/4 derived/inferred | Model output or results from analyses of Level M/3 (or lower level) Data i.e., attributes that might not be directly observable by the Sensor(s) but are derived from observations in combination with other external incl. non-observational Data using techniques like modelling or machine learning (AI). |
+From http://doi.org/10.2760/46796</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>- ISO 19112:2019, 3.1.2</t>
+          <t>- VIM: 1993, 2.6</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
@@ -6207,37 +6249,26 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Earth Spheres</t>
+          <t>Policy Target</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>- core
-description: Spheres dividing planet Earth into subsystems, which are collectives of (physical) matter sharing specific traits.</t>
+          <t>- high-impact
+description: Specific level or rate set for the Policy Objective.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Spheres dividing planet Earth into subsystems, which are collectives of (physical) matter sharing specific traits.</t>
+          <t>Specific level or rate set for the Policy Objective.</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>- Atmosphere
-- Hydrosphere
-- Cryosphere
-- Biosphere
-- Lithosphere
-- Anthroposphere</t>
-        </is>
-      </c>
+      <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>- Hugget, R., et al., 2024, DOI: 10.1177/03091333241275465
-- Guth, P., et al., 2021, https://doi.org/10.3390/rs13183581
-- Martin, Y.E., et al., 2012</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
@@ -6260,26 +6291,35 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Deprecated Product</t>
+          <t>Spatial Extent</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>- core
-description: Products and collections that have been superseded by a newer version and are still available, but whose use is discouraged since they will be decommissioned in the future.</t>
+description: Zone or region of space described by a geographic identifier in the form of a label or code, or by a bounding box, representing the maximum spatial boundary within which the user is requesting data.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Products and collections that have been superseded by a newer version and are still available, but whose use is discouraged since they will be decommissioned in the future.</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
+          <t>Zone or region of space described by a geographic identifier in the form of a label or code, or by a bounding box. Represents the maximum extent (the spatial boundary or limits) within which the User is requesting data.
+The attribute represents the maximum spatial extent of the AOI, and in case the AOI is made of many discontinuous zones then it represents the maximum extent of the union of all the zones.</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>- WIGOS metadata standard defines it as the typical spatial georeferenced volume covered by the observations.</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>- If a User is requesting information about degradation of African protected sites, then the AOIs are the protected sites, and the spatial extent is the African continent.</t>
+        </is>
+      </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- Adapted from ISO 19170-1:2021</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
@@ -6302,26 +6342,26 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Replicability</t>
+          <t>Provisional Product</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>- core
-description: Property enabling other researchers to conduct an independent study with different data and similar but not identical methods, yet arriving at results that confirm the original study's hypothesis.</t>
+description: Products in a research and development phase not yet published into a standardized collection.</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Property enabling other researchers to conduct an independent study with different data and similar but not identical methods, yet arriving at results that confirm the original study's hypothesis.</t>
+          <t>Products in a research and development phase not yet published into a standardized collection.</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>- Craglia, M., et al. (2018).</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
@@ -6344,30 +6384,26 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>- base
-description: Abstraction of real-world phenomena.</t>
+description: Entity with a well-defined boundary and identity that encapsulates state and behaviour.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Abstraction of real-world phenomena.</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>- A feature may occur as a type or an instance.</t>
-        </is>
-      </c>
+          <t>Entity with a well-defined boundary and identity that encapsulates state and behaviour.</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>- ISO 19101-1:2014, 4.1.11, modified</t>
+          <t>- ISO/IEC 19501:2005</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
@@ -6390,30 +6426,26 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Final Product Version</t>
+          <t>Forecast Range</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>- core
-description: Product within an EO Collection that is not expected to be updated.</t>
+description: The forecast period.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Product within an EO Collection that is not expected to be updated.</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>- In its production, all of the prerequisite auxiliary data were used as input.</t>
-        </is>
-      </c>
+          <t>The forecast period.</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
@@ -6436,35 +6468,26 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Spatial Extent</t>
+          <t>Policy Milestone</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>- core
-description: Zone or region of space described by a geographic identifier in the form of a label or code, or by a bounding box, representing the maximum spatial boundary within which the user is requesting data.</t>
+          <t>- high-impact
+description: Markers of significant progress in addressing specific issues, or crucial decision points where significant choices are made within a policy process.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Zone or region of space described by a geographic identifier in the form of a label or code, or by a bounding box. Represents the maximum extent (the spatial boundary or limits) within which the User is requesting data.
-The attribute represents the maximum spatial extent of the AOI, and in case the AOI is made of many discontinuous zones then it represents the maximum extent of the union of all the zones.</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>- WIGOS metadata standard defines it as the typical spatial georeferenced volume covered by the observations.</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>- If a User is requesting information about degradation of African protected sites, then the AOIs are the protected sites, and the spatial extent is the African continent.</t>
-        </is>
-      </c>
+          <t>Markers of significant progress in addressing specific issues, or crucial decision points where significant choices are made. Concrete examples include: policy planning and proposing, impact assessment, implementation, or implementation cycles (e.g., Water Framework Directive, Marine Strategy Framework Directive), achievement of Policy Objectives and Policy Targets, and evaluating and improving existing laws.</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>- Adapted from ISO 19170-1:2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
@@ -6487,26 +6510,30 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Policy Cycle</t>
+          <t>Dwell Time</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>- high-impact
-description: Well-established concept typically taught as the rational model of policy decision-making, representing an idealised view of the policy process.</t>
+          <t>- core
+description: Time that an antenna beam spends on a target.</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Well-established concept, typically taught as the rational model of policy decision-making. Idealised view of the policy process.</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
+          <t>Time that an antenna beam spends on a target.</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>- In the context of radar sensing.</t>
+        </is>
+      </c>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>- [ESA/CEOS?, modified](https://digital-strategy.ec.europa.eu/en/library/quality-public-administration-toolbox-practitioners)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
@@ -6529,26 +6556,26 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Data Licencing</t>
+          <t>Location Error</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>- core
-description: Legal instrument by which a copyright holder may grant rights over the protected work.</t>
+description: Measure of the agreement between the represented Location of an Object and the true Location.</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Legal instrument by which a copyright holder may grant rights over the protected work. Data and content is open if it is subject to an explicitly-applied licence that conforms to the Open Definition. A range of standard open licences are available, such as the Creative Commons CC-BY licence, which requires only attribution.</t>
+          <t>Measure of the agreement between the represented Location of an Object and the true Location.</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>- CEOS Wiki</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
@@ -6571,26 +6598,22 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Representativeness</t>
+          <t>Expanded Uncertainty</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
           <t>- core
-description: Quality or characteristic of a measurement or observation to accurately represent a specific geographic location, time period, or environmental condition.</t>
+description: Standard Uncertainty multiplied by a coverage factor k, chosen to obtain a desired level of confidence.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Quality or characteristic of a measurement or Observation to accurately represent a specific geographic location, time Period, or environmental condition.</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>- WIGOS metadata standard defines representativeness as the extent of the region around the Observation of which it is representative.</t>
-        </is>
-      </c>
+          <t>Standard Uncertainty multiplied by a coverage factor, k. The coverage factor is chosen to obtain a desired level of confidence. Most commonly a 95% confidence interval is chosen. For a Gaussian distribution, this is achieved with a coverage factor k = 2. (Note that strictly this provides a 95.45% confidence interval.)</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
@@ -6617,28 +6640,20 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Reproducibility</t>
+          <t>Environmental Process</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>- core
-description: Concerned with the validity of the results of a particular study, enabling readers to check whether results have been manipulated by reproducing exactly the same study using the same data and methods.</t>
+description: ""</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>Concerned with the validity of the results of a particular study, i.e., the possibility for readers to check whether results have been manipulated, by reproducing exactly the same study using the same data and methods.</t>
-        </is>
-      </c>
+      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>- Ostermann and Granell (2015)</t>
-        </is>
-      </c>
+      <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
@@ -6659,30 +6674,30 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Custodian</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>- core
-description: Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
+          <t>- controversial
+description: An, often numeric, theoretical (or otherwise abstract) representation of an Entity intended to generate Data describing one or more of its traits.</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
+          <t>An, often numeric, theoretical (or otherwise abstract) representation of an Entity intended to generate Data describing one or more of its traits (as a result of pre-set conditions).</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>- See also Steward.</t>
+          <t>- The Process of generating Data using a model is called modelling.</t>
         </is>
       </c>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
@@ -6705,26 +6720,26 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Geosphere</t>
+          <t>Classification System</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>- core
-description: The masses of minerals that constitute planet Earth.</t>
+- approved</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>The masses of minerals that constitute planet Earth.</t>
+          <t>Nomenclature used to classify Information into categorical thematic classes (e.g., EUNIS, MAES ecosystems, Corine Land Cover, LCCS).</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
@@ -6747,30 +6762,26 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Cell</t>
+          <t>Spectral Bandwidth</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+description: Range of the Spectral Band.</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Spatial, spatio-temporal zone or temporal unit of geometry with dimensionality greater than 0, associated with a zone.</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>- Cells are the unit of geometry in a DGGS, and the geometry of the region of space-time occupied by a zone is a Cell.</t>
-        </is>
-      </c>
+          <t>Range of the Spectral Band.</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>- ISO 19170:2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
@@ -6793,30 +6804,26 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Geographic Coordinate Reference System</t>
+          <t>Collection</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>- core
-description: Coordinate Reference System (CRS) that has a geodetic Reference frame and an ellipsoidal coordinate system.</t>
+- approved</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Coordinate Reference System (CRS) that has a geodetic Reference frame and an ellipsoidal coordinate system.</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>- Also known as geographic CRS.</t>
-        </is>
-      </c>
+          <t>Group of products that have been processed using a consistent radiometric calibration, geometric registration base, data/metadata format, and version of processing algorithms.</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>- ISO 19111:2019, 3.1.35</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
@@ -6839,34 +6846,20 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Vertical Levels</t>
+          <t>Continuity</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>- core
-description: Levels of a vertical discretization, e.g. pressure levels in an atmospheric model reanalysis or height levels in a forest biomass EO product.</t>
+  - to be defined</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>Levels of a vertical discretization. Examples may be pressure levels in an atmospheric model reanalysis or height levels in a forest biomass EO product.</t>
-        </is>
-      </c>
+      <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>| Entry format example                | Valid unit           |
-|------------------------------------|----------------------|
-| 1, 5, 10 meter; 1000, 850, 500 hPa | meter, hPa, unitless |</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
@@ -6887,26 +6880,26 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Anthroposphere</t>
+          <t>Policy File</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>- core
-- approved</t>
+          <t>- high-impact
+description: Policy documents that represent the official written reference for a given Policy.</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>One of the Earth spheres consisting predominantly of matter processed by humans, such as construction wood, bricks, concrete, asphalt, glass, or plastics.</t>
+          <t>Policy documents that represent the official written reference for a given Policy.</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
@@ -6929,26 +6922,22 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Dwell Time</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>- core
-description: Time that an antenna beam spends on a target.</t>
+          <t>- high-impact
+description: Deliberate system of guidelines to guide decisions and achieve rational outcomes, implemented as a procedure or protocol and typically promulgated through official written documents.</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Time that an antenna beam spends on a target.</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>- In the context of radar sensing.</t>
-        </is>
-      </c>
+          <t>Deliberate system of guidelines to guide decisions and achieve rational outcomes. Statement of intent implemented as a procedure or protocol. Typically promulgated through official written documents.</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
@@ -6975,33 +6964,30 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Duration</t>
+          <t>Geographic Identifier</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
           <t>- core
-description: Non-negative interval Quantity of time equal to the difference between the final and initial instants of a time interval.</t>
+description: Spatial reference in the form of a label or code that identifies a Location.</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Non-negative interval Quantity of time equal to the difference between the final and initial instants of a time interval.</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>- Duration is one of the base quantities in the International System of Quantities (ISQ) on which the International System of Units (SI) is based. The term "time" instead of "duration" is often used in this context and also for an infinitesimal duration.
-- For the term "duration", expressions such as "time" or "time interval" are often used, but the term "time" is not recommended in this sense and the term "time interval" is deprecated in this sense to avoid confusion with the concept of "time interval".
-- The exact duration of a time scale unit depends on the time scale used. For example, the durations of a year, month, week, day, hour or minute may depend on when they occur (in a Gregorian calendar, a calendar month can have a duration of 28, 29, 30, or 31 days; in a 24-hour clock, a clock minute can have a duration of 59, 60, or 61 seconds, etc.). Therefore, the exact duration can only be evaluated if the exact duration of each is known.
-- This definition is closely related to NOTE 1 of the terminological entry "duration" in IEC 60050-113:2011, 113-01-13.</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr"/>
+          <t>Spatial reference in the form of a label or code that identifies a Location.</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>- "Spain" is an example of a label (country name); "SW1-3AD" is an example of a code (postcode).</t>
+        </is>
+      </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>- ISO 8601-1:2019, 3.1.1.8</t>
+          <t>- ISO 19112:2019, 3.1.2</t>
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
@@ -7024,26 +7010,31 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Lead Time</t>
+          <t>Earth Observation</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>- core
-description: Minimum time of interval between an Observation being tasked and being performed.</t>
+          <t>- high-impact
+description: Science domain dealing with technologies and methods of collecting and analyzing observations about the different Earth spheres.</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Minimum time of interval between an Observation being tasked and being performed.</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr"/>
+          <t>Science domain dealing with technologies and methods of collecting and analyzing observations about the different Earth spheres.</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>- Earth Observation (EO) can be categorised by location of the sensor into space-borne, air-borne, sea-borne, ground-based, underwater and underground EO.
+- Earth Observation (EO) includes Remote Sensing, such as satellite imagery, as well as in-situ observations, e.g., with ground-based devices.</t>
+        </is>
+      </c>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Modified GEO definition [GEO (earthobservations.org)](https://earthobservations.org/resources#key)</t>
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
@@ -7066,30 +7057,26 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>EO Space Data</t>
+          <t>Data Format</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>- core
-description: Earth Observation data generated by spaceborne missions or instruments owned by public or private organizations.</t>
+description: Structured Data that is machine readable and can be automatically read and processed by a computer, such as HDF, NetCDF, CSV, JSON, XML, etc.</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Earth Observation data generated by spaceborne missions or instruments owned by public or private organizations.</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>- See also Instrument data.</t>
-        </is>
-      </c>
+          <t>Structured Data that is machine readable and can be automatically read and processed by a computer, such as HDF, NetCDF, CSV, JSON, XML, etc.</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- CEOS Wiki</t>
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
@@ -7112,30 +7099,26 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Spatial Completeness</t>
+          <t>Geolocation Information</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>- core
-description: Presence or absence of gaps, which are missing values in an otherwise continuous spatial data series.</t>
+description: Information used to determine geographic Location.</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Presence or absence of gaps, which are missing values in an otherwise continuous spatial data series.</t>
+          <t>Information used to determine geographic Location.</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>- Surface soil moisture retrieved from microwave satellite sensors may present gaps in mountainous terrains.</t>
-        </is>
-      </c>
+      <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO 19130-1:2018, 3.34</t>
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
@@ -7158,31 +7141,26 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Derivative Product</t>
+          <t>Cryosphere</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
           <t>- core
-description: Product additionally processed from baseline or unenhanced mission data.</t>
+- approved</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Product additionally processed from baseline or unenhanced mission data.</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>- Generally either a compilation of time-series data (e.g., all time, annual, monthly or seasonal summary data, &gt; Level 3) or thematic versions of each individual data tile of baseline data.
-- Derived products are citable via a Digital Object Identifier (DOI).</t>
-        </is>
-      </c>
+          <t>Masses of frozen water, such as sea ice, ice shields, glaciers, and snow.</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
@@ -7205,26 +7183,18 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Geopositioning</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>- core
-description: Determination of the geographic Position of a point (0D) or linear (1D) Feature.</t>
+description: ""</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>Determination of the geographic Position of a point (0D) or linear (1D) Feature.</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>- Modified from: ISO 19130-1:2018, 3.36</t>
-        </is>
-      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr"/>
@@ -7247,26 +7217,36 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Spectral Band</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>- core
-description: Part of the electromagnetic spectrum of specific wavelengths, in remote sensing usually described by central wavelength and bandwidth.</t>
+          <t>- base
+description: Particular Place referenced by an identifier.</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Part of the electromagnetic spectrum of specific wavelengths. In Remote Sensing, usually described by central wavelength and bandwidth.</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
+          <t>Particular Place referenced by an identifier.</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>- While a (geo)location identifies a geographic Place, it may also be associated with objects other than the Earth.
+- While Location in principle covers 0- to 3-dimensional spatial geometries, it should not be used for 0- and 1-dimensional geometries (positions and paths).</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>- Madrid
+- California</t>
+        </is>
+      </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [ISO 19112:2019](https://www.iso.org/standard/70742.html), (E), 3.1.3, modified, note 2 added</t>
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
@@ -7289,20 +7269,34 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Consistency</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>- core
-  - to be defined</t>
+description: Device or instrument suited (through physical/chemical interaction) to measure one or more properties of a Phenomenon and thus collect factual/objective data.</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
-      <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Device or instrument suited (through physical/chemical interaction) to measure one or more properties of a Phenomenon and thus collect factual/objective data.</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>- Sensing is therefore a synonym for Observation (the Process).
+- As by their definition, sensors perform sampling.
+- Sensors used to obtain measurements must be calibrated and provide uncertainties.</t>
+        </is>
+      </c>
       <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr"/>
@@ -7323,30 +7317,36 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Geographic Data</t>
+          <t>Temporal Resolution</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
           <t>- core
-description: Data with implicit or explicit reference to a Location relative to the Earth.</t>
+description: Observation or model output representing regular intervals, specifying the length of the interval that determines the smallest event or process that can be resolved.</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Data with implicit or explicit reference to a Location relative to the Earth.</t>
+          <t>Observation or model output representing regular intervals, specifying the length of the interval that determines the smallest event or Process that can be resolved (e.g., the Period between observations, the time steps in a model).</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>- Geographic Information is also used as a term for information concerning phenomena implicitly or explicitly associated with a Location relative to the Earth.</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr"/>
+          <t>- WIGOS 2019 distinguishes between sampling time Period, as the Period over which a Measurement is taken, and temporal sampling interval as the time Period between the beginning of consecutive sampling periods. Temporal Resolution in this Glossary is equivalent to sampling time Period as used by WIGOS.</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>| Entry format example | Valid unit                     |
+|----------------------|-------------------------------|
+| 1 s, 2 h, 1 m        | second, hour, day, month, year |</t>
+        </is>
+      </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>- ISO 19109:2015, 4.13; ISO 19109:2005</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
@@ -7369,26 +7369,26 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Business Continuity</t>
+          <t>Policy Cycle</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>- core
-- approved</t>
+          <t>- high-impact
+description: Well-established concept typically taught as the rational model of policy decision-making, representing an idealised view of the policy process.</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>An organisation's readiness to continue functioning during times of disruption.</t>
+          <t>Well-established concept, typically taught as the rational model of policy decision-making. Idealised view of the policy process.</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- [ESA/CEOS?, modified](https://digital-strategy.ec.europa.eu/en/library/quality-public-administration-toolbox-practitioners)</t>
         </is>
       </c>
       <c r="H152" t="inlineStr"/>

--- a/exports/xlsx/terms.xlsx
+++ b/exports/xlsx/terms.xlsx
@@ -542,6 +542,7 @@
       <c r="B2" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Regular grid based on a Geographic Coordinate Reference System (CRS).</t>
         </is>
       </c>
@@ -584,6 +585,7 @@
       <c r="B3" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Quality or characteristic of a measurement or observation to accurately represent a specific geographic location, time period, or environmental condition.</t>
         </is>
       </c>
@@ -630,6 +632,7 @@
       <c r="B4" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Earth Observation data generated by spaceborne missions or instruments owned by public or private organizations.</t>
         </is>
       </c>
@@ -676,6 +679,7 @@
       <c r="B5" t="inlineStr">
         <is>
           <t>- core
+  - to be approved
 description: The smallest aggregation of data which is independently managed (i.e. described, inventoried, retrievable).</t>
         </is>
       </c>
@@ -722,6 +726,7 @@
       <c r="B6" t="inlineStr">
         <is>
           <t>- core
+- to be discussed
 description: Interval between successive observations.</t>
         </is>
       </c>
@@ -775,6 +780,7 @@
       <c r="B7" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Action of permanently and irrecoverably removing all copies of data held by an organization.</t>
         </is>
       </c>
@@ -817,6 +823,7 @@
       <c r="B8" t="inlineStr">
         <is>
           <t>- controversial
+- to be discussed
 description: Type of Observation performed at a significant distance from a Phenomenon.</t>
         </is>
       </c>
@@ -868,6 +875,7 @@
       <c r="B9" t="inlineStr">
         <is>
           <t>- high-impact
+  - to be discussed
 description: Data available for use with a specified (small and application dependent) latency, typically 3 hours for meteorological applications.</t>
         </is>
       </c>
@@ -910,6 +918,7 @@
       <c r="B10" t="inlineStr">
         <is>
           <t>- base
+- to be approved
 description: Value and possibly Uncertainty of a Trait of a specific Entity.</t>
         </is>
       </c>
@@ -972,6 +981,7 @@
       <c r="B11" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Coordinate Reference System (CRS) that has a geodetic Reference frame and an ellipsoidal coordinate system.</t>
         </is>
       </c>
@@ -1018,6 +1028,7 @@
       <c r="B12" t="inlineStr">
         <is>
           <t>- core
+  - to be approved
 description: The act of maintaining information in a correct and independently understandable form over the long term.</t>
         </is>
       </c>
@@ -1065,6 +1076,7 @@
       <c r="B13" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Processes and operations used to ensure data technical and intellectual survival through time.</t>
         </is>
       </c>
@@ -1112,6 +1124,7 @@
       <c r="B14" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Method of working with collections, similar to version control systems used in traditional software development but optimized to allow better processing of data and collaboration in data analytics and research contexts.</t>
         </is>
       </c>
@@ -1154,6 +1167,7 @@
       <c r="B15" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Level of categorical detail of information expressed by the number of classes.</t>
         </is>
       </c>
@@ -1196,7 +1210,7 @@
       <c r="B16" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+- to be discussed</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -1238,6 +1252,7 @@
       <c r="B17" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Property enabling other researchers to conduct an independent study with different data and similar but not identical methods, yet arriving at results that confirm the original study's hypothesis.</t>
         </is>
       </c>
@@ -1280,7 +1295,7 @@
       <c r="B18" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1326,6 +1341,7 @@
       <c r="B19" t="inlineStr">
         <is>
           <t>- core
+- to be discussed
 description: Uncertainty associated with the method of classification.</t>
         </is>
       </c>
@@ -1407,7 +1423,7 @@
       <c r="B21" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
@@ -1455,6 +1471,7 @@
       <c r="B22" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Frequency at which the product is available to users.</t>
         </is>
       </c>
@@ -1501,6 +1518,7 @@
       <c r="B23" t="inlineStr">
         <is>
           <t>- base
+- to be approved
 description: Something that has separate and distinct existence and objective or conceptual reality.</t>
         </is>
       </c>
@@ -1555,6 +1573,7 @@
       <c r="B24" t="inlineStr">
         <is>
           <t>- base
+- to be approved
 description: Part of any space referenced by an identifier.</t>
         </is>
       </c>
@@ -1597,6 +1616,7 @@
       <c r="B25" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Non-negative interval Quantity of time equal to the difference between the final and initial instants of a time interval.</t>
         </is>
       </c>
@@ -1646,6 +1666,7 @@
       <c r="B26" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Time of the day at which the variable or parameter is observed or simulated by a model.</t>
         </is>
       </c>
@@ -1699,6 +1720,7 @@
       <c r="B27" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Levels of a vertical discretization, e.g. pressure levels in an atmospheric model reanalysis or height levels in a forest biomass EO product.</t>
         </is>
       </c>
@@ -1747,6 +1769,7 @@
       <c r="B28" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Electronic data package distributable to users; content is derived from instrument data via processing involving ancillary and auxiliary data.</t>
         </is>
       </c>
@@ -1797,6 +1820,7 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>- base
+  - to be approved
 description: The result of organisation, interpretation, categorisation, classification, or some other form of processing of Data attaching to it a certain meaning that can be understood by the addressee.</t>
         </is>
       </c>
@@ -1843,6 +1867,7 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>- core
+  - to be approved
 description: The solid, inanimate outer layer of the Geosphere. For the purposes of Earth Observation, includes soils ('pedosphere').</t>
         </is>
       </c>
@@ -1885,7 +1910,7 @@
       <c r="B31" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -1974,6 +1999,7 @@
       <c r="B33" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Indicator providing sufficient information to allow all users to readily evaluate the fitness for purpose of the data or derived product.</t>
         </is>
       </c>
@@ -2016,6 +2042,7 @@
       <c r="B34" t="inlineStr">
         <is>
           <t>- base
+- to be approved
 description: Series of activities that interact to produce a result.</t>
         </is>
       </c>
@@ -2062,6 +2089,7 @@
       <c r="B35" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Standard deviation of the probability distribution describing the spread of possible values in quantitative/continuous data.</t>
         </is>
       </c>
@@ -2104,6 +2132,7 @@
       <c r="B36" t="inlineStr">
         <is>
           <t>- core
+  - to be approved
 description: The width of the smallest linear Feature that is still represented on a map.</t>
         </is>
       </c>
@@ -2146,6 +2175,7 @@
       <c r="B37" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Products and collections that have been superseded by a newer version and are still available, but whose use is discouraged since they will be decommissioned in the future.</t>
         </is>
       </c>
@@ -2188,6 +2218,7 @@
       <c r="B38" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Temporal reference in the form of a label or code that identifies a Period.</t>
         </is>
       </c>
@@ -2234,6 +2265,7 @@
       <c r="B39" t="inlineStr">
         <is>
           <t>- core
+  - to be approved
 description: Minimum time of interval between an Observation being tasked and being performed.</t>
         </is>
       </c>
@@ -2276,7 +2308,8 @@
       <c r="B40" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+- source missing
+- to be discussed</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -2314,7 +2347,7 @@
       <c r="B41" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -2356,6 +2389,7 @@
       <c r="B42" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Smallest spatial object of interest that may be used for reporting and for which the information should be aggregated.</t>
         </is>
       </c>
@@ -2402,6 +2436,7 @@
       <c r="B43" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Data required for production of an EO Collection (e.g., unenhanced satellite mission data) as well as further processed Level-1 data, or any other pre-processed format meeting program requirements.</t>
         </is>
       </c>
@@ -2444,7 +2479,7 @@
       <c r="B44" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -2490,6 +2525,7 @@
       <c r="B45" t="inlineStr">
         <is>
           <t>- high-impact
+- to be discussed
 description: Process by which governments translate their political vision into programmes and actions to deliver outcomes — desired change in the real world.</t>
         </is>
       </c>
@@ -2532,6 +2568,7 @@
       <c r="B46" t="inlineStr">
         <is>
           <t>- base
+- to be discussed
 - controversial
 description: Place referenced by a single set of coordinates within a coordinate reference system.</t>
         </is>
@@ -2579,6 +2616,7 @@
       <c r="B47" t="inlineStr">
         <is>
           <t>- core
+  - to be approved
 description: The area of the smallest Feature that is still represented on a map.</t>
         </is>
       </c>
@@ -2621,6 +2659,7 @@
       <c r="B48" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Part of the electromagnetic spectrum of specific wavelengths, in remote sensing usually described by central wavelength and bandwidth.</t>
         </is>
       </c>
@@ -2663,6 +2702,7 @@
       <c r="B49" t="inlineStr">
         <is>
           <t>- core
+- to be discussed
 description: Determination of the geographic Position of a point (0D) or linear (1D) Feature.</t>
         </is>
       </c>
@@ -2705,7 +2745,7 @@
       <c r="B50" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -2747,6 +2787,7 @@
       <c r="B51" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Provision of objective evidence that a given item fulfils specified requirements.</t>
         </is>
       </c>
@@ -2812,6 +2853,7 @@
       <c r="B52" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Higher-level processing and integration output (indicative level 4 and beyond) that goes beyond basic data processing, often designed for policy or decision-making needs.</t>
         </is>
       </c>
@@ -2856,7 +2898,8 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>- core</t>
+          <t>- core
+- to be defined</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -2890,6 +2933,7 @@
       <c r="B54" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Time period used for reporting and for which the information should be aggregated from the native temporal resolution.</t>
         </is>
       </c>
@@ -2938,6 +2982,7 @@
       <c r="B55" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Concerned with the validity of the results of a particular study, enabling readers to check whether results have been manipulated by reproducing exactly the same study using the same data and methods.</t>
         </is>
       </c>
@@ -2980,7 +3025,7 @@
       <c r="B56" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -3022,6 +3067,7 @@
       <c r="B57" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Geopositioning of an Object using a Physical Sensor Model or a True Replacement Model.</t>
         </is>
       </c>
@@ -3072,7 +3118,7 @@
       <c r="B58" t="inlineStr">
         <is>
           <t>- controversial
-- approved</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -3114,7 +3160,7 @@
       <c r="B59" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -3164,7 +3210,7 @@
       <c r="B60" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+- to be discussed</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -3206,6 +3252,7 @@
       <c r="B61" t="inlineStr">
         <is>
           <t>- core
+  - to be discussed
 description: Period between the end of sensing of a Phenomenon to the beginning of availability of a specific product.</t>
         </is>
       </c>
@@ -3282,6 +3329,7 @@
       <c r="B63" t="inlineStr">
         <is>
           <t>- core
+- to be discussed
 description: Service to disseminate Data.</t>
         </is>
       </c>
@@ -3324,6 +3372,7 @@
       <c r="B64" t="inlineStr">
         <is>
           <t>- base
+- to be approved
 description: Entity with at least one Property referenced by an identifier.</t>
         </is>
       </c>
@@ -3366,6 +3415,7 @@
       <c r="B65" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Spheres dividing planet Earth into subsystems, which are collectives of (physical) matter sharing specific traits.</t>
         </is>
       </c>
@@ -3419,6 +3469,7 @@
       <c r="B66" t="inlineStr">
         <is>
           <t>- base
+- to be approved
 description: Element of a type domain.</t>
         </is>
       </c>
@@ -3466,6 +3517,7 @@
       <c r="B67" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Period between the moment of requesting information and the moment of availability of information.</t>
         </is>
       </c>
@@ -3516,7 +3568,7 @@
       <c r="B68" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -3581,7 +3633,7 @@
       <c r="B69" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -3629,6 +3681,7 @@
       <c r="B70" t="inlineStr">
         <is>
           <t>- base
+- to be approved
 description: Property having a magnitude that can be expressed as a number from a continuous and contiguous range and a reference.</t>
         </is>
       </c>
@@ -3679,6 +3732,7 @@
       <c r="B71" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Product within an EO Collection that is not expected to be updated.</t>
         </is>
       </c>
@@ -3725,6 +3779,7 @@
       <c r="B72" t="inlineStr">
         <is>
           <t>- controversial
+  - to be discussed
 description: Act of determining the Value of a Property by interacting in a reproducible way with the Phenomenon using a Sensor.</t>
         </is>
       </c>
@@ -3772,7 +3827,7 @@
       <c r="B73" t="inlineStr">
         <is>
           <t>- base
-- approved</t>
+- to be discussed</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -3838,6 +3893,7 @@
       <c r="B74" t="inlineStr">
         <is>
           <t>- core
+  - to be approved
 description: The masses of minerals that constitute planet Earth.</t>
         </is>
       </c>
@@ -3880,6 +3936,7 @@
       <c r="B75" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Measure of the ability to resolve features in the electromagnetic spectrum.</t>
         </is>
       </c>
@@ -3922,6 +3979,7 @@
       <c r="B76" t="inlineStr">
         <is>
           <t>- core
+  - to be approved
 description: The masses of liquid water, such as oceans, lakes, and rivers.</t>
         </is>
       </c>
@@ -3964,6 +4022,7 @@
       <c r="B77" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Time of the year at which the variable is observed or simulated by a model.</t>
         </is>
       </c>
@@ -4013,6 +4072,7 @@
       <c r="B78" t="inlineStr">
         <is>
           <t>- base
+- to be approved
 description: "Line defined in an algorithmic way using at least two positions (can be open-ended). Alternative: line connecting two positions in an algorithmic way (limited by end points)."</t>
         </is>
       </c>
@@ -4059,6 +4119,7 @@
       <c r="B79" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Condition where the spatial statistical properties of the data depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
         </is>
       </c>
@@ -4101,7 +4162,7 @@
       <c r="B80" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -4147,7 +4208,7 @@
       <c r="B81" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -4189,6 +4250,7 @@
       <c r="B82" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Product additionally processed from baseline or unenhanced mission data.</t>
         </is>
       </c>
@@ -4236,6 +4298,7 @@
       <c r="B83" t="inlineStr">
         <is>
           <t>- high-impact
+- to be discussed
 description: Desired outcome that policymakers wish to achieve.</t>
         </is>
       </c>
@@ -4278,6 +4341,7 @@
       <c r="B84" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
         </is>
       </c>
@@ -4348,6 +4412,7 @@
       <c r="B85" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Period during which data was collected, observations were made, or for which the model was run.</t>
         </is>
       </c>
@@ -4399,6 +4464,7 @@
       <c r="B86" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Property of a measurement result whereby the result can be related to a reference through a documented unbroken chain of calibrations each contributing to the measurement uncertainty.</t>
         </is>
       </c>
@@ -4441,6 +4507,7 @@
       <c r="B87" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Products and collections that have been superseded by new versions and are no longer available.</t>
         </is>
       </c>
@@ -4487,6 +4554,7 @@
       <c r="B88" t="inlineStr">
         <is>
           <t>- core
+  - to be approved
 description: Network composed of two or more sets of curves in which the members of each set intersect the members of the other sets in an algorithmic way.</t>
         </is>
       </c>
@@ -4534,6 +4602,7 @@
       <c r="B89" t="inlineStr">
         <is>
           <t>- core
+  - to be discussed
 description: Observation of a Quantity.</t>
         </is>
       </c>
@@ -4580,7 +4649,7 @@
       <c r="B90" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -4626,6 +4695,7 @@
       <c r="B91" t="inlineStr">
         <is>
           <t>- core
+- to be discussed
 description: Phenomenon whose values for specific properties are known and understood with an Uncertainty significantly lower than that of the Observation with which it is compared.</t>
         </is>
       </c>
@@ -4672,6 +4742,7 @@
       <c r="B92" t="inlineStr">
         <is>
           <t>- core
+  - to be discussed
 description: Usually in-situ observations in which the Object or Phenomenon is isolated from other systems or altered in its original conditions or environment.</t>
         </is>
       </c>
@@ -4718,6 +4789,7 @@
       <c r="B93" t="inlineStr">
         <is>
           <t>- controversial
+- to be discussed
 description: Subset of one or more entities.</t>
         </is>
       </c>
@@ -4766,6 +4838,7 @@
       <c r="B94" t="inlineStr">
         <is>
           <t>- base
+- to be approved
 description: Characteristic belonging to an entity and referenced by an identifier.</t>
         </is>
       </c>
@@ -4812,6 +4885,7 @@
       <c r="B95" t="inlineStr">
         <is>
           <t>- core
+  - to be approved
 description: Data describing other data, providing an understanding of the content and utility of a product or collection.</t>
         </is>
       </c>
@@ -4859,7 +4933,7 @@
       <c r="B96" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -4939,7 +5013,7 @@
       <c r="B98" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -4985,7 +5059,7 @@
       <c r="B99" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -5027,6 +5101,7 @@
       <c r="B100" t="inlineStr">
         <is>
           <t>- core
+  - to be discussed
 description: Regarded long-term according to X. However, in the Horizon Europe Missions terminology, regarded short-term.</t>
         </is>
       </c>
@@ -5069,6 +5144,7 @@
       <c r="B101" t="inlineStr">
         <is>
           <t>- core
+  - to be approved
 description: Products or collections which have been superseded by later versions of a product or collection.</t>
         </is>
       </c>
@@ -5111,6 +5187,7 @@
       <c r="B102" t="inlineStr">
         <is>
           <t>- core
+  - to be discussed
 description: Uncertainty associated with the method of Measurement.</t>
         </is>
       </c>
@@ -5153,6 +5230,7 @@
       <c r="B103" t="inlineStr">
         <is>
           <t>- core
+- to be defined
 description: ''</t>
         </is>
       </c>
@@ -5191,6 +5269,7 @@
       <c r="B104" t="inlineStr">
         <is>
           <t>- controversial
+  - to be discussed
 description: Observations performed in the same Place where a Phenomenon occurs, normally without isolating it from other systems or altering its pre-Observation state.</t>
         </is>
       </c>
@@ -5238,6 +5317,7 @@
       <c r="B105" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Direct output from standardized satellite data processing chains (indicative levels 2 and 3), representing fundamental geophysical and biophysical variables.</t>
         </is>
       </c>
@@ -5285,6 +5365,7 @@
       <c r="B106" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Presence or absence of gaps, which are missing values in an otherwise continuous spatial data series.</t>
         </is>
       </c>
@@ -5331,6 +5412,7 @@
       <c r="B107" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Translation of one form of Location into another.</t>
         </is>
       </c>
@@ -5377,6 +5459,7 @@
       <c r="B108" t="inlineStr">
         <is>
           <t>- core
+  - to be discussed
 description: Correcting for positional displacement with respect to the surface of the Earth.</t>
         </is>
       </c>
@@ -5431,6 +5514,7 @@
       <c r="B109" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Legal instrument by which a copyright holder may grant rights over the protected work.</t>
         </is>
       </c>
@@ -5473,6 +5557,7 @@
       <c r="B110" t="inlineStr">
         <is>
           <t>- base
+- to be approved
 description: Particular era or span of time.</t>
         </is>
       </c>
@@ -5519,7 +5604,7 @@
       <c r="B111" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -5561,6 +5646,7 @@
       <c r="B112" t="inlineStr">
         <is>
           <t>- base
+- to be discussed
 description: Abstraction of real-world phenomena.</t>
         </is>
       </c>
@@ -5607,6 +5693,7 @@
       <c r="B113" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
         </is>
       </c>
@@ -5653,7 +5740,7 @@
       <c r="B114" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -5695,6 +5782,7 @@
       <c r="B115" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Entity (person, organization, institution, etc.) that is requesting data or information with certain characteristics described by needs and/or requirements.</t>
         </is>
       </c>
@@ -5749,6 +5837,7 @@
       <c r="B116" t="inlineStr">
         <is>
           <t>- core
+- to be discussed
 description: Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
         </is>
       </c>
@@ -5795,6 +5884,7 @@
       <c r="B117" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Condition where the temporal statistical properties of the sample depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
         </is>
       </c>
@@ -5837,6 +5927,7 @@
       <c r="B118" t="inlineStr">
         <is>
           <t>- core
+  - to be approved
 description: Data consisting of, derived from, or relating to information that is directly linked to specific geographical locations.</t>
         </is>
       </c>
@@ -5880,6 +5971,7 @@
       <c r="B119" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Maximum acceptable change in Uncertainty per decade.</t>
         </is>
       </c>
@@ -5926,6 +6018,7 @@
       <c r="B120" t="inlineStr">
         <is>
           <t>- base
+- to be discussed
 description: Observable Trait.</t>
         </is>
       </c>
@@ -5968,6 +6061,7 @@
       <c r="B121" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Data with implicit or explicit reference to a Location relative to the Earth.</t>
         </is>
       </c>
@@ -6014,6 +6108,7 @@
       <c r="B122" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
         </is>
       </c>
@@ -6097,6 +6192,7 @@
       <c r="B123" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Set of all the components of an interactive system that provide information and controls for the user to accomplish specific tasks with the interactive system.</t>
         </is>
       </c>
@@ -6139,6 +6235,7 @@
       <c r="B124" t="inlineStr">
         <is>
           <t>- core
+  - to be approved
 description: Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
         </is>
       </c>
@@ -6201,6 +6298,7 @@
       <c r="B125" t="inlineStr">
         <is>
           <t>- core
+  - to be approved
 description: Particular Quantity subject to Measurement.</t>
         </is>
       </c>
@@ -6214,7 +6312,8 @@
       <c r="F125" t="inlineStr">
         <is>
           <t>| Step | Process description |
-| :----- | :--------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------- |
+| :----- | :------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------
+--- |
 | (Raw) | The complete and unaltered/unprocessed set of Data acquired by one or several sensors on a platform |
 | M/0 uncalibrated | Unaltered/unprocessed Level 0 (main) Sensor Data annotated with processed Ancillary Data and supplemented by Auxiliary Data (including radiometric and geometric Calibration coefficients and geo-referencing parameters) allowing further processing to higher Levels. |
 | M/1 Sensor-calibrated | Level M/0 Sensor Data which have been calibrated (ideally traceable to SI) and spatially aligned (co-located, eventually co-gridded) to represent at-Sensor measurements (Value and Uncertainty) in Sensor nominal spatiotemporal sampling, supplemented by appropriate ancillary data. |
@@ -6255,6 +6354,7 @@
       <c r="B126" t="inlineStr">
         <is>
           <t>- high-impact
+- to be discussed
 description: Specific level or rate set for the Policy Objective.</t>
         </is>
       </c>
@@ -6297,6 +6397,7 @@
       <c r="B127" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Zone or region of space described by a geographic identifier in the form of a label or code, or by a bounding box, representing the maximum spatial boundary within which the user is requesting data.</t>
         </is>
       </c>
@@ -6348,6 +6449,7 @@
       <c r="B128" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Products in a research and development phase not yet published into a standardized collection.</t>
         </is>
       </c>
@@ -6390,6 +6492,7 @@
       <c r="B129" t="inlineStr">
         <is>
           <t>- base
+  - to be approved
 description: Entity with a well-defined boundary and identity that encapsulates state and behaviour.</t>
         </is>
       </c>
@@ -6432,6 +6535,7 @@
       <c r="B130" t="inlineStr">
         <is>
           <t>- core
+- to be discussed
 description: The forecast period.</t>
         </is>
       </c>
@@ -6474,6 +6578,7 @@
       <c r="B131" t="inlineStr">
         <is>
           <t>- high-impact
+- to be discussed
 description: Markers of significant progress in addressing specific issues, or crucial decision points where significant choices are made within a policy process.</t>
         </is>
       </c>
@@ -6516,6 +6621,7 @@
       <c r="B132" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Time that an antenna beam spends on a target.</t>
         </is>
       </c>
@@ -6562,6 +6668,7 @@
       <c r="B133" t="inlineStr">
         <is>
           <t>- core
+  - to be approved
 description: Measure of the agreement between the represented Location of an Object and the true Location.</t>
         </is>
       </c>
@@ -6604,6 +6711,7 @@
       <c r="B134" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Standard Uncertainty multiplied by a coverage factor k, chosen to obtain a desired level of confidence.</t>
         </is>
       </c>
@@ -6646,6 +6754,7 @@
       <c r="B135" t="inlineStr">
         <is>
           <t>- core
+- to be defined
 description: ""</t>
         </is>
       </c>
@@ -6680,6 +6789,7 @@
       <c r="B136" t="inlineStr">
         <is>
           <t>- controversial
+  - to be discussed
 description: An, often numeric, theoretical (or otherwise abstract) representation of an Entity intended to generate Data describing one or more of its traits.</t>
         </is>
       </c>
@@ -6726,7 +6836,7 @@
       <c r="B137" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -6768,6 +6878,7 @@
       <c r="B138" t="inlineStr">
         <is>
           <t>- core
+- to be discussed
 description: Range of the Spectral Band.</t>
         </is>
       </c>
@@ -6810,7 +6921,7 @@
       <c r="B139" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -6886,6 +6997,7 @@
       <c r="B141" t="inlineStr">
         <is>
           <t>- high-impact
+- to be discussed
 description: Policy documents that represent the official written reference for a given Policy.</t>
         </is>
       </c>
@@ -6928,6 +7040,7 @@
       <c r="B142" t="inlineStr">
         <is>
           <t>- high-impact
+- to be discussed
 description: Deliberate system of guidelines to guide decisions and achieve rational outcomes, implemented as a procedure or protocol and typically promulgated through official written documents.</t>
         </is>
       </c>
@@ -6970,6 +7083,7 @@
       <c r="B143" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Spatial reference in the form of a label or code that identifies a Location.</t>
         </is>
       </c>
@@ -7016,6 +7130,7 @@
       <c r="B144" t="inlineStr">
         <is>
           <t>- high-impact
+- to be discussed
 description: Science domain dealing with technologies and methods of collecting and analyzing observations about the different Earth spheres.</t>
         </is>
       </c>
@@ -7063,6 +7178,7 @@
       <c r="B145" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Structured Data that is machine readable and can be automatically read and processed by a computer, such as HDF, NetCDF, CSV, JSON, XML, etc.</t>
         </is>
       </c>
@@ -7105,6 +7221,7 @@
       <c r="B146" t="inlineStr">
         <is>
           <t>- core
+- to be discussed
 description: Information used to determine geographic Location.</t>
         </is>
       </c>
@@ -7147,7 +7264,7 @@
       <c r="B147" t="inlineStr">
         <is>
           <t>- core
-- approved</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -7189,6 +7306,7 @@
       <c r="B148" t="inlineStr">
         <is>
           <t>- core
+  - to be defined
 description: ""</t>
         </is>
       </c>
@@ -7223,6 +7341,7 @@
       <c r="B149" t="inlineStr">
         <is>
           <t>- base
+  - to be approved
 description: Particular Place referenced by an identifier.</t>
         </is>
       </c>
@@ -7275,6 +7394,7 @@
       <c r="B150" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Device or instrument suited (through physical/chemical interaction) to measure one or more properties of a Phenomenon and thus collect factual/objective data.</t>
         </is>
       </c>
@@ -7323,6 +7443,7 @@
       <c r="B151" t="inlineStr">
         <is>
           <t>- core
+- to be approved
 description: Observation or model output representing regular intervals, specifying the length of the interval that determines the smallest event or process that can be resolved.</t>
         </is>
       </c>
@@ -7375,6 +7496,7 @@
       <c r="B152" t="inlineStr">
         <is>
           <t>- high-impact
+- to be discussed
 description: Well-established concept typically taught as the rational model of policy decision-making, representing an idealised view of the policy process.</t>
         </is>
       </c>

--- a/exports/xlsx/terms.xlsx
+++ b/exports/xlsx/terms.xlsx
@@ -536,33 +536,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Geographic Grid</t>
+          <t>Geolocating</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Regular grid based on a Geographic Coordinate Reference System (CRS).</t>
+description: Geopositioning of an Object using a Physical Sensor Model or a True Replacement Model.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Regular grid based on a Geographic Coordinate Reference System (CRS).</t>
+          <t>Geopositioning of an Object using a Physical Sensor Model or a True Replacement Model.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>- ISO 19115-2:2009, 4.11</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Determination of the geographic location of a feature of two or more dimensions.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>- ISO 19130-1:2018, 3.36 ('geopositioning'), modified</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -579,27 +587,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Representativeness</t>
+          <t>Spectral Bandwidth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Quality or characteristic of a measurement or observation to accurately represent a specific geographic location, time period, or environmental condition.</t>
+- to be discussed
+description: Range of the Spectral Band.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Quality or characteristic of a measurement or Observation to accurately represent a specific geographic location, time Period, or environmental condition.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>- WIGOS metadata standard defines representativeness as the extent of the region around the Observation of which it is representative.</t>
-        </is>
-      </c>
+          <t>Range of the Spectral Band.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
@@ -626,25 +630,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EO Space Data</t>
+          <t>Instrument Data</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Earth Observation data generated by spaceborne missions or instruments owned by public or private organizations.</t>
+  - to be approved
+description: Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Earth Observation data generated by spaceborne missions or instruments owned by public or private organizations.</t>
+          <t>Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>- See also Instrument data.</t>
+          <t>- These data consist of instrument science and engineering data, and possibly ancillary data. Instrument engineering data is produced by engineering sensor(s) of an instrument, used either for operating the instrument or for processing the science data generated by the instrument. Instrument science data is produced by the science sensor(s) of an instrument, usually constituting the basic reason for existence of an instrument.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -653,14 +657,30 @@
           <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Data created by an instrument including scientific measurements and any engineering or ancillary data which may be included in the data packets.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Data produced and transmitted by the science and engineering sensors of an instrument, and, in the spacecraft environment, any additional data packaged with the instrument's sensor data by virtue of services provided.</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
@@ -673,41 +693,59 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Granule</t>
+          <t>Auxiliary Data</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>- core
-  - to be approved
-description: The smallest aggregation of data which is independently managed (i.e. described, inventoried, retrievable).</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>The smallest aggregation of data which is independently managed (i.e. described, inventoried, retrievable). Granules may be managed as logical granules and/or physical granules.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>- See also product.</t>
-        </is>
-      </c>
+          <t>Data that enhance the processing and utilisation of main Sensor Data. Auxiliary Data are usually not captured by the same Data collection Process or on the same platform as the main Sensor Data. Examples include meteorological Data received from ECMWF/Met Offices or DEMs. Auxiliary Data help in Data processing, but are also Data sets in their own right.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>- [NASA EarthData](https://www.earthdata.nasa.gov/learn/glossary)</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+          <t>- ESA/CEOS?, modified
+- ENMAP Glossary of Terms, https://www.enmap.org/Data/doc/EnMAP_Terms.pdf, 20210624
+- EO Data Stewardship Glossary</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Data required to perform processing of Sensor Data which is not obtained from the Sensor itself. Includes: (a) Data provided by the spacecraft (e.g. orbit Position and velocity, attitude, instrument house-keeping Data, on-board time); (b) Data not available from on-board sources.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>For EnMAP, this includes (a) orbit files, attitude files, Calibration Data, instrument house-keeping Data; (b) atmospheric parameters, reference images.</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>- ENMAP Glossary of Terms, https://www.enmap.org/Data/doc/EnMAP_Terms.pdf, 20210624
+- EO Data Stewardship Glossary</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Data required for instrument processing that does not originate in the instrument itself or from the satellite. Some Auxiliary Data will be generated in the ground segment, whilst other Data will be provided from external sources.</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>- CEOS-ARD PFS template 20220302</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
@@ -720,38 +758,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Temporal Revisit</t>
+          <t>Dispose</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>- core
-- to be discussed
-description: Interval between successive observations.</t>
+- to be approved
+description: Action of permanently and irrecoverably removing all copies of data held by an organization.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Interval between successive observations.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>- In Remote Sensing it is also called repeat cycle.
-- More generally it is known as temporal sampling interval.</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>| Entry format example | Valid unit                     |
-|----------------------|-------------------------------|
-| 1 s, 2 h             | second, hour, day, month, year |</t>
-        </is>
-      </c>
+          <t>Action of permanently and irrecoverably removing all copies of data held by an organization.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -774,27 +801,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Dispose</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>- core
-- to be approved
-description: Action of permanently and irrecoverably removing all copies of data held by an organization.</t>
+          <t>- base
+- to be discussed
+- controversial
+description: Place referenced by a single set of coordinates within a coordinate reference system.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Action of permanently and irrecoverably removing all copies of data held by an organization.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>Place referenced by a single set of coordinates within a coordinate reference system.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>- Opposite to (previous) ISO definition, Position shall be used only for 0-dimensional primitives (points).</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- ISO 19133:2005, modified to cover only points, also called 'direct position'</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -817,36 +849,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Remote Sensing</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>- controversial
-- to be discussed
-description: Type of Observation performed at a significant distance from a Phenomenon.</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Remote Observation</t>
-        </is>
-      </c>
+          <t>- core
+- to be approved
+description: Electronic data package distributable to users; content is derived from instrument data via processing involving ancillary and auxiliary data.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Type of Observation performed at a significant distance from a Phenomenon.</t>
+          <t>Electronic data package distributable to users; content is derived from instrument data via processing involving ancillary and auxiliary data.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>- 'Significant' in this context means that the distance has, or may have, a non-negligible impact on the Value of the Property observed.
-- The effect of the distance on the acquired data is the main distinction criterion between 'remote' and 'in-situ' observations.</t>
+          <t>- Products may be accompanied by metadata and browse images.
+- A Product may be part of a collection — a distinction useful for archiving and cataloguing purposes.
+- The term Product may be used to denote a product type, such as e.g. ENVISAT_ASAR_L1B_PRI data products.
+- End users may distinguish between (input, "raw") data and products, i.e., the derived geophysical parameters.
+- See also granule.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -869,27 +900,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Near Real Time Data</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>- high-impact
-  - to be discussed
-description: Data available for use with a specified (small and application dependent) latency, typically 3 hours for meteorological applications.</t>
+          <t>- base
+- to be approved
+description: Series of activities that interact to produce a result.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Data available for use with a specified (small and application dependent) latency, typically 3 hours for meteorological applications.</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>Series of activities that interact to produce a result.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>- A Process may occur once-only or be recurrent or periodic.</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- [Wikipedia](https://en.wikipedia.org/wiki/Process)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -912,51 +947,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>- base
-- to be approved
-description: Value and possibly Uncertainty of a Trait of a specific Entity.</t>
+          <t>- core
+- to be discussed
+description: Phenomenon whose values for specific properties are known and understood with an Uncertainty significantly lower than that of the Observation with which it is compared.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Value and possibly Uncertainty of a Trait of a specific Entity.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>- Data simply describe entities using certain traits and are not targeted at a particular use or audience.</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Data can be categorised into:
-- factual (i.e. obtained by Observation) or fictional (obtained e.g. through modelling, estimating or assigning)
-- quantitative (continuous) or qualitative (categorical)
-- analogue or digital
-(list not exhaustive!)</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
+          <t>Phenomenon whose values for specific properties are known and understood with an Uncertainty significantly lower (quantify?) than that of the Observation with which it is compared.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Scientific or technical measurements, values calculated therefrom, observations, or facts that can be represented by numbers, tables, graphs, models, text, or symbols which are used as a basis for reasoning and further calculation.</t>
+          <t>Sort of data acquired with an Uncertainty significantly lower (quantify?) than that of the data it is being compared with.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
+          <t>- VIM?, modified</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -975,31 +994,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Geographic Coordinate Reference System</t>
+          <t>Earth Observation Based Output</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Coordinate Reference System (CRS) that has a geodetic Reference frame and an ellipsoidal coordinate system.</t>
+description: Higher-level processing and integration output (indicative level 4 and beyond) that goes beyond basic data processing, often designed for policy or decision-making needs.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Coordinate Reference System (CRS) that has a geodetic Reference frame and an ellipsoidal coordinate system.</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>- Also known as geographic CRS.</t>
-        </is>
-      </c>
+          <t>Higher-level processing and integration output (indicative level 4 and beyond) that goes beyond basic data processing. These outputs are often designed specifically for policy or decision-making needs, and can be categorized into sub-categories:
+- Outputs from models/model integration: use of EO products as inputs in numerical models or combining them with other data sources in modelling frameworks.
+- Indicator-based outputs: EO products transformed through specialized algorithms (including statistical methods, machine learning, and pattern recognition) to create meaningful metrics based on spatio-temporal analysis.
+- Outputs from reanalysis: merging of EO products with other observations and models, creating consistent long-term records of past atmospheric, oceanic, and land surface conditions, and filling gaps through data assimilation techniques.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>- ISO 19111:2019, 3.1.35</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -1022,38 +1040,45 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Long Term Preservation</t>
+          <t>Entity</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>- core
-  - to be approved
-description: The act of maintaining information in a correct and independently understandable form over the long term.</t>
+          <t>- base
+- to be approved
+description: Something that has separate and distinct existence and objective or conceptual reality.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>The act of maintaining information in a correct and independently understandable form over the long term.</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>- Long term refers to a period of time long enough to be concerned with the impact which changing technologies, including support for media and data formats, and changing user communities will have on the information being held in a repository.
-- See also preservation.</t>
-        </is>
-      </c>
+          <t>Something that has separate and distinct existence and objective or conceptual reality.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>- ISO 19119:2016, 4.1.6</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Government or business organization that is formed to conduct business or represent the government of the day.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>CEOS Entities include Working Groups, Virtual Constellations, etc.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1070,32 +1095,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Preservation</t>
+          <t>Collection</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Processes and operations used to ensure data technical and intellectual survival through time.</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Processes and operations used to ensure data technical and intellectual survival through time.</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>- Grants data integrity, discoverability and accessibility, and facilitates its (re-)use in the long term.
-- Preservation is one of the tasks of data curation.</t>
-        </is>
-      </c>
+          <t>Group of products that have been processed using a consistent radiometric calibration, geometric registration base, data/metadata format, and version of processing algorithms.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1118,27 +1137,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Version Control</t>
+          <t>Geographic Grid</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Method of working with collections, similar to version control systems used in traditional software development but optimized to allow better processing of data and collaboration in data analytics and research contexts.</t>
+description: Regular grid based on a Geographic Coordinate Reference System (CRS).</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Method of working with collections, similar to the version control systems used in traditional software development but optimized to allow better processing of data and collaboration in the context of data analytics, research, and any other form of data analysis.</t>
+          <t>Regular grid based on a Geographic Coordinate Reference System (CRS).</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>- [Wikipedia](https://en.wikipedia.org/wiki/Data_version_control)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -1161,27 +1180,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Thematic Resolution</t>
+          <t>Archive</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Level of categorical detail of information expressed by the number of classes.</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Level of categorical detail of information expressed by the number of classes.</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>System that stores data products, guaranteeing their preservation for future use.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>- This function includes all operations to identify, store and retrieve the data and ensure their integrity.</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>- CGLS</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1204,26 +1226,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Copernicus Service Provider</t>
+          <t>Steward</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>- core
-- to be discussed</t>
+- to be discussed
+description: Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Institutional body, organisation or programme that provides reliable, trusted (authoritative?) EO Information and that has the financial resources to sustain the provision. It utilises satellite Data, ground-based measurements, and other sources to generate accurate and timely Data products related to various aspects of the Earth's environment, such as land, Atmosphere, oceans, and climate.</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>- See also Custodian.</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -1246,27 +1273,33 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Replicability</t>
+          <t>Sample</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>- core
-- to be approved
-description: Property enabling other researchers to conduct an independent study with different data and similar but not identical methods, yet arriving at results that confirm the original study's hypothesis.</t>
+          <t>- controversial
+- to be discussed
+description: Subset of one or more entities.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Property enabling other researchers to conduct an independent study with different data and similar but not identical methods, yet arriving at results that confirm the original study's hypothesis.</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+          <t>Subset of one or more entities.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>- A Sample may be spatial, temporal, spectral, or in any other dimension or Trait.
+- Each Sample is contiguous, i.e. it does not consist of more than one discontinuous geometry in any dimension.
+- The Process of obtaining a Sample is called sampling.</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>- Craglia, M., et al. (2018).</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -1289,30 +1322,36 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Coverage Interval</t>
+          <t>Temporal Extent</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>- core
-- to be approved</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Coverage extent</t>
-        </is>
-      </c>
+- to be approved
+description: Period during which data was collected, observations were made, or for which the model was run.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Range or specific subset of values associated with a coverage dataset.</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+          <t>Period during which data was collected, observations were made, or for which the model was run.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>- In W3C this is the definition of temporal coverage.
+- Time Period covered by a series of observations inclusive of the specified date/time indications (measurement history). Defined based on the beginning and end dates of observations.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>- WIGOS Metadata</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Adapted from W3C</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -1383,20 +1422,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Equivalence</t>
+          <t>Cryosphere</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>- core
-  - to be defined</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Masses of frozen water, such as sea ice, ice shields, glaciers, and snow.</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>- Guth et al. 2021</t>
+        </is>
+      </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
@@ -1417,29 +1464,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Band Central Wavelength</t>
+          <t>Spatial Reporting Unit</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>- core
-- to be approved</t>
+- to be approved
+description: Smallest spatial object of interest that may be used for reporting and for which the information should be aggregated.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Single wavelength Value within the sensitivity interval of a spectroradiometric Sensor which represents the respective band. It could be either the mean, the median, the maximum sensitivity, or any other reasonable Value chosen to be representative.</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>| Entry format example | Valid unit                                        |
-|----------------------|---------------------------------------------------|
-| 0.545 μm             | micrometre (μm), millimetre (mm), centimetre (cm) |</t>
-        </is>
-      </c>
+          <t>Smallest spatial object of interest that may be used for reporting and for which the information should be aggregated.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>- WIGOS 2019 uses 'spatial reporting interval', probably assuming observations are reported on a grid with regular spacing/intervals.</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>- KCEO</t>
@@ -1465,31 +1511,31 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Update Frequency</t>
+          <t>Decommissioned Product</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Frequency at which the product is available to users.</t>
+description: Products and collections that have been superseded by new versions and are no longer available.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Frequency at which the product is available to users.</t>
+          <t>Products and collections that have been superseded by new versions and are no longer available.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>- Also known in product catalogues as dissemination frequency.</t>
+          <t>- Decommissioned products are no longer supported, i.e. corrections will not be made, new data will not be added, and support is not available.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -1512,45 +1558,43 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Entity</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>- base
-- to be approved
-description: Something that has separate and distinct existence and objective or conceptual reality.</t>
+  - to be approved
+description: Particular Place referenced by an identifier.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Something that has separate and distinct existence and objective or conceptual reality.</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+          <t>Particular Place referenced by an identifier.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>- While a (geo)location identifies a geographic Place, it may also be associated with objects other than the Earth.
+- While Location in principle covers 0- to 3-dimensional spatial geometries, it should not be used for 0- and 1-dimensional geometries (positions and paths).</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>- Madrid
+- California</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>- ISO 19119:2016, 4.1.6</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Government or business organization that is formed to conduct business or represent the government of the day.</t>
-        </is>
-      </c>
+          <t>- [ISO 19112:2019](https://www.iso.org/standard/70742.html), (E), 3.1.3, modified, note 2 added</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>CEOS Entities include Working Groups, Virtual Constellations, etc.</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
-        </is>
-      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -1567,27 +1611,31 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Place</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>- base
 - to be approved
-description: Part of any space referenced by an identifier.</t>
+description: Particular era or span of time.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Part of any space referenced by an identifier.</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
+          <t>Particular era or span of time.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>- Periods are intervals named with a Period Identifier.</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>- ISO 19155:2012, 4.8</t>
+          <t>- ISO 19170:2021</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -1610,34 +1658,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Duration</t>
+          <t>Geospatial Data</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Non-negative interval Quantity of time equal to the difference between the final and initial instants of a time interval.</t>
+  - to be approved
+description: Data consisting of, derived from, or relating to information that is directly linked to specific geographical locations.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Non-negative interval Quantity of time equal to the difference between the final and initial instants of a time interval.</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>- Duration is one of the base quantities in the International System of Quantities (ISQ) on which the International System of Units (SI) is based. The term "time" instead of "duration" is often used in this context and also for an infinitesimal duration.
-- For the term "duration", expressions such as "time" or "time interval" are often used, but the term "time" is not recommended in this sense and the term "time interval" is deprecated in this sense to avoid confusion with the concept of "time interval".
-- The exact duration of a time scale unit depends on the time scale used. For example, the durations of a year, month, week, day, hour or minute may depend on when they occur (in a Gregorian calendar, a calendar month can have a duration of 28, 29, 30, or 31 days; in a 24-hour clock, a clock minute can have a duration of 59, 60, or 61 seconds, etc.). Therefore, the exact duration can only be evaluated if the exact duration of each is known.
-- This definition is closely related to NOTE 1 of the terminological entry "duration" in IEC 60050-113:2011, 113-01-13.</t>
-        </is>
-      </c>
+          <t>Data consisting of, derived from, or relating to information that is directly linked to specific geographical locations.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>- ISO 8601-1:2019, 3.1.1.8</t>
+          <t>- https://www.merriam-webster.com/dictionary/geospatial
+- https://isotc211.geolexica.org/Concepts/202/, accessed 20221010</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -1660,35 +1702,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Time of Day</t>
+          <t>Confidence Interval</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>- core
-- to be approved
-description: Time of the day at which the variable or parameter is observed or simulated by a model.</t>
+          <t>- controversial
+- to be approved</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Time of the day at which the variable or parameter is observed or simulated by a model.</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>- In Remote Sensing it is also known as time of overpass.</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>| Type      | Entry format example | Valid unit |
-|-----------|----------------------|------------|
-| timestamp | 18:00 h (0–24)       | Hours      |
-| timerange | 18:00 – 20:00 h      | Hours      |</t>
-        </is>
-      </c>
+          <t>Probability that the Quantity lies in the interval, conditioned on the measuring or modelling assumptions.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
           <t>- KCEO</t>
@@ -1714,33 +1744,31 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Vertical Levels</t>
+          <t>Granule</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Levels of a vertical discretization, e.g. pressure levels in an atmospheric model reanalysis or height levels in a forest biomass EO product.</t>
+  - to be approved
+description: The smallest aggregation of data which is independently managed (i.e. described, inventoried, retrievable).</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Levels of a vertical discretization. Examples may be pressure levels in an atmospheric model reanalysis or height levels in a forest biomass EO product.</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>| Entry format example                | Valid unit           |
-|------------------------------------|----------------------|
-| 1, 5, 10 meter; 1000, 850, 500 hPa | meter, hPa, unitless |</t>
-        </is>
-      </c>
+          <t>The smallest aggregation of data which is independently managed (i.e. described, inventoried, retrievable). Granules may be managed as logical granules and/or physical granules.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>- See also product.</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [NASA EarthData](https://www.earthdata.nasa.gov/learn/glossary)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -1763,35 +1791,31 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>- core
-- to be approved
-description: Electronic data package distributable to users; content is derived from instrument data via processing involving ancillary and auxiliary data.</t>
+          <t>- controversial
+  - to be discussed
+description: An, often numeric, theoretical (or otherwise abstract) representation of an Entity intended to generate Data describing one or more of its traits.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Electronic data package distributable to users; content is derived from instrument data via processing involving ancillary and auxiliary data.</t>
+          <t>An, often numeric, theoretical (or otherwise abstract) representation of an Entity intended to generate Data describing one or more of its traits (as a result of pre-set conditions).</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>- Products may be accompanied by metadata and browse images.
-- A Product may be part of a collection — a distinction useful for archiving and cataloguing purposes.
-- The term Product may be used to denote a product type, such as e.g. ENVISAT_ASAR_L1B_PRI data products.
-- End users may distinguish between (input, "raw") data and products, i.e., the derived geophysical parameters.
-- See also granule.</t>
+          <t>- The Process of generating Data using a model is called modelling.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -1814,37 +1838,45 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Georectifying</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>- base
-  - to be approved
-description: The result of organisation, interpretation, categorisation, classification, or some other form of processing of Data attaching to it a certain meaning that can be understood by the addressee.</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>- core
+  - to be discussed
+description: Correcting for positional displacement with respect to the surface of the Earth.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Orthorectifying</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>The result of organisation, interpretation, categorisation, classification, or some other form of processing of Data attaching to it a certain meaning that can be understood by the addressee.</t>
+          <t>Correcting for positional displacement with respect to the surface of the Earth.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>- Information depends on Data and is targeted.</t>
+          <t>- Source: ISO 19115-2:2019, 3.11; ISO 19115-2:2009(E); https://www.iso.org/standard/67039.html, modified</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>The correction of sample locations to achieve some sort of geometric regularity, e.g., a regular 2D geographic grid.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
@@ -1861,27 +1893,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Lithosphere</t>
+          <t>Policy Making</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>- core
-  - to be approved
-description: The solid, inanimate outer layer of the Geosphere. For the purposes of Earth Observation, includes soils ('pedosphere').</t>
+          <t>- high-impact
+- to be discussed
+description: Process by which governments translate their political vision into programmes and actions to deliver outcomes — desired change in the real world.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>The solid, inanimate outer layer of the Geosphere. For the purposes of Earth Observation, the Lithosphere is considered to include soils ('pedosphere').</t>
+          <t>Process by which governments translate their political vision into programmes and actions to deliver outcomes — desired change in the real world.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- [ESA/CEOS?, modified](https://digital-strategy.ec.europa.eu/en/library/quality-public-administration-toolbox-practitioners)</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -1904,75 +1936,112 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ancillary Data</t>
+          <t>Uncertainty</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>- core
-- to be approved</t>
+- to be approved
+description: Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Data acquired on the same platform but not obtained from the main Sensor itself (usually provided as part of Level 0 Data), with the primary purpose of serving the processing of main instrument Data (e.g. Position and velocity of platform).</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>This can be divided into data referred to as spacecraft 'engineering', 'core housekeeping' or 'subsystem' data obtained from other parts of the platform, and includes parameters such as orbit position and velocity, attitude and its range of change, time, temperatures, pressures, jet firings, water dumps, internally produced magnetic fields, and other environmental measurements. Ancillary refers to data that exist purely to serve the data processing.</t>
-        </is>
-      </c>
+          <t>Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>- ESA/CEOS?, modified
-- EO Data Stewardship Glossary</t>
+          <t>- GUM</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Data other than instrument measurements, originating in the instrument itself or from the satellite, required to perform processing of the Data. Includes orbit Data, attitude Data, time Information, and spacecraft engineering Data, Calibration Data, Data quality Information, and Data from other instruments or earth system models.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>Non-negative parameter, associated with data, which characterizes the dispersion of the values of a Trait that could reasonably be attributed to a Phenomenon by means of sensing or modelling.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>- In case of quantitative (continuous) data the uncertainty may be, for example, a standard deviation (or a given multiple of it), or the half-width of an interval having a stated level of confidence (see e.g. Standard and Expanded Uncertainty).
+- For qualitative (categorical?) data, uncertainty may be expressed by commission and omission ('confusion matrix') or overall errors.</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>- CEOS-ARD PFS template 20220302</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
+          <t>- Modified from GUM, VIM4:3.1, FIDUCEO, Notes added</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Measure of the spread of the distribution of possible values.</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>- [FIDUCEO Glossary](https://research.reading.ac.uk/fiduceo/glossary/), VIM?, modified</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Parameter, associated with the result of measurement, that characterizes the dispersion of values that could reasonably be attributed to the measurand.</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>- When the quality of accuracy or precision of measured values, such as coordinates, is to be characterized quantitatively, the quality parameter is an estimate of the uncertainty of the measurement results. Because accuracy is a qualitative concept, one should not use it quantitatively, that is associate numbers with it; numbers should be associated with measures of uncertainty instead.</t>
+        </is>
+      </c>
       <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>- ISO 19116:2004(E)</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Parameter characterizing the dispersion of the values being attributed to a measurand, based on the information used.</t>
+        </is>
+      </c>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>- VIM4: 3.1</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Consistency</t>
+          <t>Climate Projection</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>- core
-  - to be defined</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Simulated response of the climate system to a scenario of future emission or concentration of greenhouse gases (GHGs) and aerosols, generally derived using climate models. Climate Projections are distinguished from climate predictions by their dependence on the emission/concentration/radiative forcing scenario used, which is in turn based on assumptions concerning, for example, future socioeconomic and technological developments that may or may not be realised.</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>- IPCC</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
@@ -1993,20 +2062,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Quality Indicator</t>
+          <t>Data Format</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Indicator providing sufficient information to allow all users to readily evaluate the fitness for purpose of the data or derived product.</t>
+description: Structured Data that is machine readable and can be automatically read and processed by a computer, such as HDF, NetCDF, CSV, JSON, XML, etc.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Indicator providing sufficient information to allow all users to readily evaluate the fitness for purpose of the data or derived product. May be a number, set of numbers, graph, Uncertainty budget, or a simple flag.</t>
+          <t>Structured Data that is machine readable and can be automatically read and processed by a computer, such as HDF, NetCDF, CSV, JSON, XML, etc.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -2036,31 +2105,26 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Classification System Levels</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>- base
-- to be approved
-description: Series of activities that interact to produce a result.</t>
+          <t>- core
+- to be discussed</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Series of activities that interact to produce a result.</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>- A Process may occur once-only or be recurrent or periodic.</t>
-        </is>
-      </c>
+          <t>Levels in a hierarchical Classification System.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>- [Wikipedia](https://en.wikipedia.org/wiki/Process)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -2083,27 +2147,31 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Standard Uncertainty</t>
+          <t>Geocoding</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Standard deviation of the probability distribution describing the spread of possible values in quantitative/continuous data.</t>
+description: Translation of one form of Location into another.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Standard deviation of the probability distribution describing the spread of possible values in quantitative/continuous data.</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
+          <t>Translation of one form of Location into another.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>- Geocoding usually refers to the translation of "address" or "intersection" to "direct Position." Many service providers also include a "reverse geocoding" interface to their geocoder, thus extending the definition of the service as a general translator of Location. Because routing services use internal Location encodings not usually available to others, a geocoder is an integral part of the internals of such a service.</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO 19133:2005; https://www.iso.org/standard/32551.html</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -2126,27 +2194,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Minimum Mapping Width</t>
+          <t>Band Central Wavelength</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>- core
-  - to be approved
-description: The width of the smallest linear Feature that is still represented on a map.</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>The width of the smallest linear Feature that is still represented on a map.</t>
+          <t>Single wavelength Value within the sensitivity interval of a spectroradiometric Sensor which represents the respective band. It could be either the mean, the median, the maximum sensitivity, or any other reasonable Value chosen to be representative.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>| Entry format example | Valid unit                                        |
+|----------------------|---------------------------------------------------|
+| 0.545 μm             | micrometre (μm), millimetre (mm), centimetre (cm) |</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>- CGLS</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -2169,29 +2242,20 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Deprecated Product</t>
+          <t>Cartographic Projection</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Products and collections that have been superseded by a newer version and are still available, but whose use is discouraged since they will be decommissioned in the future.</t>
+- to be defined</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Products and collections that have been superseded by a newer version and are still available, but whose use is discouraged since they will be decommissioned in the future.</t>
-        </is>
-      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
-        </is>
-      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
@@ -2212,31 +2276,26 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Period Identifier</t>
+          <t>Copernicus Service Provider</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Temporal reference in the form of a label or code that identifies a Period.</t>
+- to be discussed</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Temporal reference in the form of a label or code that identifies a Period.</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>- Period Identifiers are the temporal equivalent of geographic identifiers as specified in ISO 19912.</t>
-        </is>
-      </c>
+          <t>Institutional body, organisation or programme that provides reliable, trusted (authoritative?) EO Information and that has the financial resources to sustain the provision. It utilises satellite Data, ground-based measurements, and other sources to generate accurate and timely Data products related to various aspects of the Earth's environment, such as land, Atmosphere, oceans, and climate.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>- ISO 19170:2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -2259,20 +2318,20 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Lead Time</t>
+          <t>Location Error</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>- core
   - to be approved
-description: Minimum time of interval between an Observation being tasked and being performed.</t>
+description: Measure of the agreement between the represented Location of an Object and the true Location.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Minimum time of interval between an Observation being tasked and being performed.</t>
+          <t>Measure of the agreement between the represented Location of an Object and the true Location.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2302,25 +2361,29 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Calibration</t>
+          <t>Version Control</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>- core
-- source missing
-- to be discussed</t>
+- to be approved
+description: Method of working with collections, similar to version control systems used in traditional software development but optimized to allow better processing of data and collaboration in data analytics and research contexts.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Process of quantitatively defining a system's (e.g. a Sensor or Model's) response to known, controlled inputs produced for example by references. In Remote Sensing, it implies the collection of pre-flight and in-flight calibration measurements and in-situ Data that is to be used in the Data calibration processing routine.</t>
+          <t>Method of working with collections, similar to the version control systems used in traditional software development but optimized to allow better processing of data and collaboration in the context of data analytics, research, and any other form of data analysis.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>- [Wikipedia](https://en.wikipedia.org/wiki/Data_version_control)</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
@@ -2341,26 +2404,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Climate Projection</t>
+          <t>Data Access</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>- core
-- to be approved</t>
+- to be discussed
+description: Service to disseminate Data.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Simulated response of the climate system to a scenario of future emission or concentration of greenhouse gases (GHGs) and aerosols, generally derived using climate models. Climate Projections are distinguished from climate predictions by their dependence on the emission/concentration/radiative forcing scenario used, which is in turn based on assumptions concerning, for example, future socioeconomic and technological developments that may or may not be realised.</t>
+          <t>Service to disseminate Data.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>- IPCC</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -2383,31 +2447,26 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Spatial Reporting Unit</t>
+          <t>Collection Upgrade</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Smallest spatial object of interest that may be used for reporting and for which the information should be aggregated.</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Smallest spatial object of interest that may be used for reporting and for which the information should be aggregated.</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>- WIGOS 2019 uses 'spatial reporting interval', probably assuming observations are reported on a grid with regular spacing/intervals.</t>
-        </is>
-      </c>
+          <t>New and improved major version of all products within a collection due to comprehensive reprocessing.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -2430,27 +2489,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Source Data</t>
+          <t>Thematic Resolution</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Data required for production of an EO Collection (e.g., unenhanced satellite mission data) as well as further processed Level-1 data, or any other pre-processed format meeting program requirements.</t>
+description: Level of categorical detail of information expressed by the number of classes.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Data required for production of an EO Collection (e.g., unenhanced satellite mission data) as well as further processed Level-1 data (precision geometrically and radiometrically corrected radiance at the sensor), or any other pre-processed format that suppliers are providing access to that meets program requirements.</t>
+          <t>Level of categorical detail of information expressed by the number of classes.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- CGLS</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -2473,30 +2532,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>Standard Uncertainty</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>- core
-- to be approved</t>
+- to be approved
+description: Standard deviation of the probability distribution describing the spread of possible values in quantitative/continuous data.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Proximity of Measurement results to the accepted Value; precision is the degree to which repeated or reproducible measurements under unchanged conditions show the same results.</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>- In essence, Accuracy reflects how close measurements are to the accepted Value, while precision gauges the reliability and consistency of those measurements.</t>
-        </is>
-      </c>
+          <t>Standard deviation of the probability distribution describing the spread of possible values in quantitative/continuous data.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>- BS ISO 5725-1</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -2519,27 +2575,30 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Policy Making</t>
+          <t>Coverage Interval</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>- high-impact
-- to be discussed
-description: Process by which governments translate their political vision into programmes and actions to deliver outcomes — desired change in the real world.</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>- core
+- to be approved</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Coverage extent</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Process by which governments translate their political vision into programmes and actions to deliver outcomes — desired change in the real world.</t>
+          <t>Range or specific subset of values associated with a coverage dataset.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>- [ESA/CEOS?, modified](https://digital-strategy.ec.europa.eu/en/library/quality-public-administration-toolbox-practitioners)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -2562,32 +2621,31 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Path</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>- base
-- to be discussed
-- controversial
-description: Place referenced by a single set of coordinates within a coordinate reference system.</t>
+- to be approved
+description: "Line defined in an algorithmic way using at least two positions (can be open-ended). Alternative: line connecting two positions in an algorithmic way (limited by end points)."</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Place referenced by a single set of coordinates within a coordinate reference system.</t>
+          <t>Line defined in an algorithmic way using at least two positions (can be open-ended). Alternative: line connecting two positions in an algorithmic way (limited by end points).</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>- Opposite to (previous) ISO definition, Position shall be used only for 0-dimensional primitives (points).</t>
+          <t>- A Path is a 1-dimensional Place.</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>- ISO 19133:2005, modified to cover only points, also called 'direct position'</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -2610,27 +2668,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Minimum Mapping Unit</t>
+          <t>Source Data</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>- core
-  - to be approved
-description: The area of the smallest Feature that is still represented on a map.</t>
+- to be approved
+description: Data required for production of an EO Collection (e.g., unenhanced satellite mission data) as well as further processed Level-1 data, or any other pre-processed format meeting program requirements.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>The area of the smallest Feature that is still represented on a map.</t>
+          <t>Data required for production of an EO Collection (e.g., unenhanced satellite mission data) as well as further processed Level-1 data (precision geometrically and radiometrically corrected radiance at the sensor), or any other pre-processed format that suppliers are providing access to that meets program requirements.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>- CGLS</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -2653,27 +2711,26 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Spectral Band</t>
+          <t>Atmosphere</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Part of the electromagnetic spectrum of specific wavelengths, in remote sensing usually described by central wavelength and bandwidth.</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Part of the electromagnetic spectrum of specific wavelengths. In Remote Sensing, usually described by central wavelength and bandwidth.</t>
+          <t>Layer of gases, commonly known as air, including suspended liquid and solid particles known as aerosols (incl. dust, clouds, snow and ice).</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -2696,37 +2753,65 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Geopositioning</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>- core
-- to be discussed
-description: Determination of the geographic Position of a point (0D) or linear (1D) Feature.</t>
+- to be approved
+description: Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Determination of the geographic Position of a point (0D) or linear (1D) Feature.</t>
+          <t>Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>- Modified from: ISO 19130-1:2018, 3.36</t>
+          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>- ISO/TS 19101‑2:2008, 4.41</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Process aimed at verifying that the specified requirements are achieved or compliant. Involves comparing mission products with representative reference data, considering various observation conditions, ensuring the quality and traceability of the reference data used.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>- BIPM; QA4EO; ESA?, modified</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Assurance that a product, service, or system meets the needs of the customer and other identified stakeholders. Often involves acceptance and suitability with external customers.</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>- EU-US Land Imaging EO Collaboration</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
@@ -2739,26 +2824,32 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Collection Update</t>
+          <t>Long Term Preservation</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>- core
-- to be approved</t>
+  - to be approved
+description: The act of maintaining information in a correct and independently understandable form over the long term.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Minor revisions to a relatively small number of products within a collection for the purpose of correcting errors and maintaining consistent quality.</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
+          <t>The act of maintaining information in a correct and independently understandable form over the long term.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>- Long term refers to a period of time long enough to be concerned with the impact which changing technologies, including support for media and data formats, and changing user communities will have on the information being held in a repository.
+- See also preservation.</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
@@ -2781,60 +2872,40 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Verification</t>
+          <t>Catalogue</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Provision of objective evidence that a given item fulfils specified requirements.</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Provision of objective evidence that a given item fulfils specified requirements.</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>- When applicable, measurement uncertainty should be taken into consideration.
-- The item may be, e.g. a Process, measurement procedure, material, compound, or measuring system.
-- The specified requirements may be, e.g. that a manufacturer's specifications are met.
-- Verification should not be confused with Calibration. Not every verification is a Validation.</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
+          <t>System that provides users with discovery of information on which EO products can be obtained.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>- A 'Product Catalogue' can organise products and collections with varying access levels depending on product and user type.</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>- ISO/IEC Guide 99:2007, 2.44</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Evaluation of whether or not a product, service, or system complies with a regulation requirement, specification, or imposed condition. Often an internal Process.</t>
-        </is>
-      </c>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>- EU-US Land Imaging EO Collaboration</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Means to evaluate the reliability of the data in the absence of a reference dataset, allowing for an assessment of its standalone performance. Involves confirming the consistency and internal coherence of the data without direct comparison to external reference sources.</t>
-        </is>
-      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
+      <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
@@ -2847,30 +2918,27 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Earth Observation Based Output</t>
+          <t>Minimum Mapping Unit</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Higher-level processing and integration output (indicative level 4 and beyond) that goes beyond basic data processing, often designed for policy or decision-making needs.</t>
+  - to be approved
+description: The area of the smallest Feature that is still represented on a map.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Higher-level processing and integration output (indicative level 4 and beyond) that goes beyond basic data processing. These outputs are often designed specifically for policy or decision-making needs, and can be categorized into sub-categories:
-- Outputs from models/model integration: use of EO products as inputs in numerical models or combining them with other data sources in modelling frameworks.
-- Indicator-based outputs: EO products transformed through specialized algorithms (including statistical methods, machine learning, and pattern recognition) to create meaningful metrics based on spatio-temporal analysis.
-- Outputs from reanalysis: merging of EO products with other observations and models, creating consistent long-term records of past atmospheric, oceanic, and land surface conditions, and filling gaps through data assimilation techniques.</t>
+          <t>The area of the smallest Feature that is still represented on a map.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- CGLS</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
@@ -2893,20 +2961,35 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cartographic Projection</t>
+          <t>Temporal Reporting Period</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>- core
-- to be defined</t>
+- to be approved
+description: Time period used for reporting and for which the information should be aggregated from the native temporal resolution.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Time Period used for reporting and for which the information should be aggregated from the native Temporal Resolution.</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>| Entry format example | Valid unit                     |
+|----------------------|-------------------------------|
+| 1 s, 2 h, 1 d        | second, hour, day, month, year |</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>- Modified WIGOS Metadata Standard 2019</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
@@ -2927,33 +3010,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Temporal Reporting Period</t>
+          <t>Policy File</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>- core
-- to be approved
-description: Time period used for reporting and for which the information should be aggregated from the native temporal resolution.</t>
+          <t>- high-impact
+- to be discussed
+description: Policy documents that represent the official written reference for a given Policy.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Time Period used for reporting and for which the information should be aggregated from the native Temporal Resolution.</t>
+          <t>Policy documents that represent the official written reference for a given Policy.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>| Entry format example | Valid unit                     |
-|----------------------|-------------------------------|
-| 1 s, 2 h, 1 d        | second, hour, day, month, year |</t>
-        </is>
-      </c>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>- Modified WIGOS Metadata Standard 2019</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
@@ -2976,27 +3053,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Reproducibility</t>
+          <t>Impact</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Concerned with the validity of the results of a particular study, enabling readers to check whether results have been manipulated by reproducing exactly the same study using the same data and methods.</t>
+  - to be discussed
+description: Regarded long-term according to X. However, in the Horizon Europe Missions terminology, regarded short-term.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Concerned with the validity of the results of a particular study, i.e., the possibility for readers to check whether results have been manipulated, by reproducing exactly the same study using the same data and methods.</t>
+          <t>Regarded long-term according to X. However, in the Horizon Europe Missions terminology, regarded short-term.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>- Ostermann and Granell (2015)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
@@ -3019,28 +3096,25 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Atmosphere</t>
+          <t>Calibration</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>- core
-- to be approved</t>
+- source missing
+- to be discussed</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Layer of gases, commonly known as air, including suspended liquid and solid particles known as aerosols (incl. dust, clouds, snow and ice).</t>
+          <t>Process of quantitatively defining a system's (e.g. a Sensor or Model's) response to known, controlled inputs produced for example by references. In Remote Sensing, it implies the collection of pre-flight and in-flight calibration measurements and in-situ Data that is to be used in the Data calibration processing routine.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>- Guth et al. 2021</t>
-        </is>
-      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
@@ -3061,39 +3135,51 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Geolocating</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>- core
+          <t>- base
 - to be approved
-description: Geopositioning of an Object using a Physical Sensor Model or a True Replacement Model.</t>
+description: Value and possibly Uncertainty of a Trait of a specific Entity.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Geopositioning of an Object using a Physical Sensor Model or a True Replacement Model.</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
+          <t>Value and possibly Uncertainty of a Trait of a specific Entity.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>- Data simply describe entities using certain traits and are not targeted at a particular use or audience.</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Data can be categorised into:
+- factual (i.e. obtained by Observation) or fictional (obtained e.g. through modelling, estimating or assigning)
+- quantitative (continuous) or qualitative (categorical)
+- analogue or digital
+(list not exhaustive!)</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>- ISO 19115-2:2009, 4.11</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Determination of the geographic location of a feature of two or more dimensions.</t>
+          <t>Scientific or technical measurements, values calculated therefrom, observations, or facts that can be represented by numbers, tables, graphs, models, text, or symbols which are used as a basis for reasoning and further calculation.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>- ISO 19130-1:2018, 3.36 ('geopositioning'), modified</t>
+          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
@@ -3112,32 +3198,41 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Confidence Interval</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>- controversial
-- to be approved</t>
+          <t>- base
+- to be approved
+description: Property having a magnitude that can be expressed as a number from a continuous and contiguous range and a reference.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Probability that the Quantity lies in the interval, conditioned on the measuring or modelling assumptions.</t>
+          <t>Property having a magnitude that can be expressed as a number from a continuous and contiguous range and a reference.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>- ISO/IEC Guide 99:2007, 1.1, modified — Notes omitted</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Property whose instances can be compared by ratio or only by order.</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>- gEOGlos (VIM4 Notes omitted)</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
@@ -3154,19 +3249,20 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Baseline</t>
+          <t>Policy Milestone</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>- core
-- to be approved</t>
+          <t>- high-impact
+- to be discussed
+description: Markers of significant progress in addressing specific issues, or crucial decision points where significant choices are made within a policy process.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Reference Period, time or measure against which the Information is assessed or compared.</t>
+          <t>Markers of significant progress in addressing specific issues, or crucial decision points where significant choices are made. Concrete examples include: policy planning and proposing, impact assessment, implementation, or implementation cycles (e.g., Water Framework Directive, Marine Strategy Framework Directive), achievement of Policy Objectives and Policy Targets, and evaluating and improving existing laws.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -3176,18 +3272,10 @@
           <t>- KCEO</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>Source data that has been processed to a common set of requirements and organised into a form that allows immediate analysis and interoperability through time and with other collections.</t>
-        </is>
-      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
-        </is>
-      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
@@ -3204,26 +3292,32 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Classification System Levels</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>- core
-- to be discussed</t>
+          <t>- base
+- to be approved
+description: Element of a type domain.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Levels in a hierarchical Classification System.</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
+          <t>Element of a type domain.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>- A Value may consider a possible state of an object within a class or type (domain).
+- A data value is an instance of a data type, a value without identity.</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO/IEC 19501:2005, 0000_5</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -3246,27 +3340,26 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Latency</t>
+          <t>Collection Update</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>- core
-  - to be discussed
-description: Period between the end of sensing of a Phenomenon to the beginning of availability of a specific product.</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Period between the end of sensing of a Phenomenon to the beginning of availability of a specific product.</t>
+          <t>Minor revisions to a relatively small number of products within a collection for the purpose of correcting errors and maintaining consistent quality.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>- ?</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -3289,20 +3382,33 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Laboratory Observation</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>- core
-  - to be defined</t>
+  - to be discussed
+description: Usually in-situ observations in which the Object or Phenomenon is isolated from other systems or altered in its original conditions or environment.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Usually in-situ observations in which the Object or Phenomenon is isolated from other systems or altered in its original conditions or environment.</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>- It is important to consider that Laboratory Observations are typically conducted in controlled conditions, allowing for isolation or alteration of the Object or Phenomenon from its natural environment or other systems.</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
@@ -3323,29 +3429,21 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Access</t>
+          <t>Environmental Process</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>- core
-- to be discussed
-description: Service to disseminate Data.</t>
+- to be defined
+description: ""</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Service to disseminate Data.</t>
-        </is>
-      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
@@ -3366,27 +3464,27 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Phenomenon</t>
+          <t>Measurement Uncertainty</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>- base
-- to be approved
-description: Entity with at least one Property referenced by an identifier.</t>
+          <t>- core
+  - to be discussed
+description: Uncertainty associated with the method of Measurement.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Entity with at least one Property referenced by an identifier.</t>
+          <t>Uncertainty associated with the method of Measurement.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>- KCEO, modified after Wikipedia and the Columbia Encyclopaedia 2008</t>
+          <t>- CEOS Wiki adopted from JCGM GUM</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
@@ -3409,40 +3507,20 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Earth Spheres</t>
+          <t>Continuity</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Spheres dividing planet Earth into subsystems, which are collectives of (physical) matter sharing specific traits.</t>
+  - to be defined</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Spheres dividing planet Earth into subsystems, which are collectives of (physical) matter sharing specific traits.</t>
-        </is>
-      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>- Atmosphere
-- Hydrosphere
-- Cryosphere
-- Biosphere
-- Lithosphere
-- Anthroposphere</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>- Hugget, R., et al., 2024, DOI: 10.1177/03091333241275465
-- Guth, P., et al., 2021, https://doi.org/10.3390/rs13183581
-- Martin, Y.E., et al., 2012</t>
-        </is>
-      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
@@ -3463,32 +3541,38 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Temporal Revisit</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>- base
-- to be approved
-description: Element of a type domain.</t>
+          <t>- core
+- to be discussed
+description: Interval between successive observations.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Element of a type domain.</t>
+          <t>Interval between successive observations.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>- A Value may consider a possible state of an object within a class or type (domain).
-- A data value is an instance of a data type, a value without identity.</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
+          <t>- In Remote Sensing it is also called repeat cycle.
+- More generally it is known as temporal sampling interval.</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>| Entry format example | Valid unit                     |
+|----------------------|-------------------------------|
+| 1 s, 2 h             | second, hour, day, month, year |</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>- ISO/IEC 19501:2005, 0000_5</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
@@ -3511,37 +3595,20 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Timeliness</t>
+          <t>Resolution</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Period between the moment of requesting information and the moment of availability of information.</t>
+  - to be defined</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Period between the moment of requesting information and the moment of availability of information.
-- Near Real-Time (NRT): delivered less than 3 hours after requesting information.
-- Slow-Time Critical (STC): delivered within 48 hours after requesting information.
-- Non-Time Critical (NTC): typically delivered within 1 month after requesting information.</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>- In some contexts also known as delivery time.
-- C3S URDB describes timeliness as "the ability of the publish/subscribe middleware to provide the expected service within known time bounds".</t>
-        </is>
-      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>- Adapted from ESA S3 User Guide</t>
-        </is>
-      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
@@ -3562,59 +3629,41 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Auxiliary Data</t>
+          <t>Period Identifier</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>- core
-- to be approved</t>
+- to be approved
+description: Temporal reference in the form of a label or code that identifies a Period.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Data that enhance the processing and utilisation of main Sensor Data. Auxiliary Data are usually not captured by the same Data collection Process or on the same platform as the main Sensor Data. Examples include meteorological Data received from ECMWF/Met Offices or DEMs. Auxiliary Data help in Data processing, but are also Data sets in their own right.</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr"/>
+          <t>Temporal reference in the form of a label or code that identifies a Period.</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>- Period Identifiers are the temporal equivalent of geographic identifiers as specified in ISO 19912.</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>- ESA/CEOS?, modified
-- ENMAP Glossary of Terms, https://www.enmap.org/Data/doc/EnMAP_Terms.pdf, 20210624
-- EO Data Stewardship Glossary</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Data required to perform processing of Sensor Data which is not obtained from the Sensor itself. Includes: (a) Data provided by the spacecraft (e.g. orbit Position and velocity, attitude, instrument house-keeping Data, on-board time); (b) Data not available from on-board sources.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>For EnMAP, this includes (a) orbit files, attitude files, Calibration Data, instrument house-keeping Data; (b) atmospheric parameters, reference images.</t>
-        </is>
-      </c>
+          <t>- ISO 19170:2021</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>- ENMAP Glossary of Terms, https://www.enmap.org/Data/doc/EnMAP_Terms.pdf, 20210624
-- EO Data Stewardship Glossary</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>Data required for instrument processing that does not originate in the instrument itself or from the satellite. Some Auxiliary Data will be generated in the ground segment, whilst other Data will be provided from external sources.</t>
-        </is>
-      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>- CEOS-ARD PFS template 20220302</t>
-        </is>
-      </c>
+      <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
@@ -3675,41 +3724,41 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Quantity</t>
+          <t>Timeliness</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>- base
+          <t>- core
 - to be approved
-description: Property having a magnitude that can be expressed as a number from a continuous and contiguous range and a reference.</t>
+description: Period between the moment of requesting information and the moment of availability of information.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Property having a magnitude that can be expressed as a number from a continuous and contiguous range and a reference.</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr"/>
+          <t>Period between the moment of requesting information and the moment of availability of information.
+- Near Real-Time (NRT): delivered less than 3 hours after requesting information.
+- Slow-Time Critical (STC): delivered within 48 hours after requesting information.
+- Non-Time Critical (NTC): typically delivered within 1 month after requesting information.</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>- In some contexts also known as delivery time.
+- C3S URDB describes timeliness as "the ability of the publish/subscribe middleware to provide the expected service within known time bounds".</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>- ISO/IEC Guide 99:2007, 1.1, modified — Notes omitted</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Property whose instances can be compared by ratio or only by order.</t>
-        </is>
-      </c>
+          <t>- Adapted from ESA S3 User Guide</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>- gEOGlos (VIM4 Notes omitted)</t>
-        </is>
-      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
@@ -3726,33 +3775,20 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Final Product Version</t>
+          <t>Equivalence</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Product within an EO Collection that is not expected to be updated.</t>
+  - to be defined</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Product within an EO Collection that is not expected to be updated.</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>- In its production, all of the prerequisite auxiliary data were used as input.</t>
-        </is>
-      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
-        </is>
-      </c>
+      <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
@@ -3773,32 +3809,27 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Hydrosphere</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>- controversial
-  - to be discussed
-description: Act of determining the Value of a Property by interacting in a reproducible way with the Phenomenon using a Sensor.</t>
+          <t>- core
+  - to be approved
+description: The masses of liquid water, such as oceans, lakes, and rivers.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Act of determining the Value of a Property by interacting in a reproducible way with the Phenomenon using a Sensor.</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>- The result of an Observation is a Value complemented by an Uncertainty, often itself being referred to as 'observation'.
-- An Observation result represents a Sample of the Phenomenon (otherwise it would be identical with the Phenomenon).</t>
-        </is>
-      </c>
+          <t>The masses of liquid water, such as oceans, lakes, and rivers.</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
@@ -3821,56 +3852,36 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Characteristic</t>
+          <t>Accuracy</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>- base
-- to be discussed</t>
+          <t>- core
+- to be approved</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Distinguishing Feature.</t>
+          <t>Proximity of Measurement results to the accepted Value; precision is the degree to which repeated or reproducible measurements under unchanged conditions show the same results.</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>- A Characteristic can be inherent or assigned.
-- A Characteristic can be qualitative or quantitative.
-- There are various classes of Characteristics, such as the following:
-  - physical (e.g. mechanical, electrical, chemical, biological);
-  - sensory (e.g. relating to smell, touch, taste, sight, hearing);
-  - behavioural (e.g. courtesy, honesty, veracity);
-  - temporal (e.g. punctuality, reliability, availability);
-  - ergonomic (e.g. physiological characteristic or related to human safety);
-  - functional (e.g. maximum speed of an aircraft).</t>
+          <t>- In essence, Accuracy reflects how close measurements are to the accepted Value, while precision gauges the reliability and consistency of those measurements.</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>- ISO 9000:2005, 3.5.1</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Abstraction of a Property of an Object or of a set of objects.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>- Characteristics are used for describing Concepts.</t>
-        </is>
-      </c>
+          <t>- BS ISO 5725-1</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>- ISO 1087-1:2000, 3.2.4; ISO 19146:2010(E); https://www.iso.org/standard/20057.html</t>
-        </is>
-      </c>
+      <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
@@ -3887,27 +3898,27 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Geosphere</t>
+          <t>Traceability</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>- core
-  - to be approved
-description: The masses of minerals that constitute planet Earth.</t>
+- to be approved
+description: Property of a measurement result whereby the result can be related to a reference through a documented unbroken chain of calibrations each contributing to the measurement uncertainty.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>The masses of minerals that constitute planet Earth.</t>
+          <t>Property of a measurement result whereby the result can be related to a Reference through a documented unbroken chain of calibrations, each contributing to the measurement uncertainty.</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- https://www.isobudgets.com/Measurement-traceability-complying-iso-17025-requirements/</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -3930,27 +3941,26 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Spectral Resolution</t>
+          <t>Biosphere</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Measure of the ability to resolve features in the electromagnetic spectrum.</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Measure of the ability to resolve features in the electromagnetic spectrum.</t>
+          <t>Masses of living organisms, such as vegetation and animals, including dead but still connected parts such as roots, trunks or branches.</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
@@ -3973,27 +3983,31 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Hydrosphere</t>
+          <t>Update Frequency</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>- core
-  - to be approved
-description: The masses of liquid water, such as oceans, lakes, and rivers.</t>
+- to be approved
+description: Frequency at which the product is available to users.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>The masses of liquid water, such as oceans, lakes, and rivers.</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr"/>
+          <t>Frequency at which the product is available to users.</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>- Also known in product catalogues as dissemination frequency.</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
@@ -4016,34 +4030,27 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Time of Year</t>
+          <t>Lithosphere</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Time of the year at which the variable is observed or simulated by a model.</t>
+  - to be approved
+description: The solid, inanimate outer layer of the Geosphere. For the purposes of Earth Observation, includes soils ('pedosphere').</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Time of the year at which the variable is observed or simulated by a model.</t>
+          <t>The solid, inanimate outer layer of the Geosphere. For the purposes of Earth Observation, the Lithosphere is considered to include soils ('pedosphere').</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>| Type      | Entry format example | Valid unit     |
-|-----------|----------------------|----------------|
-| timestamp | m/d                  | Not Applicable |
-| timerange | m/d - m/d            | Not Applicable |</t>
-        </is>
-      </c>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
@@ -4066,25 +4073,25 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Path</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>- base
-- to be approved
-description: "Line defined in an algorithmic way using at least two positions (can be open-ended). Alternative: line connecting two positions in an algorithmic way (limited by end points)."</t>
+  - to be approved
+description: The result of organisation, interpretation, categorisation, classification, or some other form of processing of Data attaching to it a certain meaning that can be understood by the addressee.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Line defined in an algorithmic way using at least two positions (can be open-ended). Alternative: line connecting two positions in an algorithmic way (limited by end points).</t>
+          <t>The result of organisation, interpretation, categorisation, classification, or some other form of processing of Data attaching to it a certain meaning that can be understood by the addressee.</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>- A Path is a 1-dimensional Place.</t>
+          <t>- Information depends on Data and is targeted.</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
@@ -4113,20 +4120,20 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Spatial Consistency</t>
+          <t>Temporal Consistency</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Condition where the spatial statistical properties of the data depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
+description: Condition where the temporal statistical properties of the sample depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Condition where the spatial statistical properties of the data depend only on the underlying physical processes and not on other factors such as fusing different products or sensors. Also, the validity of the assumptions of the procedure to produce information holds true across the whole spatial range.</t>
+          <t>Condition where the temporal statistical properties of the Sample depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -4156,30 +4163,32 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cell</t>
+          <t>Metadata</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>- core
-- to be approved</t>
+  - to be approved
+description: Data describing other data, providing an understanding of the content and utility of a product or collection.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Spatial, spatio-temporal zone or temporal unit of geometry with dimensionality greater than 0, associated with a zone.</t>
+          <t>Data describing other data, providing an understanding of the content and utility of a product or collection.</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>- Cells are the unit of geometry in a DGGS, and the geometry of the region of space-time occupied by a zone is a Cell.</t>
+          <t>- Metadata may be used to select data for a particular scientific investigation.
+- Metadata is intended as information describing significant aspects of a resource (Earth Observation space data in this context). They are created for the purposes of data search, discovery and access management and may exist at various levels, typically from data collection through to the individual variables of each product in a collection.</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>- ISO 19170:2021</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
@@ -4202,26 +4211,23 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Business Continuity</t>
+          <t>Spatial Resolution</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>- core
-- to be approved</t>
+- to be defined
+description: ''</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>An organisation's readiness to continue functioning during times of disruption.</t>
-        </is>
-      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
@@ -4244,32 +4250,27 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Derivative Product</t>
+          <t>Phenomenon</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>- core
+          <t>- base
 - to be approved
-description: Product additionally processed from baseline or unenhanced mission data.</t>
+description: Entity with at least one Property referenced by an identifier.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Product additionally processed from baseline or unenhanced mission data.</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>- Generally either a compilation of time-series data (e.g., all time, annual, monthly or seasonal summary data, &gt; Level 3) or thematic versions of each individual data tile of baseline data.
-- Derived products are citable via a Digital Object Identifier (DOI).</t>
-        </is>
-      </c>
+          <t>Entity with at least one Property referenced by an identifier.</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- KCEO, modified after Wikipedia and the Columbia Encyclopaedia 2008</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
@@ -4292,27 +4293,27 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Policy Objective</t>
+          <t>Geolocation Information</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>- high-impact
+          <t>- core
 - to be discussed
-description: Desired outcome that policymakers wish to achieve.</t>
+description: Information used to determine geographic Location.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Desired outcome that policymakers wish to achieve.</t>
+          <t>Information used to determine geographic Location.</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO 19130-1:2018, 3.34</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
@@ -4335,63 +4336,58 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Verification</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
+description: Provision of objective evidence that a given item fulfils specified requirements.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
+          <t>Provision of objective evidence that a given item fulfils specified requirements.</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
+          <t>- When applicable, measurement uncertainty should be taken into consideration.
+- The item may be, e.g. a Process, measurement procedure, material, compound, or measuring system.
+- The specified requirements may be, e.g. that a manufacturer's specifications are met.
+- Verification should not be confused with Calibration. Not every verification is a Validation.</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>- ISO/TS 19101‑2:2008, 4.41</t>
+          <t>- ISO/IEC Guide 99:2007, 2.44</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Process aimed at verifying that the specified requirements are achieved or compliant. Involves comparing mission products with representative reference data, considering various observation conditions, ensuring the quality and traceability of the reference data used.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
-        </is>
-      </c>
+          <t>Evaluation of whether or not a product, service, or system complies with a regulation requirement, specification, or imposed condition. Often an internal Process.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
-          <t>- BIPM; QA4EO; ESA?, modified</t>
+          <t>- EU-US Land Imaging EO Collaboration</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Assurance that a product, service, or system meets the needs of the customer and other identified stakeholders. Often involves acceptance and suitability with external customers.</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
-        </is>
-      </c>
+          <t>Means to evaluate the reliability of the data in the absence of a reference dataset, allowing for an assessment of its standalone performance. Involves confirming the consistency and internal coherence of the data without direct comparison to external reference sources.</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr">
         <is>
-          <t>- EU-US Land Imaging EO Collaboration</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="P84" t="inlineStr"/>
@@ -4406,36 +4402,27 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Temporal Extent</t>
+          <t>Property</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>- core
-- to be approved
-description: Period during which data was collected, observations were made, or for which the model was run.</t>
+          <t>- base
+- to be discussed
+description: Observable Trait.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Period during which data was collected, observations were made, or for which the model was run.</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>- In W3C this is the definition of temporal coverage.
-- Time Period covered by a series of observations inclusive of the specified date/time indications (measurement history). Defined based on the beginning and end dates of observations.</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>- WIGOS Metadata</t>
-        </is>
-      </c>
+          <t>Observable Trait.</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>- Adapted from W3C</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
@@ -4458,27 +4445,27 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Traceability</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>- core
-- to be approved
-description: Property of a measurement result whereby the result can be related to a reference through a documented unbroken chain of calibrations each contributing to the measurement uncertainty.</t>
+          <t>- base
+  - to be approved
+description: Entity with a well-defined boundary and identity that encapsulates state and behaviour.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Property of a measurement result whereby the result can be related to a Reference through a documented unbroken chain of calibrations, each contributing to the measurement uncertainty.</t>
+          <t>Entity with a well-defined boundary and identity that encapsulates state and behaviour.</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>- https://www.isobudgets.com/Measurement-traceability-complying-iso-17025-requirements/</t>
+          <t>- ISO/IEC 19501:2005</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
@@ -4501,31 +4488,38 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Decommissioned Product</t>
+          <t>Time of Day</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Products and collections that have been superseded by new versions and are no longer available.</t>
+description: Time of the day at which the variable or parameter is observed or simulated by a model.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Products and collections that have been superseded by new versions and are no longer available.</t>
+          <t>Time of the day at which the variable or parameter is observed or simulated by a model.</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>- Decommissioned products are no longer supported, i.e. corrections will not be made, new data will not be added, and support is not available.</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr"/>
+          <t>- In Remote Sensing it is also known as time of overpass.</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>| Type      | Entry format example | Valid unit |
+|-----------|----------------------|------------|
+| timestamp | 18:00 h (0–24)       | Hours      |
+| timerange | 18:00 – 20:00 h      | Hours      |</t>
+        </is>
+      </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
@@ -4548,32 +4542,27 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Grid</t>
+          <t>Obsolete Product or Collection</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>- core
   - to be approved
-description: Network composed of two or more sets of curves in which the members of each set intersect the members of the other sets in an algorithmic way.</t>
+description: Products or collections which have been superseded by later versions of a product or collection.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Network composed of two or more sets of curves in which the members of each set intersect the members of the other sets in an algorithmic way.</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>- The curves partition a space into grid cells or zones.
-- The intersection points of the curves are called nodes.</t>
-        </is>
-      </c>
+          <t>Products or collections which have been superseded by later versions of a product or collection.</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>- ISO 19123:2005, 4.1.23; Note 1 modified; Note 2 added</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
@@ -4596,37 +4585,40 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Measurement</t>
+          <t>Baseline</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>- core
-  - to be discussed
-description: Observation of a Quantity.</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Observation of a Quantity.</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>- The Process of collecting a measurement is called measuring.</t>
-        </is>
-      </c>
+          <t>Reference Period, time or measure against which the Information is assessed or compared.</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>- GEOGlos (VIM ?, modified)</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>- KCEO</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Source data that has been processed to a common set of requirements and organised into a form that allows immediate analysis and interoperability through time and with other collections.</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
@@ -4643,30 +4635,32 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Catalogue</t>
+          <t>Earth Observation</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>- core
-- to be approved</t>
+          <t>- high-impact
+- to be discussed
+description: Science domain dealing with technologies and methods of collecting and analyzing observations about the different Earth spheres.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>System that provides users with discovery of information on which EO products can be obtained.</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>- A 'Product Catalogue' can organise products and collections with varying access levels depending on product and user type.</t>
-        </is>
-      </c>
+          <t>Science domain dealing with technologies and methods of collecting and analyzing observations about the different Earth spheres.</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>- Earth Observation (EO) can be categorised by location of the sensor into space-borne, air-borne, sea-borne, ground-based, underwater and underground EO.
+- Earth Observation (EO) includes Remote Sensing, such as satellite imagery, as well as in-situ observations, e.g., with ground-based devices.</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- Modified GEO definition [GEO (earthobservations.org)](https://earthobservations.org/resources#key)</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
@@ -4689,37 +4683,24 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Tolerance</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>- core
-- to be discussed
-description: Phenomenon whose values for specific properties are known and understood with an Uncertainty significantly lower than that of the Observation with which it is compared.</t>
+  - to be defined</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Phenomenon whose values for specific properties are known and understood with an Uncertainty significantly lower (quantify?) than that of the Observation with which it is compared.</t>
-        </is>
-      </c>
+      <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Sort of data acquired with an Uncertainty significantly lower (quantify?) than that of the data it is being compared with.</t>
-        </is>
-      </c>
+      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>- VIM?, modified</t>
-        </is>
-      </c>
+      <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
@@ -4736,27 +4717,23 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Laboratory Observation</t>
+          <t>Spectral Resolution</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>- core
-  - to be discussed
-description: Usually in-situ observations in which the Object or Phenomenon is isolated from other systems or altered in its original conditions or environment.</t>
+- to be approved
+description: Measure of the ability to resolve features in the electromagnetic spectrum.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Usually in-situ observations in which the Object or Phenomenon is isolated from other systems or altered in its original conditions or environment.</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>- It is important to consider that Laboratory Observations are typically conducted in controlled conditions, allowing for isolation or alteration of the Object or Phenomenon from its natural environment or other systems.</t>
-        </is>
-      </c>
+          <t>Measure of the ability to resolve features in the electromagnetic spectrum.</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
@@ -4783,33 +4760,27 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sample</t>
+          <t>Near Real Time Data</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>- controversial
-- to be discussed
-description: Subset of one or more entities.</t>
+          <t>- high-impact
+  - to be discussed
+description: Data available for use with a specified (small and application dependent) latency, typically 3 hours for meteorological applications.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Subset of one or more entities.</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>- A Sample may be spatial, temporal, spectral, or in any other dimension or Trait.
-- Each Sample is contiguous, i.e. it does not consist of more than one discontinuous geometry in any dimension.
-- The Process of obtaining a Sample is called sampling.</t>
-        </is>
-      </c>
+          <t>Data available for use with a specified (small and application dependent) latency, typically 3 hours for meteorological applications.</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
@@ -4832,31 +4803,40 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Trait</t>
+          <t>Measurand</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>- base
-- to be approved
-description: Characteristic belonging to an entity and referenced by an identifier.</t>
+          <t>- core
+  - to be approved
+description: Particular Quantity subject to Measurement.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Characteristic belonging to an entity and referenced by an identifier.</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>- Traits can be objective (inherent?) in which case they are also observable and called properties. Traits which are not observable (directly or indirectly) need to be assigned.</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr"/>
+          <t>Particular Quantity subject to Measurement.</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>| Step | Process description |
+| :----- | :------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------
+--- |
+| (Raw) | The complete and unaltered/unprocessed set of Data acquired by one or several sensors on a platform |
+| M/0 uncalibrated | Unaltered/unprocessed Level 0 (main) Sensor Data annotated with processed Ancillary Data and supplemented by Auxiliary Data (including radiometric and geometric Calibration coefficients and geo-referencing parameters) allowing further processing to higher Levels. |
+| M/1 Sensor-calibrated | Level M/0 Sensor Data which have been calibrated (ideally traceable to SI) and spatially aligned (co-located, eventually co-gridded) to represent at-Sensor measurements (Value and Uncertainty) in Sensor nominal spatiotemporal sampling, supplemented by appropriate ancillary data. |
+| M/2 target-calibrated | Level M/1 Data processed to represent geophysical Property values (and uncertainties) for a specified target (Object, Feature of interest, e.g. surface reflectance, apparent temperature) derived from M/1 Sensor Data, as much as possible maintaining the sensors nominal spatial and temporal sampling (Observation preserving). |
+| M/3 homogenised | Level M/1 or M/2 Data which have been generalised and integrated across one or several platforms and acquisitions to achieve an increased, more regular or in any other form enhanced spatial or temporal coverage in which states geophysical values agnostic of the originally acquiring Sensor and Observation condition and thus directly comparable. This homogenisation and fusion may include measurand re-Calibration to external standards and references including use of modelling, aggregation and interpolation. |
+| M/4 derived/inferred | Model output or results from analyses of Level M/3 (or lower level) Data i.e., attributes that might not be directly observable by the Sensor(s) but are derived from observations in combination with other external incl. non-observational Data using techniques like modelling or machine learning (AI). |
+From http://doi.org/10.2760/46796</t>
+        </is>
+      </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>- Based on ISO 19143:2010, 4.21, ISO/IEC 2382:2015, 2121440, significantly modified, Note 1 added</t>
+          <t>- VIM: 1993, 2.6</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
@@ -4879,32 +4859,27 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Metadata</t>
+          <t>Latency</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>- core
-  - to be approved
-description: Data describing other data, providing an understanding of the content and utility of a product or collection.</t>
+  - to be discussed
+description: Period between the end of sensing of a Phenomenon to the beginning of availability of a specific product.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Data describing other data, providing an understanding of the content and utility of a product or collection.</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>- Metadata may be used to select data for a particular scientific investigation.
-- Metadata is intended as information describing significant aspects of a resource (Earth Observation space data in this context). They are created for the purposes of data search, discovery and access management and may exist at various levels, typically from data collection through to the individual variables of each product in a collection.</t>
-        </is>
-      </c>
+          <t>Period between the end of sensing of a Phenomenon to the beginning of availability of a specific product.</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- ?</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
@@ -4927,30 +4902,27 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Backup</t>
+          <t>Policy Target</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>- core
-- to be approved</t>
+          <t>- high-impact
+- to be discussed
+description: Specific level or rate set for the Policy Objective.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>General practice of making copies of current baseline and derived products of EO Collections at specified time intervals, and storing those copies in a manner that will not affect the data if the primary distribution environment is compromised.</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>- The emphasis is on the ability to retrieve a copy of the entire EO Collection on demand if the original data is lost or compromised.</t>
-        </is>
-      </c>
+          <t>Specific level or rate set for the Policy Objective.</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
@@ -4973,20 +4945,29 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Tolerance</t>
+          <t>Policy Objective</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>- core
-  - to be defined</t>
+          <t>- high-impact
+- to be discussed
+description: Desired outcome that policymakers wish to achieve.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Desired outcome that policymakers wish to achieve.</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
@@ -5007,30 +4988,27 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Archive</t>
+          <t>Forecast Range</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>- core
-- to be approved</t>
+- to be discussed
+description: The forecast period.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>System that stores data products, guaranteeing their preservation for future use.</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>- This function includes all operations to identify, store and retrieve the data and ensure their integrity.</t>
-        </is>
-      </c>
+          <t>The forecast period.</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
@@ -5053,26 +5031,27 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Biosphere</t>
+          <t>Quality Indicator</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>- core
-- to be approved</t>
+- to be approved
+description: Indicator providing sufficient information to allow all users to readily evaluate the fitness for purpose of the data or derived product.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Masses of living organisms, such as vegetation and animals, including dead but still connected parts such as roots, trunks or branches.</t>
+          <t>Indicator providing sufficient information to allow all users to readily evaluate the fitness for purpose of the data or derived product. May be a number, set of numbers, graph, Uncertainty budget, or a simple flag.</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- CEOS Wiki</t>
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
@@ -5095,27 +5074,27 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Impact</t>
+          <t>User Interface</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>- core
-  - to be discussed
-description: Regarded long-term according to X. However, in the Horizon Europe Missions terminology, regarded short-term.</t>
+- to be approved
+description: Set of all the components of an interactive system that provide information and controls for the user to accomplish specific tasks with the interactive system.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Regarded long-term according to X. However, in the Horizon Europe Missions terminology, regarded short-term.</t>
+          <t>Set of all the components of an interactive system that provide information and controls for the User to accomplish specific tasks with the interactive system.</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO 9241-110:2020, 3.10</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
@@ -5138,27 +5117,31 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Obsolete Product or Collection</t>
+          <t>Stability</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>- core
-  - to be approved
-description: Products or collections which have been superseded by later versions of a product or collection.</t>
+- to be approved
+description: Maximum acceptable change in Uncertainty per decade.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Products or collections which have been superseded by later versions of a product or collection.</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr"/>
+          <t>Maximum acceptable change in Uncertainty per decade.</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>- GCOS uses bias or systematic errors instead of Uncertainty.</t>
+        </is>
+      </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- Modified from GCOS 2022</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
@@ -5181,27 +5164,26 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Measurement Uncertainty</t>
+          <t>Classification System</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>- core
-  - to be discussed
-description: Uncertainty associated with the method of Measurement.</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Uncertainty associated with the method of Measurement.</t>
+          <t>Nomenclature used to classify Information into categorical thematic classes (e.g., EUNIS, MAES ecosystems, Corine Land Cover, LCCS).</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>- CEOS Wiki adopted from JCGM GUM</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
@@ -5224,18 +5206,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Spatial Resolution</t>
+          <t>Spatial Consistency</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>- core
-- to be defined
-description: ''</t>
+- to be approved
+description: Condition where the spatial statistical properties of the data depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Condition where the spatial statistical properties of the data depend only on the underlying physical processes and not on other factors such as fusing different products or sensors. Also, the validity of the assumptions of the procedure to produce information holds true across the whole spatial range.</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
@@ -5263,28 +5249,23 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>In-Situ Observation</t>
+          <t>Expanded Uncertainty</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>- controversial
-  - to be discussed
-description: Observations performed in the same Place where a Phenomenon occurs, normally without isolating it from other systems or altering its pre-Observation state.</t>
+          <t>- core
+- to be approved
+description: Standard Uncertainty multiplied by a coverage factor k, chosen to obtain a desired level of confidence.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Observations performed in the same Place where a Phenomenon occurs, normally without isolating it from other systems (its environment) or altering its pre-Observation state.</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>- The main Characteristic of such observations is that distance has no or only negligible (within Uncertainty) influence on the Value of the Property observed. In-Situ Observations therefore often require either direct physical contact or small distances between a Sensor and the observed Phenomenon.
-- Observations not fulfilling these conditions are considered Remote Sensing.</t>
-        </is>
-      </c>
+          <t>Standard Uncertainty multiplied by a coverage factor, k. The coverage factor is chosen to obtain a desired level of confidence. Most commonly a 95% confidence interval is chosen. For a Gaussian distribution, this is achieved with a coverage factor k = 2. (Note that strictly this provides a 95.45% confidence interval.)</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
@@ -5311,29 +5292,30 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Earth Observation Product</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Direct output from standardized satellite data processing chains (indicative levels 2 and 3), representing fundamental geophysical and biophysical variables.</t>
+description: Device or instrument suited (through physical/chemical interaction) to measure one or more properties of a Phenomenon and thus collect factual/objective data.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Direct output from standardized satellite data processing chains (indicative levels 2 and 3), representing fundamental geophysical and biophysical variables. These products demonstrate direct Traceability to original satellite measurements through rigorous Calibration and Validation processes. The processing methodology prioritizes the conversion of raw sensor data into quantifiable physical measurements, maintaining strict adherence to standardized processing protocols and Validation requirements.</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>- Soil moisture from microwave sensors
-- Forest canopy height from LiDAR data</t>
-        </is>
-      </c>
+          <t>Device or instrument suited (through physical/chemical interaction) to measure one or more properties of a Phenomenon and thus collect factual/objective data.</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>- Sensing is therefore a synonym for Observation (the Process).
+- As by their definition, sensors perform sampling.
+- Sensors used to obtain measurements must be calibrated and provide uncertainties.</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
           <t>- KCEO</t>
@@ -5359,31 +5341,27 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Spatial Completeness</t>
+          <t>Minimum Mapping Width</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Presence or absence of gaps, which are missing values in an otherwise continuous spatial data series.</t>
+  - to be approved
+description: The width of the smallest linear Feature that is still represented on a map.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Presence or absence of gaps, which are missing values in an otherwise continuous spatial data series.</t>
+          <t>The width of the smallest linear Feature that is still represented on a map.</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>- Surface soil moisture retrieved from microwave satellite sensors may present gaps in mountainous terrains.</t>
-        </is>
-      </c>
+      <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- CGLS</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
@@ -5406,31 +5384,30 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Geocoding</t>
+          <t>Backup</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Translation of one form of Location into another.</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Translation of one form of Location into another.</t>
+          <t>General practice of making copies of current baseline and derived products of EO Collections at specified time intervals, and storing those copies in a manner that will not affect the data if the primary distribution environment is compromised.</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>- Geocoding usually refers to the translation of "address" or "intersection" to "direct Position." Many service providers also include a "reverse geocoding" interface to their geocoder, thus extending the definition of the service as a general translator of Location. Because routing services use internal Location encodings not usually available to others, a geocoder is an integral part of the internals of such a service.</t>
+          <t>- The emphasis is on the ability to retrieve a copy of the entire EO Collection on demand if the original data is lost or compromised.</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>- ISO 19133:2005; https://www.iso.org/standard/32551.html</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
@@ -5453,45 +5430,43 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Georectifying</t>
+          <t>Temporal Resolution</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>- core
-  - to be discussed
-description: Correcting for positional displacement with respect to the surface of the Earth.</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Orthorectifying</t>
-        </is>
-      </c>
+- to be approved
+description: Observation or model output representing regular intervals, specifying the length of the interval that determines the smallest event or process that can be resolved.</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Correcting for positional displacement with respect to the surface of the Earth.</t>
+          <t>Observation or model output representing regular intervals, specifying the length of the interval that determines the smallest event or Process that can be resolved (e.g., the Period between observations, the time steps in a model).</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>- Source: ISO 19115-2:2019, 3.11; ISO 19115-2:2009(E); https://www.iso.org/standard/67039.html, modified</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>The correction of sample locations to achieve some sort of geometric regularity, e.g., a regular 2D geographic grid.</t>
-        </is>
-      </c>
+          <t>- WIGOS 2019 distinguishes between sampling time Period, as the Period over which a Measurement is taken, and temporal sampling interval as the time Period between the beginning of consecutive sampling periods. Temporal Resolution in this Glossary is equivalent to sampling time Period as used by WIGOS.</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>| Entry format example | Valid unit                     |
+|----------------------|-------------------------------|
+| 1 s, 2 h, 1 m        | second, hour, day, month, year |</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
+      <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
@@ -5508,27 +5483,27 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Licencing</t>
+          <t>Place</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>- core
+          <t>- base
 - to be approved
-description: Legal instrument by which a copyright holder may grant rights over the protected work.</t>
+description: Part of any space referenced by an identifier.</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Legal instrument by which a copyright holder may grant rights over the protected work. Data and content is open if it is subject to an explicitly-applied licence that conforms to the Open Definition. A range of standard open licences are available, such as the Creative Commons CC-BY licence, which requires only attribution.</t>
+          <t>Part of any space referenced by an identifier.</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>- CEOS Wiki</t>
+          <t>- ISO 19155:2012, 4.8</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
@@ -5551,37 +5526,45 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Period</t>
+          <t>Ancillary Data</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>- base
-- to be approved
-description: Particular era or span of time.</t>
+          <t>- core
+- to be approved</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Particular era or span of time.</t>
+          <t>Data acquired on the same platform but not obtained from the main Sensor itself (usually provided as part of Level 0 Data), with the primary purpose of serving the processing of main instrument Data (e.g. Position and velocity of platform).</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>- Periods are intervals named with a Period Identifier.</t>
+          <t>This can be divided into data referred to as spacecraft 'engineering', 'core housekeeping' or 'subsystem' data obtained from other parts of the platform, and includes parameters such as orbit position and velocity, attitude and its range of change, time, temperatures, pressures, jet firings, water dumps, internally produced magnetic fields, and other environmental measurements. Ancillary refers to data that exist purely to serve the data processing.</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>- ISO 19170:2021</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr"/>
+          <t>- ESA/CEOS?, modified
+- EO Data Stewardship Glossary</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Data other than instrument measurements, originating in the instrument itself or from the satellite, required to perform processing of the Data. Includes orbit Data, attitude Data, time Information, and spacecraft engineering Data, Calibration Data, Data quality Information, and Data from other instruments or earth system models.</t>
+        </is>
+      </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>- CEOS-ARD PFS template 20220302</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
@@ -5598,26 +5581,32 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Collection Upgrade</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>- core
-- to be approved</t>
+          <t>- controversial
+  - to be discussed
+description: Act of determining the Value of a Property by interacting in a reproducible way with the Phenomenon using a Sensor.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>New and improved major version of all products within a collection due to comprehensive reprocessing.</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
+          <t>Act of determining the Value of a Property by interacting in a reproducible way with the Phenomenon using a Sensor.</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>- The result of an Observation is a Value complemented by an Uncertainty, often itself being referred to as 'observation'.
+- An Observation result represents a Sample of the Phenomenon (otherwise it would be identical with the Phenomenon).</t>
+        </is>
+      </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
@@ -5640,31 +5629,32 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Grid</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>- base
-- to be discussed
-description: Abstraction of real-world phenomena.</t>
+          <t>- core
+  - to be approved
+description: Network composed of two or more sets of curves in which the members of each set intersect the members of the other sets in an algorithmic way.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Abstraction of real-world phenomena.</t>
+          <t>Network composed of two or more sets of curves in which the members of each set intersect the members of the other sets in an algorithmic way.</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>- A feature may occur as a type or an instance.</t>
+          <t>- The curves partition a space into grid cells or zones.
+- The intersection points of the curves are called nodes.</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>- ISO 19101-1:2014, 4.1.11, modified</t>
+          <t>- ISO 19123:2005, 4.1.23; Note 1 modified; Note 2 added</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
@@ -5687,37 +5677,45 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Custodian</t>
+          <t>User</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
+description: Entity (person, organization, institution, etc.) that is requesting data or information with certain characteristics described by needs and/or requirements.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>- See also Steward.</t>
-        </is>
-      </c>
+          <t>In the context of the KCEO, entity (person, organization, institution, etc.) that is requesting data or information with certain characteristics described by needs and/or requirements.</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
+          <t>- KCEO</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>External person, institution or system that consumes provided services.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>- Includes Data Access or Science and Service Exploitation Platforms provided by a payload data ground segment.</t>
+        </is>
+      </c>
       <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>- EO Data Stewardship Glossary</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
@@ -5734,26 +5732,36 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Anthroposphere</t>
+          <t>Remote Sensing</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>- core
-- to be approved</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr"/>
+          <t>- controversial
+- to be discussed
+description: Type of Observation performed at a significant distance from a Phenomenon.</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Remote Observation</t>
+        </is>
+      </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>One of the Earth spheres consisting predominantly of matter processed by humans, such as construction wood, bricks, concrete, asphalt, glass, or plastics.</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr"/>
+          <t>Type of Observation performed at a significant distance from a Phenomenon.</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>- 'Significant' in this context means that the distance has, or may have, a non-negligible impact on the Value of the Property observed.
+- The effect of the distance on the acquired data is the main distinction criterion between 'remote' and 'in-situ' observations.</t>
+        </is>
+      </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
@@ -5776,45 +5784,38 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>Earth Observation Product</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Entity (person, organization, institution, etc.) that is requesting data or information with certain characteristics described by needs and/or requirements.</t>
+description: Direct output from standardized satellite data processing chains (indicative levels 2 and 3), representing fundamental geophysical and biophysical variables.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>In the context of the KCEO, entity (person, organization, institution, etc.) that is requesting data or information with certain characteristics described by needs and/or requirements.</t>
+          <t>Direct output from standardized satellite data processing chains (indicative levels 2 and 3), representing fundamental geophysical and biophysical variables. These products demonstrate direct Traceability to original satellite measurements through rigorous Calibration and Validation processes. The processing methodology prioritizes the conversion of raw sensor data into quantifiable physical measurements, maintaining strict adherence to standardized processing protocols and Validation requirements.</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>- Soil moisture from microwave sensors
+- Forest canopy height from LiDAR data</t>
+        </is>
+      </c>
       <c r="G115" t="inlineStr">
         <is>
           <t>- KCEO</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>External person, institution or system that consumes provided services.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>- Includes Data Access or Science and Service Exploitation Platforms provided by a payload data ground segment.</t>
-        </is>
-      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>- EO Data Stewardship Glossary</t>
-        </is>
-      </c>
+      <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
@@ -5831,31 +5832,31 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Steward</t>
+          <t>Trait</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>- core
-- to be discussed
-description: Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
+          <t>- base
+- to be approved
+description: Characteristic belonging to an entity and referenced by an identifier.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
+          <t>Characteristic belonging to an entity and referenced by an identifier.</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>- See also Custodian.</t>
+          <t>- Traits can be objective (inherent?) in which case they are also observable and called properties. Traits which are not observable (directly or indirectly) need to be assigned.</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- Based on ISO 19143:2010, 4.21, ISO/IEC 2382:2015, 2121440, significantly modified, Note 1 added</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
@@ -5878,24 +5879,31 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Temporal Consistency</t>
+          <t>Time of Year</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Condition where the temporal statistical properties of the sample depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
+description: Time of the year at which the variable is observed or simulated by a model.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Condition where the temporal statistical properties of the Sample depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
+          <t>Time of the year at which the variable is observed or simulated by a model.</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>| Type      | Entry format example | Valid unit     |
+|-----------|----------------------|----------------|
+| timestamp | m/d                  | Not Applicable |
+| timerange | m/d - m/d            | Not Applicable |</t>
+        </is>
+      </c>
       <c r="G117" t="inlineStr">
         <is>
           <t>- KCEO</t>
@@ -5921,28 +5929,32 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Geospatial Data</t>
+          <t>In-Situ Observation</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>- core
-  - to be approved
-description: Data consisting of, derived from, or relating to information that is directly linked to specific geographical locations.</t>
+          <t>- controversial
+  - to be discussed
+description: Observations performed in the same Place where a Phenomenon occurs, normally without isolating it from other systems or altering its pre-Observation state.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Data consisting of, derived from, or relating to information that is directly linked to specific geographical locations.</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
+          <t>Observations performed in the same Place where a Phenomenon occurs, normally without isolating it from other systems (its environment) or altering its pre-Observation state.</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>- The main Characteristic of such observations is that distance has no or only negligible (within Uncertainty) influence on the Value of the Property observed. In-Situ Observations therefore often require either direct physical contact or small distances between a Sensor and the observed Phenomenon.
+- Observations not fulfilling these conditions are considered Remote Sensing.</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>- https://www.merriam-webster.com/dictionary/geospatial
-- https://isotc211.geolexica.org/Concepts/202/, accessed 20221010</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
@@ -5965,37 +5977,56 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Characteristic</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>- core
-- to be approved
-description: Maximum acceptable change in Uncertainty per decade.</t>
+          <t>- base
+- to be discussed</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Maximum acceptable change in Uncertainty per decade.</t>
+          <t>Distinguishing Feature.</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>- GCOS uses bias or systematic errors instead of Uncertainty.</t>
+          <t>- A Characteristic can be inherent or assigned.
+- A Characteristic can be qualitative or quantitative.
+- There are various classes of Characteristics, such as the following:
+  - physical (e.g. mechanical, electrical, chemical, biological);
+  - sensory (e.g. relating to smell, touch, taste, sight, hearing);
+  - behavioural (e.g. courtesy, honesty, veracity);
+  - temporal (e.g. punctuality, reliability, availability);
+  - ergonomic (e.g. physiological characteristic or related to human safety);
+  - functional (e.g. maximum speed of an aircraft).</t>
         </is>
       </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>- Modified from GCOS 2022</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr"/>
-      <c r="I119" t="inlineStr"/>
+          <t>- ISO 9000:2005, 3.5.1</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Abstraction of a Property of an Object or of a set of objects.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>- Characteristics are used for describing Concepts.</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>- ISO 1087-1:2000, 3.2.4; ISO 19146:2010(E); https://www.iso.org/standard/20057.html</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
@@ -6012,27 +6043,31 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Property</t>
+          <t>Measurement</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>- base
-- to be discussed
-description: Observable Trait.</t>
+          <t>- core
+  - to be discussed
+description: Observation of a Quantity.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Observable Trait.</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>Observation of a Quantity.</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>- The Process of collecting a measurement is called measuring.</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- GEOGlos (VIM ?, modified)</t>
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
@@ -6055,31 +6090,32 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Geographic Data</t>
+          <t>Preservation</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Data with implicit or explicit reference to a Location relative to the Earth.</t>
+description: Processes and operations used to ensure data technical and intellectual survival through time.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Data with implicit or explicit reference to a Location relative to the Earth.</t>
+          <t>Processes and operations used to ensure data technical and intellectual survival through time.</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>- Geographic Information is also used as a term for information concerning phenomena implicitly or explicitly associated with a Location relative to the Earth.</t>
+          <t>- Grants data integrity, discoverability and accessibility, and facilitates its (re-)use in the long term.
+- Preservation is one of the tasks of data curation.</t>
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>- ISO 19109:2015, 4.13; ISO 19109:2005</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
@@ -6102,113 +6138,64 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Uncertainty</t>
+          <t>Provisional Product</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
+description: Products in a research and development phase not yet published into a standardized collection.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
+          <t>Products in a research and development phase not yet published into a standardized collection.</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>- GUM</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Non-negative parameter, associated with data, which characterizes the dispersion of the values of a Trait that could reasonably be attributed to a Phenomenon by means of sensing or modelling.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>- In case of quantitative (continuous) data the uncertainty may be, for example, a standard deviation (or a given multiple of it), or the half-width of an interval having a stated level of confidence (see e.g. Standard and Expanded Uncertainty).
-- For qualitative (categorical?) data, uncertainty may be expressed by commission and omission ('confusion matrix') or overall errors.</t>
-        </is>
-      </c>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>- Modified from GUM, VIM4:3.1, FIDUCEO, Notes added</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr">
-        <is>
-          <t>Measure of the spread of the distribution of possible values.</t>
-        </is>
-      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr">
-        <is>
-          <t>- [FIDUCEO Glossary](https://research.reading.ac.uk/fiduceo/glossary/), VIM?, modified</t>
-        </is>
-      </c>
-      <c r="P122" t="inlineStr">
-        <is>
-          <t>Parameter, associated with the result of measurement, that characterizes the dispersion of values that could reasonably be attributed to the measurand.</t>
-        </is>
-      </c>
-      <c r="Q122" t="inlineStr">
-        <is>
-          <t>- When the quality of accuracy or precision of measured values, such as coordinates, is to be characterized quantitatively, the quality parameter is an estimate of the uncertainty of the measurement results. Because accuracy is a qualitative concept, one should not use it quantitatively, that is associate numbers with it; numbers should be associated with measures of uncertainty instead.</t>
-        </is>
-      </c>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr"/>
       <c r="R122" t="inlineStr"/>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>- ISO 19116:2004(E)</t>
-        </is>
-      </c>
-      <c r="T122" t="inlineStr">
-        <is>
-          <t>Parameter characterizing the dispersion of the values being attributed to a measurand, based on the information used.</t>
-        </is>
-      </c>
+      <c r="S122" t="inlineStr"/>
+      <c r="T122" t="inlineStr"/>
       <c r="U122" t="inlineStr"/>
       <c r="V122" t="inlineStr"/>
-      <c r="W122" t="inlineStr">
-        <is>
-          <t>- VIM4: 3.1</t>
-        </is>
-      </c>
+      <c r="W122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>User Interface</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Set of all the components of an interactive system that provide information and controls for the user to accomplish specific tasks with the interactive system.</t>
+  - to be defined
+description: ""</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>Set of all the components of an interactive system that provide information and controls for the User to accomplish specific tasks with the interactive system.</t>
-        </is>
-      </c>
+      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>- ISO 9241-110:2020, 3.10</t>
-        </is>
-      </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
@@ -6229,57 +6216,37 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Instrument Data</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>- core
-  - to be approved
-description: Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
+          <t>- high-impact
+- to be discussed
+description: Deliberate system of guidelines to guide decisions and achieve rational outcomes, implemented as a procedure or protocol and typically promulgated through official written documents.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>- These data consist of instrument science and engineering data, and possibly ancillary data. Instrument engineering data is produced by engineering sensor(s) of an instrument, used either for operating the instrument or for processing the science data generated by the instrument. Instrument science data is produced by the science sensor(s) of an instrument, usually constituting the basic reason for existence of an instrument.</t>
-        </is>
-      </c>
+          <t>Deliberate system of guidelines to guide decisions and achieve rational outcomes. Statement of intent implemented as a procedure or protocol. Typically promulgated through official written documents.</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Data created by an instrument including scientific measurements and any engineering or ancillary data which may be included in the data packets.</t>
-        </is>
-      </c>
+          <t>- KCEO</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
-        </is>
-      </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>Data produced and transmitted by the science and engineering sensors of an instrument, and, in the spacecraft environment, any additional data packaged with the instrument's sensor data by virtue of services provided.</t>
-        </is>
-      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr">
-        <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
-        </is>
-      </c>
+      <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr"/>
       <c r="Q124" t="inlineStr"/>
       <c r="R124" t="inlineStr"/>
@@ -6292,40 +6259,31 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Measurand</t>
+          <t>Geographic Identifier</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>- core
-  - to be approved
-description: Particular Quantity subject to Measurement.</t>
+- to be approved
+description: Spatial reference in the form of a label or code that identifies a Location.</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Particular Quantity subject to Measurement.</t>
+          <t>Spatial reference in the form of a label or code that identifies a Location.</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>| Step | Process description |
-| :----- | :------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------
---- |
-| (Raw) | The complete and unaltered/unprocessed set of Data acquired by one or several sensors on a platform |
-| M/0 uncalibrated | Unaltered/unprocessed Level 0 (main) Sensor Data annotated with processed Ancillary Data and supplemented by Auxiliary Data (including radiometric and geometric Calibration coefficients and geo-referencing parameters) allowing further processing to higher Levels. |
-| M/1 Sensor-calibrated | Level M/0 Sensor Data which have been calibrated (ideally traceable to SI) and spatially aligned (co-located, eventually co-gridded) to represent at-Sensor measurements (Value and Uncertainty) in Sensor nominal spatiotemporal sampling, supplemented by appropriate ancillary data. |
-| M/2 target-calibrated | Level M/1 Data processed to represent geophysical Property values (and uncertainties) for a specified target (Object, Feature of interest, e.g. surface reflectance, apparent temperature) derived from M/1 Sensor Data, as much as possible maintaining the sensors nominal spatial and temporal sampling (Observation preserving). |
-| M/3 homogenised | Level M/1 or M/2 Data which have been generalised and integrated across one or several platforms and acquisitions to achieve an increased, more regular or in any other form enhanced spatial or temporal coverage in which states geophysical values agnostic of the originally acquiring Sensor and Observation condition and thus directly comparable. This homogenisation and fusion may include measurand re-Calibration to external standards and references including use of modelling, aggregation and interpolation. |
-| M/4 derived/inferred | Model output or results from analyses of Level M/3 (or lower level) Data i.e., attributes that might not be directly observable by the Sensor(s) but are derived from observations in combination with other external incl. non-observational Data using techniques like modelling or machine learning (AI). |
-From http://doi.org/10.2760/46796</t>
+          <t>- "Spain" is an example of a label (country name); "SW1-3AD" is an example of a code (postcode).</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>- VIM: 1993, 2.6</t>
+          <t>- ISO 19112:2019, 3.1.2</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
@@ -6348,27 +6306,38 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Policy Target</t>
+          <t>Earth Spheres</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>- high-impact
-- to be discussed
-description: Specific level or rate set for the Policy Objective.</t>
+          <t>- core
+- to be approved
+description: Spheres dividing planet Earth into subsystems, which are collectives of (physical) matter sharing specific traits.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Specific level or rate set for the Policy Objective.</t>
+          <t>Spheres dividing planet Earth into subsystems, which are collectives of (physical) matter sharing specific traits.</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>- Atmosphere
+- Hydrosphere
+- Cryosphere
+- Biosphere
+- Lithosphere
+- Anthroposphere</t>
+        </is>
+      </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Hugget, R., et al., 2024, DOI: 10.1177/03091333241275465
+- Guth, P., et al., 2021, https://doi.org/10.3390/rs13183581
+- Martin, Y.E., et al., 2012</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
@@ -6391,36 +6360,27 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Spatial Extent</t>
+          <t>Deprecated Product</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Zone or region of space described by a geographic identifier in the form of a label or code, or by a bounding box, representing the maximum spatial boundary within which the user is requesting data.</t>
+description: Products and collections that have been superseded by a newer version and are still available, but whose use is discouraged since they will be decommissioned in the future.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Zone or region of space described by a geographic identifier in the form of a label or code, or by a bounding box. Represents the maximum extent (the spatial boundary or limits) within which the User is requesting data.
-The attribute represents the maximum spatial extent of the AOI, and in case the AOI is made of many discontinuous zones then it represents the maximum extent of the union of all the zones.</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>- WIGOS metadata standard defines it as the typical spatial georeferenced volume covered by the observations.</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>- If a User is requesting information about degradation of African protected sites, then the AOIs are the protected sites, and the spatial extent is the African continent.</t>
-        </is>
-      </c>
+          <t>Products and collections that have been superseded by a newer version and are still available, but whose use is discouraged since they will be decommissioned in the future.</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>- Adapted from ISO 19170-1:2021</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
@@ -6443,27 +6403,27 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Provisional Product</t>
+          <t>Replicability</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Products in a research and development phase not yet published into a standardized collection.</t>
+description: Property enabling other researchers to conduct an independent study with different data and similar but not identical methods, yet arriving at results that confirm the original study's hypothesis.</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Products in a research and development phase not yet published into a standardized collection.</t>
+          <t>Property enabling other researchers to conduct an independent study with different data and similar but not identical methods, yet arriving at results that confirm the original study's hypothesis.</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- Craglia, M., et al. (2018).</t>
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
@@ -6486,27 +6446,31 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Object</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>- base
-  - to be approved
-description: Entity with a well-defined boundary and identity that encapsulates state and behaviour.</t>
+- to be discussed
+description: Abstraction of real-world phenomena.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Entity with a well-defined boundary and identity that encapsulates state and behaviour.</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr"/>
+          <t>Abstraction of real-world phenomena.</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>- A feature may occur as a type or an instance.</t>
+        </is>
+      </c>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>- ISO/IEC 19501:2005</t>
+          <t>- ISO 19101-1:2014, 4.1.11, modified</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
@@ -6529,27 +6493,31 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Forecast Range</t>
+          <t>Final Product Version</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>- core
-- to be discussed
-description: The forecast period.</t>
+- to be approved
+description: Product within an EO Collection that is not expected to be updated.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>The forecast period.</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr"/>
+          <t>Product within an EO Collection that is not expected to be updated.</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>- In its production, all of the prerequisite auxiliary data were used as input.</t>
+        </is>
+      </c>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
@@ -6572,27 +6540,36 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Policy Milestone</t>
+          <t>Spatial Extent</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>- high-impact
-- to be discussed
-description: Markers of significant progress in addressing specific issues, or crucial decision points where significant choices are made within a policy process.</t>
+          <t>- core
+- to be approved
+description: Zone or region of space described by a geographic identifier in the form of a label or code, or by a bounding box, representing the maximum spatial boundary within which the user is requesting data.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Markers of significant progress in addressing specific issues, or crucial decision points where significant choices are made. Concrete examples include: policy planning and proposing, impact assessment, implementation, or implementation cycles (e.g., Water Framework Directive, Marine Strategy Framework Directive), achievement of Policy Objectives and Policy Targets, and evaluating and improving existing laws.</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
+          <t>Zone or region of space described by a geographic identifier in the form of a label or code, or by a bounding box. Represents the maximum extent (the spatial boundary or limits) within which the User is requesting data.
+The attribute represents the maximum spatial extent of the AOI, and in case the AOI is made of many discontinuous zones then it represents the maximum extent of the union of all the zones.</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>- WIGOS metadata standard defines it as the typical spatial georeferenced volume covered by the observations.</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>- If a User is requesting information about degradation of African protected sites, then the AOIs are the protected sites, and the spatial extent is the African continent.</t>
+        </is>
+      </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Adapted from ISO 19170-1:2021</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
@@ -6615,31 +6592,27 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Dwell Time</t>
+          <t>Policy Cycle</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>- core
-- to be approved
-description: Time that an antenna beam spends on a target.</t>
+          <t>- high-impact
+- to be discussed
+description: Well-established concept typically taught as the rational model of policy decision-making, representing an idealised view of the policy process.</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Time that an antenna beam spends on a target.</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>- In the context of radar sensing.</t>
-        </is>
-      </c>
+          <t>Well-established concept, typically taught as the rational model of policy decision-making. Idealised view of the policy process.</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [ESA/CEOS?, modified](https://digital-strategy.ec.europa.eu/en/library/quality-public-administration-toolbox-practitioners)</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
@@ -6662,27 +6635,27 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Location Error</t>
+          <t>Data Licencing</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>- core
-  - to be approved
-description: Measure of the agreement between the represented Location of an Object and the true Location.</t>
+- to be approved
+description: Legal instrument by which a copyright holder may grant rights over the protected work.</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Measure of the agreement between the represented Location of an Object and the true Location.</t>
+          <t>Legal instrument by which a copyright holder may grant rights over the protected work. Data and content is open if it is subject to an explicitly-applied licence that conforms to the Open Definition. A range of standard open licences are available, such as the Creative Commons CC-BY licence, which requires only attribution.</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- CEOS Wiki</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
@@ -6705,23 +6678,27 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Expanded Uncertainty</t>
+          <t>Representativeness</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Standard Uncertainty multiplied by a coverage factor k, chosen to obtain a desired level of confidence.</t>
+description: Quality or characteristic of a measurement or observation to accurately represent a specific geographic location, time period, or environmental condition.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Standard Uncertainty multiplied by a coverage factor, k. The coverage factor is chosen to obtain a desired level of confidence. Most commonly a 95% confidence interval is chosen. For a Gaussian distribution, this is achieved with a coverage factor k = 2. (Note that strictly this provides a 95.45% confidence interval.)</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr"/>
+          <t>Quality or characteristic of a measurement or Observation to accurately represent a specific geographic location, time Period, or environmental condition.</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>- WIGOS metadata standard defines representativeness as the extent of the region around the Observation of which it is representative.</t>
+        </is>
+      </c>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
@@ -6748,21 +6725,29 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Environmental Process</t>
+          <t>Reproducibility</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>- core
-- to be defined
-description: ""</t>
+- to be approved
+description: Concerned with the validity of the results of a particular study, enabling readers to check whether results have been manipulated by reproducing exactly the same study using the same data and methods.</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Concerned with the validity of the results of a particular study, i.e., the possibility for readers to check whether results have been manipulated, by reproducing exactly the same study using the same data and methods.</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>- Ostermann and Granell (2015)</t>
+        </is>
+      </c>
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
@@ -6783,31 +6768,31 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Custodian</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>- controversial
-  - to be discussed
-description: An, often numeric, theoretical (or otherwise abstract) representation of an Entity intended to generate Data describing one or more of its traits.</t>
+          <t>- core
+- to be approved
+description: Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>An, often numeric, theoretical (or otherwise abstract) representation of an Entity intended to generate Data describing one or more of its traits (as a result of pre-set conditions).</t>
+          <t>Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>- The Process of generating Data using a model is called modelling.</t>
+          <t>- See also Steward.</t>
         </is>
       </c>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
@@ -6830,26 +6815,27 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Classification System</t>
+          <t>Geosphere</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>- core
-- to be approved</t>
+  - to be approved
+description: The masses of minerals that constitute planet Earth.</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Nomenclature used to classify Information into categorical thematic classes (e.g., EUNIS, MAES ecosystems, Corine Land Cover, LCCS).</t>
+          <t>The masses of minerals that constitute planet Earth.</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
@@ -6872,27 +6858,30 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Spectral Bandwidth</t>
+          <t>Cell</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>- core
-- to be discussed
-description: Range of the Spectral Band.</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Range of the Spectral Band.</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr"/>
+          <t>Spatial, spatio-temporal zone or temporal unit of geometry with dimensionality greater than 0, associated with a zone.</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>- Cells are the unit of geometry in a DGGS, and the geometry of the region of space-time occupied by a zone is a Cell.</t>
+        </is>
+      </c>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO 19170:2021</t>
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
@@ -6915,26 +6904,31 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>Geographic Coordinate Reference System</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>- core
-- to be approved</t>
+- to be approved
+description: Coordinate Reference System (CRS) that has a geodetic Reference frame and an ellipsoidal coordinate system.</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Group of products that have been processed using a consistent radiometric calibration, geometric registration base, data/metadata format, and version of processing algorithms.</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr"/>
+          <t>Coordinate Reference System (CRS) that has a geodetic Reference frame and an ellipsoidal coordinate system.</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>- Also known as geographic CRS.</t>
+        </is>
+      </c>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- ISO 19111:2019, 3.1.35</t>
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
@@ -6957,20 +6951,35 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Continuity</t>
+          <t>Vertical Levels</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>- core
-  - to be defined</t>
+- to be approved
+description: Levels of a vertical discretization, e.g. pressure levels in an atmospheric model reanalysis or height levels in a forest biomass EO product.</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Levels of a vertical discretization. Examples may be pressure levels in an atmospheric model reanalysis or height levels in a forest biomass EO product.</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>| Entry format example                | Valid unit           |
+|------------------------------------|----------------------|
+| 1, 5, 10 meter; 1000, 850, 500 hPa | meter, hPa, unitless |</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
@@ -6991,27 +7000,26 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Policy File</t>
+          <t>Anthroposphere</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>- high-impact
-- to be discussed
-description: Policy documents that represent the official written reference for a given Policy.</t>
+          <t>- core
+- to be approved</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Policy documents that represent the official written reference for a given Policy.</t>
+          <t>One of the Earth spheres consisting predominantly of matter processed by humans, such as construction wood, bricks, concrete, asphalt, glass, or plastics.</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
@@ -7034,23 +7042,27 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Dwell Time</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>- high-impact
-- to be discussed
-description: Deliberate system of guidelines to guide decisions and achieve rational outcomes, implemented as a procedure or protocol and typically promulgated through official written documents.</t>
+          <t>- core
+- to be approved
+description: Time that an antenna beam spends on a target.</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Deliberate system of guidelines to guide decisions and achieve rational outcomes. Statement of intent implemented as a procedure or protocol. Typically promulgated through official written documents.</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr"/>
+          <t>Time that an antenna beam spends on a target.</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>- In the context of radar sensing.</t>
+        </is>
+      </c>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
@@ -7077,31 +7089,34 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Geographic Identifier</t>
+          <t>Duration</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Spatial reference in the form of a label or code that identifies a Location.</t>
+description: Non-negative interval Quantity of time equal to the difference between the final and initial instants of a time interval.</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Spatial reference in the form of a label or code that identifies a Location.</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>- "Spain" is an example of a label (country name); "SW1-3AD" is an example of a code (postcode).</t>
-        </is>
-      </c>
+          <t>Non-negative interval Quantity of time equal to the difference between the final and initial instants of a time interval.</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>- Duration is one of the base quantities in the International System of Quantities (ISQ) on which the International System of Units (SI) is based. The term "time" instead of "duration" is often used in this context and also for an infinitesimal duration.
+- For the term "duration", expressions such as "time" or "time interval" are often used, but the term "time" is not recommended in this sense and the term "time interval" is deprecated in this sense to avoid confusion with the concept of "time interval".
+- The exact duration of a time scale unit depends on the time scale used. For example, the durations of a year, month, week, day, hour or minute may depend on when they occur (in a Gregorian calendar, a calendar month can have a duration of 28, 29, 30, or 31 days; in a 24-hour clock, a clock minute can have a duration of 59, 60, or 61 seconds, etc.). Therefore, the exact duration can only be evaluated if the exact duration of each is known.
+- This definition is closely related to NOTE 1 of the terminological entry "duration" in IEC 60050-113:2011, 113-01-13.</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
-          <t>- ISO 19112:2019, 3.1.2</t>
+          <t>- ISO 8601-1:2019, 3.1.1.8</t>
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
@@ -7124,32 +7139,27 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Earth Observation</t>
+          <t>Lead Time</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>- high-impact
-- to be discussed
-description: Science domain dealing with technologies and methods of collecting and analyzing observations about the different Earth spheres.</t>
+          <t>- core
+  - to be approved
+description: Minimum time of interval between an Observation being tasked and being performed.</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Science domain dealing with technologies and methods of collecting and analyzing observations about the different Earth spheres.</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>- Earth Observation (EO) can be categorised by location of the sensor into space-borne, air-borne, sea-borne, ground-based, underwater and underground EO.
-- Earth Observation (EO) includes Remote Sensing, such as satellite imagery, as well as in-situ observations, e.g., with ground-based devices.</t>
-        </is>
-      </c>
+          <t>Minimum time of interval between an Observation being tasked and being performed.</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
-          <t>- Modified GEO definition [GEO (earthobservations.org)](https://earthobservations.org/resources#key)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
@@ -7172,27 +7182,31 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Data Format</t>
+          <t>EO Space Data</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Structured Data that is machine readable and can be automatically read and processed by a computer, such as HDF, NetCDF, CSV, JSON, XML, etc.</t>
+description: Earth Observation data generated by spaceborne missions or instruments owned by public or private organizations.</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Structured Data that is machine readable and can be automatically read and processed by a computer, such as HDF, NetCDF, CSV, JSON, XML, etc.</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr"/>
+          <t>Earth Observation data generated by spaceborne missions or instruments owned by public or private organizations.</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>- See also Instrument data.</t>
+        </is>
+      </c>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
-          <t>- CEOS Wiki</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
@@ -7215,27 +7229,31 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Geolocation Information</t>
+          <t>Spatial Completeness</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>- core
-- to be discussed
-description: Information used to determine geographic Location.</t>
+- to be approved
+description: Presence or absence of gaps, which are missing values in an otherwise continuous spatial data series.</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Information used to determine geographic Location.</t>
+          <t>Presence or absence of gaps, which are missing values in an otherwise continuous spatial data series.</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>- Surface soil moisture retrieved from microwave satellite sensors may present gaps in mountainous terrains.</t>
+        </is>
+      </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>- ISO 19130-1:2018, 3.34</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
@@ -7258,26 +7276,32 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Cryosphere</t>
+          <t>Derivative Product</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
           <t>- core
-- to be approved</t>
+- to be approved
+description: Product additionally processed from baseline or unenhanced mission data.</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Masses of frozen water, such as sea ice, ice shields, glaciers, and snow.</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr"/>
+          <t>Product additionally processed from baseline or unenhanced mission data.</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>- Generally either a compilation of time-series data (e.g., all time, annual, monthly or seasonal summary data, &gt; Level 3) or thematic versions of each individual data tile of baseline data.
+- Derived products are citable via a Digital Object Identifier (DOI).</t>
+        </is>
+      </c>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
@@ -7300,19 +7324,27 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Geopositioning</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>- core
-  - to be defined
-description: ""</t>
+- to be discussed
+description: Determination of the geographic Position of a point (0D) or linear (1D) Feature.</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
-      <c r="D148" t="inlineStr"/>
-      <c r="E148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Determination of the geographic Position of a point (0D) or linear (1D) Feature.</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>- Modified from: ISO 19130-1:2018, 3.36</t>
+        </is>
+      </c>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr"/>
@@ -7335,37 +7367,27 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Spectral Band</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>- base
-  - to be approved
-description: Particular Place referenced by an identifier.</t>
+          <t>- core
+- to be approved
+description: Part of the electromagnetic spectrum of specific wavelengths, in remote sensing usually described by central wavelength and bandwidth.</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Particular Place referenced by an identifier.</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>- While a (geo)location identifies a geographic Place, it may also be associated with objects other than the Earth.
-- While Location in principle covers 0- to 3-dimensional spatial geometries, it should not be used for 0- and 1-dimensional geometries (positions and paths).</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>- Madrid
-- California</t>
-        </is>
-      </c>
+          <t>Part of the electromagnetic spectrum of specific wavelengths. In Remote Sensing, usually described by central wavelength and bandwidth.</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr">
         <is>
-          <t>- [ISO 19112:2019](https://www.iso.org/standard/70742.html), (E), 3.1.3, modified, note 2 added</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
@@ -7388,35 +7410,20 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Consistency</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Device or instrument suited (through physical/chemical interaction) to measure one or more properties of a Phenomenon and thus collect factual/objective data.</t>
+  - to be defined</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>Device or instrument suited (through physical/chemical interaction) to measure one or more properties of a Phenomenon and thus collect factual/objective data.</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>- Sensing is therefore a synonym for Observation (the Process).
-- As by their definition, sensors perform sampling.
-- Sensors used to obtain measurements must be calibrated and provide uncertainties.</t>
-        </is>
-      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
+      <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr"/>
@@ -7437,37 +7444,31 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Temporal Resolution</t>
+          <t>Geographic Data</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Observation or model output representing regular intervals, specifying the length of the interval that determines the smallest event or process that can be resolved.</t>
+description: Data with implicit or explicit reference to a Location relative to the Earth.</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Observation or model output representing regular intervals, specifying the length of the interval that determines the smallest event or Process that can be resolved (e.g., the Period between observations, the time steps in a model).</t>
+          <t>Data with implicit or explicit reference to a Location relative to the Earth.</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>- WIGOS 2019 distinguishes between sampling time Period, as the Period over which a Measurement is taken, and temporal sampling interval as the time Period between the beginning of consecutive sampling periods. Temporal Resolution in this Glossary is equivalent to sampling time Period as used by WIGOS.</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>| Entry format example | Valid unit                     |
-|----------------------|-------------------------------|
-| 1 s, 2 h, 1 m        | second, hour, day, month, year |</t>
-        </is>
-      </c>
+          <t>- Geographic Information is also used as a term for information concerning phenomena implicitly or explicitly associated with a Location relative to the Earth.</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO 19109:2015, 4.13; ISO 19109:2005</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
@@ -7490,27 +7491,26 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Policy Cycle</t>
+          <t>Business Continuity</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>- high-impact
-- to be discussed
-description: Well-established concept typically taught as the rational model of policy decision-making, representing an idealised view of the policy process.</t>
+          <t>- core
+- to be approved</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Well-established concept, typically taught as the rational model of policy decision-making. Idealised view of the policy process.</t>
+          <t>An organisation's readiness to continue functioning during times of disruption.</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr">
         <is>
-          <t>- [ESA/CEOS?, modified](https://digital-strategy.ec.europa.eu/en/library/quality-public-administration-toolbox-practitioners)</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H152" t="inlineStr"/>

--- a/exports/xlsx/terms.xlsx
+++ b/exports/xlsx/terms.xlsx
@@ -536,41 +536,33 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Geolocating</t>
+          <t>Geographic Grid</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Geopositioning of an Object using a Physical Sensor Model or a True Replacement Model.</t>
+description: Regular grid based on a Geographic Coordinate Reference System (CRS).</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Geopositioning of an Object using a Physical Sensor Model or a True Replacement Model.</t>
+          <t>Regular grid based on a Geographic Coordinate Reference System (CRS).</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>- ISO 19115-2:2009, 4.11</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Determination of the geographic location of a feature of two or more dimensions.</t>
-        </is>
-      </c>
+          <t>- KCEO</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>- ISO 19130-1:2018, 3.36 ('geopositioning'), modified</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -587,23 +579,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Spectral Bandwidth</t>
+          <t>Representativeness</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>- core
-- to be discussed
-description: Range of the Spectral Band.</t>
+- to be approved
+description: Quality or characteristic of a measurement or observation to accurately represent a specific geographic location, time period, or environmental condition.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Range of the Spectral Band.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>Quality or characteristic of a measurement or Observation to accurately represent a specific geographic location, time Period, or environmental condition.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>- WIGOS metadata standard defines representativeness as the extent of the region around the Observation of which it is representative.</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
@@ -630,25 +626,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Instrument Data</t>
+          <t>EO Space Data</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>- core
-  - to be approved
-description: Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
+- to be approved
+description: Earth Observation data generated by spaceborne missions or instruments owned by public or private organizations.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
+          <t>Earth Observation data generated by spaceborne missions or instruments owned by public or private organizations.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>- These data consist of instrument science and engineering data, and possibly ancillary data. Instrument engineering data is produced by engineering sensor(s) of an instrument, used either for operating the instrument or for processing the science data generated by the instrument. Instrument science data is produced by the science sensor(s) of an instrument, usually constituting the basic reason for existence of an instrument.</t>
+          <t>- See also Instrument data.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -657,30 +653,14 @@
           <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Data created by an instrument including scientific measurements and any engineering or ancillary data which may be included in the data packets.</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Data produced and transmitted by the science and engineering sensors of an instrument, and, in the spacecraft environment, any additional data packaged with the instrument's sensor data by virtue of services provided.</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
-        </is>
-      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
@@ -693,59 +673,41 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Auxiliary Data</t>
+          <t>Granule</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>- core
-- to be approved</t>
+  - to be approved
+description: The smallest aggregation of data which is independently managed (i.e. described, inventoried, retrievable).</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Data that enhance the processing and utilisation of main Sensor Data. Auxiliary Data are usually not captured by the same Data collection Process or on the same platform as the main Sensor Data. Examples include meteorological Data received from ECMWF/Met Offices or DEMs. Auxiliary Data help in Data processing, but are also Data sets in their own right.</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>The smallest aggregation of data which is independently managed (i.e. described, inventoried, retrievable). Granules may be managed as logical granules and/or physical granules.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>- See also product.</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>- ESA/CEOS?, modified
-- ENMAP Glossary of Terms, https://www.enmap.org/Data/doc/EnMAP_Terms.pdf, 20210624
-- EO Data Stewardship Glossary</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Data required to perform processing of Sensor Data which is not obtained from the Sensor itself. Includes: (a) Data provided by the spacecraft (e.g. orbit Position and velocity, attitude, instrument house-keeping Data, on-board time); (b) Data not available from on-board sources.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>For EnMAP, this includes (a) orbit files, attitude files, Calibration Data, instrument house-keeping Data; (b) atmospheric parameters, reference images.</t>
-        </is>
-      </c>
+          <t>- [NASA EarthData](https://www.earthdata.nasa.gov/learn/glossary)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>- ENMAP Glossary of Terms, https://www.enmap.org/Data/doc/EnMAP_Terms.pdf, 20210624
-- EO Data Stewardship Glossary</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Data required for instrument processing that does not originate in the instrument itself or from the satellite. Some Auxiliary Data will be generated in the ground segment, whilst other Data will be provided from external sources.</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>- CEOS-ARD PFS template 20220302</t>
-        </is>
-      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
@@ -758,27 +720,38 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dispose</t>
+          <t>Temporal Revisit</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Action of permanently and irrecoverably removing all copies of data held by an organization.</t>
+- to be discussed
+description: Interval between successive observations.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Action of permanently and irrecoverably removing all copies of data held by an organization.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>Interval between successive observations.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>- In Remote Sensing it is also called repeat cycle.
+- More generally it is known as temporal sampling interval.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>| Entry format example | Valid unit                     |
+|----------------------|-------------------------------|
+| 1 s, 2 h             | second, hour, day, month, year |</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -801,32 +774,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Position</t>
+          <t>Dispose</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>- base
-- to be discussed
-- controversial
-description: Place referenced by a single set of coordinates within a coordinate reference system.</t>
+          <t>- core
+- to be approved
+description: Action of permanently and irrecoverably removing all copies of data held by an organization.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Place referenced by a single set of coordinates within a coordinate reference system.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>- Opposite to (previous) ISO definition, Position shall be used only for 0-dimensional primitives (points).</t>
-        </is>
-      </c>
+          <t>Action of permanently and irrecoverably removing all copies of data held by an organization.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>- ISO 19133:2005, modified to cover only points, also called 'direct position'</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -849,35 +817,36 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Product</t>
+          <t>Remote Sensing</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>- core
-- to be approved
-description: Electronic data package distributable to users; content is derived from instrument data via processing involving ancillary and auxiliary data.</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>- controversial
+- to be discussed
+description: Type of Observation performed at a significant distance from a Phenomenon.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Remote Observation</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Electronic data package distributable to users; content is derived from instrument data via processing involving ancillary and auxiliary data.</t>
+          <t>Type of Observation performed at a significant distance from a Phenomenon.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>- Products may be accompanied by metadata and browse images.
-- A Product may be part of a collection — a distinction useful for archiving and cataloguing purposes.
-- The term Product may be used to denote a product type, such as e.g. ENVISAT_ASAR_L1B_PRI data products.
-- End users may distinguish between (input, "raw") data and products, i.e., the derived geophysical parameters.
-- See also granule.</t>
+          <t>- 'Significant' in this context means that the distance has, or may have, a non-negligible impact on the Value of the Property observed.
+- The effect of the distance on the acquired data is the main distinction criterion between 'remote' and 'in-situ' observations.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -900,31 +869,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Process</t>
+          <t>Near Real Time Data</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>- base
-- to be approved
-description: Series of activities that interact to produce a result.</t>
+          <t>- high-impact
+  - to be discussed
+description: Data available for use with a specified (small and application dependent) latency, typically 3 hours for meteorological applications.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Series of activities that interact to produce a result.</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>- A Process may occur once-only or be recurrent or periodic.</t>
-        </is>
-      </c>
+          <t>Data available for use with a specified (small and application dependent) latency, typically 3 hours for meteorological applications.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>- [Wikipedia](https://en.wikipedia.org/wiki/Process)</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -947,35 +912,51 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Reference</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>- core
-- to be discussed
-description: Phenomenon whose values for specific properties are known and understood with an Uncertainty significantly lower than that of the Observation with which it is compared.</t>
+          <t>- base
+- to be approved
+description: Value and possibly Uncertainty of a Trait of a specific Entity.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Phenomenon whose values for specific properties are known and understood with an Uncertainty significantly lower (quantify?) than that of the Observation with which it is compared.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+          <t>Value and possibly Uncertainty of a Trait of a specific Entity.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>- Data simply describe entities using certain traits and are not targeted at a particular use or audience.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Data can be categorised into:
+- factual (i.e. obtained by Observation) or fictional (obtained e.g. through modelling, estimating or assigning)
+- quantitative (continuous) or qualitative (categorical)
+- analogue or digital
+(list not exhaustive!)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sort of data acquired with an Uncertainty significantly lower (quantify?) than that of the data it is being compared with.</t>
+          <t>Scientific or technical measurements, values calculated therefrom, observations, or facts that can be represented by numbers, tables, graphs, models, text, or symbols which are used as a basis for reasoning and further calculation.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>- VIM?, modified</t>
+          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -994,30 +975,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Earth Observation Based Output</t>
+          <t>Geographic Coordinate Reference System</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Higher-level processing and integration output (indicative level 4 and beyond) that goes beyond basic data processing, often designed for policy or decision-making needs.</t>
+description: Coordinate Reference System (CRS) that has a geodetic Reference frame and an ellipsoidal coordinate system.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Higher-level processing and integration output (indicative level 4 and beyond) that goes beyond basic data processing. These outputs are often designed specifically for policy or decision-making needs, and can be categorized into sub-categories:
-- Outputs from models/model integration: use of EO products as inputs in numerical models or combining them with other data sources in modelling frameworks.
-- Indicator-based outputs: EO products transformed through specialized algorithms (including statistical methods, machine learning, and pattern recognition) to create meaningful metrics based on spatio-temporal analysis.
-- Outputs from reanalysis: merging of EO products with other observations and models, creating consistent long-term records of past atmospheric, oceanic, and land surface conditions, and filling gaps through data assimilation techniques.</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>Coordinate Reference System (CRS) that has a geodetic Reference frame and an ellipsoidal coordinate system.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>- Also known as geographic CRS.</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO 19111:2019, 3.1.35</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -1040,45 +1022,38 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Entity</t>
+          <t>Long Term Preservation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>- base
-- to be approved
-description: Something that has separate and distinct existence and objective or conceptual reality.</t>
+          <t>- core
+  - to be approved
+description: The act of maintaining information in a correct and independently understandable form over the long term.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Something that has separate and distinct existence and objective or conceptual reality.</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+          <t>The act of maintaining information in a correct and independently understandable form over the long term.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>- Long term refers to a period of time long enough to be concerned with the impact which changing technologies, including support for media and data formats, and changing user communities will have on the information being held in a repository.
+- See also preservation.</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>- ISO 19119:2016, 4.1.6</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Government or business organization that is formed to conduct business or represent the government of the day.</t>
-        </is>
-      </c>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>CEOS Entities include Working Groups, Virtual Constellations, etc.</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1095,26 +1070,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Collection</t>
+          <t>Preservation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>- core
-- to be approved</t>
+- to be approved
+description: Processes and operations used to ensure data technical and intellectual survival through time.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Group of products that have been processed using a consistent radiometric calibration, geometric registration base, data/metadata format, and version of processing algorithms.</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>Processes and operations used to ensure data technical and intellectual survival through time.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>- Grants data integrity, discoverability and accessibility, and facilitates its (re-)use in the long term.
+- Preservation is one of the tasks of data curation.</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1137,27 +1118,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Geographic Grid</t>
+          <t>Version Control</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Regular grid based on a Geographic Coordinate Reference System (CRS).</t>
+description: Method of working with collections, similar to version control systems used in traditional software development but optimized to allow better processing of data and collaboration in data analytics and research contexts.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Regular grid based on a Geographic Coordinate Reference System (CRS).</t>
+          <t>Method of working with collections, similar to the version control systems used in traditional software development but optimized to allow better processing of data and collaboration in the context of data analytics, research, and any other form of data analysis.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [Wikipedia](https://en.wikipedia.org/wiki/Data_version_control)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -1180,30 +1161,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Archive</t>
+          <t>Thematic Resolution</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>- core
-- to be approved</t>
+- to be approved
+description: Level of categorical detail of information expressed by the number of classes.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>System that stores data products, guaranteeing their preservation for future use.</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>- This function includes all operations to identify, store and retrieve the data and ensure their integrity.</t>
-        </is>
-      </c>
+          <t>Level of categorical detail of information expressed by the number of classes.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- CGLS</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1226,31 +1204,26 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Steward</t>
+          <t>Copernicus Service Provider</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>- core
-- to be discussed
-description: Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
+- to be discussed</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>- See also Custodian.</t>
-        </is>
-      </c>
+          <t>Institutional body, organisation or programme that provides reliable, trusted (authoritative?) EO Information and that has the financial resources to sustain the provision. It utilises satellite Data, ground-based measurements, and other sources to generate accurate and timely Data products related to various aspects of the Earth's environment, such as land, Atmosphere, oceans, and climate.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -1273,33 +1246,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sample</t>
+          <t>Replicability</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>- controversial
-- to be discussed
-description: Subset of one or more entities.</t>
+          <t>- core
+- to be approved
+description: Property enabling other researchers to conduct an independent study with different data and similar but not identical methods, yet arriving at results that confirm the original study's hypothesis.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Subset of one or more entities.</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>- A Sample may be spatial, temporal, spectral, or in any other dimension or Trait.
-- Each Sample is contiguous, i.e. it does not consist of more than one discontinuous geometry in any dimension.
-- The Process of obtaining a Sample is called sampling.</t>
-        </is>
-      </c>
+          <t>Property enabling other researchers to conduct an independent study with different data and similar but not identical methods, yet arriving at results that confirm the original study's hypothesis.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Craglia, M., et al. (2018).</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -1322,36 +1289,30 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Temporal Extent</t>
+          <t>Coverage Interval</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Period during which data was collected, observations were made, or for which the model was run.</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+- to be approved</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Coverage extent</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Period during which data was collected, observations were made, or for which the model was run.</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>- In W3C this is the definition of temporal coverage.
-- Time Period covered by a series of observations inclusive of the specified date/time indications (measurement history). Defined based on the beginning and end dates of observations.</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>- WIGOS Metadata</t>
-        </is>
-      </c>
+          <t>Range or specific subset of values associated with a coverage dataset.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>- Adapted from W3C</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -1422,28 +1383,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cryosphere</t>
+          <t>Equivalence</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>- core
-- to be approved</t>
+  - to be defined</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Masses of frozen water, such as sea ice, ice shields, glaciers, and snow.</t>
-        </is>
-      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>- Guth et al. 2021</t>
-        </is>
-      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
@@ -1464,28 +1417,29 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Spatial Reporting Unit</t>
+          <t>Band Central Wavelength</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Smallest spatial object of interest that may be used for reporting and for which the information should be aggregated.</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Smallest spatial object of interest that may be used for reporting and for which the information should be aggregated.</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>- WIGOS 2019 uses 'spatial reporting interval', probably assuming observations are reported on a grid with regular spacing/intervals.</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>Single wavelength Value within the sensitivity interval of a spectroradiometric Sensor which represents the respective band. It could be either the mean, the median, the maximum sensitivity, or any other reasonable Value chosen to be representative.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>| Entry format example | Valid unit                                        |
+|----------------------|---------------------------------------------------|
+| 0.545 μm             | micrometre (μm), millimetre (mm), centimetre (cm) |</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>- KCEO</t>
@@ -1511,31 +1465,31 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Decommissioned Product</t>
+          <t>Update Frequency</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Products and collections that have been superseded by new versions and are no longer available.</t>
+description: Frequency at which the product is available to users.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Products and collections that have been superseded by new versions and are no longer available.</t>
+          <t>Frequency at which the product is available to users.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>- Decommissioned products are no longer supported, i.e. corrections will not be made, new data will not be added, and support is not available.</t>
+          <t>- Also known in product catalogues as dissemination frequency.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -1558,43 +1512,45 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Location</t>
+          <t>Entity</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>- base
-  - to be approved
-description: Particular Place referenced by an identifier.</t>
+- to be approved
+description: Something that has separate and distinct existence and objective or conceptual reality.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Particular Place referenced by an identifier.</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>- While a (geo)location identifies a geographic Place, it may also be associated with objects other than the Earth.
-- While Location in principle covers 0- to 3-dimensional spatial geometries, it should not be used for 0- and 1-dimensional geometries (positions and paths).</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>- Madrid
-- California</t>
-        </is>
-      </c>
+          <t>Something that has separate and distinct existence and objective or conceptual reality.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>- [ISO 19112:2019](https://www.iso.org/standard/70742.html), (E), 3.1.3, modified, note 2 added</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>- ISO 19119:2016, 4.1.6</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Government or business organization that is formed to conduct business or represent the government of the day.</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>CEOS Entities include Working Groups, Virtual Constellations, etc.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -1611,31 +1567,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Period</t>
+          <t>Place</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>- base
 - to be approved
-description: Particular era or span of time.</t>
+description: Part of any space referenced by an identifier.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Particular era or span of time.</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>- Periods are intervals named with a Period Identifier.</t>
-        </is>
-      </c>
+          <t>Part of any space referenced by an identifier.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>- ISO 19170:2021</t>
+          <t>- ISO 19155:2012, 4.8</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -1658,28 +1610,34 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Geospatial Data</t>
+          <t>Duration</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>- core
-  - to be approved
-description: Data consisting of, derived from, or relating to information that is directly linked to specific geographical locations.</t>
+- to be approved
+description: Non-negative interval Quantity of time equal to the difference between the final and initial instants of a time interval.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Data consisting of, derived from, or relating to information that is directly linked to specific geographical locations.</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
+          <t>Non-negative interval Quantity of time equal to the difference between the final and initial instants of a time interval.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>- Duration is one of the base quantities in the International System of Quantities (ISQ) on which the International System of Units (SI) is based. The term "time" instead of "duration" is often used in this context and also for an infinitesimal duration.
+- For the term "duration", expressions such as "time" or "time interval" are often used, but the term "time" is not recommended in this sense and the term "time interval" is deprecated in this sense to avoid confusion with the concept of "time interval".
+- The exact duration of a time scale unit depends on the time scale used. For example, the durations of a year, month, week, day, hour or minute may depend on when they occur (in a Gregorian calendar, a calendar month can have a duration of 28, 29, 30, or 31 days; in a 24-hour clock, a clock minute can have a duration of 59, 60, or 61 seconds, etc.). Therefore, the exact duration can only be evaluated if the exact duration of each is known.
+- This definition is closely related to NOTE 1 of the terminological entry "duration" in IEC 60050-113:2011, 113-01-13.</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>- https://www.merriam-webster.com/dictionary/geospatial
-- https://isotc211.geolexica.org/Concepts/202/, accessed 20221010</t>
+          <t>- ISO 8601-1:2019, 3.1.1.8</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -1702,23 +1660,35 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Confidence Interval</t>
+          <t>Time of Day</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>- controversial
-- to be approved</t>
+          <t>- core
+- to be approved
+description: Time of the day at which the variable or parameter is observed or simulated by a model.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Probability that the Quantity lies in the interval, conditioned on the measuring or modelling assumptions.</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+          <t>Time of the day at which the variable or parameter is observed or simulated by a model.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>- In Remote Sensing it is also known as time of overpass.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>| Type      | Entry format example | Valid unit |
+|-----------|----------------------|------------|
+| timestamp | 18:00 h (0–24)       | Hours      |
+| timerange | 18:00 – 20:00 h      | Hours      |</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>- KCEO</t>
@@ -1744,31 +1714,33 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Granule</t>
+          <t>Vertical Levels</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>- core
-  - to be approved
-description: The smallest aggregation of data which is independently managed (i.e. described, inventoried, retrievable).</t>
+- to be approved
+description: Levels of a vertical discretization, e.g. pressure levels in an atmospheric model reanalysis or height levels in a forest biomass EO product.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>The smallest aggregation of data which is independently managed (i.e. described, inventoried, retrievable). Granules may be managed as logical granules and/or physical granules.</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>- See also product.</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
+          <t>Levels of a vertical discretization. Examples may be pressure levels in an atmospheric model reanalysis or height levels in a forest biomass EO product.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>| Entry format example                | Valid unit           |
+|------------------------------------|----------------------|
+| 1, 5, 10 meter; 1000, 850, 500 hPa | meter, hPa, unitless |</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>- [NASA EarthData](https://www.earthdata.nasa.gov/learn/glossary)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -1791,31 +1763,35 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Product</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>- controversial
-  - to be discussed
-description: An, often numeric, theoretical (or otherwise abstract) representation of an Entity intended to generate Data describing one or more of its traits.</t>
+          <t>- core
+- to be approved
+description: Electronic data package distributable to users; content is derived from instrument data via processing involving ancillary and auxiliary data.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>An, often numeric, theoretical (or otherwise abstract) representation of an Entity intended to generate Data describing one or more of its traits (as a result of pre-set conditions).</t>
+          <t>Electronic data package distributable to users; content is derived from instrument data via processing involving ancillary and auxiliary data.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>- The Process of generating Data using a model is called modelling.</t>
+          <t>- Products may be accompanied by metadata and browse images.
+- A Product may be part of a collection — a distinction useful for archiving and cataloguing purposes.
+- The term Product may be used to denote a product type, such as e.g. ENVISAT_ASAR_L1B_PRI data products.
+- End users may distinguish between (input, "raw") data and products, i.e., the derived geophysical parameters.
+- See also granule.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -1838,45 +1814,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Georectifying</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>- core
-  - to be discussed
-description: Correcting for positional displacement with respect to the surface of the Earth.</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Orthorectifying</t>
-        </is>
-      </c>
+          <t>- base
+  - to be approved
+description: The result of organisation, interpretation, categorisation, classification, or some other form of processing of Data attaching to it a certain meaning that can be understood by the addressee.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Correcting for positional displacement with respect to the surface of the Earth.</t>
+          <t>The result of organisation, interpretation, categorisation, classification, or some other form of processing of Data attaching to it a certain meaning that can be understood by the addressee.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>- Source: ISO 19115-2:2019, 3.11; ISO 19115-2:2009(E); https://www.iso.org/standard/67039.html, modified</t>
+          <t>- Information depends on Data and is targeted.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>The correction of sample locations to achieve some sort of geometric regularity, e.g., a regular 2D geographic grid.</t>
-        </is>
-      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
@@ -1893,27 +1861,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Policy Making</t>
+          <t>Lithosphere</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>- high-impact
-- to be discussed
-description: Process by which governments translate their political vision into programmes and actions to deliver outcomes — desired change in the real world.</t>
+          <t>- core
+  - to be approved
+description: The solid, inanimate outer layer of the Geosphere. For the purposes of Earth Observation, includes soils ('pedosphere').</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Process by which governments translate their political vision into programmes and actions to deliver outcomes — desired change in the real world.</t>
+          <t>The solid, inanimate outer layer of the Geosphere. For the purposes of Earth Observation, the Lithosphere is considered to include soils ('pedosphere').</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>- [ESA/CEOS?, modified](https://digital-strategy.ec.europa.eu/en/library/quality-public-administration-toolbox-practitioners)</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -1936,112 +1904,75 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Uncertainty</t>
+          <t>Ancillary Data</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
+          <t>Data acquired on the same platform but not obtained from the main Sensor itself (usually provided as part of Level 0 Data), with the primary purpose of serving the processing of main instrument Data (e.g. Position and velocity of platform).</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>This can be divided into data referred to as spacecraft 'engineering', 'core housekeeping' or 'subsystem' data obtained from other parts of the platform, and includes parameters such as orbit position and velocity, attitude and its range of change, time, temperatures, pressures, jet firings, water dumps, internally produced magnetic fields, and other environmental measurements. Ancillary refers to data that exist purely to serve the data processing.</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>- GUM</t>
+          <t>- ESA/CEOS?, modified
+- EO Data Stewardship Glossary</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Non-negative parameter, associated with data, which characterizes the dispersion of the values of a Trait that could reasonably be attributed to a Phenomenon by means of sensing or modelling.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>- In case of quantitative (continuous) data the uncertainty may be, for example, a standard deviation (or a given multiple of it), or the half-width of an interval having a stated level of confidence (see e.g. Standard and Expanded Uncertainty).
-- For qualitative (categorical?) data, uncertainty may be expressed by commission and omission ('confusion matrix') or overall errors.</t>
-        </is>
-      </c>
+          <t>Data other than instrument measurements, originating in the instrument itself or from the satellite, required to perform processing of the Data. Includes orbit Data, attitude Data, time Information, and spacecraft engineering Data, Calibration Data, Data quality Information, and Data from other instruments or earth system models.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>- Modified from GUM, VIM4:3.1, FIDUCEO, Notes added</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Measure of the spread of the distribution of possible values.</t>
-        </is>
-      </c>
+          <t>- CEOS-ARD PFS template 20220302</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>- [FIDUCEO Glossary](https://research.reading.ac.uk/fiduceo/glossary/), VIM?, modified</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Parameter, associated with the result of measurement, that characterizes the dispersion of values that could reasonably be attributed to the measurand.</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>- When the quality of accuracy or precision of measured values, such as coordinates, is to be characterized quantitatively, the quality parameter is an estimate of the uncertainty of the measurement results. Because accuracy is a qualitative concept, one should not use it quantitatively, that is associate numbers with it; numbers should be associated with measures of uncertainty instead.</t>
-        </is>
-      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>- ISO 19116:2004(E)</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Parameter characterizing the dispersion of the values being attributed to a measurand, based on the information used.</t>
-        </is>
-      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>- VIM4: 3.1</t>
-        </is>
-      </c>
+      <c r="W31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Climate Projection</t>
+          <t>Consistency</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>- core
-- to be approved</t>
+  - to be defined</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Simulated response of the climate system to a scenario of future emission or concentration of greenhouse gases (GHGs) and aerosols, generally derived using climate models. Climate Projections are distinguished from climate predictions by their dependence on the emission/concentration/radiative forcing scenario used, which is in turn based on assumptions concerning, for example, future socioeconomic and technological developments that may or may not be realised.</t>
-        </is>
-      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>- IPCC</t>
-        </is>
-      </c>
+      <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
@@ -2062,20 +1993,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Format</t>
+          <t>Quality Indicator</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Structured Data that is machine readable and can be automatically read and processed by a computer, such as HDF, NetCDF, CSV, JSON, XML, etc.</t>
+description: Indicator providing sufficient information to allow all users to readily evaluate the fitness for purpose of the data or derived product.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Structured Data that is machine readable and can be automatically read and processed by a computer, such as HDF, NetCDF, CSV, JSON, XML, etc.</t>
+          <t>Indicator providing sufficient information to allow all users to readily evaluate the fitness for purpose of the data or derived product. May be a number, set of numbers, graph, Uncertainty budget, or a simple flag.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -2105,26 +2036,31 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Classification System Levels</t>
+          <t>Process</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>- core
-- to be discussed</t>
+          <t>- base
+- to be approved
+description: Series of activities that interact to produce a result.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Levels in a hierarchical Classification System.</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
+          <t>Series of activities that interact to produce a result.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>- A Process may occur once-only or be recurrent or periodic.</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [Wikipedia](https://en.wikipedia.org/wiki/Process)</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -2147,31 +2083,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Geocoding</t>
+          <t>Standard Uncertainty</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Translation of one form of Location into another.</t>
+description: Standard deviation of the probability distribution describing the spread of possible values in quantitative/continuous data.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Translation of one form of Location into another.</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>- Geocoding usually refers to the translation of "address" or "intersection" to "direct Position." Many service providers also include a "reverse geocoding" interface to their geocoder, thus extending the definition of the service as a general translator of Location. Because routing services use internal Location encodings not usually available to others, a geocoder is an integral part of the internals of such a service.</t>
-        </is>
-      </c>
+          <t>Standard deviation of the probability distribution describing the spread of possible values in quantitative/continuous data.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>- ISO 19133:2005; https://www.iso.org/standard/32551.html</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -2194,32 +2126,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Band Central Wavelength</t>
+          <t>Minimum Mapping Width</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>- core
-- to be approved</t>
+  - to be approved
+description: The width of the smallest linear Feature that is still represented on a map.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Single wavelength Value within the sensitivity interval of a spectroradiometric Sensor which represents the respective band. It could be either the mean, the median, the maximum sensitivity, or any other reasonable Value chosen to be representative.</t>
+          <t>The width of the smallest linear Feature that is still represented on a map.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>| Entry format example | Valid unit                                        |
-|----------------------|---------------------------------------------------|
-| 0.545 μm             | micrometre (μm), millimetre (mm), centimetre (cm) |</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- CGLS</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -2242,20 +2169,29 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cartographic Projection</t>
+          <t>Deprecated Product</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>- core
-- to be defined</t>
+- to be approved
+description: Products and collections that have been superseded by a newer version and are still available, but whose use is discouraged since they will be decommissioned in the future.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Products and collections that have been superseded by a newer version and are still available, but whose use is discouraged since they will be decommissioned in the future.</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
@@ -2276,26 +2212,31 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Copernicus Service Provider</t>
+          <t>Period Identifier</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>- core
-- to be discussed</t>
+- to be approved
+description: Temporal reference in the form of a label or code that identifies a Period.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Institutional body, organisation or programme that provides reliable, trusted (authoritative?) EO Information and that has the financial resources to sustain the provision. It utilises satellite Data, ground-based measurements, and other sources to generate accurate and timely Data products related to various aspects of the Earth's environment, such as land, Atmosphere, oceans, and climate.</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t>Temporal reference in the form of a label or code that identifies a Period.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>- Period Identifiers are the temporal equivalent of geographic identifiers as specified in ISO 19912.</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO 19170:2021</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -2318,20 +2259,20 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Location Error</t>
+          <t>Lead Time</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>- core
   - to be approved
-description: Measure of the agreement between the represented Location of an Object and the true Location.</t>
+description: Minimum time of interval between an Observation being tasked and being performed.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Measure of the agreement between the represented Location of an Object and the true Location.</t>
+          <t>Minimum time of interval between an Observation being tasked and being performed.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -2361,29 +2302,25 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Version Control</t>
+          <t>Calibration</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Method of working with collections, similar to version control systems used in traditional software development but optimized to allow better processing of data and collaboration in data analytics and research contexts.</t>
+- source missing
+- to be discussed</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Method of working with collections, similar to the version control systems used in traditional software development but optimized to allow better processing of data and collaboration in the context of data analytics, research, and any other form of data analysis.</t>
+          <t>Process of quantitatively defining a system's (e.g. a Sensor or Model's) response to known, controlled inputs produced for example by references. In Remote Sensing, it implies the collection of pre-flight and in-flight calibration measurements and in-situ Data that is to be used in the Data calibration processing routine.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>- [Wikipedia](https://en.wikipedia.org/wiki/Data_version_control)</t>
-        </is>
-      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
@@ -2404,27 +2341,26 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Access</t>
+          <t>Climate Projection</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>- core
-- to be discussed
-description: Service to disseminate Data.</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Service to disseminate Data.</t>
+          <t>Simulated response of the climate system to a scenario of future emission or concentration of greenhouse gases (GHGs) and aerosols, generally derived using climate models. Climate Projections are distinguished from climate predictions by their dependence on the emission/concentration/radiative forcing scenario used, which is in turn based on assumptions concerning, for example, future socioeconomic and technological developments that may or may not be realised.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- IPCC</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -2447,26 +2383,31 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Collection Upgrade</t>
+          <t>Spatial Reporting Unit</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>- core
-- to be approved</t>
+- to be approved
+description: Smallest spatial object of interest that may be used for reporting and for which the information should be aggregated.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>New and improved major version of all products within a collection due to comprehensive reprocessing.</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
+          <t>Smallest spatial object of interest that may be used for reporting and for which the information should be aggregated.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>- WIGOS 2019 uses 'spatial reporting interval', probably assuming observations are reported on a grid with regular spacing/intervals.</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -2489,27 +2430,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Thematic Resolution</t>
+          <t>Source Data</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Level of categorical detail of information expressed by the number of classes.</t>
+description: Data required for production of an EO Collection (e.g., unenhanced satellite mission data) as well as further processed Level-1 data, or any other pre-processed format meeting program requirements.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Level of categorical detail of information expressed by the number of classes.</t>
+          <t>Data required for production of an EO Collection (e.g., unenhanced satellite mission data) as well as further processed Level-1 data (precision geometrically and radiometrically corrected radiance at the sensor), or any other pre-processed format that suppliers are providing access to that meets program requirements.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>- CGLS</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -2532,27 +2473,30 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Standard Uncertainty</t>
+          <t>Accuracy</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Standard deviation of the probability distribution describing the spread of possible values in quantitative/continuous data.</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Standard deviation of the probability distribution describing the spread of possible values in quantitative/continuous data.</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
+          <t>Proximity of Measurement results to the accepted Value; precision is the degree to which repeated or reproducible measurements under unchanged conditions show the same results.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>- In essence, Accuracy reflects how close measurements are to the accepted Value, while precision gauges the reliability and consistency of those measurements.</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- BS ISO 5725-1</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -2575,30 +2519,27 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Coverage Interval</t>
+          <t>Policy Making</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>- core
-- to be approved</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Coverage extent</t>
-        </is>
-      </c>
+          <t>- high-impact
+- to be discussed
+description: Process by which governments translate their political vision into programmes and actions to deliver outcomes — desired change in the real world.</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Range or specific subset of values associated with a coverage dataset.</t>
+          <t>Process by which governments translate their political vision into programmes and actions to deliver outcomes — desired change in the real world.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [ESA/CEOS?, modified](https://digital-strategy.ec.europa.eu/en/library/quality-public-administration-toolbox-practitioners)</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -2621,31 +2562,32 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Path</t>
+          <t>Position</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>- base
-- to be approved
-description: "Line defined in an algorithmic way using at least two positions (can be open-ended). Alternative: line connecting two positions in an algorithmic way (limited by end points)."</t>
+- to be discussed
+- controversial
+description: Place referenced by a single set of coordinates within a coordinate reference system.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Line defined in an algorithmic way using at least two positions (can be open-ended). Alternative: line connecting two positions in an algorithmic way (limited by end points).</t>
+          <t>Place referenced by a single set of coordinates within a coordinate reference system.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>- A Path is a 1-dimensional Place.</t>
+          <t>- Opposite to (previous) ISO definition, Position shall be used only for 0-dimensional primitives (points).</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO 19133:2005, modified to cover only points, also called 'direct position'</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -2668,27 +2610,27 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Source Data</t>
+          <t>Minimum Mapping Unit</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Data required for production of an EO Collection (e.g., unenhanced satellite mission data) as well as further processed Level-1 data, or any other pre-processed format meeting program requirements.</t>
+  - to be approved
+description: The area of the smallest Feature that is still represented on a map.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Data required for production of an EO Collection (e.g., unenhanced satellite mission data) as well as further processed Level-1 data (precision geometrically and radiometrically corrected radiance at the sensor), or any other pre-processed format that suppliers are providing access to that meets program requirements.</t>
+          <t>The area of the smallest Feature that is still represented on a map.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- CGLS</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -2711,26 +2653,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Atmosphere</t>
+          <t>Spectral Band</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>- core
-- to be approved</t>
+- to be approved
+description: Part of the electromagnetic spectrum of specific wavelengths, in remote sensing usually described by central wavelength and bandwidth.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Layer of gases, commonly known as air, including suspended liquid and solid particles known as aerosols (incl. dust, clouds, snow and ice).</t>
+          <t>Part of the electromagnetic spectrum of specific wavelengths. In Remote Sensing, usually described by central wavelength and bandwidth.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -2753,65 +2696,37 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Validation</t>
+          <t>Geopositioning</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
+- to be discussed
+description: Determination of the geographic Position of a point (0D) or linear (1D) Feature.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
+          <t>Determination of the geographic Position of a point (0D) or linear (1D) Feature.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
+          <t>- Modified from: ISO 19130-1:2018, 3.36</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>- ISO/TS 19101‑2:2008, 4.41</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Process aimed at verifying that the specified requirements are achieved or compliant. Involves comparing mission products with representative reference data, considering various observation conditions, ensuring the quality and traceability of the reference data used.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
-        </is>
-      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>- BIPM; QA4EO; ESA?, modified</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Assurance that a product, service, or system meets the needs of the customer and other identified stakeholders. Often involves acceptance and suitability with external customers.</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
-        </is>
-      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>- EU-US Land Imaging EO Collaboration</t>
-        </is>
-      </c>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
@@ -2824,32 +2739,26 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Long Term Preservation</t>
+          <t>Collection Update</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>- core
-  - to be approved
-description: The act of maintaining information in a correct and independently understandable form over the long term.</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>The act of maintaining information in a correct and independently understandable form over the long term.</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>- Long term refers to a period of time long enough to be concerned with the impact which changing technologies, including support for media and data formats, and changing user communities will have on the information being held in a repository.
-- See also preservation.</t>
-        </is>
-      </c>
+          <t>Minor revisions to a relatively small number of products within a collection for the purpose of correcting errors and maintaining consistent quality.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
@@ -2872,40 +2781,60 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Catalogue</t>
+          <t>Verification</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>- core
-- to be approved</t>
+- to be approved
+description: Provision of objective evidence that a given item fulfils specified requirements.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>System that provides users with discovery of information on which EO products can be obtained.</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>- A 'Product Catalogue' can organise products and collections with varying access levels depending on product and user type.</t>
-        </is>
-      </c>
+          <t>Provision of objective evidence that a given item fulfils specified requirements.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>- When applicable, measurement uncertainty should be taken into consideration.
+- The item may be, e.g. a Process, measurement procedure, material, compound, or measuring system.
+- The specified requirements may be, e.g. that a manufacturer's specifications are met.
+- Verification should not be confused with Calibration. Not every verification is a Validation.</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>- ISO/IEC Guide 99:2007, 2.44</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Evaluation of whether or not a product, service, or system complies with a regulation requirement, specification, or imposed condition. Often an internal Process.</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>- EU-US Land Imaging EO Collaboration</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Means to evaluate the reliability of the data in the absence of a reference dataset, allowing for an assessment of its standalone performance. Involves confirming the consistency and internal coherence of the data without direct comparison to external reference sources.</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
@@ -2918,27 +2847,30 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Minimum Mapping Unit</t>
+          <t>Earth Observation Based Output</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>- core
-  - to be approved
-description: The area of the smallest Feature that is still represented on a map.</t>
+- to be approved
+description: Higher-level processing and integration output (indicative level 4 and beyond) that goes beyond basic data processing, often designed for policy or decision-making needs.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>The area of the smallest Feature that is still represented on a map.</t>
+          <t>Higher-level processing and integration output (indicative level 4 and beyond) that goes beyond basic data processing. These outputs are often designed specifically for policy or decision-making needs, and can be categorized into sub-categories:
+- Outputs from models/model integration: use of EO products as inputs in numerical models or combining them with other data sources in modelling frameworks.
+- Indicator-based outputs: EO products transformed through specialized algorithms (including statistical methods, machine learning, and pattern recognition) to create meaningful metrics based on spatio-temporal analysis.
+- Outputs from reanalysis: merging of EO products with other observations and models, creating consistent long-term records of past atmospheric, oceanic, and land surface conditions, and filling gaps through data assimilation techniques.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>- CGLS</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
@@ -2961,35 +2893,20 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Temporal Reporting Period</t>
+          <t>Cartographic Projection</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Time period used for reporting and for which the information should be aggregated from the native temporal resolution.</t>
+- to be defined</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Time Period used for reporting and for which the information should be aggregated from the native Temporal Resolution.</t>
-        </is>
-      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>| Entry format example | Valid unit                     |
-|----------------------|-------------------------------|
-| 1 s, 2 h, 1 d        | second, hour, day, month, year |</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>- Modified WIGOS Metadata Standard 2019</t>
-        </is>
-      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
@@ -3010,27 +2927,33 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Policy File</t>
+          <t>Temporal Reporting Period</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>- high-impact
-- to be discussed
-description: Policy documents that represent the official written reference for a given Policy.</t>
+          <t>- core
+- to be approved
+description: Time period used for reporting and for which the information should be aggregated from the native temporal resolution.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Policy documents that represent the official written reference for a given Policy.</t>
+          <t>Time Period used for reporting and for which the information should be aggregated from the native Temporal Resolution.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>| Entry format example | Valid unit                     |
+|----------------------|-------------------------------|
+| 1 s, 2 h, 1 d        | second, hour, day, month, year |</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Modified WIGOS Metadata Standard 2019</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
@@ -3053,27 +2976,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Impact</t>
+          <t>Reproducibility</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>- core
-  - to be discussed
-description: Regarded long-term according to X. However, in the Horizon Europe Missions terminology, regarded short-term.</t>
+- to be approved
+description: Concerned with the validity of the results of a particular study, enabling readers to check whether results have been manipulated by reproducing exactly the same study using the same data and methods.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Regarded long-term according to X. However, in the Horizon Europe Missions terminology, regarded short-term.</t>
+          <t>Concerned with the validity of the results of a particular study, i.e., the possibility for readers to check whether results have been manipulated, by reproducing exactly the same study using the same data and methods.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Ostermann and Granell (2015)</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
@@ -3096,25 +3019,28 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Calibration</t>
+          <t>Atmosphere</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>- core
-- source missing
-- to be discussed</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Process of quantitatively defining a system's (e.g. a Sensor or Model's) response to known, controlled inputs produced for example by references. In Remote Sensing, it implies the collection of pre-flight and in-flight calibration measurements and in-situ Data that is to be used in the Data calibration processing routine.</t>
+          <t>Layer of gases, commonly known as air, including suspended liquid and solid particles known as aerosols (incl. dust, clouds, snow and ice).</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>- Guth et al. 2021</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
@@ -3135,51 +3061,39 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Geolocating</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>- base
+          <t>- core
 - to be approved
-description: Value and possibly Uncertainty of a Trait of a specific Entity.</t>
+description: Geopositioning of an Object using a Physical Sensor Model or a True Replacement Model.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Value and possibly Uncertainty of a Trait of a specific Entity.</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>- Data simply describe entities using certain traits and are not targeted at a particular use or audience.</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Data can be categorised into:
-- factual (i.e. obtained by Observation) or fictional (obtained e.g. through modelling, estimating or assigning)
-- quantitative (continuous) or qualitative (categorical)
-- analogue or digital
-(list not exhaustive!)</t>
-        </is>
-      </c>
+          <t>Geopositioning of an Object using a Physical Sensor Model or a True Replacement Model.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO 19115-2:2009, 4.11</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Scientific or technical measurements, values calculated therefrom, observations, or facts that can be represented by numbers, tables, graphs, models, text, or symbols which are used as a basis for reasoning and further calculation.</t>
+          <t>Determination of the geographic location of a feature of two or more dimensions.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
+          <t>- ISO 19130-1:2018, 3.36 ('geopositioning'), modified</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
@@ -3198,41 +3112,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Quantity</t>
+          <t>Confidence Interval</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>- base
-- to be approved
-description: Property having a magnitude that can be expressed as a number from a continuous and contiguous range and a reference.</t>
+          <t>- controversial
+- to be approved</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Property having a magnitude that can be expressed as a number from a continuous and contiguous range and a reference.</t>
+          <t>Probability that the Quantity lies in the interval, conditioned on the measuring or modelling assumptions.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>- ISO/IEC Guide 99:2007, 1.1, modified — Notes omitted</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Property whose instances can be compared by ratio or only by order.</t>
-        </is>
-      </c>
+          <t>- KCEO</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>- gEOGlos (VIM4 Notes omitted)</t>
-        </is>
-      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
@@ -3249,20 +3154,19 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Policy Milestone</t>
+          <t>Baseline</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>- high-impact
-- to be discussed
-description: Markers of significant progress in addressing specific issues, or crucial decision points where significant choices are made within a policy process.</t>
+          <t>- core
+- to be approved</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Markers of significant progress in addressing specific issues, or crucial decision points where significant choices are made. Concrete examples include: policy planning and proposing, impact assessment, implementation, or implementation cycles (e.g., Water Framework Directive, Marine Strategy Framework Directive), achievement of Policy Objectives and Policy Targets, and evaluating and improving existing laws.</t>
+          <t>Reference Period, time or measure against which the Information is assessed or compared.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
@@ -3272,10 +3176,18 @@
           <t>- KCEO</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Source data that has been processed to a common set of requirements and organised into a form that allows immediate analysis and interoperability through time and with other collections.</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
@@ -3292,32 +3204,26 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Classification System Levels</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>- base
-- to be approved
-description: Element of a type domain.</t>
+          <t>- core
+- to be discussed</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Element of a type domain.</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>- A Value may consider a possible state of an object within a class or type (domain).
-- A data value is an instance of a data type, a value without identity.</t>
-        </is>
-      </c>
+          <t>Levels in a hierarchical Classification System.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>- ISO/IEC 19501:2005, 0000_5</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -3340,26 +3246,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Collection Update</t>
+          <t>Latency</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>- core
-- to be approved</t>
+  - to be discussed
+description: Period between the end of sensing of a Phenomenon to the beginning of availability of a specific product.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Minor revisions to a relatively small number of products within a collection for the purpose of correcting errors and maintaining consistent quality.</t>
+          <t>Period between the end of sensing of a Phenomenon to the beginning of availability of a specific product.</t>
         </is>
       </c>
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- ?</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -3382,33 +3289,20 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Laboratory Observation</t>
+          <t>Resolution</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>- core
-  - to be discussed
-description: Usually in-situ observations in which the Object or Phenomenon is isolated from other systems or altered in its original conditions or environment.</t>
+  - to be defined</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Usually in-situ observations in which the Object or Phenomenon is isolated from other systems or altered in its original conditions or environment.</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>- It is important to consider that Laboratory Observations are typically conducted in controlled conditions, allowing for isolation or alteration of the Object or Phenomenon from its natural environment or other systems.</t>
-        </is>
-      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
@@ -3429,21 +3323,29 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Environmental Process</t>
+          <t>Data Access</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>- core
-- to be defined
-description: ""</t>
+- to be discussed
+description: Service to disseminate Data.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Service to disseminate Data.</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
@@ -3464,27 +3366,27 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Measurement Uncertainty</t>
+          <t>Phenomenon</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>- core
-  - to be discussed
-description: Uncertainty associated with the method of Measurement.</t>
+          <t>- base
+- to be approved
+description: Entity with at least one Property referenced by an identifier.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Uncertainty associated with the method of Measurement.</t>
+          <t>Entity with at least one Property referenced by an identifier.</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>- CEOS Wiki adopted from JCGM GUM</t>
+          <t>- KCEO, modified after Wikipedia and the Columbia Encyclopaedia 2008</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
@@ -3507,20 +3409,40 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Continuity</t>
+          <t>Earth Spheres</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>- core
-  - to be defined</t>
+- to be approved
+description: Spheres dividing planet Earth into subsystems, which are collectives of (physical) matter sharing specific traits.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Spheres dividing planet Earth into subsystems, which are collectives of (physical) matter sharing specific traits.</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>- Atmosphere
+- Hydrosphere
+- Cryosphere
+- Biosphere
+- Lithosphere
+- Anthroposphere</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>- Hugget, R., et al., 2024, DOI: 10.1177/03091333241275465
+- Guth, P., et al., 2021, https://doi.org/10.3390/rs13183581
+- Martin, Y.E., et al., 2012</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
@@ -3541,38 +3463,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Temporal Revisit</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>- core
-- to be discussed
-description: Interval between successive observations.</t>
+          <t>- base
+- to be approved
+description: Element of a type domain.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Interval between successive observations.</t>
+          <t>Element of a type domain.</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>- In Remote Sensing it is also called repeat cycle.
-- More generally it is known as temporal sampling interval.</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>| Entry format example | Valid unit                     |
-|----------------------|-------------------------------|
-| 1 s, 2 h             | second, hour, day, month, year |</t>
-        </is>
-      </c>
+          <t>- A Value may consider a possible state of an object within a class or type (domain).
+- A data value is an instance of a data type, a value without identity.</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO/IEC 19501:2005, 0000_5</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
@@ -3595,20 +3511,37 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Timeliness</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>- core
-  - to be defined</t>
+- to be approved
+description: Period between the moment of requesting information and the moment of availability of information.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Period between the moment of requesting information and the moment of availability of information.
+- Near Real-Time (NRT): delivered less than 3 hours after requesting information.
+- Slow-Time Critical (STC): delivered within 48 hours after requesting information.
+- Non-Time Critical (NTC): typically delivered within 1 month after requesting information.</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>- In some contexts also known as delivery time.
+- C3S URDB describes timeliness as "the ability of the publish/subscribe middleware to provide the expected service within known time bounds".</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>- Adapted from ESA S3 User Guide</t>
+        </is>
+      </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
@@ -3629,41 +3562,59 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Period Identifier</t>
+          <t>Auxiliary Data</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Temporal reference in the form of a label or code that identifies a Period.</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Temporal reference in the form of a label or code that identifies a Period.</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>- Period Identifiers are the temporal equivalent of geographic identifiers as specified in ISO 19912.</t>
-        </is>
-      </c>
+          <t>Data that enhance the processing and utilisation of main Sensor Data. Auxiliary Data are usually not captured by the same Data collection Process or on the same platform as the main Sensor Data. Examples include meteorological Data received from ECMWF/Met Offices or DEMs. Auxiliary Data help in Data processing, but are also Data sets in their own right.</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>- ISO 19170:2021</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
+          <t>- ESA/CEOS?, modified
+- ENMAP Glossary of Terms, https://www.enmap.org/Data/doc/EnMAP_Terms.pdf, 20210624
+- EO Data Stewardship Glossary</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Data required to perform processing of Sensor Data which is not obtained from the Sensor itself. Includes: (a) Data provided by the spacecraft (e.g. orbit Position and velocity, attitude, instrument house-keeping Data, on-board time); (b) Data not available from on-board sources.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>For EnMAP, this includes (a) orbit files, attitude files, Calibration Data, instrument house-keeping Data; (b) atmospheric parameters, reference images.</t>
+        </is>
+      </c>
       <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>- ENMAP Glossary of Terms, https://www.enmap.org/Data/doc/EnMAP_Terms.pdf, 20210624
+- EO Data Stewardship Glossary</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Data required for instrument processing that does not originate in the instrument itself or from the satellite. Some Auxiliary Data will be generated in the ground segment, whilst other Data will be provided from external sources.</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>- CEOS-ARD PFS template 20220302</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
@@ -3724,41 +3675,41 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Timeliness</t>
+          <t>Quantity</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>- core
+          <t>- base
 - to be approved
-description: Period between the moment of requesting information and the moment of availability of information.</t>
+description: Property having a magnitude that can be expressed as a number from a continuous and contiguous range and a reference.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Period between the moment of requesting information and the moment of availability of information.
-- Near Real-Time (NRT): delivered less than 3 hours after requesting information.
-- Slow-Time Critical (STC): delivered within 48 hours after requesting information.
-- Non-Time Critical (NTC): typically delivered within 1 month after requesting information.</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>- In some contexts also known as delivery time.
-- C3S URDB describes timeliness as "the ability of the publish/subscribe middleware to provide the expected service within known time bounds".</t>
-        </is>
-      </c>
+          <t>Property having a magnitude that can be expressed as a number from a continuous and contiguous range and a reference.</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>- Adapted from ESA S3 User Guide</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>- ISO/IEC Guide 99:2007, 1.1, modified — Notes omitted</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Property whose instances can be compared by ratio or only by order.</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>- gEOGlos (VIM4 Notes omitted)</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
@@ -3775,20 +3726,33 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Equivalence</t>
+          <t>Final Product Version</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>- core
-  - to be defined</t>
+- to be approved
+description: Product within an EO Collection that is not expected to be updated.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Product within an EO Collection that is not expected to be updated.</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>- In its production, all of the prerequisite auxiliary data were used as input.</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
@@ -3809,27 +3773,32 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Hydrosphere</t>
+          <t>Observation</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>- core
-  - to be approved
-description: The masses of liquid water, such as oceans, lakes, and rivers.</t>
+          <t>- controversial
+  - to be discussed
+description: Act of determining the Value of a Property by interacting in a reproducible way with the Phenomenon using a Sensor.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>The masses of liquid water, such as oceans, lakes, and rivers.</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr"/>
+          <t>Act of determining the Value of a Property by interacting in a reproducible way with the Phenomenon using a Sensor.</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>- The result of an Observation is a Value complemented by an Uncertainty, often itself being referred to as 'observation'.
+- An Observation result represents a Sample of the Phenomenon (otherwise it would be identical with the Phenomenon).</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
@@ -3852,36 +3821,56 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>Characteristic</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>- core
-- to be approved</t>
+          <t>- base
+- to be discussed</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Proximity of Measurement results to the accepted Value; precision is the degree to which repeated or reproducible measurements under unchanged conditions show the same results.</t>
+          <t>Distinguishing Feature.</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>- In essence, Accuracy reflects how close measurements are to the accepted Value, while precision gauges the reliability and consistency of those measurements.</t>
+          <t>- A Characteristic can be inherent or assigned.
+- A Characteristic can be qualitative or quantitative.
+- There are various classes of Characteristics, such as the following:
+  - physical (e.g. mechanical, electrical, chemical, biological);
+  - sensory (e.g. relating to smell, touch, taste, sight, hearing);
+  - behavioural (e.g. courtesy, honesty, veracity);
+  - temporal (e.g. punctuality, reliability, availability);
+  - ergonomic (e.g. physiological characteristic or related to human safety);
+  - functional (e.g. maximum speed of an aircraft).</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>- BS ISO 5725-1</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
+          <t>- ISO 9000:2005, 3.5.1</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Abstraction of a Property of an Object or of a set of objects.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>- Characteristics are used for describing Concepts.</t>
+        </is>
+      </c>
       <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>- ISO 1087-1:2000, 3.2.4; ISO 19146:2010(E); https://www.iso.org/standard/20057.html</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
@@ -3898,27 +3887,27 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Traceability</t>
+          <t>Geosphere</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Property of a measurement result whereby the result can be related to a reference through a documented unbroken chain of calibrations each contributing to the measurement uncertainty.</t>
+  - to be approved
+description: The masses of minerals that constitute planet Earth.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Property of a measurement result whereby the result can be related to a Reference through a documented unbroken chain of calibrations, each contributing to the measurement uncertainty.</t>
+          <t>The masses of minerals that constitute planet Earth.</t>
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>- https://www.isobudgets.com/Measurement-traceability-complying-iso-17025-requirements/</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -3941,26 +3930,27 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Biosphere</t>
+          <t>Spectral Resolution</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>- core
-- to be approved</t>
+- to be approved
+description: Measure of the ability to resolve features in the electromagnetic spectrum.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Masses of living organisms, such as vegetation and animals, including dead but still connected parts such as roots, trunks or branches.</t>
+          <t>Measure of the ability to resolve features in the electromagnetic spectrum.</t>
         </is>
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
@@ -3983,31 +3973,27 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Update Frequency</t>
+          <t>Hydrosphere</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Frequency at which the product is available to users.</t>
+  - to be approved
+description: The masses of liquid water, such as oceans, lakes, and rivers.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Frequency at which the product is available to users.</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>- Also known in product catalogues as dissemination frequency.</t>
-        </is>
-      </c>
+          <t>The masses of liquid water, such as oceans, lakes, and rivers.</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
@@ -4030,27 +4016,34 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Lithosphere</t>
+          <t>Time of Year</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>- core
-  - to be approved
-description: The solid, inanimate outer layer of the Geosphere. For the purposes of Earth Observation, includes soils ('pedosphere').</t>
+- to be approved
+description: Time of the year at which the variable is observed or simulated by a model.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>The solid, inanimate outer layer of the Geosphere. For the purposes of Earth Observation, the Lithosphere is considered to include soils ('pedosphere').</t>
+          <t>Time of the year at which the variable is observed or simulated by a model.</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>| Type      | Entry format example | Valid unit     |
+|-----------|----------------------|----------------|
+| timestamp | m/d                  | Not Applicable |
+| timerange | m/d - m/d            | Not Applicable |</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
@@ -4073,25 +4066,25 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Path</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>- base
-  - to be approved
-description: The result of organisation, interpretation, categorisation, classification, or some other form of processing of Data attaching to it a certain meaning that can be understood by the addressee.</t>
+- to be approved
+description: "Line defined in an algorithmic way using at least two positions (can be open-ended). Alternative: line connecting two positions in an algorithmic way (limited by end points)."</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>The result of organisation, interpretation, categorisation, classification, or some other form of processing of Data attaching to it a certain meaning that can be understood by the addressee.</t>
+          <t>Line defined in an algorithmic way using at least two positions (can be open-ended). Alternative: line connecting two positions in an algorithmic way (limited by end points).</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>- Information depends on Data and is targeted.</t>
+          <t>- A Path is a 1-dimensional Place.</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
@@ -4120,20 +4113,20 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Temporal Consistency</t>
+          <t>Spatial Consistency</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Condition where the temporal statistical properties of the sample depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
+description: Condition where the spatial statistical properties of the data depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Condition where the temporal statistical properties of the Sample depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
+          <t>Condition where the spatial statistical properties of the data depend only on the underlying physical processes and not on other factors such as fusing different products or sensors. Also, the validity of the assumptions of the procedure to produce information holds true across the whole spatial range.</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -4163,32 +4156,30 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Metadata</t>
+          <t>Cell</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>- core
-  - to be approved
-description: Data describing other data, providing an understanding of the content and utility of a product or collection.</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Data describing other data, providing an understanding of the content and utility of a product or collection.</t>
+          <t>Spatial, spatio-temporal zone or temporal unit of geometry with dimensionality greater than 0, associated with a zone.</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>- Metadata may be used to select data for a particular scientific investigation.
-- Metadata is intended as information describing significant aspects of a resource (Earth Observation space data in this context). They are created for the purposes of data search, discovery and access management and may exist at various levels, typically from data collection through to the individual variables of each product in a collection.</t>
+          <t>- Cells are the unit of geometry in a DGGS, and the geometry of the region of space-time occupied by a zone is a Cell.</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- ISO 19170:2021</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
@@ -4211,23 +4202,26 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Spatial Resolution</t>
+          <t>Business Continuity</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>- core
-- to be defined
-description: ''</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>An organisation's readiness to continue functioning during times of disruption.</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
@@ -4250,27 +4244,32 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Phenomenon</t>
+          <t>Derivative Product</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>- base
+          <t>- core
 - to be approved
-description: Entity with at least one Property referenced by an identifier.</t>
+description: Product additionally processed from baseline or unenhanced mission data.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Entity with at least one Property referenced by an identifier.</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr"/>
+          <t>Product additionally processed from baseline or unenhanced mission data.</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>- Generally either a compilation of time-series data (e.g., all time, annual, monthly or seasonal summary data, &gt; Level 3) or thematic versions of each individual data tile of baseline data.
+- Derived products are citable via a Digital Object Identifier (DOI).</t>
+        </is>
+      </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>- KCEO, modified after Wikipedia and the Columbia Encyclopaedia 2008</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
@@ -4293,27 +4292,27 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Geolocation Information</t>
+          <t>Policy Objective</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>- core
+          <t>- high-impact
 - to be discussed
-description: Information used to determine geographic Location.</t>
+description: Desired outcome that policymakers wish to achieve.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Information used to determine geographic Location.</t>
+          <t>Desired outcome that policymakers wish to achieve.</t>
         </is>
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>- ISO 19130-1:2018, 3.34</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
@@ -4336,58 +4335,63 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Verification</t>
+          <t>Validation</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Provision of objective evidence that a given item fulfils specified requirements.</t>
+description: Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Provision of objective evidence that a given item fulfils specified requirements.</t>
+          <t>Process of assessing, by independent means, the quality of the data products derived from the system outputs.</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>- When applicable, measurement uncertainty should be taken into consideration.
-- The item may be, e.g. a Process, measurement procedure, material, compound, or measuring system.
-- The specified requirements may be, e.g. that a manufacturer's specifications are met.
-- Verification should not be confused with Calibration. Not every verification is a Validation.</t>
+          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>- ISO/IEC Guide 99:2007, 2.44</t>
+          <t>- ISO/TS 19101‑2:2008, 4.41</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Evaluation of whether or not a product, service, or system complies with a regulation requirement, specification, or imposed condition. Often an internal Process.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>Process aimed at verifying that the specified requirements are achieved or compliant. Involves comparing mission products with representative reference data, considering various observation conditions, ensuring the quality and traceability of the reference data used.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
+        </is>
+      </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr">
         <is>
-          <t>- EU-US Land Imaging EO Collaboration</t>
+          <t>- BIPM; QA4EO; ESA?, modified</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Means to evaluate the reliability of the data in the absence of a reference dataset, allowing for an assessment of its standalone performance. Involves confirming the consistency and internal coherence of the data without direct comparison to external reference sources.</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr"/>
+          <t>Assurance that a product, service, or system meets the needs of the customer and other identified stakeholders. Often involves acceptance and suitability with external customers.</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>- In this part of ISO 19159, the term validation is used in a limited sense and only relates to the validation of calibration data in order to control their change over time.</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- EU-US Land Imaging EO Collaboration</t>
         </is>
       </c>
       <c r="P84" t="inlineStr"/>
@@ -4402,27 +4406,36 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Property</t>
+          <t>Temporal Extent</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>- base
-- to be discussed
-description: Observable Trait.</t>
+          <t>- core
+- to be approved
+description: Period during which data was collected, observations were made, or for which the model was run.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Observable Trait.</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
+          <t>Period during which data was collected, observations were made, or for which the model was run.</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>- In W3C this is the definition of temporal coverage.
+- Time Period covered by a series of observations inclusive of the specified date/time indications (measurement history). Defined based on the beginning and end dates of observations.</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>- WIGOS Metadata</t>
+        </is>
+      </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Adapted from W3C</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
@@ -4445,27 +4458,27 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Object</t>
+          <t>Traceability</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>- base
-  - to be approved
-description: Entity with a well-defined boundary and identity that encapsulates state and behaviour.</t>
+          <t>- core
+- to be approved
+description: Property of a measurement result whereby the result can be related to a reference through a documented unbroken chain of calibrations each contributing to the measurement uncertainty.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Entity with a well-defined boundary and identity that encapsulates state and behaviour.</t>
+          <t>Property of a measurement result whereby the result can be related to a Reference through a documented unbroken chain of calibrations, each contributing to the measurement uncertainty.</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>- ISO/IEC 19501:2005</t>
+          <t>- https://www.isobudgets.com/Measurement-traceability-complying-iso-17025-requirements/</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
@@ -4488,38 +4501,31 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Time of Day</t>
+          <t>Decommissioned Product</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Time of the day at which the variable or parameter is observed or simulated by a model.</t>
+description: Products and collections that have been superseded by new versions and are no longer available.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Time of the day at which the variable or parameter is observed or simulated by a model.</t>
+          <t>Products and collections that have been superseded by new versions and are no longer available.</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>- In Remote Sensing it is also known as time of overpass.</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>| Type      | Entry format example | Valid unit |
-|-----------|----------------------|------------|
-| timestamp | 18:00 h (0–24)       | Hours      |
-| timerange | 18:00 – 20:00 h      | Hours      |</t>
-        </is>
-      </c>
+          <t>- Decommissioned products are no longer supported, i.e. corrections will not be made, new data will not be added, and support is not available.</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
@@ -4542,27 +4548,32 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Obsolete Product or Collection</t>
+          <t>Grid</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>- core
   - to be approved
-description: Products or collections which have been superseded by later versions of a product or collection.</t>
+description: Network composed of two or more sets of curves in which the members of each set intersect the members of the other sets in an algorithmic way.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Products or collections which have been superseded by later versions of a product or collection.</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr"/>
+          <t>Network composed of two or more sets of curves in which the members of each set intersect the members of the other sets in an algorithmic way.</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>- The curves partition a space into grid cells or zones.
+- The intersection points of the curves are called nodes.</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- ISO 19123:2005, 4.1.23; Note 1 modified; Note 2 added</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
@@ -4585,40 +4596,37 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Baseline</t>
+          <t>Measurement</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>- core
-- to be approved</t>
+  - to be discussed
+description: Observation of a Quantity.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Reference Period, time or measure against which the Information is assessed or compared.</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr"/>
+          <t>Observation of a Quantity.</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>- The Process of collecting a measurement is called measuring.</t>
+        </is>
+      </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Source data that has been processed to a common set of requirements and organised into a form that allows immediate analysis and interoperability through time and with other collections.</t>
-        </is>
-      </c>
+          <t>- GEOGlos (VIM ?, modified)</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>- WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data</t>
-        </is>
-      </c>
+      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
@@ -4635,32 +4643,30 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Earth Observation</t>
+          <t>Catalogue</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>- high-impact
-- to be discussed
-description: Science domain dealing with technologies and methods of collecting and analyzing observations about the different Earth spheres.</t>
+          <t>- core
+- to be approved</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Science domain dealing with technologies and methods of collecting and analyzing observations about the different Earth spheres.</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>- Earth Observation (EO) can be categorised by location of the sensor into space-borne, air-borne, sea-borne, ground-based, underwater and underground EO.
-- Earth Observation (EO) includes Remote Sensing, such as satellite imagery, as well as in-situ observations, e.g., with ground-based devices.</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr"/>
+          <t>System that provides users with discovery of information on which EO products can be obtained.</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>- A 'Product Catalogue' can organise products and collections with varying access levels depending on product and user type.</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>- Modified GEO definition [GEO (earthobservations.org)](https://earthobservations.org/resources#key)</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
@@ -4683,24 +4689,37 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Tolerance</t>
+          <t>Reference</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>- core
-  - to be defined</t>
+- to be discussed
+description: Phenomenon whose values for specific properties are known and understood with an Uncertainty significantly lower than that of the Observation with which it is compared.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Phenomenon whose values for specific properties are known and understood with an Uncertainty significantly lower (quantify?) than that of the Observation with which it is compared.</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Sort of data acquired with an Uncertainty significantly lower (quantify?) than that of the data it is being compared with.</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>- VIM?, modified</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
@@ -4717,23 +4736,27 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Spectral Resolution</t>
+          <t>Laboratory Observation</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Measure of the ability to resolve features in the electromagnetic spectrum.</t>
+  - to be discussed
+description: Usually in-situ observations in which the Object or Phenomenon is isolated from other systems or altered in its original conditions or environment.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Measure of the ability to resolve features in the electromagnetic spectrum.</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr"/>
+          <t>Usually in-situ observations in which the Object or Phenomenon is isolated from other systems or altered in its original conditions or environment.</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>- It is important to consider that Laboratory Observations are typically conducted in controlled conditions, allowing for isolation or alteration of the Object or Phenomenon from its natural environment or other systems.</t>
+        </is>
+      </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
@@ -4760,27 +4783,33 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Near Real Time Data</t>
+          <t>Sample</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>- high-impact
-  - to be discussed
-description: Data available for use with a specified (small and application dependent) latency, typically 3 hours for meteorological applications.</t>
+          <t>- controversial
+- to be discussed
+description: Subset of one or more entities.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Data available for use with a specified (small and application dependent) latency, typically 3 hours for meteorological applications.</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr"/>
+          <t>Subset of one or more entities.</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>- A Sample may be spatial, temporal, spectral, or in any other dimension or Trait.
+- Each Sample is contiguous, i.e. it does not consist of more than one discontinuous geometry in any dimension.
+- The Process of obtaining a Sample is called sampling.</t>
+        </is>
+      </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
@@ -4803,40 +4832,31 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Measurand</t>
+          <t>Trait</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>- core
-  - to be approved
-description: Particular Quantity subject to Measurement.</t>
+          <t>- base
+- to be approved
+description: Characteristic belonging to an entity and referenced by an identifier.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Particular Quantity subject to Measurement.</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>| Step | Process description |
-| :----- | :------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------
---- |
-| (Raw) | The complete and unaltered/unprocessed set of Data acquired by one or several sensors on a platform |
-| M/0 uncalibrated | Unaltered/unprocessed Level 0 (main) Sensor Data annotated with processed Ancillary Data and supplemented by Auxiliary Data (including radiometric and geometric Calibration coefficients and geo-referencing parameters) allowing further processing to higher Levels. |
-| M/1 Sensor-calibrated | Level M/0 Sensor Data which have been calibrated (ideally traceable to SI) and spatially aligned (co-located, eventually co-gridded) to represent at-Sensor measurements (Value and Uncertainty) in Sensor nominal spatiotemporal sampling, supplemented by appropriate ancillary data. |
-| M/2 target-calibrated | Level M/1 Data processed to represent geophysical Property values (and uncertainties) for a specified target (Object, Feature of interest, e.g. surface reflectance, apparent temperature) derived from M/1 Sensor Data, as much as possible maintaining the sensors nominal spatial and temporal sampling (Observation preserving). |
-| M/3 homogenised | Level M/1 or M/2 Data which have been generalised and integrated across one or several platforms and acquisitions to achieve an increased, more regular or in any other form enhanced spatial or temporal coverage in which states geophysical values agnostic of the originally acquiring Sensor and Observation condition and thus directly comparable. This homogenisation and fusion may include measurand re-Calibration to external standards and references including use of modelling, aggregation and interpolation. |
-| M/4 derived/inferred | Model output or results from analyses of Level M/3 (or lower level) Data i.e., attributes that might not be directly observable by the Sensor(s) but are derived from observations in combination with other external incl. non-observational Data using techniques like modelling or machine learning (AI). |
-From http://doi.org/10.2760/46796</t>
-        </is>
-      </c>
+          <t>Characteristic belonging to an entity and referenced by an identifier.</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>- Traits can be objective (inherent?) in which case they are also observable and called properties. Traits which are not observable (directly or indirectly) need to be assigned.</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>- VIM: 1993, 2.6</t>
+          <t>- Based on ISO 19143:2010, 4.21, ISO/IEC 2382:2015, 2121440, significantly modified, Note 1 added</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
@@ -4859,27 +4879,32 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Latency</t>
+          <t>Metadata</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>- core
-  - to be discussed
-description: Period between the end of sensing of a Phenomenon to the beginning of availability of a specific product.</t>
+  - to be approved
+description: Data describing other data, providing an understanding of the content and utility of a product or collection.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Period between the end of sensing of a Phenomenon to the beginning of availability of a specific product.</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr"/>
+          <t>Data describing other data, providing an understanding of the content and utility of a product or collection.</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>- Metadata may be used to select data for a particular scientific investigation.
+- Metadata is intended as information describing significant aspects of a resource (Earth Observation space data in this context). They are created for the purposes of data search, discovery and access management and may exist at various levels, typically from data collection through to the individual variables of each product in a collection.</t>
+        </is>
+      </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>- ?</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
@@ -4902,27 +4927,30 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Policy Target</t>
+          <t>Backup</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>- high-impact
-- to be discussed
-description: Specific level or rate set for the Policy Objective.</t>
+          <t>- core
+- to be approved</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Specific level or rate set for the Policy Objective.</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr"/>
+          <t>General practice of making copies of current baseline and derived products of EO Collections at specified time intervals, and storing those copies in a manner that will not affect the data if the primary distribution environment is compromised.</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>- The emphasis is on the ability to retrieve a copy of the entire EO Collection on demand if the original data is lost or compromised.</t>
+        </is>
+      </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
@@ -4945,29 +4973,20 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Policy Objective</t>
+          <t>Tolerance</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>- high-impact
-- to be discussed
-description: Desired outcome that policymakers wish to achieve.</t>
+          <t>- core
+  - to be defined</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Desired outcome that policymakers wish to achieve.</t>
-        </is>
-      </c>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
+      <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr"/>
@@ -4988,27 +5007,30 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Forecast Range</t>
+          <t>Archive</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>- core
-- to be discussed
-description: The forecast period.</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>The forecast period.</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr"/>
+          <t>System that stores data products, guaranteeing their preservation for future use.</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>- This function includes all operations to identify, store and retrieve the data and ensure their integrity.</t>
+        </is>
+      </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
@@ -5031,27 +5053,26 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Quality Indicator</t>
+          <t>Biosphere</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Indicator providing sufficient information to allow all users to readily evaluate the fitness for purpose of the data or derived product.</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Indicator providing sufficient information to allow all users to readily evaluate the fitness for purpose of the data or derived product. May be a number, set of numbers, graph, Uncertainty budget, or a simple flag.</t>
+          <t>Masses of living organisms, such as vegetation and animals, including dead but still connected parts such as roots, trunks or branches.</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>- CEOS Wiki</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
@@ -5074,27 +5095,27 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>User Interface</t>
+          <t>Impact</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Set of all the components of an interactive system that provide information and controls for the user to accomplish specific tasks with the interactive system.</t>
+  - to be discussed
+description: Regarded long-term according to X. However, in the Horizon Europe Missions terminology, regarded short-term.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Set of all the components of an interactive system that provide information and controls for the User to accomplish specific tasks with the interactive system.</t>
+          <t>Regarded long-term according to X. However, in the Horizon Europe Missions terminology, regarded short-term.</t>
         </is>
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>- ISO 9241-110:2020, 3.10</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
@@ -5117,31 +5138,27 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Obsolete Product or Collection</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Maximum acceptable change in Uncertainty per decade.</t>
+  - to be approved
+description: Products or collections which have been superseded by later versions of a product or collection.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Maximum acceptable change in Uncertainty per decade.</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>- GCOS uses bias or systematic errors instead of Uncertainty.</t>
-        </is>
-      </c>
+          <t>Products or collections which have been superseded by later versions of a product or collection.</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>- Modified from GCOS 2022</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
@@ -5164,26 +5181,27 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Classification System</t>
+          <t>Measurement Uncertainty</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>- core
-- to be approved</t>
+  - to be discussed
+description: Uncertainty associated with the method of Measurement.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Nomenclature used to classify Information into categorical thematic classes (e.g., EUNIS, MAES ecosystems, Corine Land Cover, LCCS).</t>
+          <t>Uncertainty associated with the method of Measurement.</t>
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- CEOS Wiki adopted from JCGM GUM</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
@@ -5206,22 +5224,18 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Spatial Consistency</t>
+          <t>Spatial Resolution</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Condition where the spatial statistical properties of the data depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
+- to be defined
+description: ''</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Condition where the spatial statistical properties of the data depend only on the underlying physical processes and not on other factors such as fusing different products or sensors. Also, the validity of the assumptions of the procedure to produce information holds true across the whole spatial range.</t>
-        </is>
-      </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
@@ -5249,23 +5263,28 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Expanded Uncertainty</t>
+          <t>In-Situ Observation</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>- core
-- to be approved
-description: Standard Uncertainty multiplied by a coverage factor k, chosen to obtain a desired level of confidence.</t>
+          <t>- controversial
+  - to be discussed
+description: Observations performed in the same Place where a Phenomenon occurs, normally without isolating it from other systems or altering its pre-Observation state.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Standard Uncertainty multiplied by a coverage factor, k. The coverage factor is chosen to obtain a desired level of confidence. Most commonly a 95% confidence interval is chosen. For a Gaussian distribution, this is achieved with a coverage factor k = 2. (Note that strictly this provides a 95.45% confidence interval.)</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr"/>
+          <t>Observations performed in the same Place where a Phenomenon occurs, normally without isolating it from other systems (its environment) or altering its pre-Observation state.</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>- The main Characteristic of such observations is that distance has no or only negligible (within Uncertainty) influence on the Value of the Property observed. In-Situ Observations therefore often require either direct physical contact or small distances between a Sensor and the observed Phenomenon.
+- Observations not fulfilling these conditions are considered Remote Sensing.</t>
+        </is>
+      </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
@@ -5292,30 +5311,29 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sensor</t>
+          <t>Earth Observation Product</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Device or instrument suited (through physical/chemical interaction) to measure one or more properties of a Phenomenon and thus collect factual/objective data.</t>
+description: Direct output from standardized satellite data processing chains (indicative levels 2 and 3), representing fundamental geophysical and biophysical variables.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Device or instrument suited (through physical/chemical interaction) to measure one or more properties of a Phenomenon and thus collect factual/objective data.</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>- Sensing is therefore a synonym for Observation (the Process).
-- As by their definition, sensors perform sampling.
-- Sensors used to obtain measurements must be calibrated and provide uncertainties.</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr"/>
+          <t>Direct output from standardized satellite data processing chains (indicative levels 2 and 3), representing fundamental geophysical and biophysical variables. These products demonstrate direct Traceability to original satellite measurements through rigorous Calibration and Validation processes. The processing methodology prioritizes the conversion of raw sensor data into quantifiable physical measurements, maintaining strict adherence to standardized processing protocols and Validation requirements.</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>- Soil moisture from microwave sensors
+- Forest canopy height from LiDAR data</t>
+        </is>
+      </c>
       <c r="G105" t="inlineStr">
         <is>
           <t>- KCEO</t>
@@ -5341,27 +5359,31 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Minimum Mapping Width</t>
+          <t>Spatial Completeness</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>- core
-  - to be approved
-description: The width of the smallest linear Feature that is still represented on a map.</t>
+- to be approved
+description: Presence or absence of gaps, which are missing values in an otherwise continuous spatial data series.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr">
         <is>
-          <t>The width of the smallest linear Feature that is still represented on a map.</t>
+          <t>Presence or absence of gaps, which are missing values in an otherwise continuous spatial data series.</t>
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>- Surface soil moisture retrieved from microwave satellite sensors may present gaps in mountainous terrains.</t>
+        </is>
+      </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>- CGLS</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
@@ -5384,30 +5406,31 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Backup</t>
+          <t>Geocoding</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>- core
-- to be approved</t>
+- to be approved
+description: Translation of one form of Location into another.</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>General practice of making copies of current baseline and derived products of EO Collections at specified time intervals, and storing those copies in a manner that will not affect the data if the primary distribution environment is compromised.</t>
+          <t>Translation of one form of Location into another.</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>- The emphasis is on the ability to retrieve a copy of the entire EO Collection on demand if the original data is lost or compromised.</t>
+          <t>- Geocoding usually refers to the translation of "address" or "intersection" to "direct Position." Many service providers also include a "reverse geocoding" interface to their geocoder, thus extending the definition of the service as a general translator of Location. Because routing services use internal Location encodings not usually available to others, a geocoder is an integral part of the internals of such a service.</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- ISO 19133:2005; https://www.iso.org/standard/32551.html</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
@@ -5430,43 +5453,45 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Temporal Resolution</t>
+          <t>Georectifying</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Observation or model output representing regular intervals, specifying the length of the interval that determines the smallest event or process that can be resolved.</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr"/>
+  - to be discussed
+description: Correcting for positional displacement with respect to the surface of the Earth.</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Orthorectifying</t>
+        </is>
+      </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Observation or model output representing regular intervals, specifying the length of the interval that determines the smallest event or Process that can be resolved (e.g., the Period between observations, the time steps in a model).</t>
+          <t>Correcting for positional displacement with respect to the surface of the Earth.</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>- WIGOS 2019 distinguishes between sampling time Period, as the Period over which a Measurement is taken, and temporal sampling interval as the time Period between the beginning of consecutive sampling periods. Temporal Resolution in this Glossary is equivalent to sampling time Period as used by WIGOS.</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>| Entry format example | Valid unit                     |
-|----------------------|-------------------------------|
-| 1 s, 2 h, 1 m        | second, hour, day, month, year |</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr"/>
+          <t>- Source: ISO 19115-2:2019, 3.11; ISO 19115-2:2009(E); https://www.iso.org/standard/67039.html, modified</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>The correction of sample locations to achieve some sort of geometric regularity, e.g., a regular 2D geographic grid.</t>
+        </is>
+      </c>
       <c r="I108" t="inlineStr"/>
       <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
@@ -5483,27 +5508,27 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Place</t>
+          <t>Data Licencing</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>- base
+          <t>- core
 - to be approved
-description: Part of any space referenced by an identifier.</t>
+description: Legal instrument by which a copyright holder may grant rights over the protected work.</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Part of any space referenced by an identifier.</t>
+          <t>Legal instrument by which a copyright holder may grant rights over the protected work. Data and content is open if it is subject to an explicitly-applied licence that conforms to the Open Definition. A range of standard open licences are available, such as the Creative Commons CC-BY licence, which requires only attribution.</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>- ISO 19155:2012, 4.8</t>
+          <t>- CEOS Wiki</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
@@ -5526,45 +5551,37 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Ancillary Data</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>- core
-- to be approved</t>
+          <t>- base
+- to be approved
+description: Particular era or span of time.</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Data acquired on the same platform but not obtained from the main Sensor itself (usually provided as part of Level 0 Data), with the primary purpose of serving the processing of main instrument Data (e.g. Position and velocity of platform).</t>
+          <t>Particular era or span of time.</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>This can be divided into data referred to as spacecraft 'engineering', 'core housekeeping' or 'subsystem' data obtained from other parts of the platform, and includes parameters such as orbit position and velocity, attitude and its range of change, time, temperatures, pressures, jet firings, water dumps, internally produced magnetic fields, and other environmental measurements. Ancillary refers to data that exist purely to serve the data processing.</t>
+          <t>- Periods are intervals named with a Period Identifier.</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>- ESA/CEOS?, modified
-- EO Data Stewardship Glossary</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Data other than instrument measurements, originating in the instrument itself or from the satellite, required to perform processing of the Data. Includes orbit Data, attitude Data, time Information, and spacecraft engineering Data, Calibration Data, Data quality Information, and Data from other instruments or earth system models.</t>
-        </is>
-      </c>
+          <t>- ISO 19170:2021</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>- CEOS-ARD PFS template 20220302</t>
-        </is>
-      </c>
+      <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
@@ -5581,32 +5598,26 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Observation</t>
+          <t>Collection Upgrade</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>- controversial
-  - to be discussed
-description: Act of determining the Value of a Property by interacting in a reproducible way with the Phenomenon using a Sensor.</t>
+          <t>- core
+- to be approved</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Act of determining the Value of a Property by interacting in a reproducible way with the Phenomenon using a Sensor.</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>- The result of an Observation is a Value complemented by an Uncertainty, often itself being referred to as 'observation'.
-- An Observation result represents a Sample of the Phenomenon (otherwise it would be identical with the Phenomenon).</t>
-        </is>
-      </c>
+          <t>New and improved major version of all products within a collection due to comprehensive reprocessing.</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
@@ -5629,32 +5640,31 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Grid</t>
+          <t>Feature</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>- core
-  - to be approved
-description: Network composed of two or more sets of curves in which the members of each set intersect the members of the other sets in an algorithmic way.</t>
+          <t>- base
+- to be discussed
+description: Abstraction of real-world phenomena.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Network composed of two or more sets of curves in which the members of each set intersect the members of the other sets in an algorithmic way.</t>
+          <t>Abstraction of real-world phenomena.</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>- The curves partition a space into grid cells or zones.
-- The intersection points of the curves are called nodes.</t>
+          <t>- A feature may occur as a type or an instance.</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>- ISO 19123:2005, 4.1.23; Note 1 modified; Note 2 added</t>
+          <t>- ISO 19101-1:2014, 4.1.11, modified</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
@@ -5677,45 +5687,37 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>Custodian</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Entity (person, organization, institution, etc.) that is requesting data or information with certain characteristics described by needs and/or requirements.</t>
+description: Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>In the context of the KCEO, entity (person, organization, institution, etc.) that is requesting data or information with certain characteristics described by needs and/or requirements.</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr"/>
+          <t>Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>- See also Steward.</t>
+        </is>
+      </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>External person, institution or system that consumes provided services.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>- Includes Data Access or Science and Service Exploitation Platforms provided by a payload data ground segment.</t>
-        </is>
-      </c>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>- EO Data Stewardship Glossary</t>
-        </is>
-      </c>
+      <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
@@ -5732,36 +5734,26 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Remote Sensing</t>
+          <t>Anthroposphere</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>- controversial
-- to be discussed
-description: Type of Observation performed at a significant distance from a Phenomenon.</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Remote Observation</t>
-        </is>
-      </c>
+          <t>- core
+- to be approved</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Type of Observation performed at a significant distance from a Phenomenon.</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>- 'Significant' in this context means that the distance has, or may have, a non-negligible impact on the Value of the Property observed.
-- The effect of the distance on the acquired data is the main distinction criterion between 'remote' and 'in-situ' observations.</t>
-        </is>
-      </c>
+          <t>One of the Earth spheres consisting predominantly of matter processed by humans, such as construction wood, bricks, concrete, asphalt, glass, or plastics.</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
@@ -5784,38 +5776,45 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Earth Observation Product</t>
+          <t>User</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Direct output from standardized satellite data processing chains (indicative levels 2 and 3), representing fundamental geophysical and biophysical variables.</t>
+description: Entity (person, organization, institution, etc.) that is requesting data or information with certain characteristics described by needs and/or requirements.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Direct output from standardized satellite data processing chains (indicative levels 2 and 3), representing fundamental geophysical and biophysical variables. These products demonstrate direct Traceability to original satellite measurements through rigorous Calibration and Validation processes. The processing methodology prioritizes the conversion of raw sensor data into quantifiable physical measurements, maintaining strict adherence to standardized processing protocols and Validation requirements.</t>
+          <t>In the context of the KCEO, entity (person, organization, institution, etc.) that is requesting data or information with certain characteristics described by needs and/or requirements.</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>- Soil moisture from microwave sensors
-- Forest canopy height from LiDAR data</t>
-        </is>
-      </c>
+      <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
           <t>- KCEO</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>External person, institution or system that consumes provided services.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>- Includes Data Access or Science and Service Exploitation Platforms provided by a payload data ground segment.</t>
+        </is>
+      </c>
       <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>- EO Data Stewardship Glossary</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
@@ -5832,31 +5831,31 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Trait</t>
+          <t>Steward</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>- base
-- to be approved
-description: Characteristic belonging to an entity and referenced by an identifier.</t>
+          <t>- core
+- to be discussed
+description: Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Characteristic belonging to an entity and referenced by an identifier.</t>
+          <t>Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>- Traits can be objective (inherent?) in which case they are also observable and called properties. Traits which are not observable (directly or indirectly) need to be assigned.</t>
+          <t>- See also Custodian.</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>- Based on ISO 19143:2010, 4.21, ISO/IEC 2382:2015, 2121440, significantly modified, Note 1 added</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
@@ -5879,31 +5878,24 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Time of Year</t>
+          <t>Temporal Consistency</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Time of the year at which the variable is observed or simulated by a model.</t>
+description: Condition where the temporal statistical properties of the sample depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Time of the year at which the variable is observed or simulated by a model.</t>
+          <t>Condition where the temporal statistical properties of the Sample depend only on the underlying physical processes and not on other factors such as fusing different products or sensors.</t>
         </is>
       </c>
       <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>| Type      | Entry format example | Valid unit     |
-|-----------|----------------------|----------------|
-| timestamp | m/d                  | Not Applicable |
-| timerange | m/d - m/d            | Not Applicable |</t>
-        </is>
-      </c>
+      <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
           <t>- KCEO</t>
@@ -5929,32 +5921,28 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>In-Situ Observation</t>
+          <t>Geospatial Data</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>- controversial
-  - to be discussed
-description: Observations performed in the same Place where a Phenomenon occurs, normally without isolating it from other systems or altering its pre-Observation state.</t>
+          <t>- core
+  - to be approved
+description: Data consisting of, derived from, or relating to information that is directly linked to specific geographical locations.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Observations performed in the same Place where a Phenomenon occurs, normally without isolating it from other systems (its environment) or altering its pre-Observation state.</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>- The main Characteristic of such observations is that distance has no or only negligible (within Uncertainty) influence on the Value of the Property observed. In-Situ Observations therefore often require either direct physical contact or small distances between a Sensor and the observed Phenomenon.
-- Observations not fulfilling these conditions are considered Remote Sensing.</t>
-        </is>
-      </c>
+          <t>Data consisting of, derived from, or relating to information that is directly linked to specific geographical locations.</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- https://www.merriam-webster.com/dictionary/geospatial
+- https://isotc211.geolexica.org/Concepts/202/, accessed 20221010</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
@@ -5977,56 +5965,37 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Characteristic</t>
+          <t>Stability</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>- base
-- to be discussed</t>
+          <t>- core
+- to be approved
+description: Maximum acceptable change in Uncertainty per decade.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Distinguishing Feature.</t>
+          <t>Maximum acceptable change in Uncertainty per decade.</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>- A Characteristic can be inherent or assigned.
-- A Characteristic can be qualitative or quantitative.
-- There are various classes of Characteristics, such as the following:
-  - physical (e.g. mechanical, electrical, chemical, biological);
-  - sensory (e.g. relating to smell, touch, taste, sight, hearing);
-  - behavioural (e.g. courtesy, honesty, veracity);
-  - temporal (e.g. punctuality, reliability, availability);
-  - ergonomic (e.g. physiological characteristic or related to human safety);
-  - functional (e.g. maximum speed of an aircraft).</t>
+          <t>- GCOS uses bias or systematic errors instead of Uncertainty.</t>
         </is>
       </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>- ISO 9000:2005, 3.5.1</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Abstraction of a Property of an Object or of a set of objects.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>- Characteristics are used for describing Concepts.</t>
-        </is>
-      </c>
+          <t>- Modified from GCOS 2022</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>- ISO 1087-1:2000, 3.2.4; ISO 19146:2010(E); https://www.iso.org/standard/20057.html</t>
-        </is>
-      </c>
+      <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
@@ -6043,31 +6012,27 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Measurement</t>
+          <t>Property</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>- core
-  - to be discussed
-description: Observation of a Quantity.</t>
+          <t>- base
+- to be discussed
+description: Observable Trait.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Observation of a Quantity.</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>- The Process of collecting a measurement is called measuring.</t>
-        </is>
-      </c>
+          <t>Observable Trait.</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>- GEOGlos (VIM ?, modified)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
@@ -6090,32 +6055,31 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Preservation</t>
+          <t>Geographic Data</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Processes and operations used to ensure data technical and intellectual survival through time.</t>
+description: Data with implicit or explicit reference to a Location relative to the Earth.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Processes and operations used to ensure data technical and intellectual survival through time.</t>
+          <t>Data with implicit or explicit reference to a Location relative to the Earth.</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>- Grants data integrity, discoverability and accessibility, and facilitates its (re-)use in the long term.
-- Preservation is one of the tasks of data curation.</t>
+          <t>- Geographic Information is also used as a term for information concerning phenomena implicitly or explicitly associated with a Location relative to the Earth.</t>
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- ISO 19109:2015, 4.13; ISO 19109:2005</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
@@ -6138,64 +6102,113 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Provisional Product</t>
+          <t>Uncertainty</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Products in a research and development phase not yet published into a standardized collection.</t>
+description: Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Products in a research and development phase not yet published into a standardized collection.</t>
+          <t>Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
         </is>
       </c>
       <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr"/>
-      <c r="I122" t="inlineStr"/>
+          <t>- GUM</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Non-negative parameter, associated with data, which characterizes the dispersion of the values of a Trait that could reasonably be attributed to a Phenomenon by means of sensing or modelling.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>- In case of quantitative (continuous) data the uncertainty may be, for example, a standard deviation (or a given multiple of it), or the half-width of an interval having a stated level of confidence (see e.g. Standard and Expanded Uncertainty).
+- For qualitative (categorical?) data, uncertainty may be expressed by commission and omission ('confusion matrix') or overall errors.</t>
+        </is>
+      </c>
       <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>- Modified from GUM, VIM4:3.1, FIDUCEO, Notes added</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Measure of the spread of the distribution of possible values.</t>
+        </is>
+      </c>
       <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr"/>
-      <c r="P122" t="inlineStr"/>
-      <c r="Q122" t="inlineStr"/>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>- [FIDUCEO Glossary](https://research.reading.ac.uk/fiduceo/glossary/), VIM?, modified</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Parameter, associated with the result of measurement, that characterizes the dispersion of values that could reasonably be attributed to the measurand.</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>- When the quality of accuracy or precision of measured values, such as coordinates, is to be characterized quantitatively, the quality parameter is an estimate of the uncertainty of the measurement results. Because accuracy is a qualitative concept, one should not use it quantitatively, that is associate numbers with it; numbers should be associated with measures of uncertainty instead.</t>
+        </is>
+      </c>
       <c r="R122" t="inlineStr"/>
-      <c r="S122" t="inlineStr"/>
-      <c r="T122" t="inlineStr"/>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>- ISO 19116:2004(E)</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Parameter characterizing the dispersion of the values being attributed to a measurand, based on the information used.</t>
+        </is>
+      </c>
       <c r="U122" t="inlineStr"/>
       <c r="V122" t="inlineStr"/>
-      <c r="W122" t="inlineStr"/>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>- VIM4: 3.1</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>User Interface</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>- core
-  - to be defined
-description: ""</t>
+- to be approved
+description: Set of all the components of an interactive system that provide information and controls for the user to accomplish specific tasks with the interactive system.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Set of all the components of an interactive system that provide information and controls for the User to accomplish specific tasks with the interactive system.</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>- ISO 9241-110:2020, 3.10</t>
+        </is>
+      </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
@@ -6216,37 +6229,57 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Instrument Data</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>- high-impact
-- to be discussed
-description: Deliberate system of guidelines to guide decisions and achieve rational outcomes, implemented as a procedure or protocol and typically promulgated through official written documents.</t>
+          <t>- core
+  - to be approved
+description: Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Deliberate system of guidelines to guide decisions and achieve rational outcomes. Statement of intent implemented as a procedure or protocol. Typically promulgated through official written documents.</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr"/>
+          <t>Data specifically associated with the instrument, either because it was generated by the instrument or included in data packets identified with that instrument.</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>- These data consist of instrument science and engineering data, and possibly ancillary data. Instrument engineering data is produced by engineering sensor(s) of an instrument, used either for operating the instrument or for processing the science data generated by the instrument. Instrument science data is produced by the science sensor(s) of an instrument, usually constituting the basic reason for existence of an instrument.</t>
+        </is>
+      </c>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr"/>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Data created by an instrument including scientific measurements and any engineering or ancillary data which may be included in the data packets.</t>
+        </is>
+      </c>
       <c r="I124" t="inlineStr"/>
       <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Data produced and transmitted by the science and engineering sensors of an instrument, and, in the spacecraft environment, any additional data packaged with the instrument's sensor data by virtue of services provided.</t>
+        </is>
+      </c>
       <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr"/>
       <c r="Q124" t="inlineStr"/>
       <c r="R124" t="inlineStr"/>
@@ -6259,31 +6292,40 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Geographic Identifier</t>
+          <t>Measurand</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Spatial reference in the form of a label or code that identifies a Location.</t>
+  - to be approved
+description: Particular Quantity subject to Measurement.</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Spatial reference in the form of a label or code that identifies a Location.</t>
+          <t>Particular Quantity subject to Measurement.</t>
         </is>
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>- "Spain" is an example of a label (country name); "SW1-3AD" is an example of a code (postcode).</t>
+          <t>| Step | Process description |
+| :----- | :------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------------
+--- |
+| (Raw) | The complete and unaltered/unprocessed set of Data acquired by one or several sensors on a platform |
+| M/0 uncalibrated | Unaltered/unprocessed Level 0 (main) Sensor Data annotated with processed Ancillary Data and supplemented by Auxiliary Data (including radiometric and geometric Calibration coefficients and geo-referencing parameters) allowing further processing to higher Levels. |
+| M/1 Sensor-calibrated | Level M/0 Sensor Data which have been calibrated (ideally traceable to SI) and spatially aligned (co-located, eventually co-gridded) to represent at-Sensor measurements (Value and Uncertainty) in Sensor nominal spatiotemporal sampling, supplemented by appropriate ancillary data. |
+| M/2 target-calibrated | Level M/1 Data processed to represent geophysical Property values (and uncertainties) for a specified target (Object, Feature of interest, e.g. surface reflectance, apparent temperature) derived from M/1 Sensor Data, as much as possible maintaining the sensors nominal spatial and temporal sampling (Observation preserving). |
+| M/3 homogenised | Level M/1 or M/2 Data which have been generalised and integrated across one or several platforms and acquisitions to achieve an increased, more regular or in any other form enhanced spatial or temporal coverage in which states geophysical values agnostic of the originally acquiring Sensor and Observation condition and thus directly comparable. This homogenisation and fusion may include measurand re-Calibration to external standards and references including use of modelling, aggregation and interpolation. |
+| M/4 derived/inferred | Model output or results from analyses of Level M/3 (or lower level) Data i.e., attributes that might not be directly observable by the Sensor(s) but are derived from observations in combination with other external incl. non-observational Data using techniques like modelling or machine learning (AI). |
+From http://doi.org/10.2760/46796</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>- ISO 19112:2019, 3.1.2</t>
+          <t>- VIM: 1993, 2.6</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
@@ -6306,38 +6348,27 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Earth Spheres</t>
+          <t>Policy Target</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>- core
-- to be approved
-description: Spheres dividing planet Earth into subsystems, which are collectives of (physical) matter sharing specific traits.</t>
+          <t>- high-impact
+- to be discussed
+description: Specific level or rate set for the Policy Objective.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Spheres dividing planet Earth into subsystems, which are collectives of (physical) matter sharing specific traits.</t>
+          <t>Specific level or rate set for the Policy Objective.</t>
         </is>
       </c>
       <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>- Atmosphere
-- Hydrosphere
-- Cryosphere
-- Biosphere
-- Lithosphere
-- Anthroposphere</t>
-        </is>
-      </c>
+      <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>- Hugget, R., et al., 2024, DOI: 10.1177/03091333241275465
-- Guth, P., et al., 2021, https://doi.org/10.3390/rs13183581
-- Martin, Y.E., et al., 2012</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
@@ -6360,27 +6391,36 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Deprecated Product</t>
+          <t>Spatial Extent</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Products and collections that have been superseded by a newer version and are still available, but whose use is discouraged since they will be decommissioned in the future.</t>
+description: Zone or region of space described by a geographic identifier in the form of a label or code, or by a bounding box, representing the maximum spatial boundary within which the user is requesting data.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Products and collections that have been superseded by a newer version and are still available, but whose use is discouraged since they will be decommissioned in the future.</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
+          <t>Zone or region of space described by a geographic identifier in the form of a label or code, or by a bounding box. Represents the maximum extent (the spatial boundary or limits) within which the User is requesting data.
+The attribute represents the maximum spatial extent of the AOI, and in case the AOI is made of many discontinuous zones then it represents the maximum extent of the union of all the zones.</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>- WIGOS metadata standard defines it as the typical spatial georeferenced volume covered by the observations.</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>- If a User is requesting information about degradation of African protected sites, then the AOIs are the protected sites, and the spatial extent is the African continent.</t>
+        </is>
+      </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- Adapted from ISO 19170-1:2021</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
@@ -6403,27 +6443,27 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Replicability</t>
+          <t>Provisional Product</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Property enabling other researchers to conduct an independent study with different data and similar but not identical methods, yet arriving at results that confirm the original study's hypothesis.</t>
+description: Products in a research and development phase not yet published into a standardized collection.</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Property enabling other researchers to conduct an independent study with different data and similar but not identical methods, yet arriving at results that confirm the original study's hypothesis.</t>
+          <t>Products in a research and development phase not yet published into a standardized collection.</t>
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr">
         <is>
-          <t>- Craglia, M., et al. (2018).</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
@@ -6446,31 +6486,27 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Object</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>- base
-- to be discussed
-description: Abstraction of real-world phenomena.</t>
+  - to be approved
+description: Entity with a well-defined boundary and identity that encapsulates state and behaviour.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Abstraction of real-world phenomena.</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>- A feature may occur as a type or an instance.</t>
-        </is>
-      </c>
+          <t>Entity with a well-defined boundary and identity that encapsulates state and behaviour.</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>- ISO 19101-1:2014, 4.1.11, modified</t>
+          <t>- ISO/IEC 19501:2005</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
@@ -6493,31 +6529,27 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Final Product Version</t>
+          <t>Forecast Range</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Product within an EO Collection that is not expected to be updated.</t>
+- to be discussed
+description: The forecast period.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Product within an EO Collection that is not expected to be updated.</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>- In its production, all of the prerequisite auxiliary data were used as input.</t>
-        </is>
-      </c>
+          <t>The forecast period.</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
@@ -6540,36 +6572,27 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Spatial Extent</t>
+          <t>Policy Milestone</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>- core
-- to be approved
-description: Zone or region of space described by a geographic identifier in the form of a label or code, or by a bounding box, representing the maximum spatial boundary within which the user is requesting data.</t>
+          <t>- high-impact
+- to be discussed
+description: Markers of significant progress in addressing specific issues, or crucial decision points where significant choices are made within a policy process.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Zone or region of space described by a geographic identifier in the form of a label or code, or by a bounding box. Represents the maximum extent (the spatial boundary or limits) within which the User is requesting data.
-The attribute represents the maximum spatial extent of the AOI, and in case the AOI is made of many discontinuous zones then it represents the maximum extent of the union of all the zones.</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>- WIGOS metadata standard defines it as the typical spatial georeferenced volume covered by the observations.</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>- If a User is requesting information about degradation of African protected sites, then the AOIs are the protected sites, and the spatial extent is the African continent.</t>
-        </is>
-      </c>
+          <t>Markers of significant progress in addressing specific issues, or crucial decision points where significant choices are made. Concrete examples include: policy planning and proposing, impact assessment, implementation, or implementation cycles (e.g., Water Framework Directive, Marine Strategy Framework Directive), achievement of Policy Objectives and Policy Targets, and evaluating and improving existing laws.</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr">
         <is>
-          <t>- Adapted from ISO 19170-1:2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
@@ -6592,27 +6615,31 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Policy Cycle</t>
+          <t>Dwell Time</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>- high-impact
-- to be discussed
-description: Well-established concept typically taught as the rational model of policy decision-making, representing an idealised view of the policy process.</t>
+          <t>- core
+- to be approved
+description: Time that an antenna beam spends on a target.</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Well-established concept, typically taught as the rational model of policy decision-making. Idealised view of the policy process.</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr"/>
+          <t>Time that an antenna beam spends on a target.</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>- In the context of radar sensing.</t>
+        </is>
+      </c>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>- [ESA/CEOS?, modified](https://digital-strategy.ec.europa.eu/en/library/quality-public-administration-toolbox-practitioners)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
@@ -6635,27 +6662,27 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Data Licencing</t>
+          <t>Location Error</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Legal instrument by which a copyright holder may grant rights over the protected work.</t>
+  - to be approved
+description: Measure of the agreement between the represented Location of an Object and the true Location.</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Legal instrument by which a copyright holder may grant rights over the protected work. Data and content is open if it is subject to an explicitly-applied licence that conforms to the Open Definition. A range of standard open licences are available, such as the Creative Commons CC-BY licence, which requires only attribution.</t>
+          <t>Measure of the agreement between the represented Location of an Object and the true Location.</t>
         </is>
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>- CEOS Wiki</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
@@ -6678,27 +6705,23 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Representativeness</t>
+          <t>Expanded Uncertainty</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Quality or characteristic of a measurement or observation to accurately represent a specific geographic location, time period, or environmental condition.</t>
+description: Standard Uncertainty multiplied by a coverage factor k, chosen to obtain a desired level of confidence.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Quality or characteristic of a measurement or Observation to accurately represent a specific geographic location, time Period, or environmental condition.</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>- WIGOS metadata standard defines representativeness as the extent of the region around the Observation of which it is representative.</t>
-        </is>
-      </c>
+          <t>Standard Uncertainty multiplied by a coverage factor, k. The coverage factor is chosen to obtain a desired level of confidence. Most commonly a 95% confidence interval is chosen. For a Gaussian distribution, this is achieved with a coverage factor k = 2. (Note that strictly this provides a 95.45% confidence interval.)</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr">
         <is>
@@ -6725,29 +6748,21 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Reproducibility</t>
+          <t>Environmental Process</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Concerned with the validity of the results of a particular study, enabling readers to check whether results have been manipulated by reproducing exactly the same study using the same data and methods.</t>
+- to be defined
+description: ""</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>Concerned with the validity of the results of a particular study, i.e., the possibility for readers to check whether results have been manipulated, by reproducing exactly the same study using the same data and methods.</t>
-        </is>
-      </c>
+      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>- Ostermann and Granell (2015)</t>
-        </is>
-      </c>
+      <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
@@ -6768,31 +6783,31 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Custodian</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>- core
-- to be approved
-description: Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
+          <t>- controversial
+  - to be discussed
+description: An, often numeric, theoretical (or otherwise abstract) representation of an Entity intended to generate Data describing one or more of its traits.</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Entity responsible for the safe custody, transport, storage of the data and implementation of business rules.</t>
+          <t>An, often numeric, theoretical (or otherwise abstract) representation of an Entity intended to generate Data describing one or more of its traits (as a result of pre-set conditions).</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>- See also Steward.</t>
+          <t>- The Process of generating Data using a model is called modelling.</t>
         </is>
       </c>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
@@ -6815,27 +6830,26 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Geosphere</t>
+          <t>Classification System</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>- core
-  - to be approved
-description: The masses of minerals that constitute planet Earth.</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>The masses of minerals that constitute planet Earth.</t>
+          <t>Nomenclature used to classify Information into categorical thematic classes (e.g., EUNIS, MAES ecosystems, Corine Land Cover, LCCS).</t>
         </is>
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
@@ -6858,30 +6872,27 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Cell</t>
+          <t>Spectral Bandwidth</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>- core
-- to be approved</t>
+- to be discussed
+description: Range of the Spectral Band.</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Spatial, spatio-temporal zone or temporal unit of geometry with dimensionality greater than 0, associated with a zone.</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>- Cells are the unit of geometry in a DGGS, and the geometry of the region of space-time occupied by a zone is a Cell.</t>
-        </is>
-      </c>
+          <t>Range of the Spectral Band.</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr">
         <is>
-          <t>- ISO 19170:2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
@@ -6904,31 +6915,26 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Geographic Coordinate Reference System</t>
+          <t>Collection</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Coordinate Reference System (CRS) that has a geodetic Reference frame and an ellipsoidal coordinate system.</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Coordinate Reference System (CRS) that has a geodetic Reference frame and an ellipsoidal coordinate system.</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>- Also known as geographic CRS.</t>
-        </is>
-      </c>
+          <t>Group of products that have been processed using a consistent radiometric calibration, geometric registration base, data/metadata format, and version of processing algorithms.</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>- ISO 19111:2019, 3.1.35</t>
+          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
@@ -6951,35 +6957,20 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Vertical Levels</t>
+          <t>Continuity</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Levels of a vertical discretization, e.g. pressure levels in an atmospheric model reanalysis or height levels in a forest biomass EO product.</t>
+  - to be defined</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>Levels of a vertical discretization. Examples may be pressure levels in an atmospheric model reanalysis or height levels in a forest biomass EO product.</t>
-        </is>
-      </c>
+      <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>| Entry format example                | Valid unit           |
-|------------------------------------|----------------------|
-| 1, 5, 10 meter; 1000, 850, 500 hPa | meter, hPa, unitless |</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>- KCEO</t>
-        </is>
-      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
@@ -7000,26 +6991,27 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Anthroposphere</t>
+          <t>Policy File</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>- core
-- to be approved</t>
+          <t>- high-impact
+- to be discussed
+description: Policy documents that represent the official written reference for a given Policy.</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>One of the Earth spheres consisting predominantly of matter processed by humans, such as construction wood, bricks, concrete, asphalt, glass, or plastics.</t>
+          <t>Policy documents that represent the official written reference for a given Policy.</t>
         </is>
       </c>
       <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr">
         <is>
-          <t>- Guth et al. 2021</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
@@ -7042,27 +7034,23 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Dwell Time</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>- core
-- to be approved
-description: Time that an antenna beam spends on a target.</t>
+          <t>- high-impact
+- to be discussed
+description: Deliberate system of guidelines to guide decisions and achieve rational outcomes, implemented as a procedure or protocol and typically promulgated through official written documents.</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Time that an antenna beam spends on a target.</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>- In the context of radar sensing.</t>
-        </is>
-      </c>
+          <t>Deliberate system of guidelines to guide decisions and achieve rational outcomes. Statement of intent implemented as a procedure or protocol. Typically promulgated through official written documents.</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
@@ -7089,34 +7077,31 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Duration</t>
+          <t>Geographic Identifier</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Non-negative interval Quantity of time equal to the difference between the final and initial instants of a time interval.</t>
+description: Spatial reference in the form of a label or code that identifies a Location.</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Non-negative interval Quantity of time equal to the difference between the final and initial instants of a time interval.</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>- Duration is one of the base quantities in the International System of Quantities (ISQ) on which the International System of Units (SI) is based. The term "time" instead of "duration" is often used in this context and also for an infinitesimal duration.
-- For the term "duration", expressions such as "time" or "time interval" are often used, but the term "time" is not recommended in this sense and the term "time interval" is deprecated in this sense to avoid confusion with the concept of "time interval".
-- The exact duration of a time scale unit depends on the time scale used. For example, the durations of a year, month, week, day, hour or minute may depend on when they occur (in a Gregorian calendar, a calendar month can have a duration of 28, 29, 30, or 31 days; in a 24-hour clock, a clock minute can have a duration of 59, 60, or 61 seconds, etc.). Therefore, the exact duration can only be evaluated if the exact duration of each is known.
-- This definition is closely related to NOTE 1 of the terminological entry "duration" in IEC 60050-113:2011, 113-01-13.</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr"/>
+          <t>Spatial reference in the form of a label or code that identifies a Location.</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>- "Spain" is an example of a label (country name); "SW1-3AD" is an example of a code (postcode).</t>
+        </is>
+      </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>- ISO 8601-1:2019, 3.1.1.8</t>
+          <t>- ISO 19112:2019, 3.1.2</t>
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
@@ -7139,27 +7124,32 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Lead Time</t>
+          <t>Earth Observation</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>- core
-  - to be approved
-description: Minimum time of interval between an Observation being tasked and being performed.</t>
+          <t>- high-impact
+- to be discussed
+description: Science domain dealing with technologies and methods of collecting and analyzing observations about the different Earth spheres.</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Minimum time of interval between an Observation being tasked and being performed.</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr"/>
+          <t>Science domain dealing with technologies and methods of collecting and analyzing observations about the different Earth spheres.</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>- Earth Observation (EO) can be categorised by location of the sensor into space-borne, air-borne, sea-borne, ground-based, underwater and underground EO.
+- Earth Observation (EO) includes Remote Sensing, such as satellite imagery, as well as in-situ observations, e.g., with ground-based devices.</t>
+        </is>
+      </c>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- Modified GEO definition [GEO (earthobservations.org)](https://earthobservations.org/resources#key)</t>
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
@@ -7182,31 +7172,27 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>EO Space Data</t>
+          <t>Data Format</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Earth Observation data generated by spaceborne missions or instruments owned by public or private organizations.</t>
+description: Structured Data that is machine readable and can be automatically read and processed by a computer, such as HDF, NetCDF, CSV, JSON, XML, etc.</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Earth Observation data generated by spaceborne missions or instruments owned by public or private organizations.</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>- See also Instrument data.</t>
-        </is>
-      </c>
+          <t>Structured Data that is machine readable and can be automatically read and processed by a computer, such as HDF, NetCDF, CSV, JSON, XML, etc.</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
-          <t>- [EO Data Stewardship Glossary](https://ceos.org/document_management/Working_Groups/WGISS/Interest_Groups/Data_Stewardship/White_Papers/EO-DataStewardshipGlossary.pdf)</t>
+          <t>- CEOS Wiki</t>
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
@@ -7229,31 +7215,27 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Spatial Completeness</t>
+          <t>Geolocation Information</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Presence or absence of gaps, which are missing values in an otherwise continuous spatial data series.</t>
+- to be discussed
+description: Information used to determine geographic Location.</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Presence or absence of gaps, which are missing values in an otherwise continuous spatial data series.</t>
+          <t>Information used to determine geographic Location.</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>- Surface soil moisture retrieved from microwave satellite sensors may present gaps in mountainous terrains.</t>
-        </is>
-      </c>
+      <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- ISO 19130-1:2018, 3.34</t>
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
@@ -7276,32 +7258,26 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Derivative Product</t>
+          <t>Cryosphere</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
           <t>- core
-- to be approved
-description: Product additionally processed from baseline or unenhanced mission data.</t>
+- to be approved</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Product additionally processed from baseline or unenhanced mission data.</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>- Generally either a compilation of time-series data (e.g., all time, annual, monthly or seasonal summary data, &gt; Level 3) or thematic versions of each individual data tile of baseline data.
-- Derived products are citable via a Digital Object Identifier (DOI).</t>
-        </is>
-      </c>
+          <t>Masses of frozen water, such as sea ice, ice shields, glaciers, and snow.</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- Guth et al. 2021</t>
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
@@ -7324,27 +7300,19 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Geopositioning</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>- core
-- to be discussed
-description: Determination of the geographic Position of a point (0D) or linear (1D) Feature.</t>
+  - to be defined
+description: ""</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>Determination of the geographic Position of a point (0D) or linear (1D) Feature.</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>- Modified from: ISO 19130-1:2018, 3.36</t>
-        </is>
-      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr"/>
@@ -7367,27 +7335,37 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Spectral Band</t>
+          <t>Location</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>- core
-- to be approved
-description: Part of the electromagnetic spectrum of specific wavelengths, in remote sensing usually described by central wavelength and bandwidth.</t>
+          <t>- base
+  - to be approved
+description: Particular Place referenced by an identifier.</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Part of the electromagnetic spectrum of specific wavelengths. In Remote Sensing, usually described by central wavelength and bandwidth.</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
+          <t>Particular Place referenced by an identifier.</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>- While a (geo)location identifies a geographic Place, it may also be associated with objects other than the Earth.
+- While Location in principle covers 0- to 3-dimensional spatial geometries, it should not be used for 0- and 1-dimensional geometries (positions and paths).</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>- Madrid
+- California</t>
+        </is>
+      </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>- KCEO</t>
+          <t>- [ISO 19112:2019](https://www.iso.org/standard/70742.html), (E), 3.1.3, modified, note 2 added</t>
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
@@ -7410,20 +7388,35 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Consistency</t>
+          <t>Sensor</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>- core
-  - to be defined</t>
+- to be approved
+description: Device or instrument suited (through physical/chemical interaction) to measure one or more properties of a Phenomenon and thus collect factual/objective data.</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
-      <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Device or instrument suited (through physical/chemical interaction) to measure one or more properties of a Phenomenon and thus collect factual/objective data.</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>- Sensing is therefore a synonym for Observation (the Process).
+- As by their definition, sensors perform sampling.
+- Sensors used to obtain measurements must be calibrated and provide uncertainties.</t>
+        </is>
+      </c>
       <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>- KCEO</t>
+        </is>
+      </c>
       <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr"/>
@@ -7444,31 +7437,37 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Geographic Data</t>
+          <t>Temporal Resolution</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
           <t>- core
 - to be approved
-description: Data with implicit or explicit reference to a Location relative to the Earth.</t>
+description: Observation or model output representing regular intervals, specifying the length of the interval that determines the smallest event or process that can be resolved.</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Data with implicit or explicit reference to a Location relative to the Earth.</t>
+          <t>Observation or model output representing regular intervals, specifying the length of the interval that determines the smallest event or Process that can be resolved (e.g., the Period between observations, the time steps in a model).</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>- Geographic Information is also used as a term for information concerning phenomena implicitly or explicitly associated with a Location relative to the Earth.</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr"/>
+          <t>- WIGOS 2019 distinguishes between sampling time Period, as the Period over which a Measurement is taken, and temporal sampling interval as the time Period between the beginning of consecutive sampling periods. Temporal Resolution in this Glossary is equivalent to sampling time Period as used by WIGOS.</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>| Entry format example | Valid unit                     |
+|----------------------|-------------------------------|
+| 1 s, 2 h, 1 m        | second, hour, day, month, year |</t>
+        </is>
+      </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>- ISO 19109:2015, 4.13; ISO 19109:2005</t>
+          <t>- KCEO</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
@@ -7491,26 +7490,27 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Business Continuity</t>
+          <t>Policy Cycle</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>- core
-- to be approved</t>
+          <t>- high-impact
+- to be discussed
+description: Well-established concept typically taught as the rational model of policy decision-making, representing an idealised view of the policy process.</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>An organisation's readiness to continue functioning during times of disruption.</t>
+          <t>Well-established concept, typically taught as the rational model of policy decision-making. Idealised view of the policy process.</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr">
         <is>
-          <t>- [WGISS Shared Collection Lifecycle Management Principles for Earth Observation Data](https://ceos.org/document_management/Working_Groups/WGISS/Documents/Shared%20Collection%20Lifecycle%20Management%20Principles%20for%20Earth%20Observation%20Data_March2025.pdf)</t>
+          <t>- [ESA/CEOS?, modified](https://digital-strategy.ec.europa.eu/en/library/quality-public-administration-toolbox-practitioners)</t>
         </is>
       </c>
       <c r="H152" t="inlineStr"/>

--- a/exports/xlsx/terms.xlsx
+++ b/exports/xlsx/terms.xlsx
@@ -19649,31 +19649,31 @@
       <c r="C406" t="inlineStr"/>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
-        </is>
-      </c>
-      <c r="E406" t="inlineStr"/>
+          <t>Non-negative parameter, associated with data, characterizing the dispersion of the values of a Trait that can reasonably be attributed to a Phenomenon by means of sensing or modelling.</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>- In case of quantitative (continuous) data the uncertainty may be, for example, a standard deviation (or a given multiple of it), or the half-width of an interval having a stated level of confidence (see e.g. Standard and Expanded Uncertainty).
+- For qualitative (categorical?) data, uncertainty may be expressed by commission and omission ('confusion matrix') or overall errors.</t>
+        </is>
+      </c>
       <c r="F406" t="inlineStr"/>
       <c r="G406" t="inlineStr">
         <is>
-          <t>- GUM</t>
+          <t>- Modified from GUM, VIM4:3.1, FIDUCEO, Notes added</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>Non-negative parameter, associated with data, which characterizes the dispersion of the values of a Trait that could reasonably be attributed to a Phenomenon by means of sensing or modelling.</t>
-        </is>
-      </c>
-      <c r="I406" t="inlineStr">
-        <is>
-          <t>- In case of quantitative (continuous) data the uncertainty may be, for example, a standard deviation (or a given multiple of it), or the half-width of an interval having a stated level of confidence (see e.g. Standard and Expanded Uncertainty).
-- For qualitative (categorical?) data, uncertainty may be expressed by commission and omission ('confusion matrix') or overall errors.</t>
-        </is>
-      </c>
+          <t>Parameter, associated with the result of a measurement, that characterises the dispersion of the values that could reasonably be attributed to the measurand.</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr"/>
       <c r="J406" t="inlineStr"/>
       <c r="K406" t="inlineStr">
         <is>
-          <t>- Modified from GUM, VIM4:3.1, FIDUCEO, Notes added</t>
+          <t>- GUM</t>
         </is>
       </c>
       <c r="L406" t="inlineStr">

--- a/exports/xlsx/terms.xlsx
+++ b/exports/xlsx/terms.xlsx
@@ -10877,7 +10877,7 @@
       <c r="B221" t="inlineStr">
         <is>
           <t>- core
-- to be approved
+- to be discussed
 - calval ingest
 - WGCV
 - WGClimate</t>
@@ -10893,7 +10893,8 @@
         <is>
           <t>- Sensing is therefore a synonym for Observation (the Process).
 - As by their definition, sensors perform sampling.
-- Sensors used to obtain measurements must be calibrated and provide uncertainties.</t>
+- Sensors used to obtain measurements must be calibrated and provide uncertainties.
+- Sensor is currently cyclic with Instrument (to be resolved)</t>
         </is>
       </c>
       <c r="F221" t="inlineStr"/>

--- a/exports/xlsx/terms.xlsx
+++ b/exports/xlsx/terms.xlsx
@@ -10733,7 +10733,11 @@
           <t>Hardware system that collects scientific or operational data, or a hardware-integrated collection of one or more sensors contributing data of one type to an investigation.</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr"/>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>- Sensor is currently cyclic with Instrument (to be resolved)</t>
+        </is>
+      </c>
       <c r="F218" t="inlineStr"/>
       <c r="G218" t="inlineStr">
         <is>
